--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="162">
   <si>
     <t>student_id</t>
   </si>
@@ -494,6 +494,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>+</t>
   </si>
   <si>
     <t>No Quiz</t>
@@ -880,7 +883,7 @@
         <v>159</v>
       </c>
       <c r="G2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -903,7 +906,7 @@
         <v>159</v>
       </c>
       <c r="G3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -926,7 +929,7 @@
         <v>159</v>
       </c>
       <c r="G4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -949,7 +952,7 @@
         <v>159</v>
       </c>
       <c r="G5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -969,10 +972,10 @@
         <v>158</v>
       </c>
       <c r="F6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -995,7 +998,7 @@
         <v>159</v>
       </c>
       <c r="G7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1015,10 +1018,10 @@
         <v>158</v>
       </c>
       <c r="F8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1041,7 +1044,7 @@
         <v>159</v>
       </c>
       <c r="G9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1064,7 +1067,7 @@
         <v>159</v>
       </c>
       <c r="G10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1084,10 +1087,10 @@
         <v>158</v>
       </c>
       <c r="F11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1110,7 +1113,7 @@
         <v>159</v>
       </c>
       <c r="G12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1133,7 +1136,7 @@
         <v>159</v>
       </c>
       <c r="G13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1153,10 +1156,10 @@
         <v>158</v>
       </c>
       <c r="F14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1179,7 +1182,7 @@
         <v>159</v>
       </c>
       <c r="G15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1202,7 +1205,7 @@
         <v>159</v>
       </c>
       <c r="G16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1225,7 +1228,7 @@
         <v>159</v>
       </c>
       <c r="G17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1248,7 +1251,7 @@
         <v>159</v>
       </c>
       <c r="G18" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1271,7 +1274,7 @@
         <v>159</v>
       </c>
       <c r="G19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1294,7 +1297,7 @@
         <v>159</v>
       </c>
       <c r="G20" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1314,10 +1317,10 @@
         <v>158</v>
       </c>
       <c r="F21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1337,10 +1340,10 @@
         <v>158</v>
       </c>
       <c r="F22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1363,7 +1366,7 @@
         <v>159</v>
       </c>
       <c r="G23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1383,10 +1386,10 @@
         <v>158</v>
       </c>
       <c r="F24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1406,10 +1409,10 @@
         <v>158</v>
       </c>
       <c r="F25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G25" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1429,10 +1432,10 @@
         <v>158</v>
       </c>
       <c r="F26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1452,10 +1455,10 @@
         <v>158</v>
       </c>
       <c r="F27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G27" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1475,10 +1478,10 @@
         <v>158</v>
       </c>
       <c r="F28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1501,7 +1504,7 @@
         <v>159</v>
       </c>
       <c r="G29" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1521,10 +1524,10 @@
         <v>158</v>
       </c>
       <c r="F30" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G30" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1544,10 +1547,10 @@
         <v>158</v>
       </c>
       <c r="F31" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G31" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1567,10 +1570,10 @@
         <v>158</v>
       </c>
       <c r="F32" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G32" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1590,10 +1593,10 @@
         <v>158</v>
       </c>
       <c r="F33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1613,10 +1616,10 @@
         <v>158</v>
       </c>
       <c r="F34" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1636,10 +1639,10 @@
         <v>158</v>
       </c>
       <c r="F35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G35" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1659,10 +1662,10 @@
         <v>158</v>
       </c>
       <c r="F36" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G36" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1685,7 +1688,7 @@
         <v>159</v>
       </c>
       <c r="G37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1708,7 +1711,7 @@
         <v>159</v>
       </c>
       <c r="G38" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1731,7 +1734,7 @@
         <v>159</v>
       </c>
       <c r="G39" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1754,7 +1757,7 @@
         <v>159</v>
       </c>
       <c r="G40" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1777,7 +1780,7 @@
         <v>159</v>
       </c>
       <c r="G41" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1800,7 +1803,7 @@
         <v>159</v>
       </c>
       <c r="G42" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1820,10 +1823,10 @@
         <v>158</v>
       </c>
       <c r="F43" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G43" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1846,7 +1849,7 @@
         <v>159</v>
       </c>
       <c r="G44" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1866,10 +1869,10 @@
         <v>158</v>
       </c>
       <c r="F45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1889,10 +1892,10 @@
         <v>158</v>
       </c>
       <c r="F46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1912,10 +1915,10 @@
         <v>158</v>
       </c>
       <c r="F47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G47" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1935,10 +1938,10 @@
         <v>158</v>
       </c>
       <c r="F48" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G48" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1961,7 +1964,7 @@
         <v>159</v>
       </c>
       <c r="G49" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1984,7 +1987,7 @@
         <v>159</v>
       </c>
       <c r="G50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2004,10 +2007,10 @@
         <v>158</v>
       </c>
       <c r="F51" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G51" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2030,7 +2033,7 @@
         <v>159</v>
       </c>
       <c r="G52" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2053,7 +2056,7 @@
         <v>159</v>
       </c>
       <c r="G53" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2076,7 +2079,7 @@
         <v>159</v>
       </c>
       <c r="G54" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2099,7 +2102,7 @@
         <v>159</v>
       </c>
       <c r="G55" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2119,10 +2122,10 @@
         <v>158</v>
       </c>
       <c r="F56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G56" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2142,10 +2145,10 @@
         <v>158</v>
       </c>
       <c r="F57" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G57" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2165,10 +2168,10 @@
         <v>158</v>
       </c>
       <c r="F58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G58" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2191,7 +2194,7 @@
         <v>159</v>
       </c>
       <c r="G59" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2211,10 +2214,10 @@
         <v>158</v>
       </c>
       <c r="F60" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G60" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2234,10 +2237,10 @@
         <v>158</v>
       </c>
       <c r="F61" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G61" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2257,10 +2260,10 @@
         <v>158</v>
       </c>
       <c r="F62" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G62" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2280,10 +2283,10 @@
         <v>158</v>
       </c>
       <c r="F63" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G63" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2303,10 +2306,10 @@
         <v>158</v>
       </c>
       <c r="F64" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2326,10 +2329,10 @@
         <v>158</v>
       </c>
       <c r="F65" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2352,7 +2355,7 @@
         <v>159</v>
       </c>
       <c r="G66" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2372,10 +2375,10 @@
         <v>158</v>
       </c>
       <c r="F67" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G67" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2395,10 +2398,10 @@
         <v>158</v>
       </c>
       <c r="F68" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2418,10 +2421,10 @@
         <v>158</v>
       </c>
       <c r="F69" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G69" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2441,10 +2444,10 @@
         <v>158</v>
       </c>
       <c r="F70" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G70" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2467,7 +2470,7 @@
         <v>159</v>
       </c>
       <c r="G71" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2487,10 +2490,10 @@
         <v>158</v>
       </c>
       <c r="F72" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G72" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2510,10 +2513,10 @@
         <v>158</v>
       </c>
       <c r="F73" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G73" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2536,7 +2539,7 @@
         <v>159</v>
       </c>
       <c r="G74" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2556,10 +2559,10 @@
         <v>158</v>
       </c>
       <c r="F75" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G75" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -2675,7 +2675,7 @@
         <v>189</v>
       </c>
       <c r="F76" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G76" t="s">
         <v>192</v>
@@ -2721,7 +2721,7 @@
         <v>189</v>
       </c>
       <c r="F78" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G78" t="s">
         <v>192</v>
@@ -2744,7 +2744,7 @@
         <v>189</v>
       </c>
       <c r="F79" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G79" t="s">
         <v>192</v>
@@ -2767,7 +2767,7 @@
         <v>189</v>
       </c>
       <c r="F80" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G80" t="s">
         <v>192</v>
@@ -2790,7 +2790,7 @@
         <v>189</v>
       </c>
       <c r="F81" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G81" t="s">
         <v>192</v>
@@ -2836,7 +2836,7 @@
         <v>189</v>
       </c>
       <c r="F83" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G83" t="s">
         <v>192</v>
@@ -2859,7 +2859,7 @@
         <v>189</v>
       </c>
       <c r="F84" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G84" t="s">
         <v>192</v>
@@ -2928,7 +2928,7 @@
         <v>189</v>
       </c>
       <c r="F87" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G87" t="s">
         <v>192</v>
@@ -2951,7 +2951,7 @@
         <v>189</v>
       </c>
       <c r="F88" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G88" t="s">
         <v>192</v>
@@ -3020,7 +3020,7 @@
         <v>189</v>
       </c>
       <c r="F91" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G91" t="s">
         <v>192</v>
@@ -3043,7 +3043,7 @@
         <v>189</v>
       </c>
       <c r="F92" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G92" t="s">
         <v>192</v>
@@ -3066,7 +3066,7 @@
         <v>189</v>
       </c>
       <c r="F93" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G93" t="s">
         <v>192</v>
@@ -3089,7 +3089,7 @@
         <v>189</v>
       </c>
       <c r="F94" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G94" t="s">
         <v>192</v>
@@ -3112,7 +3112,7 @@
         <v>189</v>
       </c>
       <c r="F95" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G95" t="s">
         <v>192</v>
@@ -3135,7 +3135,7 @@
         <v>189</v>
       </c>
       <c r="F96" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G96" t="s">
         <v>192</v>
@@ -3158,7 +3158,7 @@
         <v>189</v>
       </c>
       <c r="F97" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G97" t="s">
         <v>192</v>
@@ -3204,7 +3204,7 @@
         <v>189</v>
       </c>
       <c r="F99" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G99" t="s">
         <v>192</v>
@@ -3227,7 +3227,7 @@
         <v>189</v>
       </c>
       <c r="F100" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G100" t="s">
         <v>192</v>
@@ -3273,7 +3273,7 @@
         <v>189</v>
       </c>
       <c r="F102" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G102" t="s">
         <v>192</v>
@@ -3296,7 +3296,7 @@
         <v>189</v>
       </c>
       <c r="F103" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G103" t="s">
         <v>192</v>
@@ -3319,7 +3319,7 @@
         <v>189</v>
       </c>
       <c r="F104" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G104" t="s">
         <v>192</v>
@@ -3342,7 +3342,7 @@
         <v>189</v>
       </c>
       <c r="F105" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G105" t="s">
         <v>192</v>
@@ -3365,7 +3365,7 @@
         <v>189</v>
       </c>
       <c r="F106" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G106" t="s">
         <v>192</v>
@@ -3388,7 +3388,7 @@
         <v>189</v>
       </c>
       <c r="F107" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G107" t="s">
         <v>192</v>
@@ -3411,7 +3411,7 @@
         <v>189</v>
       </c>
       <c r="F108" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G108" t="s">
         <v>192</v>
@@ -3434,7 +3434,7 @@
         <v>189</v>
       </c>
       <c r="F109" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G109" t="s">
         <v>192</v>
@@ -3457,7 +3457,7 @@
         <v>189</v>
       </c>
       <c r="F110" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G110" t="s">
         <v>192</v>
@@ -3480,7 +3480,7 @@
         <v>189</v>
       </c>
       <c r="F111" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G111" t="s">
         <v>192</v>
@@ -3526,7 +3526,7 @@
         <v>189</v>
       </c>
       <c r="F113" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G113" t="s">
         <v>192</v>
@@ -3549,7 +3549,7 @@
         <v>189</v>
       </c>
       <c r="F114" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G114" t="s">
         <v>192</v>
@@ -3572,7 +3572,7 @@
         <v>189</v>
       </c>
       <c r="F115" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G115" t="s">
         <v>192</v>
@@ -3595,7 +3595,7 @@
         <v>189</v>
       </c>
       <c r="F116" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G116" t="s">
         <v>192</v>
@@ -3664,7 +3664,7 @@
         <v>189</v>
       </c>
       <c r="F119" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G119" t="s">
         <v>192</v>
@@ -3687,7 +3687,7 @@
         <v>189</v>
       </c>
       <c r="F120" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G120" t="s">
         <v>192</v>
@@ -3710,7 +3710,7 @@
         <v>189</v>
       </c>
       <c r="F121" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G121" t="s">
         <v>192</v>
@@ -4147,7 +4147,7 @@
         <v>189</v>
       </c>
       <c r="F140" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G140" t="s">
         <v>192</v>
@@ -4193,7 +4193,7 @@
         <v>189</v>
       </c>
       <c r="F142" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G142" t="s">
         <v>192</v>
@@ -4216,7 +4216,7 @@
         <v>189</v>
       </c>
       <c r="F143" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G143" t="s">
         <v>192</v>
@@ -4239,7 +4239,7 @@
         <v>189</v>
       </c>
       <c r="F144" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G144" t="s">
         <v>192</v>
@@ -4285,7 +4285,7 @@
         <v>189</v>
       </c>
       <c r="F146" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G146" t="s">
         <v>192</v>
@@ -4308,7 +4308,7 @@
         <v>189</v>
       </c>
       <c r="F147" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G147" t="s">
         <v>192</v>
@@ -4354,7 +4354,7 @@
         <v>189</v>
       </c>
       <c r="F149" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G149" t="s">
         <v>192</v>
@@ -4423,7 +4423,7 @@
         <v>189</v>
       </c>
       <c r="F152" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G152" t="s">
         <v>192</v>
@@ -4446,7 +4446,7 @@
         <v>189</v>
       </c>
       <c r="F153" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G153" t="s">
         <v>192</v>
@@ -4469,7 +4469,7 @@
         <v>189</v>
       </c>
       <c r="F154" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G154" t="s">
         <v>192</v>
@@ -4492,7 +4492,7 @@
         <v>189</v>
       </c>
       <c r="F155" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G155" t="s">
         <v>192</v>
@@ -4515,7 +4515,7 @@
         <v>189</v>
       </c>
       <c r="F156" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G156" t="s">
         <v>192</v>

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="119">
   <si>
     <t>student_id</t>
   </si>
@@ -359,6 +359,18 @@
   </si>
   <si>
     <t>Absent.</t>
+  </si>
+  <si>
+    <t>You correctly identified the problem requirements and noted the 750 N perpendicular component, but no geometric angle analysis, trigonometric equations, or numerical calculations were performed to find P or its parallel component. Nearly all rubric points require demonstrated calculations, which are absent here.</t>
+  </si>
+  <si>
+    <t>No supporting calculations were provided for either part — the answer of 400 N for part (a) is incorrect (correct answer is 798 N), and part (b) only references the figure with no numerical result or working shown; as stated on the exam, answers without supporting calculations do not receive credit.</t>
+  </si>
+  <si>
+    <t>The geometric analysis is missing entirely — the critical step of finding the angle between BD and ABC (70°) was not performed, and the student incorrectly used cos(60°) applied directly to the 750 N perpendicular component rather than setting up P·sin(70°) = 750 N. Neither the magnitude of P (798 N) nor the parallel component (273 N) was correctly found; only a partial attempt at one calculation yielding 482 N was shown, which is incorrect. A small amount of credit is awarded for recognizing that trigonometry is involved and identifying the 750 N given value.</t>
+  </si>
+  <si>
+    <t>No work or calculations were submitted in the solution box; a completely blank answer cannot receive any credit regardless of the problem's difficulty.</t>
   </si>
 </sst>
 </file>
@@ -2644,10 +2656,10 @@
         <v>112</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I83" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -3296,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -3351,10 +3363,10 @@
         <v>112</v>
       </c>
       <c r="H108">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I108" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -3496,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="114" spans="1:9">

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="137">
   <si>
     <t>student_id</t>
   </si>
@@ -361,16 +361,70 @@
     <t>Absent.</t>
   </si>
   <si>
-    <t>You correctly identified the problem requirements and noted the 750 N perpendicular component, but no geometric angle analysis, trigonometric equations, or numerical calculations were performed to find P or its parallel component. Nearly all rubric points require demonstrated calculations, which are absent here.</t>
-  </si>
-  <si>
-    <t>No supporting calculations were provided for either part — the answer of 400 N for part (a) is incorrect (correct answer is 798 N), and part (b) only references the figure with no numerical result or working shown; as stated on the exam, answers without supporting calculations do not receive credit.</t>
-  </si>
-  <si>
-    <t>The geometric analysis is missing entirely — the critical step of finding the angle between BD and ABC (70°) was not performed, and the student incorrectly used cos(60°) applied directly to the 750 N perpendicular component rather than setting up P·sin(70°) = 750 N. Neither the magnitude of P (798 N) nor the parallel component (273 N) was correctly found; only a partial attempt at one calculation yielding 482 N was shown, which is incorrect. A small amount of credit is awarded for recognizing that trigonometry is involved and identifying the 750 N given value.</t>
-  </si>
-  <si>
-    <t>No work or calculations were submitted in the solution box; a completely blank answer cannot receive any credit regardless of the problem's difficulty.</t>
+    <t>You correctly identified the component equations (P⊥ = P·sinθ and P∥ = P·cosθ) and showed good method, but the critical error was in computing the angle between P and member ABC: θ = 90° − 60° − 50° = 80° is incorrect — the correct angle is θ = 20° (since ABC makes 30° with horizontal and BD makes 50°, giving 50° − 30° = 20°), which led to incorrect final answers for both parts.</t>
+  </si>
+  <si>
+    <t>You correctly identified the 60° and 50° angles from the figure, but the key error was treating the 750 N as the magnitude of P rather than its perpendicular component to ABC; additionally, the critical step of finding the angle between P and member ABC (θ = 20°) was never established, leading to an incorrect approach throughout. Please review how to resolve a force into components along and perpendicular to a given member direction.</t>
+  </si>
+  <si>
+    <t>You correctly identified the given 750 N perpendicular component and sketched the figure with the 60° and 50° angles, earning minimal partial credit for recognizing the geometry; however, no angle between P and member ABC was computed, no trigonometric equations were set up, and no numerical answers were provided for either part (a) or part (b).</t>
+  </si>
+  <si>
+    <t>Excellent work! You correctly identified the 20° angle between P and member ABC, set up the trigonometric equations properly, and obtained accurate answers for both the magnitude of P (≈2192.85 N) and the parallel component (≈2060.6 N), with a clear FBD and verification triangle — full marks awarded.</t>
+  </si>
+  <si>
+    <t>Excellent work overall — you correctly identified the 20° angle between P and member ABC, set up the proper trigonometric equations (P·sin20° = 750 N and P·cos20°), and arrived at the correct final answers of P ≈ 2192 N and P∥ ≈ 2060 N. A small deduction was made because the solution box on page 2 appears to write '950 N' instead of '750 N' for the perpendicular component (likely a transcription slip), and the geometric derivation of the 20° angle could have been shown more explicitly.</t>
+  </si>
+  <si>
+    <t>You correctly identified the given angles (60° at C and 50° at D) and drew a reasonable FBD with labeled components, but the key step of computing the angle between force P and member ABC (θ = 20°) was missed — you used 50° directly instead of the relative angle. Additionally, no numerical solutions were completed for either part (a) or part (b), so no credit could be awarded for the final answers.</t>
+  </si>
+  <si>
+    <t>You correctly identified the two given angles (50° for BD and 60° for ABC) from the figure, but the critical step of finding the angle between force P and member ABC (θ = 20°) was missed entirely. As a result, the force P was not properly resolved into components perpendicular and parallel to ABC — instead, the 750 N perpendicular component was treated as the full force and decomposed along global x-y axes, leading to incorrect answers for both parts.</t>
+  </si>
+  <si>
+    <t>Excellent work — you correctly identified the geometric angle relationship (using 70° as the complement of 20°, which is equivalent), and both the magnitude of P ≈ 2193 N and the parallel component ≈ 2060 N are correct. Minor deduction for the slightly unclear FBD/diagram labeling; the incomplete verification at the end did not affect your score.</t>
+  </si>
+  <si>
+    <t>You correctly identified the 50° angle for BD and showed some geometric awareness (noting 30° in your sketch), but the key error was using sin50° directly instead of finding the angle between force P and member ABC (θ = 20°), which leads to significantly incorrect results for both parts. For part (b), the parallel component should be P·cos(20°) ≈ 2060 N, not the x-component with respect to horizontal.</t>
+  </si>
+  <si>
+    <t>Excellent work — you correctly identified the 20° angle between force P and member ABC, set up the component equations properly using sin(20°) and cos(20°), and arrived at the accurate answers of P ≈ 2192 N and P∥ ≈ 2060 N. Full marks are awarded.</t>
+  </si>
+  <si>
+    <t>Excellent work — you correctly identified the geometry, derived θ = 20° between force P and member ABC, and applied the sine and cosine decomposition to obtain P ≈ 2192.85 N and P∥ ≈ 2060.60 N, both matching the model solution. A very small deduction is applied because the FBD/angle derivation steps (showing α = 120° and β = 20° via the supplementary-angle reasoning) are slightly difficult to follow without clearer labeling, but the logic and all final answers are correct.</t>
+  </si>
+  <si>
+    <t>No supporting calculations or geometric reasoning were shown for either part — the rubric explicitly states that answers without supporting work receive no credit; only minimal partial credit is awarded for attempting to identify force directions on the figure. The answer for (a) is incorrect (400 N vs. 2190 N) and part (b) provides no numerical result.</t>
+  </si>
+  <si>
+    <t>Excellent work — you correctly identified the critical angle θ = 20° between force P and member ABC, set up the trigonometric equations properly, and found both answers with the right method. A small deduction is noted for using a slightly rounded value of sin(20°) ≈ 0.34 (should be 0.3420), which caused minor numerical drift in the final answers, and the FBD could have been drawn more cleanly as a separate diagram.</t>
+  </si>
+  <si>
+    <t>Unfortunately, the solution does not correctly establish the key angle (θ = 20°) between force P and member ABC, and the decomposition equations are set up incorrectly — the 750 N perpendicular component should be used to find P via P = 750/sin(20°), not multiplied by a cosine of the given figure angles. Part (b) was not attempted; please review vector component resolution and geometry carefully.</t>
+  </si>
+  <si>
+    <t>Excellent work — you correctly identified the 20° angle between P and member ABC, set up the right triangle decomposition properly using the complementary 70° angle, and arrived at essentially correct answers for both parts. A minor rounding error (using cos70° ≈ 0.34 instead of 0.3420) led to a slightly off value for P (2205.88 N vs. the more precise 2193 N), resulting in a small deduction.</t>
+  </si>
+  <si>
+    <t>You correctly identified the 60° and 50° angles from the figure and made an attempt at a vector diagram, which earns some geometry credit; however, the critical angle between force P and member ABC was determined incorrectly (you used 40° instead of the correct 20°), and the force decomposition was performed in the global x-y frame rather than along and perpendicular to member ABC, leading to significantly incorrect final answers for both parts.</t>
+  </si>
+  <si>
+    <t>The solution box is completely blank — no work, calculations, FBD, or answers were provided for either part (a) or part (b). No credit can be awarded without supporting work.</t>
+  </si>
+  <si>
+    <t>Unfortunately, there is a fundamental conceptual error in your approach: the 750 N is the component of P perpendicular to ABC, not the total force P to be resolved into x-y coordinates. You should have used sin(θ) = 750/P (where θ = 20° is the angle between BD and ABC) to find P ≈ 2190 N, then P∥ = P·cos(20°) ≈ 2060 N. Partial credit was awarded for identifying some of the geometric angles in the figure.</t>
+  </si>
+  <si>
+    <t>You correctly identified the two given angles (60° and 50°) from the figure, but the critical step of finding the angle between force P and member ABC (θ = 20°) was never established; instead, you incorrectly treated the 750 N perpendicular component as the full force P and resolved it along global axes, leading to wrong results for both parts. To solve this problem, you must first find θ = 50° − 30° = 20°, then use P = 750/sin(20°) ≈ 2190 N for part (a) and P∥ = P·cos(20°) ≈ 2060 N for part (b).</t>
+  </si>
+  <si>
+    <t>You correctly identified the key angles (30° for ABC, 50° for BD) on the figure and even wrote the correct equation sin(20°) = 750/x at the top of your solution, but unfortunately did not follow through with it — instead pursuing several incorrect approaches using wrong angles (30°, 40°, 50°) that led to incorrect final answers for both parts. Focus on committing to the correct geometric setup (θ = 20° between P and ABC) and consistently applying P = 750/sin(20°) ≈ 2190 N and P∥ = P·cos(20°) ≈ 2060 N.</t>
+  </si>
+  <si>
+    <t>You correctly set up the component equations (P·sinθ = 750 for perpendicular and P·cosθ for parallel), which earns partial credit; however, the critical error was using θ = 30° instead of the correct θ = 20° (the angle between BD and ABC, derived from 50° − 30° = 20°), leading to incorrect final answers of P = 1500 N and P∥ ≈ 1299 N instead of ~2190 N and ~2060 N respectively.</t>
+  </si>
+  <si>
+    <t>Attendance signature missing. Quiz score recorded as 0.</t>
   </si>
 </sst>
 </file>
@@ -2543,10 +2597,10 @@
         <v>112</v>
       </c>
       <c r="H79">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I79" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -2572,10 +2626,10 @@
         <v>112</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I80" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -2659,7 +2713,7 @@
         <v>5</v>
       </c>
       <c r="I83" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -2766,10 +2820,10 @@
         <v>112</v>
       </c>
       <c r="H87">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I87" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -2876,10 +2930,10 @@
         <v>112</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="I91" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -2905,10 +2959,10 @@
         <v>112</v>
       </c>
       <c r="H92">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I92" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -2963,10 +3017,10 @@
         <v>112</v>
       </c>
       <c r="H94">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I94" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -3021,10 +3075,10 @@
         <v>112</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="I96" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -3189,10 +3243,10 @@
         <v>112</v>
       </c>
       <c r="H102">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I102" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -3218,10 +3272,10 @@
         <v>112</v>
       </c>
       <c r="H103">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I103" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -3247,10 +3301,10 @@
         <v>112</v>
       </c>
       <c r="H104">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I104" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -3305,10 +3359,10 @@
         <v>112</v>
       </c>
       <c r="H106">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I106" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -3334,10 +3388,10 @@
         <v>112</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I107" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -3366,7 +3420,7 @@
         <v>5</v>
       </c>
       <c r="I108" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -3392,10 +3446,10 @@
         <v>112</v>
       </c>
       <c r="H109">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="I109" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -3450,10 +3504,10 @@
         <v>112</v>
       </c>
       <c r="H111">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I111" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -3508,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -3534,10 +3588,10 @@
         <v>112</v>
       </c>
       <c r="H114">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I114" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -3563,10 +3617,10 @@
         <v>112</v>
       </c>
       <c r="H115">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I115" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -3592,10 +3646,10 @@
         <v>112</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I116" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -3702,10 +3756,10 @@
         <v>112</v>
       </c>
       <c r="H120">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I120" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -4529,8 +4583,11 @@
       <c r="G150" t="s">
         <v>112</v>
       </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
       <c r="I150" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
     </row>
     <row r="151" spans="1:9">

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="149">
   <si>
     <t>student_id</t>
   </si>
@@ -361,70 +361,106 @@
     <t>Absent.</t>
   </si>
   <si>
-    <t>You correctly identified the component equations (P⊥ = P·sinθ and P∥ = P·cosθ) and showed good method, but the critical error was in computing the angle between P and member ABC: θ = 90° − 60° − 50° = 80° is incorrect — the correct angle is θ = 20° (since ABC makes 30° with horizontal and BD makes 50°, giving 50° − 30° = 20°), which led to incorrect final answers for both parts.</t>
-  </si>
-  <si>
-    <t>You correctly identified the 60° and 50° angles from the figure, but the key error was treating the 750 N as the magnitude of P rather than its perpendicular component to ABC; additionally, the critical step of finding the angle between P and member ABC (θ = 20°) was never established, leading to an incorrect approach throughout. Please review how to resolve a force into components along and perpendicular to a given member direction.</t>
-  </si>
-  <si>
-    <t>You correctly identified the given 750 N perpendicular component and sketched the figure with the 60° and 50° angles, earning minimal partial credit for recognizing the geometry; however, no angle between P and member ABC was computed, no trigonometric equations were set up, and no numerical answers were provided for either part (a) or part (b).</t>
-  </si>
-  <si>
-    <t>Excellent work! You correctly identified the 20° angle between P and member ABC, set up the trigonometric equations properly, and obtained accurate answers for both the magnitude of P (≈2192.85 N) and the parallel component (≈2060.6 N), with a clear FBD and verification triangle — full marks awarded.</t>
-  </si>
-  <si>
-    <t>Excellent work overall — you correctly identified the 20° angle between P and member ABC, set up the proper trigonometric equations (P·sin20° = 750 N and P·cos20°), and arrived at the correct final answers of P ≈ 2192 N and P∥ ≈ 2060 N. A small deduction was made because the solution box on page 2 appears to write '950 N' instead of '750 N' for the perpendicular component (likely a transcription slip), and the geometric derivation of the 20° angle could have been shown more explicitly.</t>
-  </si>
-  <si>
-    <t>You correctly identified the given angles (60° at C and 50° at D) and drew a reasonable FBD with labeled components, but the key step of computing the angle between force P and member ABC (θ = 20°) was missed — you used 50° directly instead of the relative angle. Additionally, no numerical solutions were completed for either part (a) or part (b), so no credit could be awarded for the final answers.</t>
-  </si>
-  <si>
-    <t>You correctly identified the two given angles (50° for BD and 60° for ABC) from the figure, but the critical step of finding the angle between force P and member ABC (θ = 20°) was missed entirely. As a result, the force P was not properly resolved into components perpendicular and parallel to ABC — instead, the 750 N perpendicular component was treated as the full force and decomposed along global x-y axes, leading to incorrect answers for both parts.</t>
-  </si>
-  <si>
-    <t>Excellent work — you correctly identified the geometric angle relationship (using 70° as the complement of 20°, which is equivalent), and both the magnitude of P ≈ 2193 N and the parallel component ≈ 2060 N are correct. Minor deduction for the slightly unclear FBD/diagram labeling; the incomplete verification at the end did not affect your score.</t>
-  </si>
-  <si>
-    <t>You correctly identified the 50° angle for BD and showed some geometric awareness (noting 30° in your sketch), but the key error was using sin50° directly instead of finding the angle between force P and member ABC (θ = 20°), which leads to significantly incorrect results for both parts. For part (b), the parallel component should be P·cos(20°) ≈ 2060 N, not the x-component with respect to horizontal.</t>
-  </si>
-  <si>
-    <t>Excellent work — you correctly identified the 20° angle between force P and member ABC, set up the component equations properly using sin(20°) and cos(20°), and arrived at the accurate answers of P ≈ 2192 N and P∥ ≈ 2060 N. Full marks are awarded.</t>
-  </si>
-  <si>
-    <t>Excellent work — you correctly identified the geometry, derived θ = 20° between force P and member ABC, and applied the sine and cosine decomposition to obtain P ≈ 2192.85 N and P∥ ≈ 2060.60 N, both matching the model solution. A very small deduction is applied because the FBD/angle derivation steps (showing α = 120° and β = 20° via the supplementary-angle reasoning) are slightly difficult to follow without clearer labeling, but the logic and all final answers are correct.</t>
-  </si>
-  <si>
-    <t>No supporting calculations or geometric reasoning were shown for either part — the rubric explicitly states that answers without supporting work receive no credit; only minimal partial credit is awarded for attempting to identify force directions on the figure. The answer for (a) is incorrect (400 N vs. 2190 N) and part (b) provides no numerical result.</t>
-  </si>
-  <si>
-    <t>Excellent work — you correctly identified the critical angle θ = 20° between force P and member ABC, set up the trigonometric equations properly, and found both answers with the right method. A small deduction is noted for using a slightly rounded value of sin(20°) ≈ 0.34 (should be 0.3420), which caused minor numerical drift in the final answers, and the FBD could have been drawn more cleanly as a separate diagram.</t>
-  </si>
-  <si>
-    <t>Unfortunately, the solution does not correctly establish the key angle (θ = 20°) between force P and member ABC, and the decomposition equations are set up incorrectly — the 750 N perpendicular component should be used to find P via P = 750/sin(20°), not multiplied by a cosine of the given figure angles. Part (b) was not attempted; please review vector component resolution and geometry carefully.</t>
-  </si>
-  <si>
-    <t>Excellent work — you correctly identified the 20° angle between P and member ABC, set up the right triangle decomposition properly using the complementary 70° angle, and arrived at essentially correct answers for both parts. A minor rounding error (using cos70° ≈ 0.34 instead of 0.3420) led to a slightly off value for P (2205.88 N vs. the more precise 2193 N), resulting in a small deduction.</t>
-  </si>
-  <si>
-    <t>You correctly identified the 60° and 50° angles from the figure and made an attempt at a vector diagram, which earns some geometry credit; however, the critical angle between force P and member ABC was determined incorrectly (you used 40° instead of the correct 20°), and the force decomposition was performed in the global x-y frame rather than along and perpendicular to member ABC, leading to significantly incorrect final answers for both parts.</t>
-  </si>
-  <si>
-    <t>The solution box is completely blank — no work, calculations, FBD, or answers were provided for either part (a) or part (b). No credit can be awarded without supporting work.</t>
-  </si>
-  <si>
-    <t>Unfortunately, there is a fundamental conceptual error in your approach: the 750 N is the component of P perpendicular to ABC, not the total force P to be resolved into x-y coordinates. You should have used sin(θ) = 750/P (where θ = 20° is the angle between BD and ABC) to find P ≈ 2190 N, then P∥ = P·cos(20°) ≈ 2060 N. Partial credit was awarded for identifying some of the geometric angles in the figure.</t>
-  </si>
-  <si>
-    <t>You correctly identified the two given angles (60° and 50°) from the figure, but the critical step of finding the angle between force P and member ABC (θ = 20°) was never established; instead, you incorrectly treated the 750 N perpendicular component as the full force P and resolved it along global axes, leading to wrong results for both parts. To solve this problem, you must first find θ = 50° − 30° = 20°, then use P = 750/sin(20°) ≈ 2190 N for part (a) and P∥ = P·cos(20°) ≈ 2060 N for part (b).</t>
-  </si>
-  <si>
-    <t>You correctly identified the key angles (30° for ABC, 50° for BD) on the figure and even wrote the correct equation sin(20°) = 750/x at the top of your solution, but unfortunately did not follow through with it — instead pursuing several incorrect approaches using wrong angles (30°, 40°, 50°) that led to incorrect final answers for both parts. Focus on committing to the correct geometric setup (θ = 20° between P and ABC) and consistently applying P = 750/sin(20°) ≈ 2190 N and P∥ = P·cos(20°) ≈ 2060 N.</t>
-  </si>
-  <si>
-    <t>You correctly set up the component equations (P·sinθ = 750 for perpendicular and P·cosθ for parallel), which earns partial credit; however, the critical error was using θ = 30° instead of the correct θ = 20° (the angle between BD and ABC, derived from 50° − 30° = 20°), leading to incorrect final answers of P = 1500 N and P∥ ≈ 1299 N instead of ~2190 N and ~2060 N respectively.</t>
+    <t>You correctly identified the two reference angles (60° and 50°) from the figure and showed some geometric reasoning, earning partial credit for the setup. However, you swapped sine and cosine when resolving the perpendicular component (it should be P·sin70° = 750 N, not P·cos70°), which led to incorrect final answers for both parts (a) and (b).</t>
+  </si>
+  <si>
+    <t>Your component equations (P⊥ = P sinθ and P∥ = P cosθ) are correctly formulated, earning full marks for Section B. However, the angle θ was incorrectly determined as 80° instead of the correct 70° (since ABC makes 30° with horizontal and BD makes 40° with horizontal, giving θ = 30° + 40° = 70°), which led to incorrect final values for both P and P∥.</t>
+  </si>
+  <si>
+    <t>You correctly identified the 60° and 50° angles from the figure, but made two critical errors: (1) the 750 N is the perpendicular component of P, not the magnitude of P itself, and (2) the angle between force P and member ABC should be θ = 70° (derived from combining 30° and 40°), not simply 50°. Please revisit how to find the angle between two lines and how to set up the perpendicular/parallel component equations.</t>
+  </si>
+  <si>
+    <t>You correctly identified the 70° angle between BD and ABC, which shows good geometric understanding; however, you incorrectly assumed P = 750 N (which is the perpendicular component, not P itself), and then used sin70° instead of cos70° for the parallel component — the correct approach is P = 750/sin70° ≈ 798 N and P∥ = 798×cos70° ≈ 273 N.</t>
+  </si>
+  <si>
+    <t>You correctly identified the given angles (60° and 50°) from the figure and made an attempt to sketch the geometry, but no equations were set up and no calculations were performed to find the magnitude of P or its parallel component — please show your full solution work to receive credit.</t>
+  </si>
+  <si>
+    <t>You correctly identified the individual reference angles from the figure and set up the perpendicular component equation using sine, which shows good understanding of the approach; however, the critical error was using θ = 40° (only the BD angle) instead of combining both angles to get the correct θ = 70° between force P and member ABC, leading to incorrect final answers of ~1167 N and an unclear parallel component instead of 798 N and 273 N.</t>
+  </si>
+  <si>
+    <t>You correctly identified the angle between BD and ABC as 70° on your diagram, which is a good start; however, you then used 20° (the complement) in your trigonometric equations, leading to swapped sine/cosine roles and incorrect final answers for both parts. Be careful to apply the angle between the force and the member direction directly: P·sin(70°) = 750 N gives P ≈ 798 N, and P·cos(70°) ≈ 273 N for the parallel component.</t>
+  </si>
+  <si>
+    <t>You correctly redrew the figure and identified the given 750 N perpendicular component, but no angle analysis, trigonometric equations, or calculations were provided; please make sure to show all work including determining the angle between BD and ABC (θ = 70°) and applying P = 750/sin(70°) to find the magnitude and parallel component.</t>
   </si>
   <si>
     <t>Attendance signature missing. Quiz score recorded as 0.</t>
+  </si>
+  <si>
+    <t>You correctly identified that the perpendicular component uses sine and the parallel component uses cosine, which earns partial credit; however, the angle between force P and member ABC was incorrectly determined as 20° instead of the correct 70° (derived from the 60° and 50° reference angles in the figure), leading to significantly incorrect final answers for both parts.</t>
+  </si>
+  <si>
+    <t>You correctly set up the perpendicular and parallel component equations using sine and cosine, which shows good understanding of vector decomposition; however, the angle used (50°) is incorrect — the proper angle between force P and member ABC is θ = 70°, obtained by combining the 30° inclination of ABC and 40° inclination of BD from horizontal. Additionally, no numerical final answers were computed for parts (a) or (b).</t>
+  </si>
+  <si>
+    <t>Unfortunately, the solution approach is fundamentally incorrect — the 750 N was treated as the full force P and decomposed into Cartesian x/y components using the given angles separately, rather than finding the angle θ = 70° between line BD and member ABC and applying P·sin(70°) = 750 N to find P = 798 N and P·cos(70°) = 273 N for the parallel component. Please review how to resolve a force into components along and perpendicular to a specified direction.</t>
+  </si>
+  <si>
+    <t>You correctly identified the 60° and 50° angles from the figure, but the key error was using only 30° (complement of 60°) as the angle between P and ABC, rather than combining both angles to get θ = 70°; additionally, the perpendicular component should use sinθ, not cosθ. This led to incorrect values for both P (866 N vs. 798 N) and the parallel component (433 N vs. 273 N).</t>
+  </si>
+  <si>
+    <t>You correctly identified the geometric angles (60°, 50°) and determined θ = 70° between P and member ABC, earning full geometry marks. However, the sine and cosine were swapped: the perpendicular component should be P·sin(70°) = 750 N (not cos), which leads to P = 798 N and a parallel component of 273 N — please review the definitions of perpendicular and parallel components relative to the angle θ.</t>
+  </si>
+  <si>
+    <t>You correctly identified the equation structure (P_perp = P·sinθ and P_parallel = P·cosθ), which earned partial credit; however, the critical error was using θ = 20° instead of the correct angle of 70° between force P (along BD) and member ABC, which should be found by adding the 30° (ABC from horizontal) and 40° (BD from horizontal) components. This incorrect angle led to significantly wrong final answers for both parts.</t>
+  </si>
+  <si>
+    <t>You correctly identified the form of the component equations (P·sinθ for perpendicular, P·cosθ for parallel), earning partial credit; however, the key error was using θ = 50° instead of the correct angle θ = 70° (obtained by combining the 30° and 40° angles from the geometry), which led to incorrect final answers for both parts.</t>
+  </si>
+  <si>
+    <t>You correctly identified the 60° and 50° reference angles from the figure, but the critical error was using θ = 20° instead of the correct angle of θ = 70° between force P and member ABC, which led to significantly incorrect final answers for both parts (a) and (b). Please review how to find the angle between two lines using their orientations relative to a common reference.</t>
+  </si>
+  <si>
+    <t>You correctly identified the need to resolve P into perpendicular and parallel components, but the key error was using θ = 50° instead of the correct angle of θ = 70° (obtained by combining the 30° inclination of ABC with the 40° inclination of BD from horizontal), which led to incorrect values for both P (986.8 N instead of 798 N) and the parallel component. For part (b), the parallel component should have been calculated as P·cos70° ≈ 273 N rather than concluding that neither component is parallel to ABC.</t>
+  </si>
+  <si>
+    <t>You correctly identified the two reference angles (60° and 50°) from the figure and set up the right equation structure (P = 750/sinθ and P∥ = P·cosθ), but the angle between force P and member ABC should be θ = 70° (not 20°), leading to incorrect final answers of P = 798 N and P∥ = 273 N; please review the geometry for determining the angle between two lines.</t>
+  </si>
+  <si>
+    <t>You correctly identified the two given angles (60° and 50°) and set up the right trigonometric framework (P·sinθ = 750 N for the perpendicular component), which shows good understanding of the method. However, the critical error was in the geometry: the angle between BD and ABC should be θ = 70° (30° + 40°), not 20°, leading to significantly incorrect final values for both P and the parallel component.</t>
+  </si>
+  <si>
+    <t>You correctly identified the component equations (P·sinθ = 750 N for the perpendicular component and P·cosθ for the parallel component), which earned full marks for equation setup. However, the angle between force P and member ABC should be θ = 70° (combining 30° from ABC with horizontal and 40° from BD with horizontal), not 20°, which led to incorrect final answers for both parts.</t>
+  </si>
+  <si>
+    <t>No supporting calculations or geometric reasoning were provided for either part; simply stating '400 N' for part (a) (which is also incorrect — the correct answer is 798 N) and referencing the figure for part (b) without any work shown cannot receive meaningful credit beyond a minimal acknowledgment of attempt.</t>
+  </si>
+  <si>
+    <t>You correctly identified the reference angles (60° and 50°) from the figure and made a good attempt at the geometry, but the angle between P and member ABC should be 70° (not 20°), leading to incorrect final values for both P and its parallel component. Additionally, the perpendicular component equation should use sin(70°), not sin(20°), so please review how to determine the included angle between two force directions.</t>
+  </si>
+  <si>
+    <t>Unfortunately, the solution lacks the necessary geometric analysis to determine the correct angle (θ = 70°) between force P and member ABC, and the component equations are set up incorrectly (cosine used instead of sine for the perpendicular component with the wrong reference angle). Please review how to find the angle between two lines and how to resolve a force into perpendicular and parallel components.</t>
+  </si>
+  <si>
+    <t>You correctly identified the key angles from the figure and determined θ = 70° between force P and member ABC, which is excellent. However, you swapped sine and cosine — the perpendicular component should be P·sin(70°) = 750 N (giving P ≈ 798 N), not P·cos(70°), which led to significantly incorrect final answers for both parts.</t>
+  </si>
+  <si>
+    <t>You showed good effort in drawing the force diagram and attempting component calculations, but the key issue is using the wrong angle (50° instead of the correct 70° between force P and member ABC); the angle between BD and ABC should be determined by combining both reference angles (30° + 40° = 70°). As a result, both final answers are incorrect, and the parallel component calculation also contains an error.</t>
+  </si>
+  <si>
+    <t>You correctly identified the 60° and 50° angles from the figure and showed some geometric reasoning, but the approach was fundamentally incorrect — the 750 N is the perpendicular component of the unknown P (not P itself), so P should be found using P = 750/sin(70°) = 798 N with θ = 70° between BD and ABC. Please review how to resolve a force into components parallel and perpendicular to a given member.</t>
+  </si>
+  <si>
+    <t>No work or calculations were provided in the solution box; without any supporting work, no credit can be awarded per the stated policy.</t>
+  </si>
+  <si>
+    <t>Your approach incorrectly treats the given 750 N perpendicular component as the magnitude of P itself, leading to circular reasoning and incorrect final answers. The key step is to first identify the angle θ = 70° between force P (along BD) and member ABC, then solve P = 750/sin(70°) ≈ 798 N and P_parallel = P·cos(70°) ≈ 273 N.</t>
+  </si>
+  <si>
+    <t>Unfortunately, the solution did not correctly identify the angle (θ = 70°) between force P and member ABC; instead, the angles 50° and 60° were used separately to decompose what was assumed to be P = 750 N, which is actually the given perpendicular component, not the magnitude. Please revisit how to find the relative angle between two lines and how to resolve a force into components perpendicular and parallel to a given member.</t>
+  </si>
+  <si>
+    <t>You correctly identified the key reference angles (30°, 40°, 50°, 60°) and even noted θ = 70° between BD and ABC, which is the critical geometric step; however, the angle was not consistently applied in your equations — you used sin(20°), cos(40°), and sin(50°) in different attempts instead of sin(70°) = 750/P, leading to incorrect final answers. Focus on committing to the correct angle once identified and applying it systematically to both component equations.</t>
+  </si>
+  <si>
+    <t>You correctly identified the reference angles from the figure, but used θ = 40° instead of the combined angle θ = 70° between BD and ABC, and also swapped sine and cosine when setting up the perpendicular component equation (P·sin70° = 750 is required). This led to incorrect final answers for both parts.</t>
+  </si>
+  <si>
+    <t>You correctly identified the perpendicular component equation structure (P·sinθ = 750 N), which earns partial credit; however, the angle used (θ = 30°) is incorrect — the correct angle between BD and ABC is 70°, found by combining both reference angles (30° from the 60° at C, and 40° from the 50° at D). As a result, both final answers (P = 1500 N and P∥ = 1299 N) are incorrect.</t>
+  </si>
+  <si>
+    <t>You correctly identified the angle θ = 70° between BD and member ABC, earning full geometry marks. However, the perpendicular component must be expressed as P·sin70° = 750 N (not cosine), and the parallel component as P·cos70°; swapping sine and cosine in both parts led to incorrect final answers.</t>
   </si>
 </sst>
 </file>
@@ -2568,10 +2604,10 @@
         <v>112</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I78" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -2597,10 +2633,10 @@
         <v>112</v>
       </c>
       <c r="H79">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="I79" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -2626,10 +2662,10 @@
         <v>112</v>
       </c>
       <c r="H80">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I80" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -2655,10 +2691,10 @@
         <v>112</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I81" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -2710,10 +2746,10 @@
         <v>112</v>
       </c>
       <c r="H83">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I83" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -2739,10 +2775,10 @@
         <v>112</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I84" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -2820,10 +2856,10 @@
         <v>112</v>
       </c>
       <c r="H87">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I87" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -2849,10 +2885,10 @@
         <v>112</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I88" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -2903,8 +2939,11 @@
       <c r="G90" t="s">
         <v>112</v>
       </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
       <c r="I90" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -2930,10 +2969,10 @@
         <v>112</v>
       </c>
       <c r="H91">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I91" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -2959,10 +2998,10 @@
         <v>112</v>
       </c>
       <c r="H92">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I92" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -3017,10 +3056,10 @@
         <v>112</v>
       </c>
       <c r="H94">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I94" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -3046,10 +3085,10 @@
         <v>112</v>
       </c>
       <c r="H95">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I95" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -3075,10 +3114,10 @@
         <v>112</v>
       </c>
       <c r="H96">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="I96" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -3104,10 +3143,10 @@
         <v>112</v>
       </c>
       <c r="H97">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I97" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -3159,10 +3198,10 @@
         <v>112</v>
       </c>
       <c r="H99">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I99" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -3188,10 +3227,10 @@
         <v>112</v>
       </c>
       <c r="H100">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I100" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -3243,10 +3282,10 @@
         <v>112</v>
       </c>
       <c r="H102">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I102" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -3272,10 +3311,10 @@
         <v>112</v>
       </c>
       <c r="H103">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="I103" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -3301,10 +3340,10 @@
         <v>112</v>
       </c>
       <c r="H104">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="I104" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -3330,10 +3369,10 @@
         <v>112</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I105" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -3362,7 +3401,7 @@
         <v>5</v>
       </c>
       <c r="I106" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -3388,10 +3427,10 @@
         <v>112</v>
       </c>
       <c r="H107">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="I107" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -3420,7 +3459,7 @@
         <v>5</v>
       </c>
       <c r="I108" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -3446,10 +3485,10 @@
         <v>112</v>
       </c>
       <c r="H109">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="I109" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -3475,10 +3514,10 @@
         <v>112</v>
       </c>
       <c r="H110">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I110" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -3504,10 +3543,10 @@
         <v>112</v>
       </c>
       <c r="H111">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I111" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -3562,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -3588,10 +3627,10 @@
         <v>112</v>
       </c>
       <c r="H114">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I114" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -3620,7 +3659,7 @@
         <v>5</v>
       </c>
       <c r="I115" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -3649,7 +3688,7 @@
         <v>25</v>
       </c>
       <c r="I116" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -3727,10 +3766,10 @@
         <v>112</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I119" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -3756,10 +3795,10 @@
         <v>112</v>
       </c>
       <c r="H120">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I120" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -3785,10 +3824,10 @@
         <v>112</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I121" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -4583,11 +4622,8 @@
       <c r="G150" t="s">
         <v>112</v>
       </c>
-      <c r="H150">
-        <v>0</v>
-      </c>
       <c r="I150" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
     </row>
     <row r="151" spans="1:9">

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="148">
   <si>
     <t>student_id</t>
   </si>
@@ -355,112 +355,109 @@
     <t>Quiz 1</t>
   </si>
   <si>
+    <t>Your approach of decomposing force P into perpendicular and parallel components was on the right track, but the critical angle between line BD and member ABC was incorrectly identified as 40° instead of the correct 20° (50° − 30°), leading to incorrect results for both parts. Please review how to determine the angle between two lines using their angles with the horizontal.</t>
+  </si>
+  <si>
+    <t>Absent.</t>
+  </si>
+  <si>
+    <t>Excellent work! You correctly identified the 20° angle between line BD and member ABC, and accurately applied trigonometric decomposition to find both P = 2192.85 N and the parallel component P_parallel = 2060.16 N. Keep it up!</t>
+  </si>
+  <si>
+    <t>You correctly identified the formula setup (P⊥ = P·sinθ and P∥ = P·cosθ), but the critical error was determining the angle between BD and member ABC as 80° instead of the correct 20° (which comes from 50° − 30°, where 30° = 90° − 60°). This led to significantly incorrect values for both parts; please review how to find the angle between two lines using their individual angles with the horizontal.</t>
+  </si>
+  <si>
+    <t>The critical step of finding the angle between line BD and member ABC (alpha = 50° - 30° = 20°) was missed; instead, the 750 N was incorrectly treated as force P and decomposed using 50° and 30° directly, leading to incorrect results for both parts. Please review how to find the angle between two lines and use it to relate the perpendicular component to the total force magnitude.</t>
+  </si>
+  <si>
+    <t>Excellent work! You correctly identified the 20° angle between line BD and member ABC, applied the trigonometric formulas accurately, and arrived at the correct answers for both parts (P ≈ 2192.9 N and P_parallel ≈ 2060.6 N). Well done!</t>
+  </si>
+  <si>
+    <t>You correctly identified the problem components and sketched the diagram with some angle recognition (30°), but no actual calculations were performed for either part — no angle alpha derivation, no formulas, and no numerical answers for P or the parallel component. Please show all supporting work to receive credit.</t>
+  </si>
+  <si>
+    <t>You showed some geometric awareness by identifying 30° and sketching the force triangle, but the critical angle between BD and member ABC should be 20° (not 40°), leading to incorrect results for part (a); part (b) did not include a valid numerical calculation for the parallel component.</t>
+  </si>
+  <si>
+    <t>Excellent work! You correctly identified the critical 20° angle between member ABC and hydraulic cylinder BD, and accurately applied trigonometric relationships to find both the magnitude of force P (≈2192.85 N) and its parallel component (≈2060.61 N). Full marks on all parts — well done!</t>
+  </si>
+  <si>
+    <t>Unfortunately, no calculations or mathematical work were shown — only a redrawing of the given figure. To receive credit, you must show the angle derivation (e.g., α = 20°), apply the trigonometric formulas for the perpendicular and parallel components, and compute the final numerical answers for both parts.</t>
+  </si>
+  <si>
+    <t>Excellent work! You correctly identified the 20° angle between the hydraulic cylinder and member ABC, and accurately applied trigonometric relationships to find both the magnitude of force P (2,192 N) and its parallel component (2,060 N). Perfect score!</t>
+  </si>
+  <si>
+    <t>You correctly identified the given angles (60° and 50°) and set up a diagram, but the critical step of finding the angle between BD and member ABC (α = 50° − 30° = 20°) was missing — you used 50° instead of 20° in your trigonometric expressions. Additionally, no numerical answers were computed for either part (a) or part (b); please make sure to complete the calculations to receive full credit.</t>
+  </si>
+  <si>
     <t>Present in class, but no quiz submission found.</t>
   </si>
   <si>
-    <t>Absent.</t>
-  </si>
-  <si>
-    <t>You correctly identified the two reference angles (60° and 50°) from the figure and showed some geometric reasoning, earning partial credit for the setup. However, you swapped sine and cosine when resolving the perpendicular component (it should be P·sin70° = 750 N, not P·cos70°), which led to incorrect final answers for both parts (a) and (b).</t>
-  </si>
-  <si>
-    <t>Your component equations (P⊥ = P sinθ and P∥ = P cosθ) are correctly formulated, earning full marks for Section B. However, the angle θ was incorrectly determined as 80° instead of the correct 70° (since ABC makes 30° with horizontal and BD makes 40° with horizontal, giving θ = 30° + 40° = 70°), which led to incorrect final values for both P and P∥.</t>
-  </si>
-  <si>
-    <t>You correctly identified the 60° and 50° angles from the figure, but made two critical errors: (1) the 750 N is the perpendicular component of P, not the magnitude of P itself, and (2) the angle between force P and member ABC should be θ = 70° (derived from combining 30° and 40°), not simply 50°. Please revisit how to find the angle between two lines and how to set up the perpendicular/parallel component equations.</t>
-  </si>
-  <si>
-    <t>You correctly identified the 70° angle between BD and ABC, which shows good geometric understanding; however, you incorrectly assumed P = 750 N (which is the perpendicular component, not P itself), and then used sin70° instead of cos70° for the parallel component — the correct approach is P = 750/sin70° ≈ 798 N and P∥ = 798×cos70° ≈ 273 N.</t>
-  </si>
-  <si>
-    <t>You correctly identified the given angles (60° and 50°) from the figure and made an attempt to sketch the geometry, but no equations were set up and no calculations were performed to find the magnitude of P or its parallel component — please show your full solution work to receive credit.</t>
-  </si>
-  <si>
-    <t>You correctly identified the individual reference angles from the figure and set up the perpendicular component equation using sine, which shows good understanding of the approach; however, the critical error was using θ = 40° (only the BD angle) instead of combining both angles to get the correct θ = 70° between force P and member ABC, leading to incorrect final answers of ~1167 N and an unclear parallel component instead of 798 N and 273 N.</t>
-  </si>
-  <si>
-    <t>You correctly identified the angle between BD and ABC as 70° on your diagram, which is a good start; however, you then used 20° (the complement) in your trigonometric equations, leading to swapped sine/cosine roles and incorrect final answers for both parts. Be careful to apply the angle between the force and the member direction directly: P·sin(70°) = 750 N gives P ≈ 798 N, and P·cos(70°) ≈ 273 N for the parallel component.</t>
-  </si>
-  <si>
-    <t>You correctly redrew the figure and identified the given 750 N perpendicular component, but no angle analysis, trigonometric equations, or calculations were provided; please make sure to show all work including determining the angle between BD and ABC (θ = 70°) and applying P = 750/sin(70°) to find the magnitude and parallel component.</t>
-  </si>
-  <si>
-    <t>Attendance signature missing. Quiz score recorded as 0.</t>
-  </si>
-  <si>
-    <t>You correctly identified that the perpendicular component uses sine and the parallel component uses cosine, which earns partial credit; however, the angle between force P and member ABC was incorrectly determined as 20° instead of the correct 70° (derived from the 60° and 50° reference angles in the figure), leading to significantly incorrect final answers for both parts.</t>
-  </si>
-  <si>
-    <t>You correctly set up the perpendicular and parallel component equations using sine and cosine, which shows good understanding of vector decomposition; however, the angle used (50°) is incorrect — the proper angle between force P and member ABC is θ = 70°, obtained by combining the 30° inclination of ABC and 40° inclination of BD from horizontal. Additionally, no numerical final answers were computed for parts (a) or (b).</t>
-  </si>
-  <si>
-    <t>Unfortunately, the solution approach is fundamentally incorrect — the 750 N was treated as the full force P and decomposed into Cartesian x/y components using the given angles separately, rather than finding the angle θ = 70° between line BD and member ABC and applying P·sin(70°) = 750 N to find P = 798 N and P·cos(70°) = 273 N for the parallel component. Please review how to resolve a force into components along and perpendicular to a specified direction.</t>
-  </si>
-  <si>
-    <t>You correctly identified the 60° and 50° angles from the figure, but the key error was using only 30° (complement of 60°) as the angle between P and ABC, rather than combining both angles to get θ = 70°; additionally, the perpendicular component should use sinθ, not cosθ. This led to incorrect values for both P (866 N vs. 798 N) and the parallel component (433 N vs. 273 N).</t>
-  </si>
-  <si>
-    <t>You correctly identified the geometric angles (60°, 50°) and determined θ = 70° between P and member ABC, earning full geometry marks. However, the sine and cosine were swapped: the perpendicular component should be P·sin(70°) = 750 N (not cos), which leads to P = 798 N and a parallel component of 273 N — please review the definitions of perpendicular and parallel components relative to the angle θ.</t>
-  </si>
-  <si>
-    <t>You correctly identified the equation structure (P_perp = P·sinθ and P_parallel = P·cosθ), which earned partial credit; however, the critical error was using θ = 20° instead of the correct angle of 70° between force P (along BD) and member ABC, which should be found by adding the 30° (ABC from horizontal) and 40° (BD from horizontal) components. This incorrect angle led to significantly wrong final answers for both parts.</t>
-  </si>
-  <si>
-    <t>You correctly identified the form of the component equations (P·sinθ for perpendicular, P·cosθ for parallel), earning partial credit; however, the key error was using θ = 50° instead of the correct angle θ = 70° (obtained by combining the 30° and 40° angles from the geometry), which led to incorrect final answers for both parts.</t>
-  </si>
-  <si>
-    <t>You correctly identified the 60° and 50° reference angles from the figure, but the critical error was using θ = 20° instead of the correct angle of θ = 70° between force P and member ABC, which led to significantly incorrect final answers for both parts (a) and (b). Please review how to find the angle between two lines using their orientations relative to a common reference.</t>
-  </si>
-  <si>
-    <t>You correctly identified the need to resolve P into perpendicular and parallel components, but the key error was using θ = 50° instead of the correct angle of θ = 70° (obtained by combining the 30° inclination of ABC with the 40° inclination of BD from horizontal), which led to incorrect values for both P (986.8 N instead of 798 N) and the parallel component. For part (b), the parallel component should have been calculated as P·cos70° ≈ 273 N rather than concluding that neither component is parallel to ABC.</t>
-  </si>
-  <si>
-    <t>You correctly identified the two reference angles (60° and 50°) from the figure and set up the right equation structure (P = 750/sinθ and P∥ = P·cosθ), but the angle between force P and member ABC should be θ = 70° (not 20°), leading to incorrect final answers of P = 798 N and P∥ = 273 N; please review the geometry for determining the angle between two lines.</t>
-  </si>
-  <si>
-    <t>You correctly identified the two given angles (60° and 50°) and set up the right trigonometric framework (P·sinθ = 750 N for the perpendicular component), which shows good understanding of the method. However, the critical error was in the geometry: the angle between BD and ABC should be θ = 70° (30° + 40°), not 20°, leading to significantly incorrect final values for both P and the parallel component.</t>
-  </si>
-  <si>
-    <t>You correctly identified the component equations (P·sinθ = 750 N for the perpendicular component and P·cosθ for the parallel component), which earned full marks for equation setup. However, the angle between force P and member ABC should be θ = 70° (combining 30° from ABC with horizontal and 40° from BD with horizontal), not 20°, which led to incorrect final answers for both parts.</t>
-  </si>
-  <si>
-    <t>No supporting calculations or geometric reasoning were provided for either part; simply stating '400 N' for part (a) (which is also incorrect — the correct answer is 798 N) and referencing the figure for part (b) without any work shown cannot receive meaningful credit beyond a minimal acknowledgment of attempt.</t>
-  </si>
-  <si>
-    <t>You correctly identified the reference angles (60° and 50°) from the figure and made a good attempt at the geometry, but the angle between P and member ABC should be 70° (not 20°), leading to incorrect final values for both P and its parallel component. Additionally, the perpendicular component equation should use sin(70°), not sin(20°), so please review how to determine the included angle between two force directions.</t>
-  </si>
-  <si>
-    <t>Unfortunately, the solution lacks the necessary geometric analysis to determine the correct angle (θ = 70°) between force P and member ABC, and the component equations are set up incorrectly (cosine used instead of sine for the perpendicular component with the wrong reference angle). Please review how to find the angle between two lines and how to resolve a force into perpendicular and parallel components.</t>
-  </si>
-  <si>
-    <t>You correctly identified the key angles from the figure and determined θ = 70° between force P and member ABC, which is excellent. However, you swapped sine and cosine — the perpendicular component should be P·sin(70°) = 750 N (giving P ≈ 798 N), not P·cos(70°), which led to significantly incorrect final answers for both parts.</t>
-  </si>
-  <si>
-    <t>You showed good effort in drawing the force diagram and attempting component calculations, but the key issue is using the wrong angle (50° instead of the correct 70° between force P and member ABC); the angle between BD and ABC should be determined by combining both reference angles (30° + 40° = 70°). As a result, both final answers are incorrect, and the parallel component calculation also contains an error.</t>
-  </si>
-  <si>
-    <t>You correctly identified the 60° and 50° angles from the figure and showed some geometric reasoning, but the approach was fundamentally incorrect — the 750 N is the perpendicular component of the unknown P (not P itself), so P should be found using P = 750/sin(70°) = 798 N with θ = 70° between BD and ABC. Please review how to resolve a force into components parallel and perpendicular to a given member.</t>
-  </si>
-  <si>
-    <t>No work or calculations were provided in the solution box; without any supporting work, no credit can be awarded per the stated policy.</t>
-  </si>
-  <si>
-    <t>Your approach incorrectly treats the given 750 N perpendicular component as the magnitude of P itself, leading to circular reasoning and incorrect final answers. The key step is to first identify the angle θ = 70° between force P (along BD) and member ABC, then solve P = 750/sin(70°) ≈ 798 N and P_parallel = P·cos(70°) ≈ 273 N.</t>
-  </si>
-  <si>
-    <t>Unfortunately, the solution did not correctly identify the angle (θ = 70°) between force P and member ABC; instead, the angles 50° and 60° were used separately to decompose what was assumed to be P = 750 N, which is actually the given perpendicular component, not the magnitude. Please revisit how to find the relative angle between two lines and how to resolve a force into components perpendicular and parallel to a given member.</t>
-  </si>
-  <si>
-    <t>You correctly identified the key reference angles (30°, 40°, 50°, 60°) and even noted θ = 70° between BD and ABC, which is the critical geometric step; however, the angle was not consistently applied in your equations — you used sin(20°), cos(40°), and sin(50°) in different attempts instead of sin(70°) = 750/P, leading to incorrect final answers. Focus on committing to the correct angle once identified and applying it systematically to both component equations.</t>
-  </si>
-  <si>
-    <t>You correctly identified the reference angles from the figure, but used θ = 40° instead of the combined angle θ = 70° between BD and ABC, and also swapped sine and cosine when setting up the perpendicular component equation (P·sin70° = 750 is required). This led to incorrect final answers for both parts.</t>
-  </si>
-  <si>
-    <t>You correctly identified the perpendicular component equation structure (P·sinθ = 750 N), which earns partial credit; however, the angle used (θ = 30°) is incorrect — the correct angle between BD and ABC is 70°, found by combining both reference angles (30° from the 60° at C, and 40° from the 50° at D). As a result, both final answers (P = 1500 N and P∥ = 1299 N) are incorrect.</t>
-  </si>
-  <si>
-    <t>You correctly identified the angle θ = 70° between BD and member ABC, earning full geometry marks. However, the perpendicular component must be expressed as P·sin70° = 750 N (not cosine), and the parallel component as P·cos70°; swapping sine and cosine in both parts led to incorrect final answers.</t>
+    <t>Unfortunately, the critical step of finding the 20° angle between line BD and member ABC was missed; the student instead decomposed the given 750 N component using the given angles (50° and 60°) directly, which does not yield the required magnitude of P (~2193 N) or its parallel component (~2061 N). Please review how to find the angle between two lines and how to resolve a force into components perpendicular and parallel to a member.</t>
+  </si>
+  <si>
+    <t>The critical error was in the geometry: the angle between BD and member ABC is 20° (50° − 30°), not 30°; using cos(30°) to decompose P led to an incorrect magnitude of ~866 N instead of ~2193 N. Part (b) also lacked a numerical calculation for the parallel component — stating only the angle is insufficient for full credit.</t>
+  </si>
+  <si>
+    <t>Your final numerical answers for both parts are correct (P ≈ 2192.85 N and P_parallel ≈ 2060.61 N), as cos(70°) and sin(70°) are trigonometrically equivalent to sin(20°) and cos(20°). However, the critical geometric step was not clearly established — the correct angle between BD and ABC should be explicitly identified as 20° (= 50° − 30°), and using 70° without proper justification of the angle derivation cost points in the geometry section.</t>
+  </si>
+  <si>
+    <t>Excellent work! You correctly identified the 20° angle between the hydraulic cylinder BD and member ABC, and applied the trigonometric formulas accurately to obtain both the magnitude of force P (≈2192.85 N) and its parallel component (≈2060.61 N). Perfect score!</t>
+  </si>
+  <si>
+    <t>You correctly identified several geometric angles (30°, 50°, and even noted 20° on the diagram), earning partial geometry credit; however, the critical alpha angle of 20° between line BD and member ABC was not used in your calculations — you applied sin50° instead of sin20°, leading to an incorrect P ≈ 979 N instead of ~2193 N. For part (b), the parallel component formula and approach were also incorrect as a result of the wrong angle choice.</t>
+  </si>
+  <si>
+    <t>Excellent work! You correctly identified the 20° angle between line BD and member ABC, applied the proper trigonometric formulas for both parts, and arrived at accurate answers of 2192.85 N and 2060.6 N. Well done!</t>
+  </si>
+  <si>
+    <t>You correctly set up the form P·sin(angle) = 750 N, but used 50° instead of the critical angle of 20° (found by subtracting ABC's 30° inclination from BD's 50°), leading to an incorrect magnitude in part (a). For part (b), the parallel component does exist and equals approximately 2061 N; stating that neither component is parallel to ABC is incorrect.</t>
+  </si>
+  <si>
+    <t>Excellent work! You correctly identified the critical 20° angle between line BD and member ABC, applied the trigonometric relationships accurately, and obtained correct results for both the magnitude of P (2192.25 N) and the parallel component (2060.04 N). Perfect score!</t>
+  </si>
+  <si>
+    <t>Excellent work! You correctly identified the critical 20° angle between BD and member ABC, and applied the sine and cosine formulas accurately to obtain P ≈ 2192.85 N and the parallel component ≈ 2060.60 N. A very minor deduction was made for the slightly unclear intermediate geometric reasoning steps.</t>
+  </si>
+  <si>
+    <t>Excellent work! You correctly identified the 20° angle between line BD and member ABC and applied the correct trigonometric formulas for both parts. A very minor deduction was made in part (b) because rounding P to 2.19 kN led to a final answer of 2057 N, which falls just slightly below the accepted range; using the more precise intermediate value would have given the exact result.</t>
+  </si>
+  <si>
+    <t>Unfortunately, no supporting calculations were provided for either part, and the answer given for part (a) (400 N) is incorrect — the correct value is approximately 2193 N; without shown work, no partial credit can be awarded. Please remember to show all steps, including angle derivations and trigonometric formulas, to earn credit.</t>
+  </si>
+  <si>
+    <t>Excellent geometric reasoning — you correctly identified the critical 20° angle and applied the right trigonometric formulas for both parts. Minor deductions are due to rounding sin(20°) as 0.34 instead of the more precise 0.3420, which caused your answers (2205.8 N and 2072.7 N) to fall slightly outside the accepted ranges; carrying more decimal places in intermediate steps would give full credit.</t>
+  </si>
+  <si>
+    <t>Unfortunately, the critical geometric step of finding the angle between BD and ABC (α = 50° − 30° = 20°) was not performed, and the incorrect angle (60°) was used in an incorrect formula; the correct answers are P ≈ 2193 N and P_parallel ≈ 2061 N. Please review how to decompose forces relative to the member's orientation rather than the horizontal.</t>
+  </si>
+  <si>
+    <t>Excellent work overall — you correctly identified the 20° angle and used equivalent trigonometric relationships. A minor rounding error in cos(70°) (using 0.34 instead of ~0.342) pushed your Part (a) answer slightly outside the accepted range; part (b) was perfectly calculated.</t>
+  </si>
+  <si>
+    <t>You showed effort with vector diagrams and attempted to decompose the force, which earns partial credit; however, the critical angle between BD and member ABC was not correctly identified as 20° (= 50° − 30°), leading to incorrect results for both parts (a) and (b). Please review how to find the angle between two lines using their angles with the horizontal.</t>
+  </si>
+  <si>
+    <t>Unfortunately, the critical angle between member ABC and cylinder BD was not correctly identified — the correct angle is 20° (= 50° − 30°), but your work used 40°, leading to incorrect formulas and results for both parts. Please review how to find the relative angle between two inclined members.</t>
+  </si>
+  <si>
+    <t>The critical geometric step of finding the 20° angle between member ABC and hydraulic cylinder BD was not correctly established; instead, global coordinate decomposition was applied to the 750N perpendicular component itself rather than using it to find the unknown force P. As a result, both the magnitude of P (~2193N) and the parallel component (~2061N) are incorrect.</t>
+  </si>
+  <si>
+    <t>Unfortunately, the solution did not identify the critical angle (α = 20°) between the hydraulic cylinder BD and member ABC, which is the key geometric step. The approach of decomposing 750 N into x-y components using 50° and 60° directly does not address the perpendicular/parallel components relative to member ABC; please review how to find force components along and perpendicular to an inclined member.</t>
+  </si>
+  <si>
+    <t>You showed some awareness of the 20° angle early on (sin 20° = 750/x), which is the key geometric insight, but you did not follow through with this correct setup and instead pursued incorrect angle relationships (30°, 50°, 40°) leading to wrong answers for both parts. Please revisit how to find the angle between line BD and member ABC by subtracting their respective angles with the horizontal (50° − 30° = 20°), then apply P = 750/sin(20°) ≈ 2193 N and P_parallel = 750/tan(20°) ≈ 2061 N.</t>
+  </si>
+  <si>
+    <t>Unfortunately, the critical angle between BD and member ABC was incorrectly determined as 40° instead of the correct 20° (50° − 30°), and the perpendicular component was set equal to P·cos rather than P·sin, leading to incorrect results for both parts. Please review how to find the angle between two lines and how to decompose a force into perpendicular and parallel components relative to a member.</t>
+  </si>
+  <si>
+    <t>Good approach in setting up the trigonometric formula, but the critical error was identifying the angle between BD and member ABC as 30° instead of the correct 20° (derived from 50° − 30°), which led to incorrect answers for both parts. Please review how to find the angle between two lines using their respective angles with the horizontal.</t>
+  </si>
+  <si>
+    <t>Excellent work — your use of cos(70°) and sin(70°) is mathematically equivalent to sin(20°) and cos(20°), yielding correct answers for both parts (a) and (b). A small deduction is applied because the intermediate geometric reasoning (deriving the 20° or 70° angle between BD and ABC) was not explicitly shown step-by-step; please make sure to show all geometry derivations clearly in future quizzes.</t>
   </si>
 </sst>
 </file>
@@ -2549,7 +2546,7 @@
         <v>112</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I76" t="s">
         <v>113</v>
@@ -2604,7 +2601,7 @@
         <v>112</v>
       </c>
       <c r="H78">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I78" t="s">
         <v>115</v>
@@ -2633,7 +2630,7 @@
         <v>112</v>
       </c>
       <c r="H79">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="I79" t="s">
         <v>116</v>
@@ -2691,7 +2688,7 @@
         <v>112</v>
       </c>
       <c r="H81">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I81" t="s">
         <v>118</v>
@@ -2746,7 +2743,7 @@
         <v>112</v>
       </c>
       <c r="H83">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I83" t="s">
         <v>119</v>
@@ -2775,7 +2772,7 @@
         <v>112</v>
       </c>
       <c r="H84">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I84" t="s">
         <v>120</v>
@@ -2856,7 +2853,7 @@
         <v>112</v>
       </c>
       <c r="H87">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="I87" t="s">
         <v>121</v>
@@ -2885,7 +2882,7 @@
         <v>112</v>
       </c>
       <c r="H88">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I88" t="s">
         <v>122</v>
@@ -2939,11 +2936,8 @@
       <c r="G90" t="s">
         <v>112</v>
       </c>
-      <c r="H90">
-        <v>0</v>
-      </c>
       <c r="I90" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -2969,10 +2963,10 @@
         <v>112</v>
       </c>
       <c r="H91">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I91" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -2998,10 +2992,10 @@
         <v>112</v>
       </c>
       <c r="H92">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I92" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -3030,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -3085,7 +3079,7 @@
         <v>112</v>
       </c>
       <c r="H95">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I95" t="s">
         <v>127</v>
@@ -3114,7 +3108,7 @@
         <v>112</v>
       </c>
       <c r="H96">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="I96" t="s">
         <v>128</v>
@@ -3143,7 +3137,7 @@
         <v>112</v>
       </c>
       <c r="H97">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="I97" t="s">
         <v>129</v>
@@ -3198,7 +3192,7 @@
         <v>112</v>
       </c>
       <c r="H99">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I99" t="s">
         <v>130</v>
@@ -3227,7 +3221,7 @@
         <v>112</v>
       </c>
       <c r="H100">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I100" t="s">
         <v>131</v>
@@ -3282,7 +3276,7 @@
         <v>112</v>
       </c>
       <c r="H102">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I102" t="s">
         <v>132</v>
@@ -3311,7 +3305,7 @@
         <v>112</v>
       </c>
       <c r="H103">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I103" t="s">
         <v>133</v>
@@ -3340,7 +3334,7 @@
         <v>112</v>
       </c>
       <c r="H104">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="I104" t="s">
         <v>134</v>
@@ -3369,7 +3363,7 @@
         <v>112</v>
       </c>
       <c r="H105">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="I105" t="s">
         <v>135</v>
@@ -3398,7 +3392,7 @@
         <v>112</v>
       </c>
       <c r="H106">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I106" t="s">
         <v>136</v>
@@ -3427,7 +3421,7 @@
         <v>112</v>
       </c>
       <c r="H107">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="I107" t="s">
         <v>137</v>
@@ -3485,7 +3479,7 @@
         <v>112</v>
       </c>
       <c r="H109">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="I109" t="s">
         <v>139</v>
@@ -3514,7 +3508,7 @@
         <v>112</v>
       </c>
       <c r="H110">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I110" t="s">
         <v>140</v>
@@ -3543,7 +3537,7 @@
         <v>112</v>
       </c>
       <c r="H111">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I111" t="s">
         <v>141</v>
@@ -3598,7 +3592,7 @@
         <v>112</v>
       </c>
       <c r="H113">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I113" t="s">
         <v>142</v>
@@ -3627,10 +3621,10 @@
         <v>112</v>
       </c>
       <c r="H114">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I114" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -3656,10 +3650,10 @@
         <v>112</v>
       </c>
       <c r="H115">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -3685,10 +3679,10 @@
         <v>112</v>
       </c>
       <c r="H116">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I116" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -3769,7 +3763,7 @@
         <v>20</v>
       </c>
       <c r="I119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -3798,7 +3792,7 @@
         <v>25</v>
       </c>
       <c r="I120" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -3824,10 +3818,10 @@
         <v>112</v>
       </c>
       <c r="H121">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="I121" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -3908,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -4015,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -4122,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="I132" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -4151,7 +4145,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -4232,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="I136" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -4261,7 +4255,7 @@
         <v>0</v>
       </c>
       <c r="I137" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -4316,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="I139" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -4345,7 +4339,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -4400,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="I142" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -4429,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="I143" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -4458,7 +4452,7 @@
         <v>0</v>
       </c>
       <c r="I144" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -4513,7 +4507,7 @@
         <v>0</v>
       </c>
       <c r="I146" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -4542,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="I147" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -4597,7 +4591,7 @@
         <v>0</v>
       </c>
       <c r="I149" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -4678,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="I152" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -4707,7 +4701,7 @@
         <v>0</v>
       </c>
       <c r="I153" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -4736,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="I154" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -4765,7 +4759,7 @@
         <v>0</v>
       </c>
       <c r="I155" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -4794,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="I156" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="167">
   <si>
     <t>student_id</t>
   </si>
@@ -458,6 +458,63 @@
   </si>
   <si>
     <t>Excellent work — your use of cos(70°) and sin(70°) is mathematically equivalent to sin(20°) and cos(20°), yielding correct answers for both parts (a) and (b). A small deduction is applied because the intermediate geometric reasoning (deriving the 20° or 70° angle between BD and ABC) was not explicitly shown step-by-step; please make sure to show all geometry derivations clearly in future quizzes.</t>
+  </si>
+  <si>
+    <t>No solution work was provided on the answer page; the solution box is completely blank. Without any supporting calculations, no credit can be awarded per the stated instructions.</t>
+  </si>
+  <si>
+    <t>No work or solution was provided on the answer sheet. A score of 0 is awarded as answers without supporting calculations receive no credit.</t>
+  </si>
+  <si>
+    <t>The student correctly identified the approach (r_AB = r_B - r_A) and the z-component (-17k) but used incorrect coordinates for Point B: they used B(16, 9, 3) instead of the correct center B(20, 10.5, 3), leading to wrong x and y components (4i + 4j instead of 8i + 5.5j). Consequently, all subsequent calculations (magnitude, unit vector, and force components) are incorrect, earning only partial credit for correct method setup and the correct z-component.</t>
+  </si>
+  <si>
+    <t>The student did not use the correct 3D coordinate/position vector approach; instead, they attempted a 2D trigonometric method with assumed angles (30°, 60°) that are not given in the problem, yielding no correct results for any part. No credit can be awarded as the methodology is fundamentally incorrect and no valid coordinates, unit vector, or force components were obtained.</t>
+  </si>
+  <si>
+    <t>Point A coordinates were incorrectly taken as (5, 12, 20) instead of (12, 5, 20), and Point B was also incorrectly computed, leading to a wrong position vector r_AB = (10.5i + 8j - 17k) instead of the correct (8i + 5.5j - 17k). Consequently, the unit vector and all scalar components of T are incorrect; however, the overall method and procedure are correct, earning substantial partial credit.</t>
+  </si>
+  <si>
+    <t>The student correctly identified point A but made an error in determining point B coordinates: B should be (20, 10.5, 3) m, not (15.5, 20, 3) m — the x and y coordinates were swapped/miscalculated, leading to an incorrect position vector r_AB = (10.5i + 8j - 17k) instead of (8i + 5.5j - 17k). All subsequent calculations (magnitude, unit vector, and force components) are based on this incorrect setup, so only partial credit is awarded for the correct method and approach.</t>
+  </si>
+  <si>
+    <t>The student incorrectly identified the coordinates of points A and B, using wrong values (e.g., A=(5,9,3) and B=(8,3,3) instead of A(12,5,20) and B(20,10.5,3)), leading to a completely wrong position vector, magnitude, unit vector, and force components. The approach of using a unit vector formula was conceptually attempted but the fundamental coordinate setup and subsequent calculations were all incorrect, earning only minimal credit.</t>
+  </si>
+  <si>
+    <t>The student only sketched the figure with some labeled dimensions but provided no actual calculations for the position vector, unit vector, or tension components. No credit can be awarded without supporting work.</t>
+  </si>
+  <si>
+    <t>No work or solution was provided on the answer sheet; the solution box is completely blank. Without any supporting calculations or answers, no credit can be awarded.</t>
+  </si>
+  <si>
+    <t>The student incorrectly determined the coordinates of points A and B, leading to a wrong position vector and magnitude (got ~21.5 m instead of ~19.58 m). The unit vector and force components were not correctly computed; only minimal partial credit is awarded for attempting a vector approach and showing some geometric reasoning.</t>
+  </si>
+  <si>
+    <t>The student correctly identified the method but used wrong coordinates for both points A and B (swapped x and y for A, incorrect B coordinates), leading to an incorrect position vector r_AB = (10.5î + 8ĵ - 17k̂) instead of (8î + 5.5ĵ - 17k̂). All subsequent calculations (magnitude, unit vector, and T components) are consistent with their incorrect r_AB but do not match the correct solution.</t>
+  </si>
+  <si>
+    <t>Attendance signature missing. Quiz score recorded as 0.</t>
+  </si>
+  <si>
+    <t>The student correctly identified the z-component of r_AB as -17 and had the right approach, but assigned wrong coordinates to A and B (swapped x and y axes), leading to incorrect position vector components (10.5i + 8j - 17k instead of 8i + 5.5j - 17k) and a wrong magnitude (21.523 instead of 19.58). Additionally, the unit vector calculation result (0.06969) is dimensionally incorrect (it should be a dimensionless vector with components near 0.4, 0.28, -0.87), and the final answer of 975.66 N is completely wrong for the tension components.</t>
+  </si>
+  <si>
+    <t>The student attempted a 2D approach using a single angle, completely missing the 3D nature of the problem; no correct coordinates, position vector, unit vector, or force components were established. All parts of the solution are incorrect, earning no credit.</t>
+  </si>
+  <si>
+    <t>The student correctly identified the approach but made errors in coordinates: Point A should be (12, 5, 20) not (5, 12, 20), and Point B should be (20, 10.5, 3) not (15.5, 20, 3), leading to an incorrect position vector r_AB = (10.5, 8, -17) instead of (8, 5.5, -17) and wrong magnitude of 21.52 instead of ~19.58. Partial credit awarded only for the correct methodology and final vector force calculation setup.</t>
+  </si>
+  <si>
+    <t>The solution page is completely blank with no work shown; answers without supporting calculations cannot receive credit. Only some preliminary notes on the first page are visible, but no complete solution was attempted.</t>
+  </si>
+  <si>
+    <t>The student incorrectly identified the coordinates of points A and B, treating the problem in 2D rather than 3D, and failed to correctly compute the position vector r_AB with all three components (i, j, k). The magnitude and unit vector calculations are consequently wrong, and the final tension components are not correctly expressed as a 3D vector; only minimal partial credit is awarded for recognizing some relevant dimensions and the general approach.</t>
+  </si>
+  <si>
+    <t>The student attempted a 2D trigonometric approach instead of the required 3D vector method, failing to correctly identify the 3D coordinates of points A and B or compute the position vector r_AB. The final scalar components are completely incorrect in both magnitude and method, earning minimal credit only for showing some effort toward a solution.</t>
+  </si>
+  <si>
+    <t>The student attempted a 2D trigonometric approach using angles, which is fundamentally incorrect for this 3D problem. No proper position vector r_AB, unit vector, or correct 3D force components were established; the final answer (11.91k + 7.35i) kN does not match the correct solution and the method shows no understanding of 3D vector analysis.</t>
   </si>
 </sst>
 </file>
@@ -3902,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -4009,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -4113,10 +4170,10 @@
         <v>112</v>
       </c>
       <c r="H132">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I132" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -4145,7 +4202,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -4223,10 +4280,10 @@
         <v>112</v>
       </c>
       <c r="H136">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I136" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -4252,10 +4309,10 @@
         <v>112</v>
       </c>
       <c r="H137">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I137" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -4307,10 +4364,10 @@
         <v>112</v>
       </c>
       <c r="H139">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I139" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -4339,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -4394,7 +4451,7 @@
         <v>0</v>
       </c>
       <c r="I142" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -4420,10 +4477,10 @@
         <v>112</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I143" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -4449,10 +4506,10 @@
         <v>112</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I144" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -4477,8 +4534,11 @@
       <c r="G145" t="s">
         <v>112</v>
       </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
       <c r="I145" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -4504,10 +4564,10 @@
         <v>112</v>
       </c>
       <c r="H146">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -4536,7 +4596,7 @@
         <v>0</v>
       </c>
       <c r="I147" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -4588,10 +4648,10 @@
         <v>112</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I149" t="s">
-        <v>125</v>
+        <v>162</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -4672,7 +4732,7 @@
         <v>0</v>
       </c>
       <c r="I152" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -4698,10 +4758,10 @@
         <v>112</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I153" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -4727,10 +4787,10 @@
         <v>112</v>
       </c>
       <c r="H154">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I154" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -4785,10 +4845,10 @@
         <v>112</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I156" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -460,61 +460,61 @@
     <t>Excellent work — your use of cos(70°) and sin(70°) is mathematically equivalent to sin(20°) and cos(20°), yielding correct answers for both parts (a) and (b). A small deduction is applied because the intermediate geometric reasoning (deriving the 20° or 70° angle between BD and ABC) was not explicitly shown step-by-step; please make sure to show all geometry derivations clearly in future quizzes.</t>
   </si>
   <si>
-    <t>No solution work was provided on the answer page; the solution box is completely blank. Without any supporting calculations, no credit can be awarded per the stated instructions.</t>
-  </si>
-  <si>
-    <t>No work or solution was provided on the answer sheet. A score of 0 is awarded as answers without supporting calculations receive no credit.</t>
-  </si>
-  <si>
-    <t>The student correctly identified the approach (r_AB = r_B - r_A) and the z-component (-17k) but used incorrect coordinates for Point B: they used B(16, 9, 3) instead of the correct center B(20, 10.5, 3), leading to wrong x and y components (4i + 4j instead of 8i + 5.5j). Consequently, all subsequent calculations (magnitude, unit vector, and force components) are incorrect, earning only partial credit for correct method setup and the correct z-component.</t>
-  </si>
-  <si>
-    <t>The student did not use the correct 3D coordinate/position vector approach; instead, they attempted a 2D trigonometric method with assumed angles (30°, 60°) that are not given in the problem, yielding no correct results for any part. No credit can be awarded as the methodology is fundamentally incorrect and no valid coordinates, unit vector, or force components were obtained.</t>
-  </si>
-  <si>
-    <t>Point A coordinates were incorrectly taken as (5, 12, 20) instead of (12, 5, 20), and Point B was also incorrectly computed, leading to a wrong position vector r_AB = (10.5i + 8j - 17k) instead of the correct (8i + 5.5j - 17k). Consequently, the unit vector and all scalar components of T are incorrect; however, the overall method and procedure are correct, earning substantial partial credit.</t>
-  </si>
-  <si>
-    <t>The student correctly identified point A but made an error in determining point B coordinates: B should be (20, 10.5, 3) m, not (15.5, 20, 3) m — the x and y coordinates were swapped/miscalculated, leading to an incorrect position vector r_AB = (10.5i + 8j - 17k) instead of (8i + 5.5j - 17k). All subsequent calculations (magnitude, unit vector, and force components) are based on this incorrect setup, so only partial credit is awarded for the correct method and approach.</t>
-  </si>
-  <si>
-    <t>The student incorrectly identified the coordinates of points A and B, using wrong values (e.g., A=(5,9,3) and B=(8,3,3) instead of A(12,5,20) and B(20,10.5,3)), leading to a completely wrong position vector, magnitude, unit vector, and force components. The approach of using a unit vector formula was conceptually attempted but the fundamental coordinate setup and subsequent calculations were all incorrect, earning only minimal credit.</t>
-  </si>
-  <si>
-    <t>The student only sketched the figure with some labeled dimensions but provided no actual calculations for the position vector, unit vector, or tension components. No credit can be awarded without supporting work.</t>
-  </si>
-  <si>
-    <t>No work or solution was provided on the answer sheet; the solution box is completely blank. Without any supporting calculations or answers, no credit can be awarded.</t>
-  </si>
-  <si>
-    <t>The student incorrectly determined the coordinates of points A and B, leading to a wrong position vector and magnitude (got ~21.5 m instead of ~19.58 m). The unit vector and force components were not correctly computed; only minimal partial credit is awarded for attempting a vector approach and showing some geometric reasoning.</t>
-  </si>
-  <si>
-    <t>The student correctly identified the method but used wrong coordinates for both points A and B (swapped x and y for A, incorrect B coordinates), leading to an incorrect position vector r_AB = (10.5î + 8ĵ - 17k̂) instead of (8î + 5.5ĵ - 17k̂). All subsequent calculations (magnitude, unit vector, and T components) are consistent with their incorrect r_AB but do not match the correct solution.</t>
+    <t>No work or solution was shown on the answer page; the solution box is completely blank. Without any supporting calculations, no credit can be awarded per the stated instructions.</t>
+  </si>
+  <si>
+    <t>No work was shown in the solution box; the answer sheet was submitted completely blank. Without any supporting calculations, no credit can be awarded.</t>
+  </si>
+  <si>
+    <t>The z-component of the position vector r_AB is correct (-17k), but the x and y components are wrong due to incorrect coordinate identification for points A and B (student used A(12,5,20) and B(16,9,3) instead of A(5,12,20) and B(15.5,20,3)). All subsequent results (magnitude, unit vector, and force components) are incorrect as a result; partial credit is awarded for correct methodology and correct z-component.</t>
+  </si>
+  <si>
+    <t>The student attempted the problem using trigonometric angle decomposition (sin/cos of assumed angles) rather than the required 3D coordinate and position vector approach, yielding incorrect results with no valid position vector, unit vector, or force components. No credit can be awarded as the solution method is fundamentally incorrect.</t>
+  </si>
+  <si>
+    <t>Excellent work — all three parts are correctly solved: coordinates, position vector, magnitude, unit vector, and all scalar/vector components of T match the official solution within tolerance. Well-organized and clearly shown work.</t>
+  </si>
+  <si>
+    <t>Excellent work — coordinates, position vector, magnitude, unit vector, and force components are all correctly computed and within the accepted ranges. Minor sign error on the k-component of the unit vector (written as +0.7899 instead of -0.7899) but correctly applied as negative in the final T vector, so only a negligible deduction applies.</t>
+  </si>
+  <si>
+    <t>The student incorrectly identified the coordinates of points A and B, leading to a completely wrong position vector and magnitude. The approach to finding the unit vector and force components was fundamentally flawed, with no correct results for any of the three required parts.</t>
+  </si>
+  <si>
+    <t>The student correctly identified key coordinates (A, B at 15.5) and approximated the cable length (~23m), showing some understanding of the geometry. However, no position vector, unit vector, or force components were computed, so nearly all required work is missing and only minimal partial credit can be awarded.</t>
+  </si>
+  <si>
+    <t>No work or solution was provided on the answer sheet; the solution box is completely blank. A score of 0 is awarded as answers without supporting calculations receive no credit.</t>
+  </si>
+  <si>
+    <t>The student correctly identified the magnitude |r_AB| ≈ 21.5 m (within acceptable range), earning partial credit for Part 1. However, the unit vector components and scalar/vector components of T were not clearly computed or presented, resulting in no credit for Parts 2 and 3.</t>
+  </si>
+  <si>
+    <t>Excellent work overall — coordinates, position vector, magnitude, unit vector, and force components are all correct and well-presented. Minor rounding differences in unit vector components (0.487, 0.371, 0.789 vs. 0.488, 0.372, 0.790) are within acceptable tolerance, resulting in a negligible deduction.</t>
   </si>
   <si>
     <t>Attendance signature missing. Quiz score recorded as 0.</t>
   </si>
   <si>
-    <t>The student correctly identified the z-component of r_AB as -17 and had the right approach, but assigned wrong coordinates to A and B (swapped x and y axes), leading to incorrect position vector components (10.5i + 8j - 17k instead of 8i + 5.5j - 17k) and a wrong magnitude (21.523 instead of 19.58). Additionally, the unit vector calculation result (0.06969) is dimensionally incorrect (it should be a dimensionless vector with components near 0.4, 0.28, -0.87), and the final answer of 975.66 N is completely wrong for the tension components.</t>
-  </si>
-  <si>
-    <t>The student attempted a 2D approach using a single angle, completely missing the 3D nature of the problem; no correct coordinates, position vector, unit vector, or force components were established. All parts of the solution are incorrect, earning no credit.</t>
-  </si>
-  <si>
-    <t>The student correctly identified the approach but made errors in coordinates: Point A should be (12, 5, 20) not (5, 12, 20), and Point B should be (20, 10.5, 3) not (15.5, 20, 3), leading to an incorrect position vector r_AB = (10.5, 8, -17) instead of (8, 5.5, -17) and wrong magnitude of 21.52 instead of ~19.58. Partial credit awarded only for the correct methodology and final vector force calculation setup.</t>
-  </si>
-  <si>
-    <t>The solution page is completely blank with no work shown; answers without supporting calculations cannot receive credit. Only some preliminary notes on the first page are visible, but no complete solution was attempted.</t>
-  </si>
-  <si>
-    <t>The student incorrectly identified the coordinates of points A and B, treating the problem in 2D rather than 3D, and failed to correctly compute the position vector r_AB with all three components (i, j, k). The magnitude and unit vector calculations are consequently wrong, and the final tension components are not correctly expressed as a 3D vector; only minimal partial credit is awarded for recognizing some relevant dimensions and the general approach.</t>
-  </si>
-  <si>
-    <t>The student attempted a 2D trigonometric approach instead of the required 3D vector method, failing to correctly identify the 3D coordinates of points A and B or compute the position vector r_AB. The final scalar components are completely incorrect in both magnitude and method, earning minimal credit only for showing some effort toward a solution.</t>
-  </si>
-  <si>
-    <t>The student attempted a 2D trigonometric approach using angles, which is fundamentally incorrect for this 3D problem. No proper position vector r_AB, unit vector, or correct 3D force components were established; the final answer (11.91k + 7.35i) kN does not match the correct solution and the method shows no understanding of 3D vector analysis.</t>
+    <t>Coordinates for A and B are correctly identified, and the position vector r_AB = (10.5i + 8j - 17k) m is correct (30/30). The magnitude |r_AB| ≈ 21.523 m is correct (within range), earning full credit for that part (15/30 for the unit vector setup shown). However, the student made a critical error: instead of dividing each component individually to find the unit vector components (n ≈ 0.488i + 0.372j - 0.790k), they summed the components first and divided, arriving at a scalar 0.06969 rather than a proper unit vector, and then multiplied by 14000 N to get a single scalar force (975.66 N) rather than the vector components of T — the final part (40 pts) is essentially not correctly completed.</t>
+  </si>
+  <si>
+    <t>The student attempted a 2D approach using a single angle, which is fundamentally incorrect for this 3D problem; no proper position vector r_AB or unit vector was established. The scalar components obtained (T_x ≈ 6.5, T_y ≈ 12.39, T_z = 0) are all incorrect, earning minimal credit only for showing some effort with tension decomposition.</t>
+  </si>
+  <si>
+    <t>Excellent work — coordinates, position vector, magnitude, unit vector, and force components are all correctly computed and match the official solution. Minor deduction for not explicitly writing the unit vector n separately before computing T, but the overall solution is complete and accurate.</t>
+  </si>
+  <si>
+    <t>The student correctly identified points A(5, 12, 20) and B(15.5, 20, 3) and began computing the magnitude using √697, but the solution page is blank with no complete working shown. Partial credit is awarded only for the coordinate identification and initial magnitude setup visible on the question page; no unit vector or force components were computed.</t>
+  </si>
+  <si>
+    <t>The student shows some awareness of the problem dimensions (noting 9+1.5, 20-3, and 17) but the approach is fundamentally flawed—the position vector is not correctly established in 3D (missing the y-component properly, treating it as a 2D problem), and the magnitude calculation is incorrect (using sqrt(20²-10.5²) instead of sqrt(10.5²+8²+17²)). The unit vector and final tension components are not correctly derived, resulting in minimal partial credit only for identifying some correct dimensional differences.</t>
+  </si>
+  <si>
+    <t>The student attempted the problem using a 2D angle-based approach rather than the required 3D position vector method, resulting in incorrect coordinate setup and completely wrong results. No correct position vector r_AB, unit vector, or tensor components were established per the rubric.</t>
+  </si>
+  <si>
+    <t>The student attempted a 2D trigonometric approach using angles (58.3°) rather than the required 3D vector method, failing to establish correct coordinates for points A and B or compute the position vector r_AB. The final answer (11.91k + 7.35i kN) is incorrect and missing the j-component entirely; only minimal partial credit is awarded for recognizing T = 14 kN and attempting some decomposition.</t>
   </si>
 </sst>
 </file>
@@ -4170,7 +4170,7 @@
         <v>112</v>
       </c>
       <c r="H132">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I132" t="s">
         <v>150</v>
@@ -4280,7 +4280,7 @@
         <v>112</v>
       </c>
       <c r="H136">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="I136" t="s">
         <v>152</v>
@@ -4309,7 +4309,7 @@
         <v>112</v>
       </c>
       <c r="H137">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="I137" t="s">
         <v>153</v>
@@ -4393,7 +4393,7 @@
         <v>112</v>
       </c>
       <c r="H140">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I140" t="s">
         <v>155</v>
@@ -4477,7 +4477,7 @@
         <v>112</v>
       </c>
       <c r="H143">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I143" t="s">
         <v>157</v>
@@ -4506,7 +4506,7 @@
         <v>112</v>
       </c>
       <c r="H144">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="I144" t="s">
         <v>158</v>
@@ -4564,7 +4564,7 @@
         <v>112</v>
       </c>
       <c r="H146">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="I146" t="s">
         <v>160</v>
@@ -4593,7 +4593,7 @@
         <v>112</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I147" t="s">
         <v>161</v>
@@ -4648,7 +4648,7 @@
         <v>112</v>
       </c>
       <c r="H149">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="I149" t="s">
         <v>162</v>
@@ -4729,7 +4729,7 @@
         <v>112</v>
       </c>
       <c r="H152">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I152" t="s">
         <v>163</v>
@@ -4758,7 +4758,7 @@
         <v>112</v>
       </c>
       <c r="H153">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I153" t="s">
         <v>164</v>

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="294">
   <si>
     <t>student_id</t>
   </si>
@@ -814,88 +814,88 @@
     <t>Absent from class.</t>
   </si>
   <si>
-    <t>You correctly calculated the individual pressure terms for freshwater (5.886 kPa) and mercury (13.342 kPa), and properly converted units from cm to meters. However, your manometer path equation setup is incorrect — you added the freshwater and mercury terms instead of subtracting one from the other, and you did not properly combine all terms to find the pressure difference (P_fw - P_sw); the seawater term should be subtracted and the final answer should be approximately 3.39 kPa, not 15.168 kPa.</t>
-  </si>
-  <si>
-    <t>You correctly identified the relevant fluid terms and performed the individual pressure calculations with proper unit conversions, but your approach of separately computing absolute pressures from atmospheric reference (P_atm = 100 kPa) rather than tracing a connected manometer path led to an incorrect setup — for example, you added the air column height (70 cm) to the freshwater side instead of treating it as negligible, and the two sides of the manometer are not independent systems. The correct manometer path equation gives P_fw - P_sw = -ρ_w·g·h_w + ρ_Hg·g·h_Hg - ρ_sw·g·h_sw ≈ 3.39 kPa, not 10.26 kPa.</t>
-  </si>
-  <si>
-    <t>You correctly identified the relevant fluid columns and performed some individual pressure calculations, but your manometer path equation was not properly set up — you did not correctly combine the freshwater, mercury, and seawater terms into a single coherent hydrostatic balance, leading to an incorrect final answer of 5886 Pa instead of the correct ~3394 Pa. Additionally, your unit labeling (writing 'kPa' for values that are in Pa) caused further confusion, so be careful to track units throughout your calculations.</t>
-  </si>
-  <si>
-    <t>You correctly identified the relevant densities and used P = ρgh, and your individual calculations for water (588.6 Pa) and mercury (1334.16 Pa) are close to correct. However, your manometer path equation setup is incorrect — you did not properly combine all pressure terms along the fluid path from the freshwater to the seawater pipe, used wrong column heights (e.g., 3 cm and 1 cm instead of 60 cm and 10 cm in several places), and your final answer of 550.8 Pa does not match the correct pressure difference of approximately 3394 Pa (3.39 kPa).</t>
-  </si>
-  <si>
-    <t>You attempted to set up a manometer equation, but your path equation is fundamentally incorrect — you combined the mercury and seawater terms incorrectly and used wrong height values (e.g., h_Hg = 0.4 m instead of 0.1 m, and h_w = 0.6 m used for mercury), leading to a final answer of ~33,309 Pa instead of the correct ~3,394 Pa. You did earn partial credit for converting some heights to meters and attempting hydrostatic pressure calculations with correct density and gravity values, but please revisit how to trace the manometer path step-by-step, carefully assigning the correct height to each fluid column.</t>
-  </si>
-  <si>
-    <t>You correctly set up the manometer path equation, converted units properly, and identified all fluid densities — great work overall! However, you made a small arithmetic error in the mercury column calculation (13600 × 0.1 × 9.81 = 13341.6, not 13341.6 as written but your intermediate value '136' suggests you may have dropped g temporarily), and your seawater term shows '3.53' instead of the correct 4061.34 Pa, leading to a final answer of ~3.44 kPa instead of the correct ~3.39 kPa; these minor calculation errors cost you a few points.</t>
-  </si>
-  <si>
-    <t>You only wrote a partial calculation (1035 * 0.4 = 414 N, likely the seawater pressure term without gravity) and did not set up the manometer path equation, perform unit conversions, or calculate the other pressure terms and the final pressure difference. Please make sure to show your complete work, including the full manometer equation and all intermediate steps, to receive full credit.</t>
-  </si>
-  <si>
-    <t>You correctly set up the manometer path equation with proper unit conversions and correctly identified the air term as negligible — great work on the physics! However, your individual pressure term calculations are slightly rounded (5.9, 13.3, 4.1 kPa instead of 5.886, 13.342, 4.061 kPa), and your final answer of P_sea = P_water - 3.3 kPa is close but slightly off from the correct value of 3.39 kPa, and you are also missing explicit units on your final answer, which costs you points.</t>
-  </si>
-  <si>
-    <t>You correctly identified all fluid densities, converted units to meters, and calculated each individual pressure term accurately (freshwater: 5.886 kPa, seawater: 4.061 kPa, mercury: 13.341 kPa). However, your manometer path equation setup is incorrect — you added the freshwater and mercury pressure terms together instead of subtracting the freshwater and seawater contributions from the mercury term, leading to a final answer of 15.1 kPa rather than the correct ~3.39 kPa; please review the sign convention for traversing up and down through fluid columns in a manometer.</t>
-  </si>
-  <si>
-    <t>You correctly identified the densities and computed individual pressure terms (freshwater: 5886 Pa, seawater: 4061 Pa, mercury: 13341.6 Pa), and your final answer of approximately 3394 Pa is within the accepted range. However, your manometer path equation setup is unclear and disorganized — you did not explicitly write out the full hydrostatic balance equation with correct signs before substituting numbers, which cost you significant points in Parts 1 and 3; make sure to clearly show the signed pressure-path equation from one pipe to the other.</t>
-  </si>
-  <si>
-    <t>You correctly identified the fluid components and attempted to set up a pressure balance, but your manometer path equation is fundamentally incorrect — you added all pressure terms instead of applying the correct signs (+ for going down, − for going up) along the fluid path from freshwater to seawater. Additionally, you forgot to multiply by g (9.81 m/s²) in your pressure calculations, using only ρh instead of ρgh, and you did not convert cm to meters before calculating, which resulted in a vastly incorrect final answer of 237.4 kPa instead of approximately 3.39 kPa.</t>
-  </si>
-  <si>
-    <t>You correctly set up the manometer path equation with proper signs and successfully arrived at the right pressure difference structure. However, you used g = 9.98 m/s² instead of the correct value of 9.81 m/s², which led to a slightly off numerical result (3453.08 Pa instead of ~3394 Pa); please double-check your given constants in future problems. Your unit conversions and overall approach were solid, earning strong partial credit.</t>
-  </si>
-  <si>
-    <t>You correctly identified the relevant fluid terms and arrived at a final answer of approximately 3.39 kPa, which is within the accepted range — great job on the final result! However, your initial equation setup shows some organizational confusion (treating densities as simple multipliers without clearly applying g, and an unclear handling of the air column term), and your intermediate steps contain inconsistencies that cost you points in Parts 1 and 2; make sure to clearly write out each term as rho * g * h with proper unit conversions from the start.</t>
-  </si>
-  <si>
-    <t>You correctly identified the individual pressure terms (5886 Pa, 13341.6 Pa, 4061.34 Pa) and nearly reached the correct final answer of 3394.26 Pa, showing strong understanding of the hydrostatic path. However, you made a critical sign error in your manometer equation setup — the air and seawater terms have incorrect signs, and you did not properly account for the negligible air density, leaving 'P_air' as an unknown rather than setting it to zero, which cost you significant points in Parts 1 and 3.</t>
-  </si>
-  <si>
-    <t>You correctly calculated all three individual pressure terms (seawater, freshwater, and mercury) and earned full credit for Part 2. However, your manometer path equation is incorrectly set up — you added the freshwater and mercury terms together and subtracted seawater, which does not reflect the correct hydrostatic pressure balance along the fluid path; the correct relationship gives P_fw - P_sw = -5886 + 13341.6 - 4061.34 = 3394.26 Pa ≈ 3.39 kPa, not 15166.2 Pa, and your final answer is also missing proper units and a clear pressure difference conclusion.</t>
-  </si>
-  <si>
-    <t>You correctly set up the manometer path equation with proper unit conversions and signs, and your numerical result of 3394.26 Pa is exactly correct. However, you lost points for not explicitly showing the individual pressure term calculations and for presenting the final answer as 'P_Fresh - 3394.26P = P_salt' rather than clearly stating P_fw - P_sw = 3394.26 Pa (or ~3.39 kPa) with proper units — make sure to write units clearly (Pa or kPa) in your final answer.</t>
-  </si>
-  <si>
-    <t>You attempted to set up the manometer equation, but your approach contains significant conceptual errors: air density should be treated as negligible (rho_air ≈ 0), not solved for as an unknown, and you used g ≈ 10 m/s² instead of 9.81 m/s², and did not properly account for the seawater column term. Your unit conversions from cm to meters were partially correct, but the overall pressure balance equation and final answer (974.28) are incorrect — the correct answer is approximately 3394 Pa (3.39 kPa).</t>
-  </si>
-  <si>
-    <t>You correctly identified the individual pressure terms (freshwater and mercury) and calculated their values with proper unit conversions, earning partial credit. However, your manometer path equation is incorrectly set up — you wrote P_sw = P_fw + P_m + P_air instead of properly balancing the hydrostatic path with correct signs, and you did not include the seawater column term or arrive at a final pressure difference (P_fw - P_sw); the simplified formula at the bottom is also not applied to reach a numerical answer.</t>
-  </si>
-  <si>
-    <t>You correctly set up the manometer path equation with proper unit conversions and correct signs for the freshwater, mercury, and seawater terms — well done on the equation structure (full Part 1 credit). However, your final numerical answer of 2.9 kPa is incorrect; the correct result is approximately 3.39 kPa, suggesting an arithmetic error in combining the pressure terms. Additionally, your final answer is missing explicit units written alongside a clear numerical computation showing each individual pressure term, which cost you points in Parts 2 and 3.</t>
-  </si>
-  <si>
-    <t>You correctly identified all densities, converted units properly, and arrived at the correct final answer of 3394.26 Pa — great work! However, your manometer path equation setup was not clearly written (the intermediate algebra with variable 'x' is confusing and lacks explicit sign justification), so partial deductions apply for equation presentation in Parts 1 and 2.</t>
-  </si>
-  <si>
-    <t>You showed an attempt to set up the manometer path equation, but your equation setup has significant issues: you included an atmospheric pressure term ('1 atm') incorrectly as a fluid density term, did not properly apply g = 9.81 m/s² (using values like .40, .70, .10, .60 as if they are already pressures rather than heights requiring multiplication by rho and g), and the final answer of 7365 kg/m² uses incorrect units and is far from the correct value of ~3394 Pa. You earned partial credit for identifying the relevant fluid densities (1035, 13600, 1000 kg/m³) and the correct column heights, but please review how to correctly write and evaluate the hydrostatic pressure equation P = ρgh with proper SI units.</t>
-  </si>
-  <si>
-    <t>You correctly identified all fluid densities and converted the heights, and you showed a diagram which is a good start. However, your manometer path equation setup has a critical sign error — you added the mercury and seawater pressure terms together instead of subtracting the freshwater term properly, leading to an incorrect final answer of ~11,516 Pa instead of the correct ~3,394 Pa. Additionally, the units in your intermediate steps appear to be in 'g' (density × height without gravity), which suggests gravity was applied only at the very end — be careful to keep track of units throughout, and make sure to correctly apply the signs (+ and −) to each column based on whether you are moving up or down in the fluid path.</t>
-  </si>
-  <si>
-    <t>You correctly identified all densities, converted units properly, and computed each pressure term accurately (5886 Pa, 13341.6 Pa, 4061.34 Pa). However, your final answer of -3394.26 Pa has an inverted sign — since the problem asks for P_fw - P_sw, the correct result is +3394.26 Pa (≈ +3.39 kPa), so 5 points are deducted for the sign error, and an additional 5 points are deducted because the units on the final answer were not clearly stated.</t>
-  </si>
-  <si>
-    <t>You correctly calculated all three individual pressure terms (freshwater, mercury, and seawater) and your intermediate arithmetic is accurate, earning strong marks for Parts 1 and 2. However, your final answer of 9278 Pa is incorrect — you added the freshwater term (5886) to the magnitude of P_fw - P_sw (3394.26), which is not the correct final step; the pressure difference P_fw - P_sw = 3394.26 Pa ≈ 3.39 kPa was already correctly found in your intermediate work, and that should have been your final answer.</t>
-  </si>
-  <si>
-    <t>You showed a reasonable attempt at setting up the manometer equation and correctly identified the relevant fluid terms, earning partial credit for your setup. However, your approach fundamentally went off track — instead of solving for the pressure difference (P_fw - P_sw), you attempted to solve for air density (ρ_air), which is not what the problem asks; gravity (g = 9.81 m/s²) was also omitted from your pressure calculations, and your final answer of 308.144 kg/m³ has incorrect units and does not represent a pressure difference.</t>
-  </si>
-  <si>
-    <t>You correctly calculated the individual pressure terms (freshwater, mercury, seawater) and earned full credit for Part 2, but your manometer path equation setup is incorrect — you added the seawater and mercury terms together without properly accounting for the signs of each fluid column, leading to a final answer of 11.52 kPa instead of the correct ~3.39 kPa. Additionally, the units appear to be mPa (millipascals?) which is unclear; be sure to clearly state your units as Pa or kPa, and double-check your manometer traversal signs (going up decreases pressure, going down increases it) to correctly set up P_fw - P_sw.</t>
-  </si>
-  <si>
-    <t>You correctly identified and computed the individual pressure terms (freshwater: 600g, seawater: 414g, mercury: 0.1×13600×g = 1360g) and showed the correct unit conversions from cm to meters. However, your manometer path equation setup has significant sign errors — you added the seawater term instead of subtracting it, and your final expression was not fully evaluated to a numerical answer with proper units, so you could not receive credit for Part 3. Make sure to carefully trace the pressure path direction (going down adds pressure, going up subtracts it) and always finalize your answer with correct numerical value and units.</t>
-  </si>
-  <si>
-    <t>You correctly calculated all three individual pressure terms (freshwater: 5886 Pa, mercury: 13341.6 Pa, seawater: 4061.34 Pa) and converted units properly — great work on those parts! However, your manometer path equation setup is incorrect: you added all terms together instead of applying the correct signs (P_fw - P_sw = -5886 + 13341.6 - 4061.34 = 3394.26 Pa ≈ 3.39 kPa), and your final answer of 15.166 kPa does not reflect the correct pressure difference between the two pipelines.</t>
+    <t>You correctly calculated the individual terms (freshwater: 5.886 kPa, mercury: 13.342 kPa, seawater: 4.061 kPa), earning significant partial credit for your arithmetic. However, your manometer path equation is fundamentally incorrect: you added all terms on the left side and set them equal to a mysterious 'P_air' quantity, rather than properly computing P_fw - P_sw by subtracting the freshwater and seawater terms and adding the mercury term. The correct result is P_fw - P_sw = -5.886 + 13.342 - 4.061 ≈ 3.39 kPa; your final answer of 15.168 kPa is not within the acceptable range and reflects an incorrect sign convention and equation setup throughout.</t>
+  </si>
+  <si>
+    <t>You demonstrated some understanding of the hydrostatic pressure formula P = P_atm + ρgh, and your individual density and height values are mostly correct. However, your approach is fundamentally flawed: instead of writing a single connected manometer path equation from P1 to P2, you calculated absolute pressures for each side separately using P_atm as a base, which is not the correct method for a double U-tube manometer problem. This led to an incorrect final answer of 10.26 (in unclear units) instead of the correct ~3.39 kPa. Additionally, your units are missing throughout, and the path equation setup does not properly account for the manometer fluid connections. Partial credit of 25/100 is awarded for recognizing the relevant fluid columns and densities.</t>
+  </si>
+  <si>
+    <t>You demonstrated a correct diagram and showed understanding of the individual fluid terms, but your manometer path equation is incomplete and incorrectly set up — you did not properly link all fluid columns through a single continuous hydrostatic path from P_fw to P_sw. Your intermediate calculations for the seawater term (4057.2 Pa) and freshwater term (11512.8 Pa) are computed in isolation rather than combined correctly, and your final answer of 5886 Pa does not match the correct result of approximately 3394 Pa. You receive partial credit (25/100) for correctly identifying the relevant fluid densities, drawing a reasonable diagram, and computing some individual pressure terms.</t>
+  </si>
+  <si>
+    <t>You demonstrated some correct understanding by identifying the relevant fluids and their densities, and you correctly applied P = ρgh for individual terms. However, your manometer path equation is incorrectly set up — you did not properly trace the hydrostatic path from the freshwater pipeline to the seawater pipeline, leading to an incorrect final answer (550.8 Pa instead of ~3394 Pa). You used incorrect column heights (e.g., 0.03 m for seawater instead of 0.4 m, and 0.01 m for mercury instead of 0.1 m), and the overall pressure difference equation was not properly formulated. Partial credit of 25/100 is awarded for recognizing the basic principle and attempting calculations.</t>
+  </si>
+  <si>
+    <t>You demonstrated some understanding of the problem by identifying the relevant fluid densities and attempting pressure terms, but your manometer path equation is fundamentally incorrect — you set up a gage pressure approach rather than tracing the correct hydrostatic path from P_fw to P_sw, and your height assignments are wrong (e.g., using 0.4 m and 0.6 m for mercury and freshwater terms respectively in an incorrect combination). The correct path gives P_fw - P_sw = -(1000×9.81×0.6) + (13600×9.81×0.1) - (1035×9.81×0.4) ≈ 3394 Pa; your final answer of ~33,309 Pa is far from the correct value. Partial credit of 25/100 is awarded for recognizing relevant fluid properties and attempting calculations.</t>
+  </si>
+  <si>
+    <t>You demonstrated a strong understanding of the manometer path equation and correctly identified all densities and height conversions. Your individual terms (5886, 13341.6, 4061.34 Pa) are correct, and your final answer of ~3.44 kPa is within the acceptable range; however, your final answer is written as '3.44 Pa' instead of '3.44 kPa', so 5 points are deducted for the incorrect unit label on the final result. Great work overall!</t>
+  </si>
+  <si>
+    <t>You only wrote a partial calculation (1035 × 0.4 = 414 N, seemingly the seawater term) without setting up the manometer path equation, performing the other required calculations, or reaching a final answer. This earns minimal partial credit; please make sure to show the complete hydrostatic path equation and all substitution steps in future quizzes.</t>
+  </si>
+  <si>
+    <t>You demonstrated a good understanding of the manometer path setup and correctly identified all fluid terms including the freshwater, mercury, and seawater terms with proper unit conversions. However, your final answer of P_sea = P_water - (3.3) has a sign issue (it should be P_fw - P_sw = +3.39 kPa, not -3.3), costing 5 pts, and your intermediate term calculations show slight rounding (5.9 instead of 5.886, 13.3 instead of 13.342, 4.1 instead of 4.061), costing 5 pts for arithmetic inaccuracy. Additionally, your final answer is missing clear units (Pa or kPa), costing 5 pts, and the partially illegible air/middle term in your equation makes it unclear if that term was properly handled, costing 13 pts.</t>
+  </si>
+  <si>
+    <t>You correctly identified all densities, converted units properly, and calculated each individual pressure term accurately (freshwater: 5.886 kPa, mercury: 13.341 kPa, seawater: 4.061 kPa). However, your manometer path equation is incorrect — instead of applying the proper hydrostatic path (P_fw - P_sw = -ρ_w·g·h_w + ρ_Hg·g·h_Hg - ρ_sw·g·h_sw = 3.39 kPa), you added the freshwater and mercury terms together and then subtracted seawater, yielding 15.1 kPa, which does not reflect the correct pressure balance along the manometer path. This incorrect setup results in a 40-point deduction for Part 1 (manometer equation) and a 5-point deduction for the incorrect final answer in Part 3.</t>
+  </si>
+  <si>
+    <t>You correctly identified all fluid densities and computed the individual pressure terms (freshwater: 5886 Pa, seawater/mercury: 13341 Pa, seawater column: 4061 Pa), showing solid understanding of hydrostatic pressure — great effort! However, your final manometer path equation setup is incomplete and unclear (the signs and combination of terms are not properly organized as P_fw - P_sw = -ρ_w·g·h_w + ρ_Hg·g·h_Hg - ρ_sw·g·h_sw), leading to an incorrect final answer of approximately 2455 Pa instead of the correct ~3394 Pa; deducting 20 pts for the incorrect path/equation setup and 18 pts for the resulting incorrect final answer.</t>
+  </si>
+  <si>
+    <t>You correctly identified the relevant fluid columns and computed individual pressure terms (though you dropped g, using ρh instead of ρgh, which is a significant error). More critically, your manometer path equation is fundamentally incorrect: you added all pressure terms together instead of applying the proper hydrostatic path with alternating signs (P_fw + ρ_w·g·h_w − ρ_Hg·g·h_Hg + ρ_sw·g·h_sw = P_sw), leading to a completely wrong final answer of 237.4 kPa instead of approximately 3.39 kPa. Partial credit is awarded for identifying the correct fluid columns and attempting a structured approach.</t>
+  </si>
+  <si>
+    <t>You demonstrate a solid understanding of the manometer path equation and correctly identify all relevant terms. Your final answer of 3453.08 Pa is very close to the accepted range (3350–3450 Pa) — the small discrepancy arises from using g = 9.98 m/s² instead of the standard 9.81 m/s², which accounts for a minor arithmetic deviation (-5 pts), and your intermediate grouping approach (splitting into two sub-equations) is creative but led to a slight numerical drift (-8 pts). Overall, great work setting up the physics correctly and showing your calculations clearly!</t>
+  </si>
+  <si>
+    <t>You demonstrated a solid understanding of the manometer path and correctly identified all relevant fluid terms, arriving at a final answer of approximately 3.39 kPa which is within the acceptable range. However, your intermediate work shows some confusion with units (mixing density values as if they were pressures, e.g., treating 1035·0.40 = 41400 without multiplying by g properly in early steps), which warrants a 10 pt deduction for the setup/substitution section, and your final answer label 'P_sa' is ambiguous rather than clearly stating P_fw - P_sw, resulting in a 5 pt deduction for presentation. Keep up the good work and be careful with unit consistency throughout your calculations!</t>
+  </si>
+  <si>
+    <t>You demonstrated a good understanding of the manometer diagram and correctly identified the individual pressure terms (freshwater: 5886 Pa, mercury: 13341.6 Pa, seawater: 4061.34 Pa), which is excellent. However, your equation setup is incorrect — you treated air density as non-negligible and attempted to solve for P_air rather than recognizing it is negligible, and your path equation sign conventions are wrong (the mercury term should be positive in P_fw - P_sw, not negative as set up). Your final answer of -3394.26 - P_air does not yield the correct numerical result of approximately +3394.26 Pa; I'm deducting 30 pts for the incorrect equation setup and path sign errors, and 15 pts for the incorrect final answer due to the unresolved P_air term and missing clear units on the final result.</t>
+  </si>
+  <si>
+    <t>You correctly calculated all three individual pressure terms (seawater: 4061.34 Pa, freshwater: 5886 Pa, mercury: 13341.6 Pa), earning strong partial credit for Part 2. However, your manometer path equation setup in Part 1 is not clearly established with proper sign conventions and physical reasoning (showing which side gains/loses pressure along the path), costing you most of Part 1's points. Your final combination (13341.6 + 5886 - 4061.34 = 15166.2) uses incorrect signs — the freshwater term should be subtracted, not added — leading to a wrong final answer of ~15166 Pa instead of the correct ~3394 Pa, and no clear final units or ΔP statement was provided, resulting in deductions across Parts 1 and 3.</t>
+  </si>
+  <si>
+    <t>You correctly set up the manometer path equation with the right terms and densities, and your numerical calculation of 3394.26 Pa is spot-on. However, you expressed the final result as 'P_Fresh - 3394.26p = P_salt' rather than the clean pressure difference 'P_fw - P_sw = 3394.26 Pa', and units are written ambiguously ('p' instead of 'Pa'), so 5 pts are deducted for the unclear final answer presentation and 10 pts for not explicitly isolating and stating the pressure difference with proper units.</t>
+  </si>
+  <si>
+    <t>You showed some effort in setting up a manometer path equation and attempted to include multiple fluid terms, which earns partial credit. However, your approach has significant errors: you incorrectly solved for an air density (treating air as having a meaningful density equal to that of water divided by height ratio, yielding 714.28 kg/m³), the manometer path equation is not correctly structured (signs and terms are not properly assigned for freshwater, mercury, and seawater), and your final answer of 974.28 does not match the correct pressure difference of approximately 3394 Pa. The correct path is P_fw - P_sw = -(ρ_w·g·h_w) + (ρ_Hg·g·h_Hg) - (ρ_sw·g·h_sw) ≈ 3394 Pa; keep practicing the hydrostatic path method!</t>
+  </si>
+  <si>
+    <t>You correctly identified that the air term is negligible and computed the freshwater term (5.886 kPa) and mercury term (13.3416 kPa) correctly, which earns partial credit. However, your manometer path equation is incomplete and incorrect — you did not properly account for the seawater column with the correct signs, you did not arrive at a correct final pressure difference (P_fw - P_sw ≈ 3.39 kPa), and the expression P1 - P2 = (ρ2 - ρ1)·h·g at the bottom is an incorrect formula for this multi-fluid manometer. A full hydrostatic path traversal from P_fw to P_sw accounting for all fluid columns with proper signs was required to earn full credit.</t>
+  </si>
+  <si>
+    <t>You correctly set up the manometer path equation with the right terms and signs, earning strong partial credit for Part 1 (30/40). However, your final answer of 2.9 kPa is significantly off from the correct value of ~3.39 kPa — you appear to have skipped showing the intermediate arithmetic steps, making it impossible to identify where the calculation went wrong (Part 2: 10/40, Part 3: 10/20). Always show your full substitution and computation to receive full credit.</t>
+  </si>
+  <si>
+    <t>Excellent work! You correctly identified all relevant densities, set up the manometer path equation properly, computed each pressure term accurately (freshwater: 5886 Pa, mercury: 13341.6 Pa, seawater: 4061.34 Pa), and arrived at the correct final answer of ΔP = 3394.26 Pa with proper units. Well done!</t>
+  </si>
+  <si>
+    <t>You demonstrated a basic understanding of the ρgh pressure concept and attempted to include the relevant fluid columns, which is a good start. However, your manometer path equation is incorrectly set up — you used 'atm' as a density placeholder and g=10 (approximation) instead of the correct densities (ρ_w=1000, ρ_Hg=13600, ρ_sw=1035 kg/m³) with g=9.81 m/s², the signs in your path equation are inconsistent with a proper hydrostatic traversal, and your final answer of 7365 kg/m² uses incorrect units and is far outside the acceptable range of 3350–3450 Pa; these errors result in significant deductions across all three parts.</t>
+  </si>
+  <si>
+    <t>You correctly identified all three fluid densities and set up the individual pressure terms (freshwater: 600g, mercury: 1360g, seawater: 414g), which shows a good fundamental understanding of the problem. However, your manometer path equation is incorrect — you added the mercury and seawater terms together and then subtracted the freshwater term, rather than correctly applying the hydrostatic path as P_fw - P_sw = -(rho_w·g·h_w) + (rho_Hg·g·h_Hg) - (rho_sw·g·h_sw), leading to a final answer of ~11,516 Pa instead of the correct ~3,394 Pa; this error in the path setup costs significant points across Parts 1, 2, and 3.</t>
+  </si>
+  <si>
+    <t>You demonstrated excellent understanding of the manometer path equation and correctly identified all fluid terms and their values, arriving at the correct magnitude of 3394.26 Pa. However, your final answer is presented as a negative value (-3394.26 Pa), which indicates an inverted sign — deducting 5 pts. Also, the units appear slightly unclear in the final answer — deducting 5 pts. Overall, great work on the methodology and calculations!</t>
+  </si>
+  <si>
+    <t>You demonstrated correct calculation of the individual pressure terms (freshwater: 5886 Pa, mercury: 13341.6 Pa, seawater: 4061.34 Pa) and your methodology shows understanding of the hydrostatic path. However, you made a critical error in the mercury height: you used 0.6 m instead of 0.1 m (h_Hg = 10 cm = 0.1 m), which led to an incorrect intermediate result of -7455.6 Pa instead of the correct +1569.6 Pa. Additionally, your final answer of 9278 Pa is incorrect due to this propagated error; the correct answer is approximately 3394 Pa. You lose 40 pts for the incorrect mercury height substitution and resulting calculation errors, and 5 pts for the incorrect final answer.</t>
+  </si>
+  <si>
+    <t>You demonstrated some understanding of the manometer path by including the correct fluid terms, but unfortunately your approach went in the wrong direction — instead of solving for the pressure difference (P_fw - P_sw), you attempted to solve for the density of air, which is not what the problem asks. Your initial equation setup has the right components but incorrect sign conventions and rearrangement, leading to a fundamentally different problem being solved. The final answer of 308.144 kg/m³ is not a pressure difference and does not match the expected result of ~3.39 kPa; partial credit of 20/100 is awarded for recognizing the relevant fluid columns and including them in an equation.</t>
+  </si>
+  <si>
+    <t>You correctly calculated the individual pressure terms (freshwater, mercury, seawater) and showed your work, earning partial credit. However, your manometer path equation is fundamentally incorrect — you added the seawater and mercury terms together instead of setting up the proper hydrostatic path from one pipeline to the other (P_fw + ρ_w·g·h_w - ρ_Hg·g·h_Hg + ρ_sw·g·h_sw = P_sw), which led to a final answer of 11.52 mPa that is far from the correct value of ~3.39 kPa. The equation setup accounts for 40 pts, the substitution for 40 pts, and the final answer for 20 pts; since only the individual term calculations were partially correct, 25/100 is awarded.</t>
+  </si>
+  <si>
+    <t>You show some correct individual density/height term calculations (e.g., rho_w*g*h_w = 600g, rho_sw*g*h_sw = 414g, mercury term = 0.1*13600*g = 1360g), earning partial credit for Part 1 and Part 2 setup. However, your manometer path equation is incorrectly assembled — the air column term (0.7*d_air*g) appears in the equation instead of being dropped (air density is negligible and that column height is not needed), and the seawater column height used (0.3 m) is incorrect (should be 0.4 m); additionally, no final numerical answer in Pa or kPa is computed, so you lose the majority of points for Parts 2 and 3.</t>
+  </si>
+  <si>
+    <t>You correctly identified the three fluid terms (freshwater: 5886 Pa, mercury: 13341.6 Pa, seawater: 4061.34 Pa) and computed each one accurately, earning solid partial credit. However, your manometer path equation is incorrectly set up: you added the freshwater and mercury terms together instead of combining them with the correct signs to find P_fw - P_sw; the correct result is P_fw - P_sw = -5886 + 13341.6 - 4061.34 ≈ 3394 Pa (≈ 3.39 kPa), not 15.166 kPa. This fundamental sign/path error in Part 1 (−15 pts) carries through to an incorrect final answer in Part 3 (−20 pts), and the substitution structure in Part 2 is also affected (−40 pts reduced to a partial award of 25 pts total for correctly computing the individual terms).</t>
   </si>
 </sst>
 </file>
@@ -5233,8 +5233,8 @@
       </c>
     </row>
     <row r="157" spans="1:9">
-      <c r="A157">
-        <v>2003675</v>
+      <c r="A157" t="s">
+        <v>44</v>
       </c>
       <c r="B157" t="s">
         <v>141</v>
@@ -5259,8 +5259,8 @@
       </c>
     </row>
     <row r="158" spans="1:9">
-      <c r="A158">
-        <v>2003743</v>
+      <c r="A158" t="s">
+        <v>45</v>
       </c>
       <c r="B158" t="s">
         <v>142</v>
@@ -5285,8 +5285,8 @@
       </c>
     </row>
     <row r="159" spans="1:9">
-      <c r="A159">
-        <v>2101812</v>
+      <c r="A159" t="s">
+        <v>46</v>
       </c>
       <c r="B159" t="s">
         <v>143</v>
@@ -5311,8 +5311,8 @@
       </c>
     </row>
     <row r="160" spans="1:9">
-      <c r="A160">
-        <v>2102438</v>
+      <c r="A160" t="s">
+        <v>47</v>
       </c>
       <c r="B160" t="s">
         <v>144</v>
@@ -5333,15 +5333,15 @@
         <v>210</v>
       </c>
       <c r="H160">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I160" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="161" spans="1:9">
-      <c r="A161">
-        <v>2104775</v>
+      <c r="A161" t="s">
+        <v>48</v>
       </c>
       <c r="B161" t="s">
         <v>145</v>
@@ -5362,15 +5362,15 @@
         <v>210</v>
       </c>
       <c r="H161">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I161" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="162" spans="1:9">
-      <c r="A162">
-        <v>2200784</v>
+      <c r="A162" t="s">
+        <v>49</v>
       </c>
       <c r="B162" t="s">
         <v>146</v>
@@ -5395,8 +5395,8 @@
       </c>
     </row>
     <row r="163" spans="1:9">
-      <c r="A163">
-        <v>2202739</v>
+      <c r="A163" t="s">
+        <v>50</v>
       </c>
       <c r="B163" t="s">
         <v>147</v>
@@ -5417,15 +5417,15 @@
         <v>210</v>
       </c>
       <c r="H163">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I163" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="164" spans="1:9">
-      <c r="A164">
-        <v>2202877</v>
+      <c r="A164" t="s">
+        <v>51</v>
       </c>
       <c r="B164" t="s">
         <v>148</v>
@@ -5450,8 +5450,8 @@
       </c>
     </row>
     <row r="165" spans="1:9">
-      <c r="A165">
-        <v>2364766</v>
+      <c r="A165" t="s">
+        <v>52</v>
       </c>
       <c r="B165" t="s">
         <v>149</v>
@@ -5472,15 +5472,15 @@
         <v>210</v>
       </c>
       <c r="H165">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I165" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="166" spans="1:9">
-      <c r="A166">
-        <v>2366349</v>
+      <c r="A166" t="s">
+        <v>53</v>
       </c>
       <c r="B166" t="s">
         <v>150</v>
@@ -5501,15 +5501,15 @@
         <v>210</v>
       </c>
       <c r="H166">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I166" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="167" spans="1:9">
-      <c r="A167">
-        <v>2366648</v>
+      <c r="A167" t="s">
+        <v>54</v>
       </c>
       <c r="B167" t="s">
         <v>151</v>
@@ -5530,15 +5530,15 @@
         <v>210</v>
       </c>
       <c r="H167">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I167" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="168" spans="1:9">
-      <c r="A168">
-        <v>2366734</v>
+      <c r="A168" t="s">
+        <v>55</v>
       </c>
       <c r="B168" t="s">
         <v>152</v>
@@ -5563,8 +5563,8 @@
       </c>
     </row>
     <row r="169" spans="1:9">
-      <c r="A169">
-        <v>2366906</v>
+      <c r="A169" t="s">
+        <v>56</v>
       </c>
       <c r="B169" t="s">
         <v>153</v>
@@ -5592,8 +5592,8 @@
       </c>
     </row>
     <row r="170" spans="1:9">
-      <c r="A170">
-        <v>2366917</v>
+      <c r="A170" t="s">
+        <v>57</v>
       </c>
       <c r="B170" t="s">
         <v>154</v>
@@ -5618,8 +5618,8 @@
       </c>
     </row>
     <row r="171" spans="1:9">
-      <c r="A171">
-        <v>2367037</v>
+      <c r="A171" t="s">
+        <v>58</v>
       </c>
       <c r="B171" t="s">
         <v>155</v>
@@ -5647,8 +5647,8 @@
       </c>
     </row>
     <row r="172" spans="1:9">
-      <c r="A172">
-        <v>2368580</v>
+      <c r="A172" t="s">
+        <v>59</v>
       </c>
       <c r="B172" t="s">
         <v>156</v>
@@ -5669,15 +5669,15 @@
         <v>210</v>
       </c>
       <c r="H172">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I172" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="173" spans="1:9">
-      <c r="A173">
-        <v>2472843</v>
+      <c r="A173" t="s">
+        <v>60</v>
       </c>
       <c r="B173" t="s">
         <v>157</v>
@@ -5698,15 +5698,15 @@
         <v>210</v>
       </c>
       <c r="H173">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="I173" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="174" spans="1:9">
-      <c r="A174">
-        <v>2476099</v>
+      <c r="A174" t="s">
+        <v>61</v>
       </c>
       <c r="B174" t="s">
         <v>158</v>
@@ -5727,15 +5727,15 @@
         <v>210</v>
       </c>
       <c r="H174">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I174" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="175" spans="1:9">
-      <c r="A175">
-        <v>2477970</v>
+      <c r="A175" t="s">
+        <v>62</v>
       </c>
       <c r="B175" t="s">
         <v>159</v>
@@ -5756,15 +5756,15 @@
         <v>210</v>
       </c>
       <c r="H175">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I175" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="176" spans="1:9">
-      <c r="A176">
-        <v>2482073</v>
+      <c r="A176" t="s">
+        <v>63</v>
       </c>
       <c r="B176" t="s">
         <v>160</v>
@@ -5785,15 +5785,15 @@
         <v>210</v>
       </c>
       <c r="H176">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="I176" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="177" spans="1:9">
-      <c r="A177">
-        <v>2482445</v>
+      <c r="A177" t="s">
+        <v>64</v>
       </c>
       <c r="B177" t="s">
         <v>161</v>
@@ -5814,15 +5814,15 @@
         <v>210</v>
       </c>
       <c r="H177">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I177" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="178" spans="1:9">
-      <c r="A178">
-        <v>2483328</v>
+      <c r="A178" t="s">
+        <v>65</v>
       </c>
       <c r="B178" t="s">
         <v>162</v>
@@ -5843,15 +5843,15 @@
         <v>210</v>
       </c>
       <c r="H178">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="I178" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="179" spans="1:9">
-      <c r="A179">
-        <v>2483434</v>
+      <c r="A179" t="s">
+        <v>66</v>
       </c>
       <c r="B179" t="s">
         <v>163</v>
@@ -5872,15 +5872,15 @@
         <v>210</v>
       </c>
       <c r="H179">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I179" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="180" spans="1:9">
-      <c r="A180">
-        <v>2483834</v>
+      <c r="A180" t="s">
+        <v>67</v>
       </c>
       <c r="B180" t="s">
         <v>164</v>
@@ -5901,15 +5901,15 @@
         <v>210</v>
       </c>
       <c r="H180">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I180" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="181" spans="1:9">
-      <c r="A181">
-        <v>2483956</v>
+      <c r="A181" t="s">
+        <v>68</v>
       </c>
       <c r="B181" t="s">
         <v>165</v>
@@ -5930,15 +5930,15 @@
         <v>210</v>
       </c>
       <c r="H181">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I181" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="182" spans="1:9">
-      <c r="A182">
-        <v>2483960</v>
+      <c r="A182" t="s">
+        <v>69</v>
       </c>
       <c r="B182" t="s">
         <v>166</v>
@@ -5959,15 +5959,15 @@
         <v>210</v>
       </c>
       <c r="H182">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I182" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="183" spans="1:9">
-      <c r="A183">
-        <v>2484028</v>
+      <c r="A183" t="s">
+        <v>70</v>
       </c>
       <c r="B183" t="s">
         <v>167</v>
@@ -5988,15 +5988,15 @@
         <v>210</v>
       </c>
       <c r="H183">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="I183" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="184" spans="1:9">
-      <c r="A184">
-        <v>2484186</v>
+      <c r="A184" t="s">
+        <v>71</v>
       </c>
       <c r="B184" t="s">
         <v>168</v>
@@ -6021,8 +6021,8 @@
       </c>
     </row>
     <row r="185" spans="1:9">
-      <c r="A185">
-        <v>2484262</v>
+      <c r="A185" t="s">
+        <v>72</v>
       </c>
       <c r="B185" t="s">
         <v>169</v>
@@ -6047,8 +6047,8 @@
       </c>
     </row>
     <row r="186" spans="1:9">
-      <c r="A186">
-        <v>2484542</v>
+      <c r="A186" t="s">
+        <v>73</v>
       </c>
       <c r="B186" t="s">
         <v>170</v>
@@ -6069,15 +6069,15 @@
         <v>210</v>
       </c>
       <c r="H186">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I186" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="187" spans="1:9">
-      <c r="A187">
-        <v>2500744</v>
+      <c r="A187" t="s">
+        <v>74</v>
       </c>
       <c r="B187" t="s">
         <v>171</v>
@@ -6098,15 +6098,15 @@
         <v>210</v>
       </c>
       <c r="H187">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I187" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="188" spans="1:9">
-      <c r="A188">
-        <v>2501122</v>
+      <c r="A188" t="s">
+        <v>75</v>
       </c>
       <c r="B188" t="s">
         <v>172</v>
@@ -6127,15 +6127,15 @@
         <v>210</v>
       </c>
       <c r="H188">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="I188" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="189" spans="1:9">
-      <c r="A189">
-        <v>2593530</v>
+      <c r="A189" t="s">
+        <v>76</v>
       </c>
       <c r="B189" t="s">
         <v>173</v>
@@ -6156,15 +6156,15 @@
         <v>210</v>
       </c>
       <c r="H189">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="I189" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="190" spans="1:9">
-      <c r="A190">
-        <v>2596196</v>
+      <c r="A190" t="s">
+        <v>77</v>
       </c>
       <c r="B190" t="s">
         <v>174</v>
@@ -6189,8 +6189,8 @@
       </c>
     </row>
     <row r="191" spans="1:9">
-      <c r="A191">
-        <v>2599154</v>
+      <c r="A191" t="s">
+        <v>78</v>
       </c>
       <c r="B191" t="s">
         <v>175</v>
@@ -6215,8 +6215,8 @@
       </c>
     </row>
     <row r="192" spans="1:9">
-      <c r="A192">
-        <v>2599631</v>
+      <c r="A192" t="s">
+        <v>79</v>
       </c>
       <c r="B192" t="s">
         <v>176</v>
@@ -6237,15 +6237,15 @@
         <v>210</v>
       </c>
       <c r="H192">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I192" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="193" spans="1:9">
-      <c r="A193">
-        <v>2599634</v>
+      <c r="A193" t="s">
+        <v>80</v>
       </c>
       <c r="B193" t="s">
         <v>177</v>
@@ -6266,15 +6266,15 @@
         <v>210</v>
       </c>
       <c r="H193">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I193" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="194" spans="1:9">
-      <c r="A194">
-        <v>2599868</v>
+      <c r="A194" t="s">
+        <v>81</v>
       </c>
       <c r="B194" t="s">
         <v>178</v>
@@ -6295,15 +6295,15 @@
         <v>210</v>
       </c>
       <c r="H194">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="I194" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="195" spans="1:9">
-      <c r="A195">
-        <v>2616909</v>
+      <c r="A195" t="s">
+        <v>82</v>
       </c>
       <c r="B195" t="s">
         <v>179</v>
@@ -6324,7 +6324,7 @@
         <v>210</v>
       </c>
       <c r="H195">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I195" t="s">
         <v>293</v>

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -814,88 +814,88 @@
     <t>Absent from class.</t>
   </si>
   <si>
-    <t>You correctly calculated the individual terms (freshwater: 5.886 kPa, mercury: 13.342 kPa, seawater: 4.061 kPa), earning significant partial credit for your arithmetic. However, your manometer path equation is fundamentally incorrect: you added all terms on the left side and set them equal to a mysterious 'P_air' quantity, rather than properly computing P_fw - P_sw by subtracting the freshwater and seawater terms and adding the mercury term. The correct result is P_fw - P_sw = -5.886 + 13.342 - 4.061 ≈ 3.39 kPa; your final answer of 15.168 kPa is not within the acceptable range and reflects an incorrect sign convention and equation setup throughout.</t>
-  </si>
-  <si>
-    <t>You demonstrated some understanding of the hydrostatic pressure formula P = P_atm + ρgh, and your individual density and height values are mostly correct. However, your approach is fundamentally flawed: instead of writing a single connected manometer path equation from P1 to P2, you calculated absolute pressures for each side separately using P_atm as a base, which is not the correct method for a double U-tube manometer problem. This led to an incorrect final answer of 10.26 (in unclear units) instead of the correct ~3.39 kPa. Additionally, your units are missing throughout, and the path equation setup does not properly account for the manometer fluid connections. Partial credit of 25/100 is awarded for recognizing the relevant fluid columns and densities.</t>
-  </si>
-  <si>
-    <t>You demonstrated a correct diagram and showed understanding of the individual fluid terms, but your manometer path equation is incomplete and incorrectly set up — you did not properly link all fluid columns through a single continuous hydrostatic path from P_fw to P_sw. Your intermediate calculations for the seawater term (4057.2 Pa) and freshwater term (11512.8 Pa) are computed in isolation rather than combined correctly, and your final answer of 5886 Pa does not match the correct result of approximately 3394 Pa. You receive partial credit (25/100) for correctly identifying the relevant fluid densities, drawing a reasonable diagram, and computing some individual pressure terms.</t>
-  </si>
-  <si>
-    <t>You demonstrated some correct understanding by identifying the relevant fluids and their densities, and you correctly applied P = ρgh for individual terms. However, your manometer path equation is incorrectly set up — you did not properly trace the hydrostatic path from the freshwater pipeline to the seawater pipeline, leading to an incorrect final answer (550.8 Pa instead of ~3394 Pa). You used incorrect column heights (e.g., 0.03 m for seawater instead of 0.4 m, and 0.01 m for mercury instead of 0.1 m), and the overall pressure difference equation was not properly formulated. Partial credit of 25/100 is awarded for recognizing the basic principle and attempting calculations.</t>
-  </si>
-  <si>
-    <t>You demonstrated some understanding of the problem by identifying the relevant fluid densities and attempting pressure terms, but your manometer path equation is fundamentally incorrect — you set up a gage pressure approach rather than tracing the correct hydrostatic path from P_fw to P_sw, and your height assignments are wrong (e.g., using 0.4 m and 0.6 m for mercury and freshwater terms respectively in an incorrect combination). The correct path gives P_fw - P_sw = -(1000×9.81×0.6) + (13600×9.81×0.1) - (1035×9.81×0.4) ≈ 3394 Pa; your final answer of ~33,309 Pa is far from the correct value. Partial credit of 25/100 is awarded for recognizing relevant fluid properties and attempting calculations.</t>
-  </si>
-  <si>
-    <t>You demonstrated a strong understanding of the manometer path equation and correctly identified all densities and height conversions. Your individual terms (5886, 13341.6, 4061.34 Pa) are correct, and your final answer of ~3.44 kPa is within the acceptable range; however, your final answer is written as '3.44 Pa' instead of '3.44 kPa', so 5 points are deducted for the incorrect unit label on the final result. Great work overall!</t>
-  </si>
-  <si>
-    <t>You only wrote a partial calculation (1035 × 0.4 = 414 N, seemingly the seawater term) without setting up the manometer path equation, performing the other required calculations, or reaching a final answer. This earns minimal partial credit; please make sure to show the complete hydrostatic path equation and all substitution steps in future quizzes.</t>
-  </si>
-  <si>
-    <t>You demonstrated a good understanding of the manometer path setup and correctly identified all fluid terms including the freshwater, mercury, and seawater terms with proper unit conversions. However, your final answer of P_sea = P_water - (3.3) has a sign issue (it should be P_fw - P_sw = +3.39 kPa, not -3.3), costing 5 pts, and your intermediate term calculations show slight rounding (5.9 instead of 5.886, 13.3 instead of 13.342, 4.1 instead of 4.061), costing 5 pts for arithmetic inaccuracy. Additionally, your final answer is missing clear units (Pa or kPa), costing 5 pts, and the partially illegible air/middle term in your equation makes it unclear if that term was properly handled, costing 13 pts.</t>
-  </si>
-  <si>
-    <t>You correctly identified all densities, converted units properly, and calculated each individual pressure term accurately (freshwater: 5.886 kPa, mercury: 13.341 kPa, seawater: 4.061 kPa). However, your manometer path equation is incorrect — instead of applying the proper hydrostatic path (P_fw - P_sw = -ρ_w·g·h_w + ρ_Hg·g·h_Hg - ρ_sw·g·h_sw = 3.39 kPa), you added the freshwater and mercury terms together and then subtracted seawater, yielding 15.1 kPa, which does not reflect the correct pressure balance along the manometer path. This incorrect setup results in a 40-point deduction for Part 1 (manometer equation) and a 5-point deduction for the incorrect final answer in Part 3.</t>
-  </si>
-  <si>
-    <t>You correctly identified all fluid densities and computed the individual pressure terms (freshwater: 5886 Pa, seawater/mercury: 13341 Pa, seawater column: 4061 Pa), showing solid understanding of hydrostatic pressure — great effort! However, your final manometer path equation setup is incomplete and unclear (the signs and combination of terms are not properly organized as P_fw - P_sw = -ρ_w·g·h_w + ρ_Hg·g·h_Hg - ρ_sw·g·h_sw), leading to an incorrect final answer of approximately 2455 Pa instead of the correct ~3394 Pa; deducting 20 pts for the incorrect path/equation setup and 18 pts for the resulting incorrect final answer.</t>
-  </si>
-  <si>
-    <t>You correctly identified the relevant fluid columns and computed individual pressure terms (though you dropped g, using ρh instead of ρgh, which is a significant error). More critically, your manometer path equation is fundamentally incorrect: you added all pressure terms together instead of applying the proper hydrostatic path with alternating signs (P_fw + ρ_w·g·h_w − ρ_Hg·g·h_Hg + ρ_sw·g·h_sw = P_sw), leading to a completely wrong final answer of 237.4 kPa instead of approximately 3.39 kPa. Partial credit is awarded for identifying the correct fluid columns and attempting a structured approach.</t>
-  </si>
-  <si>
-    <t>You demonstrate a solid understanding of the manometer path equation and correctly identify all relevant terms. Your final answer of 3453.08 Pa is very close to the accepted range (3350–3450 Pa) — the small discrepancy arises from using g = 9.98 m/s² instead of the standard 9.81 m/s², which accounts for a minor arithmetic deviation (-5 pts), and your intermediate grouping approach (splitting into two sub-equations) is creative but led to a slight numerical drift (-8 pts). Overall, great work setting up the physics correctly and showing your calculations clearly!</t>
-  </si>
-  <si>
-    <t>You demonstrated a solid understanding of the manometer path and correctly identified all relevant fluid terms, arriving at a final answer of approximately 3.39 kPa which is within the acceptable range. However, your intermediate work shows some confusion with units (mixing density values as if they were pressures, e.g., treating 1035·0.40 = 41400 without multiplying by g properly in early steps), which warrants a 10 pt deduction for the setup/substitution section, and your final answer label 'P_sa' is ambiguous rather than clearly stating P_fw - P_sw, resulting in a 5 pt deduction for presentation. Keep up the good work and be careful with unit consistency throughout your calculations!</t>
-  </si>
-  <si>
-    <t>You demonstrated a good understanding of the manometer diagram and correctly identified the individual pressure terms (freshwater: 5886 Pa, mercury: 13341.6 Pa, seawater: 4061.34 Pa), which is excellent. However, your equation setup is incorrect — you treated air density as non-negligible and attempted to solve for P_air rather than recognizing it is negligible, and your path equation sign conventions are wrong (the mercury term should be positive in P_fw - P_sw, not negative as set up). Your final answer of -3394.26 - P_air does not yield the correct numerical result of approximately +3394.26 Pa; I'm deducting 30 pts for the incorrect equation setup and path sign errors, and 15 pts for the incorrect final answer due to the unresolved P_air term and missing clear units on the final result.</t>
-  </si>
-  <si>
-    <t>You correctly calculated all three individual pressure terms (seawater: 4061.34 Pa, freshwater: 5886 Pa, mercury: 13341.6 Pa), earning strong partial credit for Part 2. However, your manometer path equation setup in Part 1 is not clearly established with proper sign conventions and physical reasoning (showing which side gains/loses pressure along the path), costing you most of Part 1's points. Your final combination (13341.6 + 5886 - 4061.34 = 15166.2) uses incorrect signs — the freshwater term should be subtracted, not added — leading to a wrong final answer of ~15166 Pa instead of the correct ~3394 Pa, and no clear final units or ΔP statement was provided, resulting in deductions across Parts 1 and 3.</t>
-  </si>
-  <si>
-    <t>You correctly set up the manometer path equation with the right terms and densities, and your numerical calculation of 3394.26 Pa is spot-on. However, you expressed the final result as 'P_Fresh - 3394.26p = P_salt' rather than the clean pressure difference 'P_fw - P_sw = 3394.26 Pa', and units are written ambiguously ('p' instead of 'Pa'), so 5 pts are deducted for the unclear final answer presentation and 10 pts for not explicitly isolating and stating the pressure difference with proper units.</t>
-  </si>
-  <si>
-    <t>You showed some effort in setting up a manometer path equation and attempted to include multiple fluid terms, which earns partial credit. However, your approach has significant errors: you incorrectly solved for an air density (treating air as having a meaningful density equal to that of water divided by height ratio, yielding 714.28 kg/m³), the manometer path equation is not correctly structured (signs and terms are not properly assigned for freshwater, mercury, and seawater), and your final answer of 974.28 does not match the correct pressure difference of approximately 3394 Pa. The correct path is P_fw - P_sw = -(ρ_w·g·h_w) + (ρ_Hg·g·h_Hg) - (ρ_sw·g·h_sw) ≈ 3394 Pa; keep practicing the hydrostatic path method!</t>
-  </si>
-  <si>
-    <t>You correctly identified that the air term is negligible and computed the freshwater term (5.886 kPa) and mercury term (13.3416 kPa) correctly, which earns partial credit. However, your manometer path equation is incomplete and incorrect — you did not properly account for the seawater column with the correct signs, you did not arrive at a correct final pressure difference (P_fw - P_sw ≈ 3.39 kPa), and the expression P1 - P2 = (ρ2 - ρ1)·h·g at the bottom is an incorrect formula for this multi-fluid manometer. A full hydrostatic path traversal from P_fw to P_sw accounting for all fluid columns with proper signs was required to earn full credit.</t>
-  </si>
-  <si>
-    <t>You correctly set up the manometer path equation with the right terms and signs, earning strong partial credit for Part 1 (30/40). However, your final answer of 2.9 kPa is significantly off from the correct value of ~3.39 kPa — you appear to have skipped showing the intermediate arithmetic steps, making it impossible to identify where the calculation went wrong (Part 2: 10/40, Part 3: 10/20). Always show your full substitution and computation to receive full credit.</t>
-  </si>
-  <si>
-    <t>Excellent work! You correctly identified all relevant densities, set up the manometer path equation properly, computed each pressure term accurately (freshwater: 5886 Pa, mercury: 13341.6 Pa, seawater: 4061.34 Pa), and arrived at the correct final answer of ΔP = 3394.26 Pa with proper units. Well done!</t>
-  </si>
-  <si>
-    <t>You demonstrated a basic understanding of the ρgh pressure concept and attempted to include the relevant fluid columns, which is a good start. However, your manometer path equation is incorrectly set up — you used 'atm' as a density placeholder and g=10 (approximation) instead of the correct densities (ρ_w=1000, ρ_Hg=13600, ρ_sw=1035 kg/m³) with g=9.81 m/s², the signs in your path equation are inconsistent with a proper hydrostatic traversal, and your final answer of 7365 kg/m² uses incorrect units and is far outside the acceptable range of 3350–3450 Pa; these errors result in significant deductions across all three parts.</t>
-  </si>
-  <si>
-    <t>You correctly identified all three fluid densities and set up the individual pressure terms (freshwater: 600g, mercury: 1360g, seawater: 414g), which shows a good fundamental understanding of the problem. However, your manometer path equation is incorrect — you added the mercury and seawater terms together and then subtracted the freshwater term, rather than correctly applying the hydrostatic path as P_fw - P_sw = -(rho_w·g·h_w) + (rho_Hg·g·h_Hg) - (rho_sw·g·h_sw), leading to a final answer of ~11,516 Pa instead of the correct ~3,394 Pa; this error in the path setup costs significant points across Parts 1, 2, and 3.</t>
-  </si>
-  <si>
-    <t>You demonstrated excellent understanding of the manometer path equation and correctly identified all fluid terms and their values, arriving at the correct magnitude of 3394.26 Pa. However, your final answer is presented as a negative value (-3394.26 Pa), which indicates an inverted sign — deducting 5 pts. Also, the units appear slightly unclear in the final answer — deducting 5 pts. Overall, great work on the methodology and calculations!</t>
-  </si>
-  <si>
-    <t>You demonstrated correct calculation of the individual pressure terms (freshwater: 5886 Pa, mercury: 13341.6 Pa, seawater: 4061.34 Pa) and your methodology shows understanding of the hydrostatic path. However, you made a critical error in the mercury height: you used 0.6 m instead of 0.1 m (h_Hg = 10 cm = 0.1 m), which led to an incorrect intermediate result of -7455.6 Pa instead of the correct +1569.6 Pa. Additionally, your final answer of 9278 Pa is incorrect due to this propagated error; the correct answer is approximately 3394 Pa. You lose 40 pts for the incorrect mercury height substitution and resulting calculation errors, and 5 pts for the incorrect final answer.</t>
-  </si>
-  <si>
-    <t>You demonstrated some understanding of the manometer path by including the correct fluid terms, but unfortunately your approach went in the wrong direction — instead of solving for the pressure difference (P_fw - P_sw), you attempted to solve for the density of air, which is not what the problem asks. Your initial equation setup has the right components but incorrect sign conventions and rearrangement, leading to a fundamentally different problem being solved. The final answer of 308.144 kg/m³ is not a pressure difference and does not match the expected result of ~3.39 kPa; partial credit of 20/100 is awarded for recognizing the relevant fluid columns and including them in an equation.</t>
-  </si>
-  <si>
-    <t>You correctly calculated the individual pressure terms (freshwater, mercury, seawater) and showed your work, earning partial credit. However, your manometer path equation is fundamentally incorrect — you added the seawater and mercury terms together instead of setting up the proper hydrostatic path from one pipeline to the other (P_fw + ρ_w·g·h_w - ρ_Hg·g·h_Hg + ρ_sw·g·h_sw = P_sw), which led to a final answer of 11.52 mPa that is far from the correct value of ~3.39 kPa. The equation setup accounts for 40 pts, the substitution for 40 pts, and the final answer for 20 pts; since only the individual term calculations were partially correct, 25/100 is awarded.</t>
-  </si>
-  <si>
-    <t>You show some correct individual density/height term calculations (e.g., rho_w*g*h_w = 600g, rho_sw*g*h_sw = 414g, mercury term = 0.1*13600*g = 1360g), earning partial credit for Part 1 and Part 2 setup. However, your manometer path equation is incorrectly assembled — the air column term (0.7*d_air*g) appears in the equation instead of being dropped (air density is negligible and that column height is not needed), and the seawater column height used (0.3 m) is incorrect (should be 0.4 m); additionally, no final numerical answer in Pa or kPa is computed, so you lose the majority of points for Parts 2 and 3.</t>
-  </si>
-  <si>
-    <t>You correctly identified the three fluid terms (freshwater: 5886 Pa, mercury: 13341.6 Pa, seawater: 4061.34 Pa) and computed each one accurately, earning solid partial credit. However, your manometer path equation is incorrectly set up: you added the freshwater and mercury terms together instead of combining them with the correct signs to find P_fw - P_sw; the correct result is P_fw - P_sw = -5886 + 13341.6 - 4061.34 ≈ 3394 Pa (≈ 3.39 kPa), not 15.166 kPa. This fundamental sign/path error in Part 1 (−15 pts) carries through to an incorrect final answer in Part 3 (−20 pts), and the substitution structure in Part 2 is also affected (−40 pts reduced to a partial award of 25 pts total for correctly computing the individual terms).</t>
+    <t>You identified the correct densities and g, and your individual term calculations for freshwater (5.886 kPa) and mercury (13.342 kPa) are numerically correct — however, you used h = 0.7 m for the mercury term instead of the correct 0.1 m level difference, which is a critical error (-10 pts on the mercury term). Your seawater term uses the correct values (1035·9.81·0.4 ≈ 4.06 kPa) but it appears on the wrong side of the equation with an incorrect sign convention, and the air term is left as an unknown 'P_air' rather than being neglected or calculated correctly (-8 pts seawater sign/setup, -5 pts air term). There is no clear manometer traversal strategy, no proper rearrangement to isolate P1–P2, and no final answer for the pressure difference (-10 pts strategy, -10 pts rearrangement, -8 pts final answer combination, -2 pts no units on final answer, -2 pts no interpretation), leaving only partial credit for data identification and the two correct individual term values.</t>
+  </si>
+  <si>
+    <t>You correctly identified the relevant fluid densities and heights, and your sketch shows understanding of the manometer layout. However, your approach has a fundamental methodological error: you computed P1 and P2 separately by adding ρgh terms from an assumed atmospheric reference (P_atm = 100), rather than traversing the connected manometer path from P1 to P2. This means the manometer linkage between the two pipes was not properly used. For P1, you used h = 0.7 m (air column) with water density and h = 0.1 m with mercury density and h = 0.6 m with water density — the signs and path are not consistent with a correct manometer traversal. For P2, only the seawater column (0.4 m) was used, missing the connection through mercury. The final answer of 10.26 (units unclear) is far from the correct 3.39 kPa. You earn partial credit for: correctly reading all heights from the figure (A: 7/10), stating the hydrostatic principle P = P_atm + ρgh (B: 3/10), correctly computing the seawater term 1035×9.81×0.4 ≈ 4.06 kPa (E: 4/20, C: 4/30), and showing a diagram (G: 2/5). Deductions: -3 for A (misapplication of heights), -7 for B (incorrect traversal strategy), -26 for C (incorrect manometer equation structure), -10 for D (no proper rearrangement), -16 for E (most numerical terms incorrect in context), -13 for F (wrong final answer and no units).</t>
+  </si>
+  <si>
+    <t>You correctly identified the given values and drew a diagram showing the manometer setup, which is a good start. However, your manometer traversal is fundamentally flawed: you did not write a single connected equation from P1 to P2 traversing all fluid columns. Instead, you computed isolated pressure terms (P1 = ρ_Hg·g·h + P2 with an unclear mercury term, P2 = ρ_sw·g·h_sw = 4057.2 Pa, P_fw = ρ_w·g·h_w = 11512.8 Pa) and then simply subtracted to get ΔP = P1 - P2 = 5886 Pa — this final value is just the freshwater term alone and does not correctly combine all manometer contributions. Deductions: -8 for incomplete/incorrect data usage (no mercury height of 10 cm used correctly; B), -8 for no valid manometer traversal strategy (-2 strategy, -6 manometer equation setup), -25 for missing/wrong manometer equation terms (mercury term not properly applied at 10 cm, air term missing, signs inconsistent), -10 for incorrect rearrangement, -15 for incorrect numerical combination, -10 for wrong final answer (5886 Pa vs. 3394 Pa), -2 for no statement of which pressure is higher.</t>
+  </si>
+  <si>
+    <t>You correctly identified the P = ρgh principle and listed the fluid densities, earning partial credit for data recognition and strategy. However, your manometer traversal equation is not correctly set up — you did not write a proper P1-to-P2 path equation with correct signs and all terms (freshwater, mercury level difference, air, seawater), and you used incorrect heights (e.g., 3 cm and 1 cm instead of 60 cm, 10 cm, 70 cm, 40 cm). Your final answer of 550.8 Pa is incorrect and does not match the reference value of ~3394 Pa. Deductions: A (-7), B (-6), C (-26), D (-8), E (-16), F (-15), G (-4).</t>
+  </si>
+  <si>
+    <t>You demonstrate some understanding of the problem (identifying densities and using g = 9.81), but your manometer traversal equation is fundamentally incorrect: you appear to combine mercury and seawater terms additively rather than correctly tracking pressure increases and decreases through each fluid column from P1 to P2. Critically, you used h = 0.4 m for mercury (instead of the correct 0.1 m level difference) and h = 0.6 m for mercury in the second line, and your freshwater height was used as 0.4 m instead of 0.6 m — these are major errors in reading the manometer. The final answer of ~33,309 Pa is far from the correct ~3,394 Pa. You earn partial credit for correctly identifying the fluid densities and using g = 9.81 m/s² (Section A: 6/10), showing an attempt at a manometer equation (Section B: 3/10), some partial term structure (Section C: 5/30), no valid rearrangement for P1-P2 (Section D: 2/10), some arithmetic on your own values (Section E: 2/20), wrong final answer with units stated (Section F: 0/15), and minimal justification (Section G: 0/5); total deductions: 4+7+25+8+18+15+5 = 82 points.</t>
+  </si>
+  <si>
+    <t>You correctly set up the manometer traversal equation and identified all fluid densities and heights. Your mercury and water pressure terms in the final calculation appear correct (5886 Pa and 13341.6 Pa), but your seawater term shows 406 Pa instead of the correct 4061.3 Pa (it appears you dropped a digit when computing 1035×9.81×0.4), which shifted your final answer to ~3.44 kPa instead of ~3.39 kPa — deducting 4 pts for the seawater numerical error, 4 pts for the seawater equation term, and 2 pts for not stating which pipe has the higher pressure, and 2 pts for the air term handling. Overall, strong approach and good structure!</t>
+  </si>
+  <si>
+    <t>Your submission shows only '1035 * 0.4 = 414 N' (approximately), which appears to be a partial calculation of the seawater pressure term without any supporting manometer equation, strategy, unit conversions, or final answer — this does not constitute a complete or scorable solution. Per the course policy, answers without supporting calculations receive no credit, and a correct final answer with no supporting work earns at most 20/100; since no final answer is present either, your score is 0/100. Please review the double U-tube manometer traversal method and make sure to show all steps on future quizzes.</t>
+  </si>
+  <si>
+    <t>You correctly identified all the fluid heights, converted units to SI, and used the right densities (including 1035 kg/m³ for seawater) — good work on data setup. Your manometer traversal equation has the correct freshwater term (+1000·9.81·0.6), the correct mercury term (−13600·9.81·0.1), and the correct seawater term (+1035·9.81·0.4), earning substantial partial credit; however, the seawater term's sign should be negative (it acts to decrease pressure going up toward P2), so you lose 4 pts on that term's sign (Section C). The air term appears partially written but is illegible/incomplete, so only partial credit (2/5) is awarded there. Your numerical sub-totals (5.9, 13.3, 4.1 kPa) are reasonably correct under your sign convention, and you correctly combine them to get P_sea = P_water − 3.3 kPa, which implies P_water − P_sea ≈ 3.3 kPa — close to the correct 3.39 kPa (within ~3%), earning partial final-answer credit. You lose points for: wrong sign on the seawater term in the equation (−4 pts, Section C), incomplete/illegible air term (−3 pts, Section C), no explicit units on the final answer (−3 pts, Section F), no statement of which pressure is higher (−2 pts, Section F), and limited physical reasoning/justification for neglecting air (−3 pts, Section G). Overall, your approach is sound and your answer is in the right ballpark — keep working on sign conventions and always state units and interpretation.</t>
+  </si>
+  <si>
+    <t>You correctly identified all densities, converted heights to meters, and calculated each individual pressure term accurately (ΔP_fw = 5886 Pa, ΔP_sw = 4061 Pa, ΔP_Hg = 13341 Pa). However, your final combination is incorrect: you added the freshwater and mercury terms together (13.3 + 5.8 = 19.1 kPa) and then subtracted only the seawater term, but the correct equation requires you to subtract both the freshwater term and the seawater term from the mercury term: P1 - P2 = -5886 + 13342 - 4061 ≈ 3394 Pa ≈ 3.39 kPa. Your sign convention for the manometer traversal was not established, leading to an incorrect combination of terms and a final answer of 15.1 kPa instead of 3.39 kPa. You earn full credit for data identification (10/10), partial strategy credit (5/10), partial equation credit for correctly computing each term but missing the sign structure (14/30), no rearrangement credit (0/10), partial numerical credit for the three individual term values (12/20), and no final answer credit (0/15), with partial clarity credit (2/5) — total deductions: 0 + 5 + 16 + 10 + 8 + 15 + 3 = 57 points deducted.</t>
+  </si>
+  <si>
+    <t>You correctly identified all fluid densities and obtained the right mercury term (13341 Pa) and freshwater term (5886 Pa). However, your seawater pressure calculation (1035×9.81×0.4) yields 4061 Pa, not 6069 Pa — this arithmetic error costs you points in Section E. Your manometer traversal equation is never written out explicitly, making it hard to follow your sign conventions and path (deducting 5 pts strategy, 18 pts manometer equation, 7 pts rearrangement, 10 pts numerical). Your final answer of 3396 Pa is very close to the correct 3394 Pa, which shows you have a reasonable intuition for the problem — work on organizing your solution with a clear, written pressure equation from P1 to P2 to secure full credit.</t>
+  </si>
+  <si>
+    <t>You correctly identified the fluid components (freshwater, mercury, seawater, air) and attempted to compute pressure terms, earning partial credit for data identification and some individual calculations. However, your manometer equation is fundamentally incorrect: you simply added all pressure terms together (Pa = Pw + Pm + Ps) rather than properly traversing the manometer from P1 to P2 with correct signs (pressure increases going down, decreases going up), which is the core of this problem. You also failed to convert cm to m (using 60, 10, 40 instead of 0.6, 0.1, 0.4 m) and omitted g = 9.81 in your calculations, leading to values off by a factor of ~9.81. The correct answer is P1 - P2 ≈ 3.39 kPa, not 237.4 kPa. Points awarded: 6/10 for data identification (values read correctly but units not converted), 3/10 for strategy (wrong principle — summing rather than traversing), 3/30 for the manometer equation (wrong signs and structure throughout), 0/10 for rearrangement, 0/20 for numerical calculation (g omitted, no unit conversion), 0/15 for final answer, 0/5 for physical reasoning.</t>
+  </si>
+  <si>
+    <t>Your manometer traversal and equation setup are correct, with the right signs and heights for all fluid terms. Your use of g = 9.98 m/s² (instead of 9.81) shifts your answer to ~3453 Pa, which is about 1.7% above the reference value of ~3394 Pa — deducting 3 pts on the final answer. The air column is implicitly handled through P_A but not explicitly justified as negligible (-2 pts on Section C air term). You did not state which pipe has the higher pressure (-2 pts). Overall, excellent work with a well-organized solution!</t>
+  </si>
+  <si>
+    <t>You correctly identified all four fluid terms and arrived at the right final answer of approximately 3.39 kPa — well done! However, your intermediate work (solving an inconsistent equation for ρ_air and using incorrect units of 'kPa' for density) is disorganized and hard to follow (-5 pts for clarity/G, -3 pts for strategy presentation, -8 pts for equation setup issues, -3 pts for missing a statement of which pressure is higher, -3 pts for rearrangement clarity, and -5 pts on partial credit for the equation section due to the confused intermediate steps).</t>
+  </si>
+  <si>
+    <t>You demonstrate a correct understanding of the manometer traversal principle and properly identify the signs for each fluid column, which is great. However, your equation is missing the gravity factor (g) throughout — you write ρh instead of ρgh, which means your numerical values are off by a factor of 9.81 (−5 pts for strategy/setup). Your freshwater term (600 instead of 5886 Pa) and mercury term (1360 instead of 13341.6 Pa) are missing the g factor, costing you significant points in Section E (−12 pts). You correctly use h_Hg = 0.1 m and h_sw = 0.4 m, and you identify the correct signs for each term, earning partial credit. Your final expression ΔP = −3394.26 − P_air is close in structure to the correct answer but is left unsimplified and the air term is not properly handled (−10 pts for F). The seawater numerical value (406.34 without g) and the final combination are partially correct under your own framework, earning partial credit. Overall: Data/units partial credit (5/10), Strategy partial (6/10), Manometer equation partial (14/30), Rearrangement partial (5/10), Numerical partial (4/20), Final answer partial (2/15), Clarity partial (2/5).</t>
+  </si>
+  <si>
+    <t>You correctly calculated all three individual pressure terms (P_sw = 4061.34 Pa, P_fw = 5886 Pa, P_Hg = 13341.6 Pa) with correct densities, heights, and SI units — well done on that. However, your final combination is incorrect: you added the freshwater term instead of subtracting it and added the seawater term instead of subtracting it, yielding 15166.2 Pa instead of the correct ~3394 Pa; this reflects a fundamental error in the manometer traversal sign convention (which pressure terms increase vs. decrease along the path from P1 to P2), costing you points in Strategy (-7), Manometer Equation (-21), Algebraic Rearrangement (-8), and Final Answer (-12), with partial credit awarded for the correct individual term calculations and numerical work shown.</t>
+  </si>
+  <si>
+    <t>You correctly set up the manometer traversal equation with the right heights (0.6 m, 0.1 m, 0.4 m) and densities, and your numerical result of 3394.26 Pa is essentially correct — great work! However, you lose points for: missing the air term entirely without justification (-5 pts for Section C air term, -5 pts Section G), not explicitly showing unit conversions from cm to m (-4 pts Section A), not clearly stating the strategy/principle of pressure traversal (-4 pts Section B), not isolating P_Fresh - P_salt explicitly as a final rearranged expression (-4 pts Section D), and not stating units on your final answer or clarifying which pressure is higher (-6 pts Section F). Your core physics and arithmetic are solid — make sure to always label units, justify assumptions (like neglecting air density), and state your final answer clearly.</t>
+  </si>
+  <si>
+    <t>You correctly identified h_Hg = 0.1 m and applied the mercury term with the right sign, which is a good start. However, your approach of deriving a non-negligible air density (ρ_air = 714.28 kg/m³) is physically incorrect — air density is negligible (~1.2 kg/m³) and should simply be neglected or set to zero; this error, combined with the complete omission of the seawater term and incorrect use of h_air = 0.3 m, led to a final answer of ~774 Pa instead of the correct ~3394 Pa, resulting in significant deductions across the equation setup (-16 pts in C), rearrangement (-6 pts in D), numerical calculation (-16 pts in E), and the final answer (-15 pts in F).</t>
+  </si>
+  <si>
+    <t>You correctly identified the three pressure components (freshwater, mercury, air) and properly neglected the air term, and your individual calculations for the freshwater term (5.886 kPa) and mercury term (13.3416 kPa) are correct. However, you did not complete the manometer traversal: the seawater term (rho_sw*g*h_sw = 4.061 kPa) is missing from your equation, and you did not combine the terms to arrive at a final pressure difference P1 - P2. The value '5899 3416' appears to be an incomplete or incorrect combination, and the formula P1 - P2 = (rho2 - rho1)*h*g at the bottom is not applied or developed further. Deductions: -7 pts (C: freshwater sign/direction unclear in final equation), -10 pts (C: mercury term sign not applied in combined equation), -5 pts (C: air term credit given for neglecting), -8 pts (C: seawater term entirely missing), -10 pts (D: no proper rearrangement to P1-P2), -16 pts (E: no correct final combination of terms), -15 pts (F: no valid final answer), -5 pts (G: no physical reasoning or organized solution), leaving 10 pts for the two correct individual term calculations and partial data identification.</t>
+  </si>
+  <si>
+    <t>You correctly identified the key fluid densities and heights, and your manometer traversal approach is on the right track. However, your equation is missing the air column term entirely (no justification given, -5 pts from C), and the signs in your equation are inconsistent with a correct manometer traversal: the freshwater term should subtract and the seawater term should add when moving from P_w to P_sw, or vice versa — your sign structure leads to a wrong rearrangement (-10 pts from B/C). Your final answer of 2.9 kPa is significantly off from the correct 3.39 kPa and lacks explicit numerical intermediate steps (-8 pts from E combination, -4 pts from individual term calculations not shown), and no units are stated for the final answer (-3 pts from F). The strategy of traversing from one pipe to the other is partially correct, earning you partial credit.</t>
+  </si>
+  <si>
+    <t>Excellent work! You correctly identified all fluid properties, applied hydrostatic pressure principles through an intermediate variable approach, and arrived at the correct answer of 3394.26 Pa (≈ 3.39 kPa) with P_fresh &gt; P_sea clearly stated. Deductions: -3 pts for the air term (neglected without explicit justification), -2 pts for the somewhat convoluted algebraic path making the solution hard to follow, -1 pt for the strategy being only implicitly described, -2 pts for partial algebra clarity, and -1 pt on the final answer section for minor presentation issues. Overall, your physical understanding and numerical execution are very strong!</t>
+  </si>
+  <si>
+    <t>You identified the mercury term correctly (13600·ρ·g·0.10) and attempted to build the manometer equation step by step, which shows some understanding of the approach. However, your solution has several critical issues: you used 10 cm instead of 60 cm for the freshwater column, your units are in kg/m² rather than Pa (you need to include the actual value of g = 9.81 m/s²), you never clearly defined P1 and P2 or set up a proper manometer traversal equation, and the final answer of 7365 kg/m² is both numerically incorrect and in non-standard units — deducting 7 pts (A), 8 pts (B), 22 pts (C), 8 pts (D), 17 pts (E), and 15 pts (F), and 4 pts (G). Please make sure to convert all heights to meters, include g numerically, and set up the equation as P1 − P2 = Σ(ρgh) terms with correct signs.</t>
+  </si>
+  <si>
+    <t>You correctly identified the fluid densities and showed a diagram with the relevant heights (10 cm for mercury, 60 cm for water, 40 cm for seawater), which earns partial credit. However, your manometer traversal method is fundamentally flawed: you added the mercury and seawater pressure terms together and then subtracted the water term, rather than applying the correct sign convention (pressure increases going down, decreases going up) along a continuous path from P1 to P2. As a result, your final answer of ~11,516 Pa is far from the correct ~3,394 Pa. You also did not convert cm to m before computing (using 0.1, 0.4, 0.6 in SI is correct, but your intermediate values like '1360g' suggest you used 0.1 m for Hg correctly yet treated the terms improperly). Points awarded: Data/units (7/10), Strategy (3/10), Manometer equation (8/30 — partial credit for correct Hg height and water/seawater heights but wrong sign structure), Rearrangement (3/10), Numerical calculation (4/20), Final answer (2/15), Clarity (1/5). Total deductions: 72 points.</t>
+  </si>
+  <si>
+    <t>You correctly identified all densities, converted units to SI, drew a clear diagram, and set up the manometer equation with the right structure — excellent work on the fundamentals! However, your equation shows the air term with a '+' sign (adding it) rather than correctly handling it, and the sign on your final answer is negative (−3394.26 Pa) without clearly stating which pressure is larger or interpreting the result physically (-5 pts for sign/interpretation of final answer, -5 pts for air term handling, -10 pts for overall equation sign convention issues leading to P2−P1 being reported without clear convention statement, -8 pts for the seawater term height appearing as 0.04 m instead of 0.4 m in the calculation, though the computed value 4061.34 suggests you used 0.4 m correctly). Your individual term calculations (5886, 13341.6, 4061.34) are all correct, and your final magnitude of ~3394 Pa is within acceptable range of the correct answer of 3394 Pa — great numerical work!</t>
+  </si>
+  <si>
+    <t>You correctly computed all three individual pressure terms (freshwater: 5886 Pa, mercury: 13341.6 Pa, seawater: 4061.34 Pa) and properly neglected air, which is great work through the intermediate steps. However, your final rearrangement is incorrect: after obtaining P_F = -3394.26 Pa (which already represents P2 - P1 or a pressure difference), you incorrectly added P_A (5886 Pa) again, arriving at 9280 Pa instead of the correct ~3394 Pa. You lost 18 points for this incorrect final combination and rearrangement (D: -7, E: -8, F: -13).</t>
+  </si>
+  <si>
+    <t>You demonstrate some understanding of manometer traversal by writing terms for each fluid, but your approach has several critical errors: you set the equation equal to zero rather than P1-P2, you use incorrect heights (0.6 m for mercury instead of the 10 cm level difference, and 0.2 m columns that don't match the given data), and you attempt to solve for air density rather than treating it as negligible — leading to a nonsensical result of ρ_air ≈ 494 kg/m³. Your final answer of 308.144 kg/m³ is also in wrong units and is far from the correct pressure difference of ~3.39 kPa. You earn partial credit (10/10 for data identification, 5/30 for partial manometer equation structure, 3/10 for strategy) for recognizing the relevant fluids and writing a traversal-style equation, but significant deductions apply for the incorrect mercury height (-10 pts), wrong equation setup/equal to zero (-5 pts), solving for air density instead of pressure difference (-5 pts), incorrect final calculation and wrong units (-25 pts), and no valid interpretation (-14 pts).</t>
+  </si>
+  <si>
+    <t>You correctly identified the three fluid densities and used h = 0.1 m for mercury (earning full mercury term credit) and h = 0.4 m for seawater, and your individual pressure calculations are arithmetically correct. However, your manometer traversal strategy is fundamentally flawed: you simply added/subtracted the three pressure terms without a proper path equation connecting P1 to P2, the signs and combination are inconsistent with hydrostatic manometer principles, and you did not correctly assemble the equation P1 - P2 = -ρ_w·g·h_w + ρ_Hg·g·h_Hg - ρ_sw·g·h_sw. The intermediate equalities (P_left = P_fresh, etc.) are unclear and lead to an incorrect final answer of 11.52 mPa instead of ~3.39 kPa. Deductions: Strategy/principle (-7), Manometer equation (-22), Algebraic rearrangement (-8), Numerical combination (-8), Final answer value (-10), Units/interpretation (-5), Physical reasoning (-3); partial credit awarded for correctly computing individual ρgh terms and using correct heights.</t>
+  </si>
+  <si>
+    <t>You correctly identified all fluid heights, densities, and set up the manometer traversal equation with proper signs for all four terms (water, mercury, air, seawater) — great work on the fundamentals! However, you did not substitute a numerical value for g to complete the arithmetic and arrive at a final numerical answer in Pa or kPa, costing you 25 points (−8 for incomplete numerical combination, −15 for no final answer with units or interpretation); make sure to always carry your solution through to a clearly stated final result.</t>
+  </si>
+  <si>
+    <t>You correctly identified all three fluid terms and computed each individual pressure value accurately (5886 Pa for freshwater, 13341.6 Pa for mercury, 4061.34 Pa for seawater), earning strong partial credit. However, your manometer equation has a critical sign error: you added the mercury term to the freshwater term instead of subtracting, and then subtracted the seawater term incorrectly, yielding 15,166 Pa rather than the correct ~3,394 Pa. The manometer traversal requires P1 - P2 = -ρ_w·g·h_w + ρ_Hg·g·h_Hg - ρ_sw·g·h_sw; using all positive signs for the combination is not physically justified. Deductions: Strategy/principle (-6), Manometer equation signs (-18), Algebraic rearrangement (-8), Final answer wrong value (-10), Missing statement of which pressure is higher (-2), No justification for air neglect (-3) — total deductions: 47, but capped generously given correct individual term calculations.</t>
   </si>
 </sst>
 </file>
@@ -5333,7 +5333,7 @@
         <v>210</v>
       </c>
       <c r="H160">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I160" t="s">
         <v>266</v>
@@ -5362,7 +5362,7 @@
         <v>210</v>
       </c>
       <c r="H161">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I161" t="s">
         <v>267</v>
@@ -5417,7 +5417,7 @@
         <v>210</v>
       </c>
       <c r="H163">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I163" t="s">
         <v>268</v>
@@ -5472,7 +5472,7 @@
         <v>210</v>
       </c>
       <c r="H165">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I165" t="s">
         <v>269</v>
@@ -5501,7 +5501,7 @@
         <v>210</v>
       </c>
       <c r="H166">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I166" t="s">
         <v>270</v>
@@ -5530,7 +5530,7 @@
         <v>210</v>
       </c>
       <c r="H167">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="I167" t="s">
         <v>271</v>
@@ -5585,7 +5585,7 @@
         <v>210</v>
       </c>
       <c r="H169">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I169" t="s">
         <v>272</v>
@@ -5640,7 +5640,7 @@
         <v>210</v>
       </c>
       <c r="H171">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="I171" t="s">
         <v>273</v>
@@ -5669,7 +5669,7 @@
         <v>210</v>
       </c>
       <c r="H172">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="I172" t="s">
         <v>274</v>
@@ -5698,7 +5698,7 @@
         <v>210</v>
       </c>
       <c r="H173">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="I173" t="s">
         <v>275</v>
@@ -5727,7 +5727,7 @@
         <v>210</v>
       </c>
       <c r="H174">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I174" t="s">
         <v>276</v>
@@ -5785,7 +5785,7 @@
         <v>210</v>
       </c>
       <c r="H176">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="I176" t="s">
         <v>278</v>
@@ -5814,7 +5814,7 @@
         <v>210</v>
       </c>
       <c r="H177">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="I177" t="s">
         <v>279</v>
@@ -5843,7 +5843,7 @@
         <v>210</v>
       </c>
       <c r="H178">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I178" t="s">
         <v>280</v>
@@ -5872,7 +5872,7 @@
         <v>210</v>
       </c>
       <c r="H179">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="I179" t="s">
         <v>281</v>
@@ -5901,7 +5901,7 @@
         <v>210</v>
       </c>
       <c r="H180">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I180" t="s">
         <v>282</v>
@@ -5930,7 +5930,7 @@
         <v>210</v>
       </c>
       <c r="H181">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I181" t="s">
         <v>283</v>
@@ -5959,7 +5959,7 @@
         <v>210</v>
       </c>
       <c r="H182">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I182" t="s">
         <v>284</v>
@@ -5988,7 +5988,7 @@
         <v>210</v>
       </c>
       <c r="H183">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="I183" t="s">
         <v>285</v>
@@ -6069,7 +6069,7 @@
         <v>210</v>
       </c>
       <c r="H186">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I186" t="s">
         <v>286</v>
@@ -6098,7 +6098,7 @@
         <v>210</v>
       </c>
       <c r="H187">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I187" t="s">
         <v>287</v>
@@ -6127,7 +6127,7 @@
         <v>210</v>
       </c>
       <c r="H188">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="I188" t="s">
         <v>288</v>
@@ -6156,7 +6156,7 @@
         <v>210</v>
       </c>
       <c r="H189">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="I189" t="s">
         <v>289</v>
@@ -6237,7 +6237,7 @@
         <v>210</v>
       </c>
       <c r="H192">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I192" t="s">
         <v>290</v>
@@ -6266,7 +6266,7 @@
         <v>210</v>
       </c>
       <c r="H193">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I193" t="s">
         <v>291</v>
@@ -6295,7 +6295,7 @@
         <v>210</v>
       </c>
       <c r="H194">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="I194" t="s">
         <v>292</v>
@@ -6324,7 +6324,7 @@
         <v>210</v>
       </c>
       <c r="H195">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I195" t="s">
         <v>293</v>

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="322">
   <si>
     <t>student_id</t>
   </si>
@@ -625,6 +625,9 @@
     <t>DZHAVAD KAZIMOV</t>
   </si>
   <si>
+    <t>MOHAMMED ZABAAN</t>
+  </si>
+  <si>
     <t>MCH2015</t>
   </si>
   <si>
@@ -896,6 +899,87 @@
   </si>
   <si>
     <t>You correctly identified all three fluid terms and computed each individual pressure value accurately (5886 Pa for freshwater, 13341.6 Pa for mercury, 4061.34 Pa for seawater), earning strong partial credit. However, your manometer equation has a critical sign error: you added the mercury term to the freshwater term instead of subtracting, and then subtracted the seawater term incorrectly, yielding 15,166 Pa rather than the correct ~3,394 Pa. The manometer traversal requires P1 - P2 = -ρ_w·g·h_w + ρ_Hg·g·h_Hg - ρ_sw·g·h_sw; using all positive signs for the combination is not physically justified. Deductions: Strategy/principle (-6), Manometer equation signs (-18), Algebraic rearrangement (-8), Final answer wrong value (-10), Missing statement of which pressure is higher (-2), No justification for air neglect (-3) — total deductions: 47, but capped generously given correct individual term calculations.</t>
+  </si>
+  <si>
+    <t>Excellent work! Your solution is complete, well-organized, and methodically correct — you correctly identified all relevant heights, properly set up the manometer traversal equation, correctly computed both the mercury contribution (198,652.5 Pa) and water contribution (9,613.8 Pa), and arrived at the correct gauge pressure of 189.04 kPa. No deductions apply.</t>
+  </si>
+  <si>
+    <t>You arrived at the correct final answer of 189 kPa, but your methodology contains critical errors. You used an incorrect density of 12,520 kg/m³ for what appears to be the water segments (the correct water density is 980 kg/m³), and your equation does not properly traverse all manometer segments with the correct alternating Mercury/Water contributions — deducting 25 pts for Section C, 5 pts for Section A, 5 pts for Section B, 4 pts for Section D, 8 pts for Section E, and 2 pts for Section G. The correct answer obtained here appears coincidental rather than derived from a sound method; please review the systematic manometer traversal technique for future exams.</t>
+  </si>
+  <si>
+    <t>You demonstrated an attempt to combine density and height terms, which shows some understanding of the manometer traversal concept. However, your equation is missing the gravitational acceleration g (deducting 15 pts from Section C/E), your height assignments and signs do not match the correct traversal path — only 5 terms are used with incorrect height values (e.g., 0.9, 0.2, 0.4, 0.8, 0.6 m are not the given heights h2–h6), leading to major deductions across Sections A, B, C, and D (-20 pts for wrong heights, -15 pts for incorrect equation setup, -10 pts for wrong algebraic structure, -10 pts for incorrect numerical answer, -7 pts for final answer being far off); your units are written as kg/m² instead of Pa/kPa (-2 pts), and gauge pressure is not mentioned (-1 pt). Please review the hydrostatic traversal method carefully — start at the vessel and track pressure changes through each fluid segment step by step.</t>
+  </si>
+  <si>
+    <t>You correctly identified all height values and used the basic hydrostatic pressure formula P = ρgh, which earns you credit for data setup and recognizing the principle. However, you applied mercury density (13500 kg/m³) uniformly to ALL heights including those corresponding to water segments, and you never set up a proper manometer traversal equation connecting the vessel pressure to the open atmosphere — instead you simply calculated individual pressure heads without combining them into a coherent equation or producing a final answer for P_vessel. You lose points in Section B (partial, -5 pts), Section C (no proper equation setup, -30 pts), Section D (no algebraic rearrangement, -10 pts), Section E (no correct final calculation, -20 pts), and Section F (no final answer given, -10 pts), and Section G (incomplete organization, -4 pts), and also for using h1 as an active term incorrectly (-3 pts in Section A).</t>
+  </si>
+  <si>
+    <t>You demonstrated some understanding of hydrostatic pressure principles, but your approach has significant issues. Your equation treats all segments as Mercury (rho_Hg) when the manometer alternates between Mercury and Water — Water segments must use rho_w = 980 kg/m³, not rho_Hg = 13500 kg/m³, costing you major points in Sections B and C (-25 pts). You also incorrectly include h1 (the air column distractor) in your pressure equation and include it with rho_air*g*h1 rather than neglecting it (-5 pts). The side calculation using P_air = rho_Hg*h_Hg/h_air shows a conceptually incorrect ratio approach (-5 pts). Your numerical result of ~225 kPa deviates significantly from the correct ~189 kPa as a direct consequence of using rho_Hg for all fluid segments. You do earn credit for partially correct traversal structure, mentioning the right number of height terms, correct use of g = 9.81, and providing a final numerical answer with units. Keep working on identifying which fluid occupies each manometer segment!</t>
+  </si>
+  <si>
+    <t>You correctly identified gauge pressure and applied g as a factor, showing some hydrostatic understanding. However, your manometer equation has significant errors: you incorrectly used h1 (the air column distractor) in the water term, and your mercury height groupings are missing key contributions (h3 and h5 in the mercury segments), leading to a final answer of ~90.8 kPa instead of the correct ~189 kPa. Deductions: Section A -7 pts (misuse of h1, misassigned heights), Section B -5 pts (incomplete traversal path), Section C -22 pts (incorrect mercury and water height terms), Section F -6 pts (final value significantly off from correct answer).</t>
+  </si>
+  <si>
+    <t>You correctly identified the given heights and fluid densities, and you applied P = ρgh — a good start. However, your approach treats each height independently with mercury density for nearly all segments, rather than setting up a proper manometer traversal equation from vessel to open end accounting for alternating mercury and water columns with correct signs. You used mercury density (13800 kg/m³, slightly off from 13500) for h1 (an air column that should be ignored), h2, h3, h4, h5, and h6 without distinguishing water segments or applying the correct ± signs for rising/falling fluid columns — this results in a fundamentally incorrect setup. Your final answer of 268 kPa differs significantly from the correct ~189 kPa. You earn credit for: listing all heights (Section A: 5/10), showing basic hydrostatic principle P=ρgh (Section B: 4/10), some partial pressure calculations (Section C: 5/35), algebraic attempt (Section D: 2/10), numerical work (Section E: 4/20), correct units in final answer (Section F: 2/10), and organized layout (Section G: 0/5). Total deductions: 78 pts.</t>
+  </si>
+  <si>
+    <t>You demonstrated an understanding that the manometer involves alternating mercury and water segments, which earns you credit for the basic hydrostatic principle. However, your equation setup is fundamentally incorrect: you added all pressure terms rather than properly alternating signs (adding when going down into a fluid, subtracting when going up), and your grouping of heights (e.g., using 1.2 m for mercury and 2.5 m for water) does not correctly reflect the individual segment heights from the problem. The correct mercury effective height is 1.5 m and water effective height is 1.0 m, giving ~189 kPa gauge. You lose 35 pts in Section C for incorrect equation setup and sign errors, 10 pts in Section D for incorrect algebraic grouping, 20 pts in Section E for the wrong numerical result (~205 kPa vs ~189 kPa), and 6 pts in Section F for the incorrect final answer (though units are stated correctly and partial credit is awarded for showing work).</t>
+  </si>
+  <si>
+    <t>You correctly identified the fluid densities (rho_Hg = 13,500 kg/m³ and rho_w = 980 kg/m³), which earns partial credit. However, your solution does not show a proper hydrostatic traversal equation from the vessel to the open end — you are missing the core manometer equation setup (Sections B and C), the correct algebraic rearrangement, and a valid numerical result with proper units. Your approach of computing individual pressure terms (e.g., h6·rho_Hg, h5·rho_w) without a coherent connected path through all manometer segments, and your final answer of 13,255 (with no units or gauge statement), does not reflect the correct methodology. Deductions: Section A –2 pts, Section B –10 pts, Section C –35 pts, Section D –10 pts, Section E –20 pts, Section F –10 pts, Section G –5 pts, totaling –92 pts.</t>
+  </si>
+  <si>
+    <t>Your solution page was submitted completely blank — no work, equations, or answers are present, so no credit can be awarded. Please make sure to show all calculations on your next quiz to receive partial credit.</t>
+  </si>
+  <si>
+    <t>You identified the correct heights and densities, which is a good start. However, your approach is fundamentally flawed: you multiplied each height by only rho_Hg*g (ignoring g entirely and using rho=13500 instead of rho*g), did not use water density contributions at all, did not properly set up the manometer traversal equation with correct signs and segment-by-segment pressure changes, and simply summed all terms without a physical basis — losing nearly all points in Sections B, C, D, E, and F. Specifically: -10 pts Section B (no hydrostatic traversal strategy shown), -35 pts Section C (manometer equation not set up correctly; water segments entirely missing; signs not addressed), -10 pts Section D (no algebraic isolation of P_vessel), -17 pts Section E (g=9.81 not applied; water contributions absent; final arithmetic does not yield correct result), -7 pts Section F (final answer ~8.13 kPa is far from 189 kPa; no gauge pressure statement).</t>
+  </si>
+  <si>
+    <t>You demonstrated a clear step-by-step segment traversal approach, which is the correct strategy (+10 pts for hydrostatic principle and +5 pts for clarity). However, your solution contains critical errors in height assignments and traversal direction: you used h6 for the first mercury segment (0.5 m), h5 for the first water segment (0.1 m), h4 for the second mercury segment (0.7 m), h3 for the second water segment (0.3 m), h2 for the third mercury segment (0.5 m), and then added h1 (0.4 m) as a water segment — misidentifying h1 as a water column and incorrectly including it while misassigning all height labels throughout (-20 pts Section A/C). Additionally, you appear to be traversing from the open end toward the vessel but start at the wrong reference (you begin computing from the open-end mercury column outward rather than setting P_atm = 0 at the open end), and your final answer of 56.15 kPa is far from the correct 189 kPa (-30 pts Section C, -10 pts Section D, -18 pts Section E, -5 pts Section F). The correct answer is approximately 189 kPa (gauge); please review how to assign h1–h6 from the figure and traverse consistently from vessel to atmosphere.</t>
+  </si>
+  <si>
+    <t>Excellent work! Your manometer traversal equation is perfectly set up, all height groupings are correct, and your numerical calculations lead precisely to the correct gauge pressure of 189 kPa. You clearly understood the hydrostatic principle, handled all fluid segments with correct signs, and properly identified the result as gauge pressure. Full marks!</t>
+  </si>
+  <si>
+    <t>You demonstrated some understanding of the step-by-step pressure traversal approach (Section B partial credit), but your individual segment pressure contributions appear to use incorrect heights and/or fluid densities, leading to wrong intermediate values (66.219, 1922.76, 7691.04, 52979, 79461) and a final answer of ~208.2 kPa instead of the correct ~189 kPa. Your signs are all positive throughout, which indicates you did not correctly account for pressure decreases when traversing upward through a fluid column — deducting 25 pts for Section C (incorrect segment heights/densities and missing sign changes), 10 pts for Section D (algebraic setup does not reflect correct manometer traversal), 13 pts for Section E (incorrect numerical values carried through), 5 pts for Section F (final answer ~208 kPa vs. correct ~189 kPa, though units and gauge statement are present), and 5 pts for Section G (work is partially organized but lacks clear labeling of fluids and heights). Please review the hydrostatic pressure traversal method carefully — you are on the right track with the sequential approach!</t>
+  </si>
+  <si>
+    <t>Your work shows only very early and incomplete attempts at the manometer traversal — you correctly identified that air (h1) contributes a water pressure term and attempted to involve mercury, but you did not complete a full path from vessel to the open atmosphere, missed multiple fluid segments (water and mercury legs for h3–h6), did not apply gravitational acceleration (g = 9.81 m/s²) consistently, and reached no final numerical answer or gauge pressure statement. You earn partial credit for Section A (3/10) for some correct height/fluid identification, a small portion of Section B (2/10) for showing some hydrostatic reasoning, and minimal Section C credit (3/35) for the first partial step; all other sections (D, E, F, G) receive 0. Total deductions: 92 pts.</t>
+  </si>
+  <si>
+    <t>You correctly identified all heights and fluid densities, which is a great start. However, your manometer equation setup is fundamentally incorrect — you added all pressure terms together using only positive signs without applying the correct hydrostatic traversal logic (pressure increases going down, decreases going up, with alternating signs for mercury and water segments). You also divided the total sum by 980 (water density) without physical justification, and used h1 (the air column distractor) in your calculation, which should be neglected. Additionally, your final answer of 348.05 kPa is far from the correct value of ~189 kPa. You earn points for correctly listing the given data (Section A: 6/10), recognizing fluid densities (partial Section B: 2/10), and attempting numerical calculations (partial Section E: 3/20), but lose significant credit for the incorrect equation setup (-35/35 Section C), incorrect algebra (-10/10 Section D), incorrect final answer (-7/10 Section F), and unclear physical reasoning (-5/5 Section G). Total deductions: 5 (Section A) + 8 (Section B) + 35 (Section C) + 10 (Section D) + 17 (Section E) + 7 (Section F) = 82 points deducted.</t>
+  </si>
+  <si>
+    <t>You correctly identified all given values and properly noted that h1 is an air column, but then incorrectly included h1 in your mercury height calculation — air pressure is negligible and h1 should not appear in your manometer traversal equation (-10 pts, Section C). Your manometer equation setup is fundamentally incorrect: you incorrectly grouped the water and mercury segments, using h2+h4 for water and h1+h3+h5-h6 for mercury, which does not reflect the proper hydrostatic traversal through each fluid segment (-25 pts, Section C). As a result, your mercury net height sum of 0.3 m and water sum of 1.2 m are both wrong, leading to an incorrect final answer of -28.19 kPa instead of the correct ~189 kPa (-20 pts, Sections D &amp; E). You did correctly state gauge pressure, use SI units, and show organized work, earning partial credit in Sections A, B, F, and G.</t>
+  </si>
+  <si>
+    <t>Your overall approach and manometer traversal equation are excellent — you correctly identified all fluid segments and applied hydrostatic principles properly. However, your height assignments contain some errors: you used h2-h3 = 0.2 m (correct), but assigned h4-h3 = 0.4 m instead of the correct 0.4 m — actually that appears correct; however you used h4+h5 = 0.8 m (correct) and h5+h6 = 0.6 m (correct), which are all consistent with the reference solution. The issue is in your first Mercury term: you used rho_Hg*g*h2 = 13500*9.81*0.5 = 66217.5, which is correct. Re-examining your numerical line, the arithmetic for the Mercury segment 2 shows -52,974 which corresponds to 13500*9.81*0.4 = 52,974 — correct. Your water density was written as 980 but in the equation header you wrote rho_w = 980, yet the reference uses 980 kg/m³ giving water term = 980*9.81*1.0 = 9613.8 Pa, while your calculation yields 1922.76 + 7699.04 = 9621.8 Pa (slight rounding difference — acceptable). Your final answer of 189.03 kPa (gauge) is essentially correct and within ±1% of the reference answer of 189.04 kPa. Deducting 10 pts for using rho_w = 980 instead of the specified 980 kg/m³ (no actual deduction needed here) — actually, reviewing carefully, your Section C water segment 1 uses (h2-h3) = 0.2 m but the reference gives 0.5-0.3 = 0.2 m (correct), and your equation structure matches the reference almost perfectly. The only notable issue is that your equation omits explicit mention of neglecting air column weight (h1), so deducting 3 pts for Section A/B clarity on h1 handling, and 5 pts for Section G organization/clarity since some intermediate arithmetic steps are hard to follow. Your final answer is correct and well-stated as gauge pressure — great work!</t>
+  </si>
+  <si>
+    <t>You correctly identified the fluid densities, applied the general hydrostatic traversal concept, and properly neglected the air column — these are good foundations. However, your height assignments for several segments are incorrect (e.g., using 0.4 m and 1.0 m where the correct combinations should be h2=0.5, h4-h3=0.4, h6+h5=0.6, etc.), which propagates through all segment calculations and leads to a final answer of 69.07 kPa instead of the correct ~189 kPa (-6 pts Section A, -4 pts Section B, -20 pts Section C, -6 pts Section D, -15 pts Section E, -7 pts Section F, -2 pts Section G). Please review how to carefully read heights from a multitube manometer figure and correctly identify the vertical extents of each fluid column.</t>
+  </si>
+  <si>
+    <t>You demonstrated a correct understanding of the hydrostatic traversal method and properly structured the manometer equation with the right sign conventions and fluid segments — well done on the methodology. However, your height values are significantly misread from the figure (e.g., h2=0.15 instead of 0.5 m, h3=0.13 instead of 0.3 m, h4=0.47 instead of 0.7 m, h6 not explicitly used), which caused your final answer of ~19.47 kPa to be far from the correct ~189 kPa; deducting 7 pts (Section A), 10 pts (Section C), 15 pts (Section E), and smaller deductions across other sections for a total of 44 pts off.</t>
+  </si>
+  <si>
+    <t>Your manometer traversal equation is largely correct in structure and you correctly applied the hydrostatic principle, earning strong marks for your approach. However, you made several errors: (1) you wrote ρ_water = 580 kg/m³ (should be 980 kg/m³), though your numerical calculations appear to use 980 — deducting 3 pts for the inconsistency; (2) your final mercury segment uses only h6 instead of (h6 + h5), missing the h5 contribution to that leg — deducting 6 pts across Sections A and C; (3) your final numerical result is ~175.8 kPa gauge (not 53.1), and reporting it as MPa instead of kPa is a critical unit error — deducting 10 pts for the incorrect value and 5 pts for the unit error. The correct gauge pressure is approximately 189 kPa. Keep up the good systematic work!</t>
+  </si>
+  <si>
+    <t>You show familiarity with the basic hydrostatic pressure formula (P = ρgh) and correctly identify the relevant fluids and heights, earning credit for Section A and partial credit for Section B. However, your approach treats each height segment independently and simply adds pressure contributions rather than traversing the manometer as a connected system from the vessel to the open end — this means your equation setup (Section C) does not reflect the correct multi-tube manometer traversal path, and the signs/combinations of segments are not properly accounted for, resulting in a fundamentally incorrect setup and a final answer of 167.2 kPa instead of ~189 kPa. You receive: 7/10 for Section A (heights mostly identified, SI units used), 5/10 for Section B (partial understanding of hydrostatics shown), 0/35 for Section C (no correct traversal equation written), 0/10 for Section D, 0/20 for Section E, and 0/10 for Section F (final answer inconsistent with correct method), resulting in a deduction of 88 points total. Please review how to write a single continuous pressure-balance equation traversing each fluid segment from vessel to atmosphere.</t>
+  </si>
+  <si>
+    <t>You demonstrate understanding of the hydrostatic traversal approach and correctly identify that gauge pressure is the target, which earns you credit in Sections B and F. However, your manometer equation setup has significant issues: you appear to use g = 9.8 m/s² and densities in non-SI units (rho_w ≈ 0.98 and rho_Hg ≈ 13.5 in kN/m³ context), and your traversal introduces an unknown 'h' (solving for an unknown height rather than directly computing pressure), which indicates a fundamental misapplication of the manometer equation — deducting 25 pts in Section C. Your equation setup is also missing proper segment-by-segment sign structure consistent with the reference solution, deducting 10 pts in Section D. Your final numerical answer of ~184.26 kPa is within about 2.5% of the correct 189 kPa, which earns partial credit in Section E and F, but the methodology used to arrive there (solving for an unknown height rather than P_vessel directly) is incorrect — deducting 15 pts in Section E. You correctly state gauge pressure and use kPa units (+3 pts in Section F). Overall: deductions of 25 (Section C) + 10 (Section D) + 15 (Section E) + 7 (Section A, misapplied density/unit approach) + 5 (Section G, unclear layout) = 62 pts deducted, yielding a score of 38/100.</t>
+  </si>
+  <si>
+    <t>You demonstrated awareness of the basic hydrostatic pressure formula (P = ρgh) and correctly identified the fluid densities (ρ_water = 980 kg/m³, ρ_Hg = 13500 kg/m³), earning partial credit in Sections A and B. However, your solution does not establish a proper manometer traversal equation connecting the vessel pressure to the open atmosphere — you computed individual pressure contributions for each height separately without combining them with correct signs through the multitube manometer path, which is the core of the problem (−35 pts for Section C, −10 pts for Section D). Your mercury-to-water ratio approach at the bottom appears incomplete and yields no final answer (−13 pts across Sections E and F). You lose 5 pts in Section G for overall disorganization and incompleteness. Please review the manometer traversal method: start at the vessel, add/subtract ρgh terms as you move down/up through each fluid segment, and set the result equal to atmospheric pressure (gauge = 0) at the open end.</t>
+  </si>
+  <si>
+    <t>You correctly identified the need to traverse from the vessel to the open atmosphere and properly recognized gauge vs. absolute pressure, which is a good start. However, your manometer equation has significant errors: the height combinations for each fluid segment are incorrect (e.g., you used h5=0.1 m alone for water rather than the correct composite heights like h2-h3 for the first water segment, and h4+h5 for the second), and mercury density was applied to segments that should use water density — leading to a final answer of 83.44 kPa instead of the correct ~189 kPa (gauge). Deductions: Section A -7 pts (heights misassigned), Section B -3 pts (path partially implied), Section C -25 pts (incorrect segment heights and fluid assignments), Section D -5 pts (incomplete algebraic rearrangement), Section E -15 pts (numerical errors from wrong equation), Section F -8 pts (wrong final value), Section G -2 pts (clarity).</t>
+  </si>
+  <si>
+    <t>You demonstrated a solid understanding of the traversal strategy and correctly applied hydrostatic principles segment by segment, earning good partial credit. However, your pressure path contains errors in fluid assignment around the h4 segment — you subtracted a water term for h4 and then separately added a mercury term for h4, effectively double-counting that height, which caused your final answer (176.15 kPa) to deviate from the correct value (~189 kPa); this accounts for the main deductions of approximately 14 pts in Section C, 8 pts in Section E, and 6 pts in Section F.</t>
+  </si>
+  <si>
+    <t>You correctly identified the basic hydrostatic pressure formula (ΔP = ρgh) and attempted to compute individual pressure contributions, which earns you partial credit for hydrostatic principle (Section B: 5/10). However, your approach is fundamentally flawed: you simply summed all pressure segments as positive without accounting for the signs (increases going down, decreases going up) as you traverse the manometer from vessel to open end. The correct solution requires alternating signs based on fluid direction, yielding ~189 kPa, not 265.8 kPa. You also incorrectly used h4=0.7 m and h3=0.3 m as independent mercury/water columns without the proper composite height combinations (e.g., h4−h3, h2−h3, h5+h6, h5+h4). Additionally, ΔP5 uses water density (980) but you wrote 980×9.81×0.6 — h5 should be 0.1 m, not 0.6 m (−5 pts figure interpretation). Your final gauge pressure addition step (+1) is unclear and physically unjustified. Deductions: Section A −5 (h5 misread as 0.6 m), Section B −5 (incomplete path strategy), Section C −28 (all segments treated as positive additions, incorrect height combinations), Section D −8 (no proper algebraic traversal), Section E −18 (wrong numerical result), Section F −16 (wrong final answer, gauge statement unclear), Section G −3 (disorganized presentation). Keep practicing the sign convention for manometer traversal — you're on the right track with the basic formula!</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I195"/>
+  <dimension ref="A1:I231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1267,19 +1351,19 @@
         <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D2">
         <v>901</v>
       </c>
       <c r="E2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1290,19 +1374,19 @@
         <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D3">
         <v>901</v>
       </c>
       <c r="E3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1313,19 +1397,19 @@
         <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D4">
         <v>901</v>
       </c>
       <c r="E4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1336,19 +1420,19 @@
         <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D5">
         <v>901</v>
       </c>
       <c r="E5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1359,19 +1443,19 @@
         <v>110</v>
       </c>
       <c r="C6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D6">
         <v>901</v>
       </c>
       <c r="E6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1382,19 +1466,19 @@
         <v>111</v>
       </c>
       <c r="C7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D7">
         <v>901</v>
       </c>
       <c r="E7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1405,19 +1489,19 @@
         <v>112</v>
       </c>
       <c r="C8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D8">
         <v>901</v>
       </c>
       <c r="E8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1428,19 +1512,19 @@
         <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D9">
         <v>901</v>
       </c>
       <c r="E9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1451,19 +1535,19 @@
         <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D10">
         <v>901</v>
       </c>
       <c r="E10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1474,19 +1558,19 @@
         <v>115</v>
       </c>
       <c r="C11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D11">
         <v>901</v>
       </c>
       <c r="E11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1497,19 +1581,19 @@
         <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D12">
         <v>901</v>
       </c>
       <c r="E12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1520,19 +1604,19 @@
         <v>117</v>
       </c>
       <c r="C13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D13">
         <v>901</v>
       </c>
       <c r="E13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1543,19 +1627,19 @@
         <v>118</v>
       </c>
       <c r="C14" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D14">
         <v>901</v>
       </c>
       <c r="E14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1566,19 +1650,19 @@
         <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D15">
         <v>901</v>
       </c>
       <c r="E15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1589,19 +1673,19 @@
         <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D16">
         <v>901</v>
       </c>
       <c r="E16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1612,19 +1696,19 @@
         <v>121</v>
       </c>
       <c r="C17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D17">
         <v>901</v>
       </c>
       <c r="E17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1635,19 +1719,19 @@
         <v>122</v>
       </c>
       <c r="C18" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D18">
         <v>901</v>
       </c>
       <c r="E18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F18" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1658,19 +1742,19 @@
         <v>123</v>
       </c>
       <c r="C19" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D19">
         <v>901</v>
       </c>
       <c r="E19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F19" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1681,19 +1765,19 @@
         <v>124</v>
       </c>
       <c r="C20" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D20">
         <v>901</v>
       </c>
       <c r="E20" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F20" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G20" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1704,19 +1788,19 @@
         <v>125</v>
       </c>
       <c r="C21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D21">
         <v>901</v>
       </c>
       <c r="E21" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G21" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1727,19 +1811,19 @@
         <v>126</v>
       </c>
       <c r="C22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D22">
         <v>901</v>
       </c>
       <c r="E22" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G22" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1750,19 +1834,19 @@
         <v>127</v>
       </c>
       <c r="C23" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D23">
         <v>901</v>
       </c>
       <c r="E23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F23" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1773,19 +1857,19 @@
         <v>128</v>
       </c>
       <c r="C24" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D24">
         <v>901</v>
       </c>
       <c r="E24" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F24" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G24" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1796,19 +1880,19 @@
         <v>129</v>
       </c>
       <c r="C25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D25">
         <v>901</v>
       </c>
       <c r="E25" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F25" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G25" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1819,19 +1903,19 @@
         <v>130</v>
       </c>
       <c r="C26" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D26">
         <v>901</v>
       </c>
       <c r="E26" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F26" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G26" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1842,19 +1926,19 @@
         <v>131</v>
       </c>
       <c r="C27" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D27">
         <v>901</v>
       </c>
       <c r="E27" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F27" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G27" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1865,19 +1949,19 @@
         <v>132</v>
       </c>
       <c r="C28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D28">
         <v>901</v>
       </c>
       <c r="E28" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G28" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1888,19 +1972,19 @@
         <v>133</v>
       </c>
       <c r="C29" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D29">
         <v>901</v>
       </c>
       <c r="E29" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F29" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G29" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1911,19 +1995,19 @@
         <v>134</v>
       </c>
       <c r="C30" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D30">
         <v>901</v>
       </c>
       <c r="E30" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F30" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G30" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1934,19 +2018,19 @@
         <v>135</v>
       </c>
       <c r="C31" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D31">
         <v>901</v>
       </c>
       <c r="E31" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G31" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1957,19 +2041,19 @@
         <v>136</v>
       </c>
       <c r="C32" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D32">
         <v>901</v>
       </c>
       <c r="E32" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F32" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1980,19 +2064,19 @@
         <v>137</v>
       </c>
       <c r="C33" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D33">
         <v>901</v>
       </c>
       <c r="E33" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F33" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G33" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2003,19 +2087,19 @@
         <v>138</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D34">
         <v>901</v>
       </c>
       <c r="E34" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F34" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G34" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2026,19 +2110,19 @@
         <v>139</v>
       </c>
       <c r="C35" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D35">
         <v>901</v>
       </c>
       <c r="E35" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F35" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G35" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2049,19 +2133,19 @@
         <v>140</v>
       </c>
       <c r="C36" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D36">
         <v>901</v>
       </c>
       <c r="E36" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F36" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G36" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2072,19 +2156,19 @@
         <v>141</v>
       </c>
       <c r="C37" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D37">
         <v>902</v>
       </c>
       <c r="E37" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F37" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G37" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2095,19 +2179,19 @@
         <v>142</v>
       </c>
       <c r="C38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D38">
         <v>902</v>
       </c>
       <c r="E38" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F38" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G38" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2118,19 +2202,19 @@
         <v>143</v>
       </c>
       <c r="C39" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D39">
         <v>902</v>
       </c>
       <c r="E39" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G39" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2141,19 +2225,19 @@
         <v>144</v>
       </c>
       <c r="C40" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D40">
         <v>902</v>
       </c>
       <c r="E40" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F40" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G40" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2164,19 +2248,19 @@
         <v>145</v>
       </c>
       <c r="C41" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D41">
         <v>902</v>
       </c>
       <c r="E41" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F41" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G41" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2187,19 +2271,19 @@
         <v>146</v>
       </c>
       <c r="C42" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D42">
         <v>902</v>
       </c>
       <c r="E42" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F42" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G42" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2210,19 +2294,19 @@
         <v>147</v>
       </c>
       <c r="C43" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D43">
         <v>902</v>
       </c>
       <c r="E43" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F43" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G43" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2233,19 +2317,19 @@
         <v>148</v>
       </c>
       <c r="C44" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D44">
         <v>902</v>
       </c>
       <c r="E44" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F44" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G44" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2256,19 +2340,19 @@
         <v>149</v>
       </c>
       <c r="C45" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D45">
         <v>902</v>
       </c>
       <c r="E45" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F45" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G45" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2279,19 +2363,19 @@
         <v>150</v>
       </c>
       <c r="C46" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D46">
         <v>902</v>
       </c>
       <c r="E46" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F46" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G46" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2302,19 +2386,19 @@
         <v>151</v>
       </c>
       <c r="C47" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D47">
         <v>902</v>
       </c>
       <c r="E47" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F47" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G47" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2325,19 +2409,19 @@
         <v>152</v>
       </c>
       <c r="C48" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D48">
         <v>902</v>
       </c>
       <c r="E48" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F48" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G48" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2348,19 +2432,19 @@
         <v>153</v>
       </c>
       <c r="C49" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D49">
         <v>902</v>
       </c>
       <c r="E49" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F49" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G49" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2371,19 +2455,19 @@
         <v>154</v>
       </c>
       <c r="C50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D50">
         <v>902</v>
       </c>
       <c r="E50" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F50" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G50" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2394,19 +2478,19 @@
         <v>155</v>
       </c>
       <c r="C51" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D51">
         <v>902</v>
       </c>
       <c r="E51" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F51" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G51" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2417,19 +2501,19 @@
         <v>156</v>
       </c>
       <c r="C52" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D52">
         <v>902</v>
       </c>
       <c r="E52" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F52" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G52" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2440,19 +2524,19 @@
         <v>157</v>
       </c>
       <c r="C53" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D53">
         <v>902</v>
       </c>
       <c r="E53" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F53" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G53" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2463,19 +2547,19 @@
         <v>158</v>
       </c>
       <c r="C54" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D54">
         <v>902</v>
       </c>
       <c r="E54" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F54" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G54" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2486,19 +2570,19 @@
         <v>159</v>
       </c>
       <c r="C55" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D55">
         <v>902</v>
       </c>
       <c r="E55" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F55" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G55" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2509,19 +2593,19 @@
         <v>160</v>
       </c>
       <c r="C56" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D56">
         <v>902</v>
       </c>
       <c r="E56" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F56" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G56" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2532,19 +2616,19 @@
         <v>161</v>
       </c>
       <c r="C57" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D57">
         <v>902</v>
       </c>
       <c r="E57" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F57" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G57" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2555,19 +2639,19 @@
         <v>162</v>
       </c>
       <c r="C58" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D58">
         <v>902</v>
       </c>
       <c r="E58" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F58" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G58" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2578,19 +2662,19 @@
         <v>163</v>
       </c>
       <c r="C59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D59">
         <v>902</v>
       </c>
       <c r="E59" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F59" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G59" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2601,19 +2685,19 @@
         <v>164</v>
       </c>
       <c r="C60" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D60">
         <v>902</v>
       </c>
       <c r="E60" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F60" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G60" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2624,19 +2708,19 @@
         <v>165</v>
       </c>
       <c r="C61" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D61">
         <v>902</v>
       </c>
       <c r="E61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F61" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G61" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2647,19 +2731,19 @@
         <v>166</v>
       </c>
       <c r="C62" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D62">
         <v>902</v>
       </c>
       <c r="E62" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F62" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G62" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2670,19 +2754,19 @@
         <v>167</v>
       </c>
       <c r="C63" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D63">
         <v>902</v>
       </c>
       <c r="E63" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F63" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G63" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2693,19 +2777,19 @@
         <v>168</v>
       </c>
       <c r="C64" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D64">
         <v>902</v>
       </c>
       <c r="E64" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G64" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -2716,19 +2800,19 @@
         <v>169</v>
       </c>
       <c r="C65" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D65">
         <v>902</v>
       </c>
       <c r="E65" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F65" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -2739,19 +2823,19 @@
         <v>170</v>
       </c>
       <c r="C66" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D66">
         <v>902</v>
       </c>
       <c r="E66" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F66" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G66" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -2762,19 +2846,19 @@
         <v>171</v>
       </c>
       <c r="C67" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D67">
         <v>902</v>
       </c>
       <c r="E67" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F67" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G67" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -2785,19 +2869,19 @@
         <v>172</v>
       </c>
       <c r="C68" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D68">
         <v>902</v>
       </c>
       <c r="E68" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F68" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G68" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -2808,19 +2892,19 @@
         <v>173</v>
       </c>
       <c r="C69" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D69">
         <v>902</v>
       </c>
       <c r="E69" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F69" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G69" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -2831,19 +2915,19 @@
         <v>174</v>
       </c>
       <c r="C70" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D70">
         <v>902</v>
       </c>
       <c r="E70" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F70" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G70" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -2854,19 +2938,19 @@
         <v>175</v>
       </c>
       <c r="C71" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D71">
         <v>902</v>
       </c>
       <c r="E71" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F71" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G71" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -2877,19 +2961,19 @@
         <v>176</v>
       </c>
       <c r="C72" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D72">
         <v>902</v>
       </c>
       <c r="E72" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F72" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G72" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -2900,19 +2984,19 @@
         <v>177</v>
       </c>
       <c r="C73" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D73">
         <v>902</v>
       </c>
       <c r="E73" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F73" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G73" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -2923,19 +3007,19 @@
         <v>178</v>
       </c>
       <c r="C74" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D74">
         <v>902</v>
       </c>
       <c r="E74" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F74" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G74" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -2946,19 +3030,19 @@
         <v>179</v>
       </c>
       <c r="C75" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D75">
         <v>902</v>
       </c>
       <c r="E75" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F75" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G75" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -2969,25 +3053,25 @@
         <v>106</v>
       </c>
       <c r="C76" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D76">
         <v>901</v>
       </c>
       <c r="E76" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F76" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G76" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H76">
         <v>23</v>
       </c>
       <c r="I76" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -2998,22 +3082,22 @@
         <v>146</v>
       </c>
       <c r="C77" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D77">
         <v>901</v>
       </c>
       <c r="E77" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F77" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G77" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I77" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -3024,25 +3108,25 @@
         <v>147</v>
       </c>
       <c r="C78" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D78">
         <v>901</v>
       </c>
       <c r="E78" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F78" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G78" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H78">
         <v>100</v>
       </c>
       <c r="I78" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -3053,25 +3137,25 @@
         <v>180</v>
       </c>
       <c r="C79" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D79">
         <v>901</v>
       </c>
       <c r="E79" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F79" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G79" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H79">
         <v>26</v>
       </c>
       <c r="I79" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -3082,25 +3166,25 @@
         <v>117</v>
       </c>
       <c r="C80" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D80">
         <v>901</v>
       </c>
       <c r="E80" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F80" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G80" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H80">
         <v>10</v>
       </c>
       <c r="I80" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -3111,25 +3195,25 @@
         <v>181</v>
       </c>
       <c r="C81" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D81">
         <v>901</v>
       </c>
       <c r="E81" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F81" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G81" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H81">
         <v>100</v>
       </c>
       <c r="I81" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -3140,22 +3224,22 @@
         <v>119</v>
       </c>
       <c r="C82" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D82">
         <v>901</v>
       </c>
       <c r="E82" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F82" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G82" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I82" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -3166,25 +3250,25 @@
         <v>120</v>
       </c>
       <c r="C83" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D83">
         <v>901</v>
       </c>
       <c r="E83" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F83" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G83" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H83">
         <v>5</v>
       </c>
       <c r="I83" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -3195,25 +3279,25 @@
         <v>149</v>
       </c>
       <c r="C84" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D84">
         <v>901</v>
       </c>
       <c r="E84" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F84" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G84" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H84">
         <v>15</v>
       </c>
       <c r="I84" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -3224,22 +3308,22 @@
         <v>182</v>
       </c>
       <c r="C85" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D85">
         <v>901</v>
       </c>
       <c r="E85" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F85" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G85" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I85" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -3250,22 +3334,22 @@
         <v>183</v>
       </c>
       <c r="C86" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D86">
         <v>901</v>
       </c>
       <c r="E86" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F86" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G86" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I86" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -3276,25 +3360,25 @@
         <v>184</v>
       </c>
       <c r="C87" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D87">
         <v>901</v>
       </c>
       <c r="E87" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F87" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G87" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H87">
         <v>100</v>
       </c>
       <c r="I87" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -3305,25 +3389,25 @@
         <v>150</v>
       </c>
       <c r="C88" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D88">
         <v>901</v>
       </c>
       <c r="E88" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F88" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G88" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H88">
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -3334,22 +3418,22 @@
         <v>152</v>
       </c>
       <c r="C89" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D89">
         <v>901</v>
       </c>
       <c r="E89" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F89" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G89" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I89" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -3360,22 +3444,22 @@
         <v>185</v>
       </c>
       <c r="C90" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D90">
         <v>901</v>
       </c>
       <c r="E90" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F90" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G90" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I90" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -3386,25 +3470,25 @@
         <v>155</v>
       </c>
       <c r="C91" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D91">
         <v>901</v>
       </c>
       <c r="E91" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F91" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G91" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H91">
         <v>100</v>
       </c>
       <c r="I91" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -3415,25 +3499,25 @@
         <v>125</v>
       </c>
       <c r="C92" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D92">
         <v>901</v>
       </c>
       <c r="E92" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F92" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G92" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H92">
         <v>16</v>
       </c>
       <c r="I92" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -3444,25 +3528,25 @@
         <v>126</v>
       </c>
       <c r="C93" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D93">
         <v>901</v>
       </c>
       <c r="E93" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F93" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G93" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H93">
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -3473,25 +3557,25 @@
         <v>186</v>
       </c>
       <c r="C94" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D94">
         <v>901</v>
       </c>
       <c r="E94" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F94" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G94" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H94">
         <v>5</v>
       </c>
       <c r="I94" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -3502,25 +3586,25 @@
         <v>160</v>
       </c>
       <c r="C95" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D95">
         <v>901</v>
       </c>
       <c r="E95" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F95" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G95" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H95">
         <v>25</v>
       </c>
       <c r="I95" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -3531,25 +3615,25 @@
         <v>161</v>
       </c>
       <c r="C96" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D96">
         <v>901</v>
       </c>
       <c r="E96" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F96" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G96" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H96">
         <v>75</v>
       </c>
       <c r="I96" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -3560,25 +3644,25 @@
         <v>187</v>
       </c>
       <c r="C97" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D97">
         <v>901</v>
       </c>
       <c r="E97" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F97" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G97" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H97">
         <v>100</v>
       </c>
       <c r="I97" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -3589,22 +3673,22 @@
         <v>130</v>
       </c>
       <c r="C98" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D98">
         <v>901</v>
       </c>
       <c r="E98" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F98" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G98" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I98" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -3615,25 +3699,25 @@
         <v>162</v>
       </c>
       <c r="C99" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D99">
         <v>901</v>
       </c>
       <c r="E99" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F99" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G99" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H99">
         <v>22</v>
       </c>
       <c r="I99" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -3644,25 +3728,25 @@
         <v>164</v>
       </c>
       <c r="C100" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D100">
         <v>901</v>
       </c>
       <c r="E100" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F100" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G100" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H100">
         <v>100</v>
       </c>
       <c r="I100" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -3673,22 +3757,22 @@
         <v>165</v>
       </c>
       <c r="C101" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D101">
         <v>901</v>
       </c>
       <c r="E101" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F101" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G101" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I101" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -3699,25 +3783,25 @@
         <v>167</v>
       </c>
       <c r="C102" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D102">
         <v>901</v>
       </c>
       <c r="E102" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F102" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G102" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H102">
         <v>18</v>
       </c>
       <c r="I102" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -3728,25 +3812,25 @@
         <v>132</v>
       </c>
       <c r="C103" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D103">
         <v>901</v>
       </c>
       <c r="E103" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F103" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G103" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H103">
         <v>100</v>
       </c>
       <c r="I103" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -3757,25 +3841,25 @@
         <v>133</v>
       </c>
       <c r="C104" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D104">
         <v>901</v>
       </c>
       <c r="E104" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F104" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G104" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H104">
         <v>98</v>
       </c>
       <c r="I104" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -3786,25 +3870,25 @@
         <v>134</v>
       </c>
       <c r="C105" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D105">
         <v>901</v>
       </c>
       <c r="E105" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F105" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G105" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H105">
         <v>97</v>
       </c>
       <c r="I105" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -3815,25 +3899,25 @@
         <v>170</v>
       </c>
       <c r="C106" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D106">
         <v>901</v>
       </c>
       <c r="E106" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F106" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G106" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H106">
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -3844,25 +3928,25 @@
         <v>188</v>
       </c>
       <c r="C107" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D107">
         <v>901</v>
       </c>
       <c r="E107" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F107" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G107" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H107">
         <v>86</v>
       </c>
       <c r="I107" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -3873,25 +3957,25 @@
         <v>189</v>
       </c>
       <c r="C108" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D108">
         <v>901</v>
       </c>
       <c r="E108" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F108" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G108" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H108">
         <v>5</v>
       </c>
       <c r="I108" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -3902,25 +3986,25 @@
         <v>171</v>
       </c>
       <c r="C109" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D109">
         <v>901</v>
       </c>
       <c r="E109" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F109" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G109" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H109">
         <v>93</v>
       </c>
       <c r="I109" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -3931,25 +4015,25 @@
         <v>172</v>
       </c>
       <c r="C110" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D110">
         <v>901</v>
       </c>
       <c r="E110" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F110" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G110" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H110">
         <v>25</v>
       </c>
       <c r="I110" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -3960,25 +4044,25 @@
         <v>190</v>
       </c>
       <c r="C111" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D111">
         <v>901</v>
       </c>
       <c r="E111" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F111" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G111" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H111">
         <v>5</v>
       </c>
       <c r="I111" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -3989,22 +4073,22 @@
         <v>191</v>
       </c>
       <c r="C112" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D112">
         <v>901</v>
       </c>
       <c r="E112" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F112" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G112" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I112" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -4015,25 +4099,25 @@
         <v>135</v>
       </c>
       <c r="C113" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D113">
         <v>901</v>
       </c>
       <c r="E113" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F113" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G113" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H113">
         <v>5</v>
       </c>
       <c r="I113" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -4044,25 +4128,25 @@
         <v>136</v>
       </c>
       <c r="C114" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D114">
         <v>901</v>
       </c>
       <c r="E114" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F114" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G114" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H114">
         <v>0</v>
       </c>
       <c r="I114" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -4073,25 +4157,25 @@
         <v>138</v>
       </c>
       <c r="C115" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D115">
         <v>901</v>
       </c>
       <c r="E115" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F115" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G115" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H115">
         <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -4102,25 +4186,25 @@
         <v>173</v>
       </c>
       <c r="C116" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D116">
         <v>901</v>
       </c>
       <c r="E116" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F116" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G116" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H116">
         <v>20</v>
       </c>
       <c r="I116" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -4131,22 +4215,22 @@
         <v>192</v>
       </c>
       <c r="C117" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D117">
         <v>901</v>
       </c>
       <c r="E117" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F117" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G117" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I117" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -4157,22 +4241,22 @@
         <v>175</v>
       </c>
       <c r="C118" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D118">
         <v>901</v>
       </c>
       <c r="E118" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F118" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G118" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I118" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -4183,25 +4267,25 @@
         <v>176</v>
       </c>
       <c r="C119" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D119">
         <v>901</v>
       </c>
       <c r="E119" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F119" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G119" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H119">
         <v>20</v>
       </c>
       <c r="I119" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -4212,25 +4296,25 @@
         <v>177</v>
       </c>
       <c r="C120" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D120">
         <v>901</v>
       </c>
       <c r="E120" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F120" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G120" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H120">
         <v>25</v>
       </c>
       <c r="I120" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -4241,25 +4325,25 @@
         <v>178</v>
       </c>
       <c r="C121" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D121">
         <v>901</v>
       </c>
       <c r="E121" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F121" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G121" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H121">
         <v>95</v>
       </c>
       <c r="I121" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -4270,22 +4354,22 @@
         <v>142</v>
       </c>
       <c r="C122" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D122">
         <v>902</v>
       </c>
       <c r="E122" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F122" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G122" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I122" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -4296,22 +4380,22 @@
         <v>108</v>
       </c>
       <c r="C123" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D123">
         <v>902</v>
       </c>
       <c r="E123" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F123" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G123" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I123" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -4322,25 +4406,25 @@
         <v>109</v>
       </c>
       <c r="C124" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D124">
         <v>902</v>
       </c>
       <c r="E124" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F124" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G124" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H124">
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -4351,22 +4435,22 @@
         <v>143</v>
       </c>
       <c r="C125" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D125">
         <v>902</v>
       </c>
       <c r="E125" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F125" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G125" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I125" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -4377,22 +4461,22 @@
         <v>145</v>
       </c>
       <c r="C126" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D126">
         <v>902</v>
       </c>
       <c r="E126" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F126" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G126" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I126" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -4403,22 +4487,22 @@
         <v>111</v>
       </c>
       <c r="C127" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D127">
         <v>902</v>
       </c>
       <c r="E127" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F127" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G127" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I127" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -4429,25 +4513,25 @@
         <v>193</v>
       </c>
       <c r="C128" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D128">
         <v>902</v>
       </c>
       <c r="E128" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F128" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G128" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H128">
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -4458,22 +4542,22 @@
         <v>113</v>
       </c>
       <c r="C129" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D129">
         <v>902</v>
       </c>
       <c r="E129" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F129" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G129" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I129" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -4484,22 +4568,22 @@
         <v>148</v>
       </c>
       <c r="C130" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D130">
         <v>902</v>
       </c>
       <c r="E130" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F130" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G130" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I130" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -4510,22 +4594,22 @@
         <v>194</v>
       </c>
       <c r="C131" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D131">
         <v>902</v>
       </c>
       <c r="E131" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F131" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G131" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I131" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -4536,25 +4620,25 @@
         <v>195</v>
       </c>
       <c r="C132" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D132">
         <v>902</v>
       </c>
       <c r="E132" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F132" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G132" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H132">
         <v>17</v>
       </c>
       <c r="I132" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -4565,25 +4649,25 @@
         <v>196</v>
       </c>
       <c r="C133" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D133">
         <v>902</v>
       </c>
       <c r="E133" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F133" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G133" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H133">
         <v>0</v>
       </c>
       <c r="I133" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -4594,22 +4678,22 @@
         <v>114</v>
       </c>
       <c r="C134" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D134">
         <v>902</v>
       </c>
       <c r="E134" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F134" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G134" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I134" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -4620,22 +4704,22 @@
         <v>115</v>
       </c>
       <c r="C135" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D135">
         <v>902</v>
       </c>
       <c r="E135" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F135" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G135" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I135" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -4646,25 +4730,25 @@
         <v>197</v>
       </c>
       <c r="C136" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D136">
         <v>902</v>
       </c>
       <c r="E136" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F136" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G136" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H136">
         <v>100</v>
       </c>
       <c r="I136" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -4675,25 +4759,25 @@
         <v>198</v>
       </c>
       <c r="C137" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D137">
         <v>902</v>
       </c>
       <c r="E137" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F137" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G137" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H137">
         <v>97</v>
       </c>
       <c r="I137" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -4704,22 +4788,22 @@
         <v>116</v>
       </c>
       <c r="C138" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D138">
         <v>902</v>
       </c>
       <c r="E138" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F138" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G138" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I138" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -4730,25 +4814,25 @@
         <v>199</v>
       </c>
       <c r="C139" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D139">
         <v>902</v>
       </c>
       <c r="E139" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F139" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G139" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H139">
         <v>5</v>
       </c>
       <c r="I139" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -4759,25 +4843,25 @@
         <v>118</v>
       </c>
       <c r="C140" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D140">
         <v>902</v>
       </c>
       <c r="E140" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F140" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G140" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H140">
         <v>5</v>
       </c>
       <c r="I140" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -4788,22 +4872,22 @@
         <v>122</v>
       </c>
       <c r="C141" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D141">
         <v>902</v>
       </c>
       <c r="E141" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F141" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G141" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I141" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -4814,25 +4898,25 @@
         <v>153</v>
       </c>
       <c r="C142" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D142">
         <v>902</v>
       </c>
       <c r="E142" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F142" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G142" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H142">
         <v>0</v>
       </c>
       <c r="I142" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -4843,25 +4927,25 @@
         <v>124</v>
       </c>
       <c r="C143" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D143">
         <v>902</v>
       </c>
       <c r="E143" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F143" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G143" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H143">
         <v>30</v>
       </c>
       <c r="I143" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -4872,25 +4956,25 @@
         <v>200</v>
       </c>
       <c r="C144" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D144">
         <v>902</v>
       </c>
       <c r="E144" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F144" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G144" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H144">
         <v>95</v>
       </c>
       <c r="I144" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -4901,25 +4985,25 @@
         <v>157</v>
       </c>
       <c r="C145" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D145">
         <v>902</v>
       </c>
       <c r="E145" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F145" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G145" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H145">
         <v>0</v>
       </c>
       <c r="I145" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -4930,25 +5014,25 @@
         <v>158</v>
       </c>
       <c r="C146" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D146">
         <v>902</v>
       </c>
       <c r="E146" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F146" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G146" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H146">
         <v>48</v>
       </c>
       <c r="I146" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -4959,25 +5043,25 @@
         <v>201</v>
       </c>
       <c r="C147" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D147">
         <v>902</v>
       </c>
       <c r="E147" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F147" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G147" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H147">
         <v>5</v>
       </c>
       <c r="I147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -4988,22 +5072,22 @@
         <v>128</v>
       </c>
       <c r="C148" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D148">
         <v>902</v>
       </c>
       <c r="E148" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F148" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G148" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I148" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -5014,25 +5098,25 @@
         <v>159</v>
       </c>
       <c r="C149" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D149">
         <v>902</v>
       </c>
       <c r="E149" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F149" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G149" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H149">
         <v>95</v>
       </c>
       <c r="I149" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -5043,22 +5127,22 @@
         <v>163</v>
       </c>
       <c r="C150" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D150">
         <v>902</v>
       </c>
       <c r="E150" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F150" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G150" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I150" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -5069,22 +5153,22 @@
         <v>166</v>
       </c>
       <c r="C151" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D151">
         <v>902</v>
       </c>
       <c r="E151" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F151" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G151" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I151" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -5095,25 +5179,25 @@
         <v>169</v>
       </c>
       <c r="C152" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D152">
         <v>902</v>
       </c>
       <c r="E152" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F152" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G152" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H152">
         <v>15</v>
       </c>
       <c r="I152" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -5124,25 +5208,25 @@
         <v>139</v>
       </c>
       <c r="C153" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D153">
         <v>902</v>
       </c>
       <c r="E153" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F153" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G153" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H153">
         <v>12</v>
       </c>
       <c r="I153" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -5153,25 +5237,25 @@
         <v>202</v>
       </c>
       <c r="C154" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D154">
         <v>902</v>
       </c>
       <c r="E154" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F154" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G154" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H154">
         <v>5</v>
       </c>
       <c r="I154" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -5182,25 +5266,25 @@
         <v>140</v>
       </c>
       <c r="C155" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D155">
         <v>902</v>
       </c>
       <c r="E155" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F155" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G155" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H155">
         <v>0</v>
       </c>
       <c r="I155" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -5211,25 +5295,25 @@
         <v>179</v>
       </c>
       <c r="C156" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D156">
         <v>902</v>
       </c>
       <c r="E156" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F156" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G156" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H156">
         <v>10</v>
       </c>
       <c r="I156" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -5240,22 +5324,22 @@
         <v>141</v>
       </c>
       <c r="C157" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D157">
         <v>902</v>
       </c>
       <c r="E157" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F157" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G157" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I157" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -5266,22 +5350,22 @@
         <v>142</v>
       </c>
       <c r="C158" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D158">
         <v>902</v>
       </c>
       <c r="E158" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F158" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G158" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I158" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -5292,22 +5376,22 @@
         <v>143</v>
       </c>
       <c r="C159" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D159">
         <v>902</v>
       </c>
       <c r="E159" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F159" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G159" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I159" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -5318,25 +5402,25 @@
         <v>144</v>
       </c>
       <c r="C160" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D160">
         <v>902</v>
       </c>
       <c r="E160" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F160" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G160" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H160">
         <v>18</v>
       </c>
       <c r="I160" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -5347,25 +5431,25 @@
         <v>145</v>
       </c>
       <c r="C161" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D161">
         <v>902</v>
       </c>
       <c r="E161" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F161" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G161" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H161">
         <v>22</v>
       </c>
       <c r="I161" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -5376,22 +5460,22 @@
         <v>146</v>
       </c>
       <c r="C162" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D162">
         <v>902</v>
       </c>
       <c r="E162" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F162" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G162" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I162" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -5402,25 +5486,25 @@
         <v>147</v>
       </c>
       <c r="C163" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D163">
         <v>902</v>
       </c>
       <c r="E163" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F163" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G163" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H163">
         <v>22</v>
       </c>
       <c r="I163" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -5431,22 +5515,22 @@
         <v>148</v>
       </c>
       <c r="C164" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D164">
         <v>902</v>
       </c>
       <c r="E164" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F164" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G164" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I164" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -5457,25 +5541,25 @@
         <v>149</v>
       </c>
       <c r="C165" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D165">
         <v>902</v>
       </c>
       <c r="E165" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F165" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G165" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H165">
         <v>18</v>
       </c>
       <c r="I165" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -5486,25 +5570,25 @@
         <v>150</v>
       </c>
       <c r="C166" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D166">
         <v>902</v>
       </c>
       <c r="E166" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F166" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G166" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H166">
         <v>18</v>
       </c>
       <c r="I166" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -5515,25 +5599,25 @@
         <v>151</v>
       </c>
       <c r="C167" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D167">
         <v>902</v>
       </c>
       <c r="E167" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F167" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G167" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H167">
         <v>75</v>
       </c>
       <c r="I167" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -5544,22 +5628,22 @@
         <v>152</v>
       </c>
       <c r="C168" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D168">
         <v>902</v>
       </c>
       <c r="E168" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F168" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G168" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I168" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -5570,25 +5654,25 @@
         <v>153</v>
       </c>
       <c r="C169" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D169">
         <v>902</v>
       </c>
       <c r="E169" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F169" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G169" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H169">
         <v>0</v>
       </c>
       <c r="I169" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -5599,22 +5683,22 @@
         <v>154</v>
       </c>
       <c r="C170" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D170">
         <v>902</v>
       </c>
       <c r="E170" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F170" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G170" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I170" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -5625,25 +5709,25 @@
         <v>155</v>
       </c>
       <c r="C171" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D171">
         <v>902</v>
       </c>
       <c r="E171" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F171" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G171" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H171">
         <v>62</v>
       </c>
       <c r="I171" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -5654,25 +5738,25 @@
         <v>156</v>
       </c>
       <c r="C172" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D172">
         <v>902</v>
       </c>
       <c r="E172" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F172" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G172" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H172">
         <v>38</v>
       </c>
       <c r="I172" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -5683,25 +5767,25 @@
         <v>157</v>
       </c>
       <c r="C173" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D173">
         <v>902</v>
       </c>
       <c r="E173" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F173" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G173" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H173">
         <v>52</v>
       </c>
       <c r="I173" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -5712,25 +5796,25 @@
         <v>158</v>
       </c>
       <c r="C174" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D174">
         <v>902</v>
       </c>
       <c r="E174" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F174" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G174" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H174">
         <v>12</v>
       </c>
       <c r="I174" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -5741,25 +5825,25 @@
         <v>159</v>
       </c>
       <c r="C175" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D175">
         <v>902</v>
       </c>
       <c r="E175" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F175" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G175" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H175">
         <v>87</v>
       </c>
       <c r="I175" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -5770,25 +5854,25 @@
         <v>160</v>
       </c>
       <c r="C176" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D176">
         <v>902</v>
       </c>
       <c r="E176" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F176" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G176" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H176">
         <v>73</v>
       </c>
       <c r="I176" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -5799,25 +5883,25 @@
         <v>161</v>
       </c>
       <c r="C177" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D177">
         <v>902</v>
       </c>
       <c r="E177" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F177" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G177" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H177">
         <v>38</v>
       </c>
       <c r="I177" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -5828,25 +5912,25 @@
         <v>162</v>
       </c>
       <c r="C178" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D178">
         <v>902</v>
       </c>
       <c r="E178" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F178" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G178" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H178">
         <v>32</v>
       </c>
       <c r="I178" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -5857,25 +5941,25 @@
         <v>163</v>
       </c>
       <c r="C179" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D179">
         <v>902</v>
       </c>
       <c r="E179" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F179" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G179" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H179">
         <v>72</v>
       </c>
       <c r="I179" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -5886,25 +5970,25 @@
         <v>164</v>
       </c>
       <c r="C180" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D180">
         <v>902</v>
       </c>
       <c r="E180" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F180" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G180" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H180">
         <v>30</v>
       </c>
       <c r="I180" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -5915,25 +5999,25 @@
         <v>165</v>
       </c>
       <c r="C181" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D181">
         <v>902</v>
       </c>
       <c r="E181" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F181" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G181" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H181">
         <v>18</v>
       </c>
       <c r="I181" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -5944,25 +6028,25 @@
         <v>166</v>
       </c>
       <c r="C182" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D182">
         <v>902</v>
       </c>
       <c r="E182" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F182" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G182" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H182">
         <v>38</v>
       </c>
       <c r="I182" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -5973,25 +6057,25 @@
         <v>167</v>
       </c>
       <c r="C183" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D183">
         <v>902</v>
       </c>
       <c r="E183" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F183" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G183" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H183">
         <v>89</v>
       </c>
       <c r="I183" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -6002,22 +6086,22 @@
         <v>168</v>
       </c>
       <c r="C184" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D184">
         <v>902</v>
       </c>
       <c r="E184" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F184" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G184" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I184" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -6028,22 +6112,22 @@
         <v>169</v>
       </c>
       <c r="C185" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D185">
         <v>902</v>
       </c>
       <c r="E185" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F185" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G185" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I185" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -6054,25 +6138,25 @@
         <v>170</v>
       </c>
       <c r="C186" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D186">
         <v>902</v>
       </c>
       <c r="E186" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F186" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G186" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H186">
         <v>19</v>
       </c>
       <c r="I186" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -6083,25 +6167,25 @@
         <v>171</v>
       </c>
       <c r="C187" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D187">
         <v>902</v>
       </c>
       <c r="E187" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F187" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G187" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H187">
         <v>28</v>
       </c>
       <c r="I187" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -6112,25 +6196,25 @@
         <v>172</v>
       </c>
       <c r="C188" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D188">
         <v>902</v>
       </c>
       <c r="E188" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F188" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G188" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H188">
         <v>72</v>
       </c>
       <c r="I188" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -6141,25 +6225,25 @@
         <v>173</v>
       </c>
       <c r="C189" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D189">
         <v>902</v>
       </c>
       <c r="E189" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F189" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G189" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H189">
         <v>62</v>
       </c>
       <c r="I189" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -6170,22 +6254,22 @@
         <v>174</v>
       </c>
       <c r="C190" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D190">
         <v>902</v>
       </c>
       <c r="E190" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F190" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G190" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I190" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -6196,22 +6280,22 @@
         <v>175</v>
       </c>
       <c r="C191" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D191">
         <v>902</v>
       </c>
       <c r="E191" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F191" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G191" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I191" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -6222,25 +6306,25 @@
         <v>176</v>
       </c>
       <c r="C192" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D192">
         <v>902</v>
       </c>
       <c r="E192" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F192" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G192" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H192">
         <v>18</v>
       </c>
       <c r="I192" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -6251,25 +6335,25 @@
         <v>177</v>
       </c>
       <c r="C193" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D193">
         <v>902</v>
       </c>
       <c r="E193" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F193" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G193" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H193">
         <v>22</v>
       </c>
       <c r="I193" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -6280,25 +6364,25 @@
         <v>178</v>
       </c>
       <c r="C194" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D194">
         <v>902</v>
       </c>
       <c r="E194" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F194" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G194" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H194">
         <v>70</v>
       </c>
       <c r="I194" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -6309,25 +6393,1042 @@
         <v>179</v>
       </c>
       <c r="C195" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D195">
         <v>902</v>
       </c>
       <c r="E195" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F195" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G195" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H195">
         <v>28</v>
       </c>
       <c r="I195" t="s">
-        <v>293</v>
+        <v>294</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
+      <c r="A196">
+        <v>1903274</v>
+      </c>
+      <c r="B196" t="s">
+        <v>106</v>
+      </c>
+      <c r="C196" t="s">
+        <v>204</v>
+      </c>
+      <c r="D196">
+        <v>901</v>
+      </c>
+      <c r="E196" t="s">
+        <v>207</v>
+      </c>
+      <c r="F196" t="s">
+        <v>209</v>
+      </c>
+      <c r="G196" t="s">
+        <v>211</v>
+      </c>
+      <c r="H196">
+        <v>100</v>
+      </c>
+      <c r="I196" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
+      <c r="A197">
+        <v>2003052</v>
+      </c>
+      <c r="B197" t="s">
+        <v>107</v>
+      </c>
+      <c r="C197" t="s">
+        <v>204</v>
+      </c>
+      <c r="D197">
+        <v>901</v>
+      </c>
+      <c r="E197" t="s">
+        <v>207</v>
+      </c>
+      <c r="F197" t="s">
+        <v>209</v>
+      </c>
+      <c r="G197" t="s">
+        <v>211</v>
+      </c>
+      <c r="H197">
+        <v>50</v>
+      </c>
+      <c r="I197" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
+      <c r="A198">
+        <v>2100421</v>
+      </c>
+      <c r="B198" t="s">
+        <v>108</v>
+      </c>
+      <c r="C198" t="s">
+        <v>204</v>
+      </c>
+      <c r="D198">
+        <v>901</v>
+      </c>
+      <c r="E198" t="s">
+        <v>207</v>
+      </c>
+      <c r="F198" t="s">
+        <v>208</v>
+      </c>
+      <c r="G198" t="s">
+        <v>211</v>
+      </c>
+      <c r="I198" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
+      <c r="A199">
+        <v>2101613</v>
+      </c>
+      <c r="B199" t="s">
+        <v>109</v>
+      </c>
+      <c r="C199" t="s">
+        <v>204</v>
+      </c>
+      <c r="D199">
+        <v>901</v>
+      </c>
+      <c r="E199" t="s">
+        <v>207</v>
+      </c>
+      <c r="F199" t="s">
+        <v>209</v>
+      </c>
+      <c r="G199" t="s">
+        <v>211</v>
+      </c>
+      <c r="H199">
+        <v>18</v>
+      </c>
+      <c r="I199" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
+      <c r="A200">
+        <v>2105067</v>
+      </c>
+      <c r="B200" t="s">
+        <v>110</v>
+      </c>
+      <c r="C200" t="s">
+        <v>204</v>
+      </c>
+      <c r="D200">
+        <v>901</v>
+      </c>
+      <c r="E200" t="s">
+        <v>207</v>
+      </c>
+      <c r="F200" t="s">
+        <v>209</v>
+      </c>
+      <c r="G200" t="s">
+        <v>211</v>
+      </c>
+      <c r="H200">
+        <v>18</v>
+      </c>
+      <c r="I200" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
+      <c r="A201">
+        <v>2105541</v>
+      </c>
+      <c r="B201" t="s">
+        <v>203</v>
+      </c>
+      <c r="C201" t="s">
+        <v>204</v>
+      </c>
+      <c r="D201">
+        <v>901</v>
+      </c>
+      <c r="E201" t="s">
+        <v>207</v>
+      </c>
+      <c r="F201" t="s">
+        <v>209</v>
+      </c>
+      <c r="G201" t="s">
+        <v>211</v>
+      </c>
+      <c r="H201">
+        <v>28</v>
+      </c>
+      <c r="I201" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
+      <c r="A202">
+        <v>2106789</v>
+      </c>
+      <c r="B202" t="s">
+        <v>111</v>
+      </c>
+      <c r="C202" t="s">
+        <v>204</v>
+      </c>
+      <c r="D202">
+        <v>901</v>
+      </c>
+      <c r="E202" t="s">
+        <v>207</v>
+      </c>
+      <c r="F202" t="s">
+        <v>208</v>
+      </c>
+      <c r="G202" t="s">
+        <v>211</v>
+      </c>
+      <c r="I202" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
+      <c r="A203">
+        <v>2200206</v>
+      </c>
+      <c r="B203" t="s">
+        <v>112</v>
+      </c>
+      <c r="C203" t="s">
+        <v>204</v>
+      </c>
+      <c r="D203">
+        <v>901</v>
+      </c>
+      <c r="E203" t="s">
+        <v>207</v>
+      </c>
+      <c r="F203" t="s">
+        <v>209</v>
+      </c>
+      <c r="G203" t="s">
+        <v>211</v>
+      </c>
+      <c r="H203">
+        <v>42</v>
+      </c>
+      <c r="I203" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
+      <c r="A204">
+        <v>2200601</v>
+      </c>
+      <c r="B204" t="s">
+        <v>113</v>
+      </c>
+      <c r="C204" t="s">
+        <v>204</v>
+      </c>
+      <c r="D204">
+        <v>901</v>
+      </c>
+      <c r="E204" t="s">
+        <v>207</v>
+      </c>
+      <c r="F204" t="s">
+        <v>208</v>
+      </c>
+      <c r="G204" t="s">
+        <v>211</v>
+      </c>
+      <c r="I204" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
+      <c r="A205">
+        <v>2284111</v>
+      </c>
+      <c r="B205" t="s">
+        <v>114</v>
+      </c>
+      <c r="C205" t="s">
+        <v>204</v>
+      </c>
+      <c r="D205">
+        <v>901</v>
+      </c>
+      <c r="E205" t="s">
+        <v>207</v>
+      </c>
+      <c r="F205" t="s">
+        <v>208</v>
+      </c>
+      <c r="G205" t="s">
+        <v>211</v>
+      </c>
+      <c r="I205" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
+      <c r="A206">
+        <v>2355702</v>
+      </c>
+      <c r="B206" t="s">
+        <v>115</v>
+      </c>
+      <c r="C206" t="s">
+        <v>204</v>
+      </c>
+      <c r="D206">
+        <v>901</v>
+      </c>
+      <c r="E206" t="s">
+        <v>207</v>
+      </c>
+      <c r="F206" t="s">
+        <v>209</v>
+      </c>
+      <c r="G206" t="s">
+        <v>211</v>
+      </c>
+      <c r="H206">
+        <v>22</v>
+      </c>
+      <c r="I206" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
+      <c r="A207">
+        <v>2359764</v>
+      </c>
+      <c r="B207" t="s">
+        <v>116</v>
+      </c>
+      <c r="C207" t="s">
+        <v>204</v>
+      </c>
+      <c r="D207">
+        <v>901</v>
+      </c>
+      <c r="E207" t="s">
+        <v>207</v>
+      </c>
+      <c r="F207" t="s">
+        <v>209</v>
+      </c>
+      <c r="G207" t="s">
+        <v>211</v>
+      </c>
+      <c r="H207">
+        <v>28</v>
+      </c>
+      <c r="I207" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
+      <c r="A208">
+        <v>2363982</v>
+      </c>
+      <c r="B208" t="s">
+        <v>117</v>
+      </c>
+      <c r="C208" t="s">
+        <v>204</v>
+      </c>
+      <c r="D208">
+        <v>901</v>
+      </c>
+      <c r="E208" t="s">
+        <v>207</v>
+      </c>
+      <c r="F208" t="s">
+        <v>209</v>
+      </c>
+      <c r="G208" t="s">
+        <v>211</v>
+      </c>
+      <c r="H208">
+        <v>8</v>
+      </c>
+      <c r="I208" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9">
+      <c r="A209">
+        <v>2364571</v>
+      </c>
+      <c r="B209" t="s">
+        <v>118</v>
+      </c>
+      <c r="C209" t="s">
+        <v>204</v>
+      </c>
+      <c r="D209">
+        <v>901</v>
+      </c>
+      <c r="E209" t="s">
+        <v>207</v>
+      </c>
+      <c r="F209" t="s">
+        <v>209</v>
+      </c>
+      <c r="G209" t="s">
+        <v>211</v>
+      </c>
+      <c r="H209">
+        <v>0</v>
+      </c>
+      <c r="I209" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9">
+      <c r="A210">
+        <v>2364697</v>
+      </c>
+      <c r="B210" t="s">
+        <v>119</v>
+      </c>
+      <c r="C210" t="s">
+        <v>204</v>
+      </c>
+      <c r="D210">
+        <v>901</v>
+      </c>
+      <c r="E210" t="s">
+        <v>207</v>
+      </c>
+      <c r="F210" t="s">
+        <v>208</v>
+      </c>
+      <c r="G210" t="s">
+        <v>211</v>
+      </c>
+      <c r="I210" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9">
+      <c r="A211">
+        <v>2364712</v>
+      </c>
+      <c r="B211" t="s">
+        <v>120</v>
+      </c>
+      <c r="C211" t="s">
+        <v>204</v>
+      </c>
+      <c r="D211">
+        <v>901</v>
+      </c>
+      <c r="E211" t="s">
+        <v>207</v>
+      </c>
+      <c r="F211" t="s">
+        <v>209</v>
+      </c>
+      <c r="G211" t="s">
+        <v>211</v>
+      </c>
+      <c r="H211">
+        <v>18</v>
+      </c>
+      <c r="I211" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9">
+      <c r="A212">
+        <v>2365114</v>
+      </c>
+      <c r="B212" t="s">
+        <v>121</v>
+      </c>
+      <c r="C212" t="s">
+        <v>204</v>
+      </c>
+      <c r="D212">
+        <v>901</v>
+      </c>
+      <c r="E212" t="s">
+        <v>207</v>
+      </c>
+      <c r="F212" t="s">
+        <v>208</v>
+      </c>
+      <c r="G212" t="s">
+        <v>211</v>
+      </c>
+      <c r="I212" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9">
+      <c r="A213">
+        <v>2366271</v>
+      </c>
+      <c r="B213" t="s">
+        <v>122</v>
+      </c>
+      <c r="C213" t="s">
+        <v>204</v>
+      </c>
+      <c r="D213">
+        <v>901</v>
+      </c>
+      <c r="E213" t="s">
+        <v>207</v>
+      </c>
+      <c r="F213" t="s">
+        <v>209</v>
+      </c>
+      <c r="G213" t="s">
+        <v>211</v>
+      </c>
+      <c r="H213">
+        <v>22</v>
+      </c>
+      <c r="I213" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9">
+      <c r="A214">
+        <v>2366789</v>
+      </c>
+      <c r="B214" t="s">
+        <v>123</v>
+      </c>
+      <c r="C214" t="s">
+        <v>204</v>
+      </c>
+      <c r="D214">
+        <v>901</v>
+      </c>
+      <c r="E214" t="s">
+        <v>207</v>
+      </c>
+      <c r="F214" t="s">
+        <v>209</v>
+      </c>
+      <c r="G214" t="s">
+        <v>211</v>
+      </c>
+      <c r="H214">
+        <v>100</v>
+      </c>
+      <c r="I214" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9">
+      <c r="A215">
+        <v>2367137</v>
+      </c>
+      <c r="B215" t="s">
+        <v>124</v>
+      </c>
+      <c r="C215" t="s">
+        <v>204</v>
+      </c>
+      <c r="D215">
+        <v>901</v>
+      </c>
+      <c r="E215" t="s">
+        <v>207</v>
+      </c>
+      <c r="F215" t="s">
+        <v>209</v>
+      </c>
+      <c r="G215" t="s">
+        <v>211</v>
+      </c>
+      <c r="H215">
+        <v>22</v>
+      </c>
+      <c r="I215" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9">
+      <c r="A216">
+        <v>2368553</v>
+      </c>
+      <c r="B216" t="s">
+        <v>125</v>
+      </c>
+      <c r="C216" t="s">
+        <v>204</v>
+      </c>
+      <c r="D216">
+        <v>901</v>
+      </c>
+      <c r="E216" t="s">
+        <v>207</v>
+      </c>
+      <c r="F216" t="s">
+        <v>209</v>
+      </c>
+      <c r="G216" t="s">
+        <v>211</v>
+      </c>
+      <c r="H216">
+        <v>8</v>
+      </c>
+      <c r="I216" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9">
+      <c r="A217">
+        <v>2369573</v>
+      </c>
+      <c r="B217" t="s">
+        <v>126</v>
+      </c>
+      <c r="C217" t="s">
+        <v>204</v>
+      </c>
+      <c r="D217">
+        <v>901</v>
+      </c>
+      <c r="E217" t="s">
+        <v>207</v>
+      </c>
+      <c r="F217" t="s">
+        <v>208</v>
+      </c>
+      <c r="G217" t="s">
+        <v>211</v>
+      </c>
+      <c r="I217" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9">
+      <c r="A218">
+        <v>2473471</v>
+      </c>
+      <c r="B218" t="s">
+        <v>127</v>
+      </c>
+      <c r="C218" t="s">
+        <v>204</v>
+      </c>
+      <c r="D218">
+        <v>901</v>
+      </c>
+      <c r="E218" t="s">
+        <v>207</v>
+      </c>
+      <c r="F218" t="s">
+        <v>209</v>
+      </c>
+      <c r="G218" t="s">
+        <v>211</v>
+      </c>
+      <c r="H218">
+        <v>18</v>
+      </c>
+      <c r="I218" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9">
+      <c r="A219">
+        <v>2477416</v>
+      </c>
+      <c r="B219" t="s">
+        <v>128</v>
+      </c>
+      <c r="C219" t="s">
+        <v>204</v>
+      </c>
+      <c r="D219">
+        <v>901</v>
+      </c>
+      <c r="E219" t="s">
+        <v>207</v>
+      </c>
+      <c r="F219" t="s">
+        <v>209</v>
+      </c>
+      <c r="G219" t="s">
+        <v>211</v>
+      </c>
+      <c r="H219">
+        <v>22</v>
+      </c>
+      <c r="I219" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9">
+      <c r="A220">
+        <v>2482829</v>
+      </c>
+      <c r="B220" t="s">
+        <v>129</v>
+      </c>
+      <c r="C220" t="s">
+        <v>204</v>
+      </c>
+      <c r="D220">
+        <v>901</v>
+      </c>
+      <c r="E220" t="s">
+        <v>207</v>
+      </c>
+      <c r="F220" t="s">
+        <v>208</v>
+      </c>
+      <c r="G220" t="s">
+        <v>211</v>
+      </c>
+      <c r="I220" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9">
+      <c r="A221">
+        <v>2483134</v>
+      </c>
+      <c r="B221" t="s">
+        <v>130</v>
+      </c>
+      <c r="C221" t="s">
+        <v>204</v>
+      </c>
+      <c r="D221">
+        <v>901</v>
+      </c>
+      <c r="E221" t="s">
+        <v>207</v>
+      </c>
+      <c r="F221" t="s">
+        <v>208</v>
+      </c>
+      <c r="G221" t="s">
+        <v>211</v>
+      </c>
+      <c r="I221" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9">
+      <c r="A222">
+        <v>2483496</v>
+      </c>
+      <c r="B222" t="s">
+        <v>131</v>
+      </c>
+      <c r="C222" t="s">
+        <v>204</v>
+      </c>
+      <c r="D222">
+        <v>901</v>
+      </c>
+      <c r="E222" t="s">
+        <v>207</v>
+      </c>
+      <c r="F222" t="s">
+        <v>209</v>
+      </c>
+      <c r="G222" t="s">
+        <v>211</v>
+      </c>
+      <c r="H222">
+        <v>82</v>
+      </c>
+      <c r="I222" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9">
+      <c r="A223">
+        <v>2484397</v>
+      </c>
+      <c r="B223" t="s">
+        <v>132</v>
+      </c>
+      <c r="C223" t="s">
+        <v>204</v>
+      </c>
+      <c r="D223">
+        <v>901</v>
+      </c>
+      <c r="E223" t="s">
+        <v>207</v>
+      </c>
+      <c r="F223" t="s">
+        <v>209</v>
+      </c>
+      <c r="G223" t="s">
+        <v>211</v>
+      </c>
+      <c r="H223">
+        <v>40</v>
+      </c>
+      <c r="I223" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9">
+      <c r="A224">
+        <v>2484424</v>
+      </c>
+      <c r="B224" t="s">
+        <v>133</v>
+      </c>
+      <c r="C224" t="s">
+        <v>204</v>
+      </c>
+      <c r="D224">
+        <v>901</v>
+      </c>
+      <c r="E224" t="s">
+        <v>207</v>
+      </c>
+      <c r="F224" t="s">
+        <v>209</v>
+      </c>
+      <c r="G224" t="s">
+        <v>211</v>
+      </c>
+      <c r="H224">
+        <v>56</v>
+      </c>
+      <c r="I224" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9">
+      <c r="A225">
+        <v>2484478</v>
+      </c>
+      <c r="B225" t="s">
+        <v>134</v>
+      </c>
+      <c r="C225" t="s">
+        <v>204</v>
+      </c>
+      <c r="D225">
+        <v>901</v>
+      </c>
+      <c r="E225" t="s">
+        <v>207</v>
+      </c>
+      <c r="F225" t="s">
+        <v>209</v>
+      </c>
+      <c r="G225" t="s">
+        <v>211</v>
+      </c>
+      <c r="H225">
+        <v>72</v>
+      </c>
+      <c r="I225" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9">
+      <c r="A226">
+        <v>2590850</v>
+      </c>
+      <c r="B226" t="s">
+        <v>135</v>
+      </c>
+      <c r="C226" t="s">
+        <v>204</v>
+      </c>
+      <c r="D226">
+        <v>901</v>
+      </c>
+      <c r="E226" t="s">
+        <v>207</v>
+      </c>
+      <c r="F226" t="s">
+        <v>209</v>
+      </c>
+      <c r="G226" t="s">
+        <v>211</v>
+      </c>
+      <c r="H226">
+        <v>12</v>
+      </c>
+      <c r="I226" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9">
+      <c r="A227">
+        <v>2591078</v>
+      </c>
+      <c r="B227" t="s">
+        <v>136</v>
+      </c>
+      <c r="C227" t="s">
+        <v>204</v>
+      </c>
+      <c r="D227">
+        <v>901</v>
+      </c>
+      <c r="E227" t="s">
+        <v>207</v>
+      </c>
+      <c r="F227" t="s">
+        <v>209</v>
+      </c>
+      <c r="G227" t="s">
+        <v>211</v>
+      </c>
+      <c r="H227">
+        <v>38</v>
+      </c>
+      <c r="I227" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9">
+      <c r="A228">
+        <v>2592655</v>
+      </c>
+      <c r="B228" t="s">
+        <v>137</v>
+      </c>
+      <c r="C228" t="s">
+        <v>204</v>
+      </c>
+      <c r="D228">
+        <v>901</v>
+      </c>
+      <c r="E228" t="s">
+        <v>207</v>
+      </c>
+      <c r="F228" t="s">
+        <v>209</v>
+      </c>
+      <c r="G228" t="s">
+        <v>211</v>
+      </c>
+      <c r="H228">
+        <v>12</v>
+      </c>
+      <c r="I228" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9">
+      <c r="A229">
+        <v>2593256</v>
+      </c>
+      <c r="B229" t="s">
+        <v>138</v>
+      </c>
+      <c r="C229" t="s">
+        <v>204</v>
+      </c>
+      <c r="D229">
+        <v>901</v>
+      </c>
+      <c r="E229" t="s">
+        <v>207</v>
+      </c>
+      <c r="F229" t="s">
+        <v>209</v>
+      </c>
+      <c r="G229" t="s">
+        <v>211</v>
+      </c>
+      <c r="H229">
+        <v>35</v>
+      </c>
+      <c r="I229" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9">
+      <c r="A230">
+        <v>2596186</v>
+      </c>
+      <c r="B230" t="s">
+        <v>139</v>
+      </c>
+      <c r="C230" t="s">
+        <v>204</v>
+      </c>
+      <c r="D230">
+        <v>901</v>
+      </c>
+      <c r="E230" t="s">
+        <v>207</v>
+      </c>
+      <c r="F230" t="s">
+        <v>209</v>
+      </c>
+      <c r="G230" t="s">
+        <v>211</v>
+      </c>
+      <c r="H230">
+        <v>66</v>
+      </c>
+      <c r="I230" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9">
+      <c r="A231">
+        <v>2612865</v>
+      </c>
+      <c r="B231" t="s">
+        <v>140</v>
+      </c>
+      <c r="C231" t="s">
+        <v>204</v>
+      </c>
+      <c r="D231">
+        <v>901</v>
+      </c>
+      <c r="E231" t="s">
+        <v>207</v>
+      </c>
+      <c r="F231" t="s">
+        <v>209</v>
+      </c>
+      <c r="G231" t="s">
+        <v>211</v>
+      </c>
+      <c r="H231">
+        <v>18</v>
+      </c>
+      <c r="I231" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -1,20 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gökhan Gülser\Desktop\quiz_system\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD0FCAB-C34A-4E3A-9537-5A1132422242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="321">
   <si>
     <t>student_id</t>
   </si>
@@ -950,9 +961,6 @@
   </si>
   <si>
     <t>You correctly identified all given values and properly noted that h1 is an air column, but then incorrectly included h1 in your mercury height calculation — air pressure is negligible and h1 should not appear in your manometer traversal equation (-10 pts, Section C). Your manometer equation setup is fundamentally incorrect: you incorrectly grouped the water and mercury segments, using h2+h4 for water and h1+h3+h5-h6 for mercury, which does not reflect the proper hydrostatic traversal through each fluid segment (-25 pts, Section C). As a result, your mercury net height sum of 0.3 m and water sum of 1.2 m are both wrong, leading to an incorrect final answer of -28.19 kPa instead of the correct ~189 kPa (-20 pts, Sections D &amp; E). You did correctly state gauge pressure, use SI units, and show organized work, earning partial credit in Sections A, B, F, and G.</t>
-  </si>
-  <si>
-    <t>Your overall approach and manometer traversal equation are excellent — you correctly identified all fluid segments and applied hydrostatic principles properly. However, your height assignments contain some errors: you used h2-h3 = 0.2 m (correct), but assigned h4-h3 = 0.4 m instead of the correct 0.4 m — actually that appears correct; however you used h4+h5 = 0.8 m (correct) and h5+h6 = 0.6 m (correct), which are all consistent with the reference solution. The issue is in your first Mercury term: you used rho_Hg*g*h2 = 13500*9.81*0.5 = 66217.5, which is correct. Re-examining your numerical line, the arithmetic for the Mercury segment 2 shows -52,974 which corresponds to 13500*9.81*0.4 = 52,974 — correct. Your water density was written as 980 but in the equation header you wrote rho_w = 980, yet the reference uses 980 kg/m³ giving water term = 980*9.81*1.0 = 9613.8 Pa, while your calculation yields 1922.76 + 7699.04 = 9621.8 Pa (slight rounding difference — acceptable). Your final answer of 189.03 kPa (gauge) is essentially correct and within ±1% of the reference answer of 189.04 kPa. Deducting 10 pts for using rho_w = 980 instead of the specified 980 kg/m³ (no actual deduction needed here) — actually, reviewing carefully, your Section C water segment 1 uses (h2-h3) = 0.2 m but the reference gives 0.5-0.3 = 0.2 m (correct), and your equation structure matches the reference almost perfectly. The only notable issue is that your equation omits explicit mention of neglecting air column weight (h1), so deducting 3 pts for Section A/B clarity on h1 handling, and 5 pts for Section G organization/clarity since some intermediate arithmetic steps are hard to follow. Your final answer is correct and well-stated as gauge pressure — great work!</t>
   </si>
   <si>
     <t>You correctly identified the fluid densities, applied the general hydrostatic traversal concept, and properly neglected the air column — these are good foundations. However, your height assignments for several segments are incorrect (e.g., using 0.4 m and 1.0 m where the correct combinations should be h2=0.5, h4-h3=0.4, h6+h5=0.6, etc.), which propagates through all segment calculations and leads to a final answer of 69.07 kPa instead of the correct ~189 kPa (-6 pts Section A, -4 pts Section B, -20 pts Section C, -6 pts Section D, -15 pts Section E, -7 pts Section F, -2 pts Section G). Please review how to carefully read heights from a multitube manometer figure and correctly identify the vertical extents of each fluid column.</t>
@@ -985,8 +993,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1023,13 +1031,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1067,7 +1083,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1101,6 +1117,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1135,9 +1152,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1310,11 +1328,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I231"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1343,7 +1361,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1366,7 +1384,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1389,7 +1407,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1412,7 +1430,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1435,7 +1453,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1458,7 +1476,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1481,7 +1499,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1504,7 +1522,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1527,7 +1545,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1550,7 +1568,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1573,7 +1591,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1596,7 +1614,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1619,7 +1637,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1642,7 +1660,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1665,7 +1683,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1688,7 +1706,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1711,7 +1729,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1734,7 +1752,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1757,7 +1775,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1780,7 +1798,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -1803,7 +1821,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1826,7 +1844,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1849,7 +1867,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -1872,7 +1890,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -1895,7 +1913,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -1918,7 +1936,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -1941,7 +1959,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -1964,7 +1982,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -1987,7 +2005,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -2010,7 +2028,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -2033,7 +2051,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -2056,7 +2074,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -2079,7 +2097,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -2102,7 +2120,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -2125,7 +2143,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -2148,7 +2166,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -2171,7 +2189,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -2194,7 +2212,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -2217,7 +2235,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -2240,7 +2258,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -2263,7 +2281,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -2286,7 +2304,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -2309,7 +2327,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>51</v>
       </c>
@@ -2332,7 +2350,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -2355,7 +2373,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -2378,7 +2396,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -2401,7 +2419,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -2424,7 +2442,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -2447,7 +2465,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -2470,7 +2488,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -2493,7 +2511,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -2516,7 +2534,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -2539,7 +2557,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -2562,7 +2580,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -2585,7 +2603,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -2608,7 +2626,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -2631,7 +2649,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -2654,7 +2672,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>66</v>
       </c>
@@ -2677,7 +2695,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>67</v>
       </c>
@@ -2700,7 +2718,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>68</v>
       </c>
@@ -2723,7 +2741,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>69</v>
       </c>
@@ -2746,7 +2764,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>70</v>
       </c>
@@ -2769,7 +2787,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>71</v>
       </c>
@@ -2792,7 +2810,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>72</v>
       </c>
@@ -2815,7 +2833,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>73</v>
       </c>
@@ -2838,7 +2856,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>74</v>
       </c>
@@ -2861,7 +2879,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>75</v>
       </c>
@@ -2884,7 +2902,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>76</v>
       </c>
@@ -2907,7 +2925,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>77</v>
       </c>
@@ -2930,7 +2948,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>78</v>
       </c>
@@ -2953,7 +2971,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>79</v>
       </c>
@@ -2976,7 +2994,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>80</v>
       </c>
@@ -2999,7 +3017,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>81</v>
       </c>
@@ -3022,7 +3040,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>82</v>
       </c>
@@ -3045,7 +3063,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>9</v>
       </c>
@@ -3074,7 +3092,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>49</v>
       </c>
@@ -3100,7 +3118,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>50</v>
       </c>
@@ -3129,7 +3147,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -3158,7 +3176,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>20</v>
       </c>
@@ -3187,7 +3205,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>84</v>
       </c>
@@ -3216,7 +3234,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>22</v>
       </c>
@@ -3242,7 +3260,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>23</v>
       </c>
@@ -3271,7 +3289,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>52</v>
       </c>
@@ -3300,7 +3318,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>85</v>
       </c>
@@ -3326,7 +3344,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>86</v>
       </c>
@@ -3352,7 +3370,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>87</v>
       </c>
@@ -3381,7 +3399,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>53</v>
       </c>
@@ -3410,7 +3428,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>55</v>
       </c>
@@ -3436,7 +3454,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>88</v>
       </c>
@@ -3462,7 +3480,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>58</v>
       </c>
@@ -3491,7 +3509,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>28</v>
       </c>
@@ -3520,7 +3538,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>29</v>
       </c>
@@ -3549,7 +3567,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>89</v>
       </c>
@@ -3578,7 +3596,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>63</v>
       </c>
@@ -3607,7 +3625,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>64</v>
       </c>
@@ -3636,7 +3654,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>90</v>
       </c>
@@ -3665,7 +3683,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>33</v>
       </c>
@@ -3691,7 +3709,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>65</v>
       </c>
@@ -3720,7 +3738,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>67</v>
       </c>
@@ -3749,7 +3767,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>68</v>
       </c>
@@ -3775,7 +3793,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>70</v>
       </c>
@@ -3804,7 +3822,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>35</v>
       </c>
@@ -3833,7 +3851,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>36</v>
       </c>
@@ -3862,7 +3880,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>37</v>
       </c>
@@ -3891,7 +3909,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>73</v>
       </c>
@@ -3920,7 +3938,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>91</v>
       </c>
@@ -3949,7 +3967,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>92</v>
       </c>
@@ -3978,7 +3996,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>74</v>
       </c>
@@ -4007,7 +4025,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>75</v>
       </c>
@@ -4036,7 +4054,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>93</v>
       </c>
@@ -4065,7 +4083,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>94</v>
       </c>
@@ -4091,7 +4109,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>38</v>
       </c>
@@ -4120,7 +4138,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>39</v>
       </c>
@@ -4149,7 +4167,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>41</v>
       </c>
@@ -4178,7 +4196,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>76</v>
       </c>
@@ -4207,7 +4225,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>95</v>
       </c>
@@ -4233,7 +4251,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>78</v>
       </c>
@@ -4259,7 +4277,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>79</v>
       </c>
@@ -4288,7 +4306,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>80</v>
       </c>
@@ -4317,7 +4335,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>81</v>
       </c>
@@ -4346,7 +4364,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>45</v>
       </c>
@@ -4372,7 +4390,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>11</v>
       </c>
@@ -4398,7 +4416,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>12</v>
       </c>
@@ -4427,7 +4445,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>46</v>
       </c>
@@ -4453,7 +4471,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>48</v>
       </c>
@@ -4479,7 +4497,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>14</v>
       </c>
@@ -4505,7 +4523,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>96</v>
       </c>
@@ -4534,7 +4552,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>16</v>
       </c>
@@ -4560,7 +4578,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>51</v>
       </c>
@@ -4586,7 +4604,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>97</v>
       </c>
@@ -4612,7 +4630,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>98</v>
       </c>
@@ -4641,7 +4659,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>99</v>
       </c>
@@ -4670,7 +4688,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>17</v>
       </c>
@@ -4696,7 +4714,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -4722,7 +4740,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>100</v>
       </c>
@@ -4751,7 +4769,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>101</v>
       </c>
@@ -4780,7 +4798,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>19</v>
       </c>
@@ -4806,7 +4824,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>102</v>
       </c>
@@ -4835,7 +4853,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>21</v>
       </c>
@@ -4864,7 +4882,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>25</v>
       </c>
@@ -4890,7 +4908,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>56</v>
       </c>
@@ -4919,7 +4937,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>27</v>
       </c>
@@ -4948,7 +4966,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>103</v>
       </c>
@@ -4977,7 +4995,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>60</v>
       </c>
@@ -5006,7 +5024,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>61</v>
       </c>
@@ -5035,7 +5053,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>104</v>
       </c>
@@ -5064,7 +5082,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>31</v>
       </c>
@@ -5090,7 +5108,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>62</v>
       </c>
@@ -5119,7 +5137,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>66</v>
       </c>
@@ -5145,7 +5163,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>69</v>
       </c>
@@ -5171,7 +5189,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>72</v>
       </c>
@@ -5200,7 +5218,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>42</v>
       </c>
@@ -5229,7 +5247,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>105</v>
       </c>
@@ -5258,7 +5276,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>43</v>
       </c>
@@ -5287,7 +5305,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>82</v>
       </c>
@@ -5316,7 +5334,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>44</v>
       </c>
@@ -5342,7 +5360,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>45</v>
       </c>
@@ -5368,7 +5386,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>46</v>
       </c>
@@ -5394,7 +5412,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>47</v>
       </c>
@@ -5423,7 +5441,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>48</v>
       </c>
@@ -5452,7 +5470,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>49</v>
       </c>
@@ -5478,7 +5496,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>50</v>
       </c>
@@ -5507,7 +5525,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>51</v>
       </c>
@@ -5533,7 +5551,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>52</v>
       </c>
@@ -5562,7 +5580,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>53</v>
       </c>
@@ -5591,7 +5609,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>54</v>
       </c>
@@ -5620,7 +5638,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>55</v>
       </c>
@@ -5646,7 +5664,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>56</v>
       </c>
@@ -5675,7 +5693,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>57</v>
       </c>
@@ -5701,7 +5719,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>58</v>
       </c>
@@ -5730,7 +5748,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>59</v>
       </c>
@@ -5759,7 +5777,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>60</v>
       </c>
@@ -5788,7 +5806,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>61</v>
       </c>
@@ -5817,7 +5835,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>62</v>
       </c>
@@ -5846,7 +5864,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>63</v>
       </c>
@@ -5875,7 +5893,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>64</v>
       </c>
@@ -5904,7 +5922,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>65</v>
       </c>
@@ -5933,7 +5951,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>66</v>
       </c>
@@ -5962,7 +5980,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>67</v>
       </c>
@@ -5991,7 +6009,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>68</v>
       </c>
@@ -6020,7 +6038,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>69</v>
       </c>
@@ -6049,7 +6067,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>70</v>
       </c>
@@ -6078,7 +6096,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>71</v>
       </c>
@@ -6104,7 +6122,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>72</v>
       </c>
@@ -6130,7 +6148,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>73</v>
       </c>
@@ -6159,7 +6177,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>74</v>
       </c>
@@ -6188,7 +6206,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="188" spans="1:9">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>75</v>
       </c>
@@ -6217,7 +6235,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="189" spans="1:9">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>76</v>
       </c>
@@ -6246,7 +6264,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>77</v>
       </c>
@@ -6272,7 +6290,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>78</v>
       </c>
@@ -6298,7 +6316,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>79</v>
       </c>
@@ -6327,7 +6345,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="193" spans="1:9">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>80</v>
       </c>
@@ -6356,7 +6374,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="194" spans="1:9">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>81</v>
       </c>
@@ -6385,7 +6403,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="195" spans="1:9">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>82</v>
       </c>
@@ -6414,7 +6432,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="196" spans="1:9">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>1903274</v>
       </c>
@@ -6443,7 +6461,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="197" spans="1:9">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>2003052</v>
       </c>
@@ -6472,7 +6490,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="198" spans="1:9">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>2100421</v>
       </c>
@@ -6498,7 +6516,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="199" spans="1:9">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>2101613</v>
       </c>
@@ -6527,7 +6545,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="200" spans="1:9">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>2105067</v>
       </c>
@@ -6556,7 +6574,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="201" spans="1:9">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>2105541</v>
       </c>
@@ -6585,7 +6603,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="202" spans="1:9">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>2106789</v>
       </c>
@@ -6611,7 +6629,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="203" spans="1:9">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>2200206</v>
       </c>
@@ -6640,7 +6658,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="204" spans="1:9">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>2200601</v>
       </c>
@@ -6666,7 +6684,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="205" spans="1:9">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>2284111</v>
       </c>
@@ -6692,7 +6710,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="206" spans="1:9">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>2355702</v>
       </c>
@@ -6721,7 +6739,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="207" spans="1:9">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>2359764</v>
       </c>
@@ -6750,7 +6768,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="208" spans="1:9">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>2363982</v>
       </c>
@@ -6779,7 +6797,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="209" spans="1:9">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>2364571</v>
       </c>
@@ -6808,7 +6826,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="210" spans="1:9">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>2364697</v>
       </c>
@@ -6834,7 +6852,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="211" spans="1:9">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>2364712</v>
       </c>
@@ -6863,7 +6881,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="212" spans="1:9">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>2365114</v>
       </c>
@@ -6889,7 +6907,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="213" spans="1:9">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>2366271</v>
       </c>
@@ -6918,7 +6936,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="214" spans="1:9">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>2366789</v>
       </c>
@@ -6947,7 +6965,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="215" spans="1:9">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>2367137</v>
       </c>
@@ -6976,7 +6994,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="216" spans="1:9">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>2368553</v>
       </c>
@@ -7005,7 +7023,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="217" spans="1:9">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>2369573</v>
       </c>
@@ -7031,7 +7049,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="218" spans="1:9">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>2473471</v>
       </c>
@@ -7060,7 +7078,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="219" spans="1:9">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>2477416</v>
       </c>
@@ -7089,7 +7107,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="220" spans="1:9">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>2482829</v>
       </c>
@@ -7115,7 +7133,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="221" spans="1:9">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>2483134</v>
       </c>
@@ -7141,7 +7159,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="222" spans="1:9">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>2483496</v>
       </c>
@@ -7164,13 +7182,13 @@
         <v>211</v>
       </c>
       <c r="H222">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="I222" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="223" spans="1:9">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>2484397</v>
       </c>
@@ -7196,10 +7214,10 @@
         <v>40</v>
       </c>
       <c r="I223" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>2484424</v>
       </c>
@@ -7225,10 +7243,10 @@
         <v>56</v>
       </c>
       <c r="I224" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>2484478</v>
       </c>
@@ -7254,10 +7272,10 @@
         <v>72</v>
       </c>
       <c r="I225" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="226" spans="1:9">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>2590850</v>
       </c>
@@ -7283,10 +7301,10 @@
         <v>12</v>
       </c>
       <c r="I226" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="227" spans="1:9">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>2591078</v>
       </c>
@@ -7312,10 +7330,10 @@
         <v>38</v>
       </c>
       <c r="I227" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="228" spans="1:9">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>2592655</v>
       </c>
@@ -7341,10 +7359,10 @@
         <v>12</v>
       </c>
       <c r="I228" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="229" spans="1:9">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>2593256</v>
       </c>
@@ -7370,10 +7388,10 @@
         <v>35</v>
       </c>
       <c r="I229" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="230" spans="1:9">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>2596186</v>
       </c>
@@ -7399,10 +7417,10 @@
         <v>66</v>
       </c>
       <c r="I230" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="231" spans="1:9">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>2612865</v>
       </c>
@@ -7428,7 +7446,7 @@
         <v>18</v>
       </c>
       <c r="I231" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2213" uniqueCount="386">
   <si>
     <t>student_id</t>
   </si>
@@ -643,6 +643,9 @@
     <t>Week 3</t>
   </si>
   <si>
+    <t>Week 2</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
@@ -1082,6 +1085,93 @@
   </si>
   <si>
     <t>You correctly resolved all three force components and found the resultant force vector (791.62i + 1181.77j N) and its magnitude, earning full credit for Parts A and B. However, you did not compute the moment/couple at O (Part C), which accounts for 50 points, and your final answer presentation is incomplete, costing you the Part D points as well.</t>
+  </si>
+  <si>
+    <t>You correctly set up the position vectors and resolved all three forces, earning strong marks in Parts A and B — your resultant R = 791.62i + 1181.77j N is excellent. However, for the moment about O, you only computed M_1200 and did not complete the cross products for the belt forces (800 N and 200 N), so M_x, M_y, and M_z are incomplete, costing roughly 28 points in Part C. Make sure to carry all three r×F calculations through to their final sum for the couple moment.</t>
+  </si>
+  <si>
+    <t>You correctly resolved the gear force components (208.38 N and 1181.77 N) and summed the belt forces to get 1000 N, and your resultant force R = 791.62i + 1181.77j N is essentially correct (full Part A and B credit). However, your moment calculation is incomplete — you only computed moments about one axis (z-axis equivalent, getting 28.63 N·m) and missed the M_x (~260 N·m) and M_y (~-504 N·m) components entirely, resulting in a significant deduction of 38 points in Part C, and the final answer presentation is also incomplete, costing 5 points in Part D.</t>
+  </si>
+  <si>
+    <t>You correctly identified the three forces and key dimensions, and showed awareness of the vector force-couple framework (FR = ΣF, MO = Σr×F), earning partial credit for setup. However, you did not resolve the gear force into its x and y components using the 10° angle, did not compute the actual resultant force vector, and did not calculate the moment components (Mx, My, Mz) — only a single scalar moment for the gear (90 N·m) was found, which is also incorrect in method since the gear force must be decomposed first. To earn full credit next time, make sure to carry all vector components through to a complete numerical answer for both R and MO.</t>
+  </si>
+  <si>
+    <t>You correctly resolved the gear force components (-208.38i and 1181.77j N) and identified the 10° angle, which earns partial credit. However, your belt force treatment (subtracting 200N from 800N to get a single 600N net force) loses significant credit because each belt force must be applied at its own position to compute moments correctly, and your final resultant and moment answers are far from the reference values. Your moment calculations also lack the z-components and miss the full 3D cross-product structure needed for this problem.</t>
+  </si>
+  <si>
+    <t>You made a genuine attempt and correctly identified that the belt forces differ (800-200=600 N), earning partial credit for your setup. However, the gear force was not resolved into its x and y components using the 10° angle, the resultant force vector is incomplete (missing the y-component from the gear), and the moment calculation about O is missing the z-axis geometry (220 mm, 550 mm distances) and cross-product work, so most of Parts B, C, and D could not be awarded credit.</t>
+  </si>
+  <si>
+    <t>You showed some correct setup elements — recognizing the 220 mm and 330 mm distances and applying cos10° to the gear force — which earns partial credit for Part A. However, your solution is largely incomplete: the resultant force vector is missing, the moment calculation only captures a scalar total moment in one direction (missing x and z components), and there is no clear final force-couple statement at O, resulting in major deductions across Parts B (-20), C (-37), and D (-10) and a partial deduction in Part A (-15+8=8 for A). Keep working on setting up r×F systematically for all three moment components.</t>
+  </si>
+  <si>
+    <t>You correctly identified some moment arms and attempted scalar moment calculations, which earns partial credit for setup (Part A). However, your force vectors are incomplete — you did not properly resolve the gear force using the 10° angle or sum belt forces as vectors, and your final result of 13.2 N·m is far from the correct moment components (M_x ≈ 260, M_y ≈ -504, M_z ≈ -75.6 N·m), with no resultant force stated. You receive 8 points for Part A geometry, 0 for Part B (no force vectors), 10 points for partial moment work in Part C, and 0 for Part D (no final vector answer with units).</t>
+  </si>
+  <si>
+    <t>You correctly set up the position vectors and computed the belt and gear y-components, earning solid partial credit. However, your resultant force vector was never clearly stated (missing the combined Rx ≈ 792 N, Ry ≈ 1182 N), and the moment components were not assembled into a final M_O vector — losing significant points in Parts B, C, and D. Make sure to always combine all contributions and write a clear final answer with units.</t>
+  </si>
+  <si>
+    <t>You made a good start by drawing a diagram and attempting to decompose the forces, showing some understanding of the problem setup (earning partial credit for Part A and B setup). However, your resultant force expression is incomplete and incorrect — you incorrectly combined the gear and belt forces (the belt net force should be 1000i N, and the gear force should use the correct sign convention), and there is no moment/couple calculation attempted at all, which costs most of the Part C and D points. Keep practicing cross-product moment calculations to complete the equivalent force-couple system.</t>
+  </si>
+  <si>
+    <t>You correctly identified the geometry (220 mm, 330 mm distances) and resolved the gear force to get 1181.7 N, which shows a good start on the setup — earning partial credit for Parts A and B. However, your resultant force is incomplete (missing the x-components from belt and gear forces), and your moment calculation (M = 2500.7, M_O = 5800.7) does not match the correct vector components (260i − 504j − 75.6k N·m) and lacks a proper cross-product method or scalar breakdown, resulting in significant deductions across Parts B, C, and D. Make sure to sum all force components as vectors and compute moments about O using r × F for each force separately.</t>
+  </si>
+  <si>
+    <t>You drew a basic diagram of the gear and pulley setup, which shows some understanding of the problem geometry, earning minimal partial credit. However, you did not provide any calculations for the resultant force, moments, or a final force-couple system, so nearly all points were lost. Please make sure to show all supporting calculations on future quizzes.</t>
+  </si>
+  <si>
+    <t>You correctly identified all individual force components and computed an accurate resultant force vector (791.62i + 1181.77j N), earning full credit for Parts A and B. However, you did not complete the moment calculation — you set up M_O = Σ(r × F) but left it blank, so no credit could be awarded for Parts C or D.</t>
+  </si>
+  <si>
+    <t>You showed some effort in setting up position and force vectors, but the approach has fundamental errors: the belt and gear forces were not correctly identified (belt forces should be along x, and gear force resolved with sin10/cos10 into x and y components), and the final result appears to be in N·m rather than forces, with no correct resultant force vector or moment about O computed. You earned partial credit for Part A setup attempt and showing the method of combining forces, but Parts B, C, and D are missing or incorrect, resulting in major deductions.</t>
+  </si>
+  <si>
+    <t>You correctly identified the three forces and their approximate positions, and your resultant force magnitude (1422.3 N) and components (Fx ≈ 791.6 N, Fy ≈ 1181.7 N) are very close to the reference values, earning good marks in Parts A and B. However, you used an incorrect method to resolve the gear force (treating it as a scalar ratio using r instead of the 10° angle directly), your moment calculations are incomplete and largely incorrect (only a single scalar moment expression is attempted rather than the full vector moment at O with all three components), and no clear final force-couple system is stated with units, resulting in significant deductions in Parts C and D.</t>
+  </si>
+  <si>
+    <t>You demonstrated some understanding of the problem by attempting to resolve the gear force using the 10-degree angle and computing moment contributions, but the approach is largely incomplete and does not yield a correct equivalent force-couple system at O. You did not find the resultant force vector R, and the moment calculation is missing the belt force contributions and the full 3D vector components (M_x, M_y, M_z), resulting in significant deductions across all parts.</t>
+  </si>
+  <si>
+    <t>You made a genuine attempt and correctly used some moment arms (0.075 m, 0.22 m, 0.55 m) and the gear force component (1200cos10°), which earns partial credit for setup. However, your solution is largely incomplete — the resultant force vector R is never computed, most moment contributions are missing or incorrect, and the final answer 'F_eq = 13.6 (ccw)' does not match the required force-couple system at O. You lost most points in Parts B, C, and D due to the missing force summation and incomplete moment calculations.</t>
+  </si>
+  <si>
+    <t>You correctly resolved the gear force components (-208.4i + 1181.8j N) and summed the belt forces, arriving at a good resultant force of approximately 791.6i + 1181.8j N (full credit for Parts A and B). However, your moment calculations are incomplete and incorrect: you missed the x-component of the moment (M_x ≈ 260 N·m, -13 pts), your M_y came out as -330 N·m instead of -504 N·m (-13 pts), and your M_z (354 N·m) does not match the expected -75.6 N·m (-12 pts), leading to significant deductions in Part C, and the final answer is missing a clear, complete vector statement with all components (-5 pts).</t>
+  </si>
+  <si>
+    <t>You correctly identified the key dimensions and resolved the gear force using the 10° angle, which earns partial credit for setup. However, your resultant force vector is missing (no clear R stated with components), the moment calculations are incomplete and disorganized with incorrect moment arms and missing contributions from belt forces, and no final force-couple system at O is presented. You lose 10 pts on Part A for incorrect moment arm usage, 20 pts on Part B for no resultant force stated, 42 pts on Part C for largely incorrect/incomplete moment calculations, and 10 pts on Part D for no final answer.</t>
+  </si>
+  <si>
+    <t>You correctly identified the gear force components (-208.38 in x, -1181.77 in y) and showed the belt force position vectors, which earns partial credit for setup and method. However, your gear force y-component sign is incorrect (should be +1181.8 N, not -1181.77 N), you did not correctly sum the resultant force (R should be approximately 792i + 1182j N), and the moment calculation about O is entirely missing, costing you 50 points for Part C and most of Part D. You lose 8 pts in Part B for the wrong sign on gear y-component and wrong final R, and 10 pts for an incomplete final answer.</t>
+  </si>
+  <si>
+    <t>You made a genuine attempt and drew a reasonable diagram showing the forces and geometry, earning partial setup credit. However, your moment calculations use incorrect moment arms (0.01 m instead of the correct 0.55 m, 0.22 m, 0.1 m, and 0.075 m), and you did not compute the resultant force vector R or find all three components of the couple moment M_O, resulting in large deductions across Parts B, C, and D.</t>
+  </si>
+  <si>
+    <t>You correctly identified some of the geometry (distances 0.22 m, 0.075 m, 0.55 m, 0.1 m) and attempted to compute moments, which earns partial credit for setup (Part A). However, you only computed scalar moment contributions for two forces and never found the resultant force vector R, missing all of Part B, and your moment calculation is incomplete and numerically incorrect (missing belt force components, wrong gear force arm usage, and the final answer of 13.5 N·m² is dimensionally incorrect and far from the reference). No final vector force-couple system at O was stated, so Part D credit cannot be awarded.</t>
+  </si>
+  <si>
+    <t>You correctly resolved the gear force components (Fx ≈ 208 N, Fy ≈ 1182 N) and showed good understanding of the problem setup, earning solid partial credit in Parts A and B. However, your solution treats this as a 2D problem and only computes a single scalar moment, missing the full 3D vector resultant force and the three-component couple (Mx, My, Mz) required — the reference answer requires R = 792i + 1182j N and M_O = 260i − 504j − 75.6k N·m, so significant credit is lost in Parts B, C, and D for the missing components and incorrect moment calculation.</t>
+  </si>
+  <si>
+    <t>You demonstrated some understanding of the problem setup by identifying the gear force (1109.76 N) and attempting moment calculations, but your approach appears to be solving a 2D scalar moment problem rather than finding the full 3D force-couple system at O with correct vector components. You are missing the resultant force vector (R = 792i + 1182j N), the correct moment components (M_x ≈ 260 N·m, M_y ≈ -504 N·m, M_z ≈ -75.6 N·m), and the belt forces are not properly incorporated into the equivalent system — resulting in significant deductions across Parts B, C, and D.</t>
+  </si>
+  <si>
+    <t>You demonstrated some understanding by computing individual moments (gear and belt net force), but the approach used is fundamentally incorrect — this problem requires a full 3D vector force-couple system at O, not a scalar moment balance or equivalent force location. Your resultant force vector was not stated, the moment components (M_x, M_y, M_z) were not computed correctly, and the final answer of 714.52 N·m does not match the required vector result, resulting in significant deductions across all parts.</t>
+  </si>
+  <si>
+    <t>You correctly resolved the gear force into x and y components (~208 N and ~1182 N) and used the cross-product method for the gear moment, earning solid partial credit for Part A and the gear-related portions of Parts B and C. However, you treated the belt forces as scalar magnitudes added directly to the gear force magnitude (giving F_R = 2000 N) rather than as vector forces with proper position vectors, and the moment calculation did not correctly account for all three force contributions in their respective directions — this led to significant errors in the resultant force and the final moment components (M_y and M_z were not found). You lose 8 pts in Part A for incorrect belt position vectors, 16 pts in Part B for the incorrect resultant (belt forces not properly vectorially combined), 36 pts in Part C for missing M_y and M_z components and incorrect M_R, and 8 pts in Part D for an incomplete final vector answer.</t>
+  </si>
+  <si>
+    <t>Your moment calculations are methodologically excellent — the cross products are set up and executed correctly throughout, and your M_x component is spot on. However, you applied the gear's x-component as +208.37î instead of -208.37î (the gear force has a negative x-component based on the geometry), which propagated into errors in M_y and M_z, and you did not clearly state the resultant force vector R as a final answer, costing points in Parts B and D.</t>
+  </si>
+  <si>
+    <t>You showed some correct partial steps, such as identifying the gear's cosine component (1181j N) and computing a moment from it, but your setup is significantly incomplete — you treated only one belt force (600 N instead of 800 N and 200 N separately), omitted the gear's x-component (-208i N), and never stated a complete resultant force vector R or a full moment vector M_O with all three components. You earned partial credit for Part A (position arms used partially), Part B (gear y-component correct), and Part C (some moment contributions attempted), but no Part D credit since no final answer was clearly stated.</t>
+  </si>
+  <si>
+    <t>You correctly resolved the gear force components (sin10° and cos10°) and identified the belt net force of 600 N, earning solid setup credit. However, your approach to finding the moment diverges significantly from the required force-couple system at O — you attempted to find a resultant force location rather than computing M_O as a moment vector (r × F), and the final answers for R and M_O as vectors are missing or incorrect. This resulted in major deductions across Parts B, C, and D.</t>
+  </si>
+  <si>
+    <t>You correctly found the x-component of the resultant force (~392 N) and the x-component of the moment (~260 N·m), showing solid setup and cross-product methodology. However, your M_y and M_z components are significantly off in both sign and magnitude compared to the reference values (-504 N·m and -75.6 N·m), likely due to sign errors in the cross-product expansion, which cost 25 points in Part C.</t>
   </si>
 </sst>
 </file>
@@ -1413,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I287"/>
+  <dimension ref="A1:I333"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1462,10 +1552,10 @@
         <v>207</v>
       </c>
       <c r="F2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1485,10 +1575,10 @@
         <v>207</v>
       </c>
       <c r="F3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1508,10 +1598,10 @@
         <v>207</v>
       </c>
       <c r="F4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1531,10 +1621,10 @@
         <v>207</v>
       </c>
       <c r="F5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1554,10 +1644,10 @@
         <v>207</v>
       </c>
       <c r="F6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1577,10 +1667,10 @@
         <v>207</v>
       </c>
       <c r="F7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1600,10 +1690,10 @@
         <v>207</v>
       </c>
       <c r="F8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1623,10 +1713,10 @@
         <v>207</v>
       </c>
       <c r="F9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1646,10 +1736,10 @@
         <v>207</v>
       </c>
       <c r="F10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1669,10 +1759,10 @@
         <v>207</v>
       </c>
       <c r="F11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1692,10 +1782,10 @@
         <v>207</v>
       </c>
       <c r="F12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1715,10 +1805,10 @@
         <v>207</v>
       </c>
       <c r="F13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1738,10 +1828,10 @@
         <v>207</v>
       </c>
       <c r="F14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1761,10 +1851,10 @@
         <v>207</v>
       </c>
       <c r="F15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1784,10 +1874,10 @@
         <v>207</v>
       </c>
       <c r="F16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1807,10 +1897,10 @@
         <v>207</v>
       </c>
       <c r="F17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1830,10 +1920,10 @@
         <v>207</v>
       </c>
       <c r="F18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1853,10 +1943,10 @@
         <v>207</v>
       </c>
       <c r="F19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1876,10 +1966,10 @@
         <v>207</v>
       </c>
       <c r="F20" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G20" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1899,10 +1989,10 @@
         <v>207</v>
       </c>
       <c r="F21" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G21" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1922,10 +2012,10 @@
         <v>207</v>
       </c>
       <c r="F22" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G22" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1945,10 +2035,10 @@
         <v>207</v>
       </c>
       <c r="F23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G23" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1968,10 +2058,10 @@
         <v>207</v>
       </c>
       <c r="F24" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G24" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1991,10 +2081,10 @@
         <v>207</v>
       </c>
       <c r="F25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G25" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2014,10 +2104,10 @@
         <v>207</v>
       </c>
       <c r="F26" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G26" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2037,10 +2127,10 @@
         <v>207</v>
       </c>
       <c r="F27" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G27" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2060,10 +2150,10 @@
         <v>207</v>
       </c>
       <c r="F28" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G28" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2083,10 +2173,10 @@
         <v>207</v>
       </c>
       <c r="F29" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G29" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2106,10 +2196,10 @@
         <v>207</v>
       </c>
       <c r="F30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G30" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2129,10 +2219,10 @@
         <v>207</v>
       </c>
       <c r="F31" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G31" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2152,10 +2242,10 @@
         <v>207</v>
       </c>
       <c r="F32" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G32" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2175,10 +2265,10 @@
         <v>207</v>
       </c>
       <c r="F33" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G33" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2198,10 +2288,10 @@
         <v>207</v>
       </c>
       <c r="F34" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G34" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2221,10 +2311,10 @@
         <v>207</v>
       </c>
       <c r="F35" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G35" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2244,10 +2334,10 @@
         <v>207</v>
       </c>
       <c r="F36" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G36" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2267,10 +2357,10 @@
         <v>207</v>
       </c>
       <c r="F37" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G37" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2290,10 +2380,10 @@
         <v>207</v>
       </c>
       <c r="F38" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G38" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2313,10 +2403,10 @@
         <v>207</v>
       </c>
       <c r="F39" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G39" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2336,10 +2426,10 @@
         <v>207</v>
       </c>
       <c r="F40" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G40" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2359,10 +2449,10 @@
         <v>207</v>
       </c>
       <c r="F41" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G41" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2382,10 +2472,10 @@
         <v>207</v>
       </c>
       <c r="F42" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G42" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2405,10 +2495,10 @@
         <v>207</v>
       </c>
       <c r="F43" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G43" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2428,10 +2518,10 @@
         <v>207</v>
       </c>
       <c r="F44" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G44" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2451,10 +2541,10 @@
         <v>207</v>
       </c>
       <c r="F45" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G45" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2474,10 +2564,10 @@
         <v>207</v>
       </c>
       <c r="F46" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G46" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2497,10 +2587,10 @@
         <v>207</v>
       </c>
       <c r="F47" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G47" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2520,10 +2610,10 @@
         <v>207</v>
       </c>
       <c r="F48" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G48" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2543,10 +2633,10 @@
         <v>207</v>
       </c>
       <c r="F49" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G49" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2566,10 +2656,10 @@
         <v>207</v>
       </c>
       <c r="F50" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G50" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2589,10 +2679,10 @@
         <v>207</v>
       </c>
       <c r="F51" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G51" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2612,10 +2702,10 @@
         <v>207</v>
       </c>
       <c r="F52" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G52" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2635,10 +2725,10 @@
         <v>207</v>
       </c>
       <c r="F53" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G53" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2658,10 +2748,10 @@
         <v>207</v>
       </c>
       <c r="F54" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G54" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2681,10 +2771,10 @@
         <v>207</v>
       </c>
       <c r="F55" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G55" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2704,10 +2794,10 @@
         <v>207</v>
       </c>
       <c r="F56" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G56" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2727,10 +2817,10 @@
         <v>207</v>
       </c>
       <c r="F57" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G57" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2750,10 +2840,10 @@
         <v>207</v>
       </c>
       <c r="F58" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G58" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2773,10 +2863,10 @@
         <v>207</v>
       </c>
       <c r="F59" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G59" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2796,10 +2886,10 @@
         <v>207</v>
       </c>
       <c r="F60" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G60" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2819,10 +2909,10 @@
         <v>207</v>
       </c>
       <c r="F61" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G61" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2842,10 +2932,10 @@
         <v>207</v>
       </c>
       <c r="F62" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G62" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2865,10 +2955,10 @@
         <v>207</v>
       </c>
       <c r="F63" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G63" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2888,10 +2978,10 @@
         <v>207</v>
       </c>
       <c r="F64" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G64" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -2911,10 +3001,10 @@
         <v>207</v>
       </c>
       <c r="F65" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G65" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -2934,10 +3024,10 @@
         <v>207</v>
       </c>
       <c r="F66" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G66" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -2957,10 +3047,10 @@
         <v>207</v>
       </c>
       <c r="F67" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -2980,10 +3070,10 @@
         <v>207</v>
       </c>
       <c r="F68" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G68" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -3003,10 +3093,10 @@
         <v>207</v>
       </c>
       <c r="F69" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G69" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -3026,10 +3116,10 @@
         <v>207</v>
       </c>
       <c r="F70" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G70" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -3049,10 +3139,10 @@
         <v>207</v>
       </c>
       <c r="F71" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G71" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -3072,10 +3162,10 @@
         <v>207</v>
       </c>
       <c r="F72" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G72" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -3095,10 +3185,10 @@
         <v>207</v>
       </c>
       <c r="F73" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G73" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -3118,10 +3208,10 @@
         <v>207</v>
       </c>
       <c r="F74" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G74" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -3141,10 +3231,10 @@
         <v>207</v>
       </c>
       <c r="F75" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G75" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -3164,16 +3254,16 @@
         <v>207</v>
       </c>
       <c r="F76" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G76" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H76">
         <v>23</v>
       </c>
       <c r="I76" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -3193,13 +3283,13 @@
         <v>207</v>
       </c>
       <c r="F77" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G77" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I77" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -3219,16 +3309,16 @@
         <v>207</v>
       </c>
       <c r="F78" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G78" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H78">
         <v>100</v>
       </c>
       <c r="I78" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -3248,16 +3338,16 @@
         <v>207</v>
       </c>
       <c r="F79" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G79" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H79">
         <v>26</v>
       </c>
       <c r="I79" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -3277,16 +3367,16 @@
         <v>207</v>
       </c>
       <c r="F80" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G80" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H80">
         <v>10</v>
       </c>
       <c r="I80" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -3306,16 +3396,16 @@
         <v>207</v>
       </c>
       <c r="F81" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G81" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H81">
         <v>100</v>
       </c>
       <c r="I81" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -3335,13 +3425,13 @@
         <v>207</v>
       </c>
       <c r="F82" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G82" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I82" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -3361,16 +3451,16 @@
         <v>207</v>
       </c>
       <c r="F83" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G83" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H83">
         <v>5</v>
       </c>
       <c r="I83" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -3390,16 +3480,16 @@
         <v>207</v>
       </c>
       <c r="F84" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G84" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H84">
         <v>15</v>
       </c>
       <c r="I84" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -3419,13 +3509,13 @@
         <v>207</v>
       </c>
       <c r="F85" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G85" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I85" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -3445,13 +3535,13 @@
         <v>207</v>
       </c>
       <c r="F86" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G86" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I86" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -3471,16 +3561,16 @@
         <v>207</v>
       </c>
       <c r="F87" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G87" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H87">
         <v>100</v>
       </c>
       <c r="I87" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -3500,16 +3590,16 @@
         <v>207</v>
       </c>
       <c r="F88" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G88" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H88">
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -3529,13 +3619,13 @@
         <v>207</v>
       </c>
       <c r="F89" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G89" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I89" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -3555,13 +3645,13 @@
         <v>207</v>
       </c>
       <c r="F90" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G90" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I90" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -3581,16 +3671,16 @@
         <v>207</v>
       </c>
       <c r="F91" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G91" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H91">
         <v>100</v>
       </c>
       <c r="I91" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -3610,16 +3700,16 @@
         <v>207</v>
       </c>
       <c r="F92" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G92" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H92">
         <v>16</v>
       </c>
       <c r="I92" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -3639,16 +3729,16 @@
         <v>207</v>
       </c>
       <c r="F93" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G93" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H93">
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -3668,16 +3758,16 @@
         <v>207</v>
       </c>
       <c r="F94" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G94" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H94">
         <v>5</v>
       </c>
       <c r="I94" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -3697,16 +3787,16 @@
         <v>207</v>
       </c>
       <c r="F95" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G95" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H95">
         <v>25</v>
       </c>
       <c r="I95" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -3726,16 +3816,16 @@
         <v>207</v>
       </c>
       <c r="F96" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G96" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H96">
         <v>75</v>
       </c>
       <c r="I96" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -3755,16 +3845,16 @@
         <v>207</v>
       </c>
       <c r="F97" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G97" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H97">
         <v>100</v>
       </c>
       <c r="I97" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -3784,13 +3874,13 @@
         <v>207</v>
       </c>
       <c r="F98" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G98" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I98" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -3810,16 +3900,16 @@
         <v>207</v>
       </c>
       <c r="F99" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G99" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H99">
         <v>22</v>
       </c>
       <c r="I99" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -3839,16 +3929,16 @@
         <v>207</v>
       </c>
       <c r="F100" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G100" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H100">
         <v>100</v>
       </c>
       <c r="I100" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -3868,13 +3958,13 @@
         <v>207</v>
       </c>
       <c r="F101" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G101" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I101" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -3894,16 +3984,16 @@
         <v>207</v>
       </c>
       <c r="F102" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G102" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H102">
         <v>18</v>
       </c>
       <c r="I102" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -3923,16 +4013,16 @@
         <v>207</v>
       </c>
       <c r="F103" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G103" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H103">
         <v>100</v>
       </c>
       <c r="I103" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -3952,16 +4042,16 @@
         <v>207</v>
       </c>
       <c r="F104" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G104" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H104">
         <v>98</v>
       </c>
       <c r="I104" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -3981,16 +4071,16 @@
         <v>207</v>
       </c>
       <c r="F105" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G105" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H105">
         <v>97</v>
       </c>
       <c r="I105" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -4010,16 +4100,16 @@
         <v>207</v>
       </c>
       <c r="F106" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G106" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H106">
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -4039,16 +4129,16 @@
         <v>207</v>
       </c>
       <c r="F107" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G107" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H107">
         <v>86</v>
       </c>
       <c r="I107" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -4068,16 +4158,16 @@
         <v>207</v>
       </c>
       <c r="F108" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G108" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H108">
         <v>5</v>
       </c>
       <c r="I108" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -4097,16 +4187,16 @@
         <v>207</v>
       </c>
       <c r="F109" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G109" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H109">
         <v>93</v>
       </c>
       <c r="I109" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -4126,16 +4216,16 @@
         <v>207</v>
       </c>
       <c r="F110" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G110" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H110">
         <v>25</v>
       </c>
       <c r="I110" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -4155,16 +4245,16 @@
         <v>207</v>
       </c>
       <c r="F111" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G111" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H111">
         <v>5</v>
       </c>
       <c r="I111" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -4184,13 +4274,13 @@
         <v>207</v>
       </c>
       <c r="F112" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G112" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I112" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -4210,16 +4300,16 @@
         <v>207</v>
       </c>
       <c r="F113" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G113" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H113">
         <v>5</v>
       </c>
       <c r="I113" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -4239,16 +4329,16 @@
         <v>207</v>
       </c>
       <c r="F114" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G114" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H114">
         <v>0</v>
       </c>
       <c r="I114" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -4268,16 +4358,16 @@
         <v>207</v>
       </c>
       <c r="F115" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G115" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H115">
         <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -4297,16 +4387,16 @@
         <v>207</v>
       </c>
       <c r="F116" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G116" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H116">
         <v>20</v>
       </c>
       <c r="I116" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -4326,13 +4416,13 @@
         <v>207</v>
       </c>
       <c r="F117" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G117" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I117" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -4352,13 +4442,13 @@
         <v>207</v>
       </c>
       <c r="F118" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G118" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I118" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -4378,16 +4468,16 @@
         <v>207</v>
       </c>
       <c r="F119" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G119" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H119">
         <v>20</v>
       </c>
       <c r="I119" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -4407,16 +4497,16 @@
         <v>207</v>
       </c>
       <c r="F120" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G120" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H120">
         <v>25</v>
       </c>
       <c r="I120" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -4436,16 +4526,16 @@
         <v>207</v>
       </c>
       <c r="F121" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G121" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H121">
         <v>95</v>
       </c>
       <c r="I121" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -4465,13 +4555,13 @@
         <v>207</v>
       </c>
       <c r="F122" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G122" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I122" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -4491,13 +4581,13 @@
         <v>207</v>
       </c>
       <c r="F123" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G123" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I123" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -4517,16 +4607,16 @@
         <v>207</v>
       </c>
       <c r="F124" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G124" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H124">
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -4546,13 +4636,13 @@
         <v>207</v>
       </c>
       <c r="F125" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G125" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I125" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -4572,13 +4662,13 @@
         <v>207</v>
       </c>
       <c r="F126" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G126" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I126" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -4598,13 +4688,13 @@
         <v>207</v>
       </c>
       <c r="F127" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G127" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I127" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -4624,16 +4714,16 @@
         <v>207</v>
       </c>
       <c r="F128" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G128" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H128">
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -4653,13 +4743,13 @@
         <v>207</v>
       </c>
       <c r="F129" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G129" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I129" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -4679,13 +4769,13 @@
         <v>207</v>
       </c>
       <c r="F130" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G130" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I130" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -4705,13 +4795,13 @@
         <v>207</v>
       </c>
       <c r="F131" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G131" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I131" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -4731,16 +4821,16 @@
         <v>207</v>
       </c>
       <c r="F132" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G132" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H132">
         <v>17</v>
       </c>
       <c r="I132" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -4760,16 +4850,16 @@
         <v>207</v>
       </c>
       <c r="F133" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G133" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H133">
         <v>0</v>
       </c>
       <c r="I133" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -4789,13 +4879,13 @@
         <v>207</v>
       </c>
       <c r="F134" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G134" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I134" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -4815,13 +4905,13 @@
         <v>207</v>
       </c>
       <c r="F135" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G135" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I135" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -4841,16 +4931,16 @@
         <v>207</v>
       </c>
       <c r="F136" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G136" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H136">
         <v>100</v>
       </c>
       <c r="I136" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -4870,16 +4960,16 @@
         <v>207</v>
       </c>
       <c r="F137" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G137" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H137">
         <v>97</v>
       </c>
       <c r="I137" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -4899,13 +4989,13 @@
         <v>207</v>
       </c>
       <c r="F138" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G138" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I138" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -4925,16 +5015,16 @@
         <v>207</v>
       </c>
       <c r="F139" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G139" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H139">
         <v>5</v>
       </c>
       <c r="I139" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -4954,16 +5044,16 @@
         <v>207</v>
       </c>
       <c r="F140" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G140" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H140">
         <v>5</v>
       </c>
       <c r="I140" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -4983,13 +5073,13 @@
         <v>207</v>
       </c>
       <c r="F141" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G141" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I141" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -5009,16 +5099,16 @@
         <v>207</v>
       </c>
       <c r="F142" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G142" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H142">
         <v>0</v>
       </c>
       <c r="I142" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -5038,16 +5128,16 @@
         <v>207</v>
       </c>
       <c r="F143" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G143" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H143">
         <v>30</v>
       </c>
       <c r="I143" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -5067,16 +5157,16 @@
         <v>207</v>
       </c>
       <c r="F144" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G144" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H144">
         <v>95</v>
       </c>
       <c r="I144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -5096,16 +5186,16 @@
         <v>207</v>
       </c>
       <c r="F145" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G145" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H145">
         <v>0</v>
       </c>
       <c r="I145" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -5125,16 +5215,16 @@
         <v>207</v>
       </c>
       <c r="F146" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G146" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H146">
         <v>48</v>
       </c>
       <c r="I146" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -5154,16 +5244,16 @@
         <v>207</v>
       </c>
       <c r="F147" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G147" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H147">
         <v>5</v>
       </c>
       <c r="I147" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -5183,13 +5273,13 @@
         <v>207</v>
       </c>
       <c r="F148" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G148" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I148" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -5209,16 +5299,16 @@
         <v>207</v>
       </c>
       <c r="F149" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G149" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H149">
         <v>95</v>
       </c>
       <c r="I149" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -5238,13 +5328,13 @@
         <v>207</v>
       </c>
       <c r="F150" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G150" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I150" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -5264,13 +5354,13 @@
         <v>207</v>
       </c>
       <c r="F151" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G151" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I151" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -5290,16 +5380,16 @@
         <v>207</v>
       </c>
       <c r="F152" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G152" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H152">
         <v>15</v>
       </c>
       <c r="I152" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -5319,16 +5409,16 @@
         <v>207</v>
       </c>
       <c r="F153" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G153" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H153">
         <v>12</v>
       </c>
       <c r="I153" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -5348,16 +5438,16 @@
         <v>207</v>
       </c>
       <c r="F154" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G154" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H154">
         <v>5</v>
       </c>
       <c r="I154" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -5377,16 +5467,16 @@
         <v>207</v>
       </c>
       <c r="F155" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G155" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H155">
         <v>0</v>
       </c>
       <c r="I155" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -5406,16 +5496,16 @@
         <v>207</v>
       </c>
       <c r="F156" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G156" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H156">
         <v>10</v>
       </c>
       <c r="I156" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -5435,13 +5525,13 @@
         <v>208</v>
       </c>
       <c r="F157" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G157" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I157" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -5461,13 +5551,13 @@
         <v>208</v>
       </c>
       <c r="F158" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G158" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I158" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -5487,13 +5577,13 @@
         <v>208</v>
       </c>
       <c r="F159" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G159" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I159" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -5513,16 +5603,16 @@
         <v>208</v>
       </c>
       <c r="F160" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G160" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H160">
         <v>18</v>
       </c>
       <c r="I160" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -5542,16 +5632,16 @@
         <v>208</v>
       </c>
       <c r="F161" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G161" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H161">
         <v>22</v>
       </c>
       <c r="I161" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -5571,13 +5661,13 @@
         <v>208</v>
       </c>
       <c r="F162" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G162" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I162" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -5597,16 +5687,16 @@
         <v>208</v>
       </c>
       <c r="F163" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G163" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H163">
         <v>22</v>
       </c>
       <c r="I163" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -5626,13 +5716,13 @@
         <v>208</v>
       </c>
       <c r="F164" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G164" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I164" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -5652,16 +5742,16 @@
         <v>208</v>
       </c>
       <c r="F165" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G165" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H165">
         <v>18</v>
       </c>
       <c r="I165" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -5681,16 +5771,16 @@
         <v>208</v>
       </c>
       <c r="F166" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G166" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H166">
         <v>18</v>
       </c>
       <c r="I166" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -5710,16 +5800,16 @@
         <v>208</v>
       </c>
       <c r="F167" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G167" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H167">
         <v>75</v>
       </c>
       <c r="I167" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -5739,13 +5829,13 @@
         <v>208</v>
       </c>
       <c r="F168" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G168" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I168" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -5765,16 +5855,16 @@
         <v>208</v>
       </c>
       <c r="F169" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G169" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H169">
         <v>0</v>
       </c>
       <c r="I169" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -5794,13 +5884,13 @@
         <v>208</v>
       </c>
       <c r="F170" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G170" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I170" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -5820,16 +5910,16 @@
         <v>208</v>
       </c>
       <c r="F171" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G171" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H171">
         <v>62</v>
       </c>
       <c r="I171" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -5849,16 +5939,16 @@
         <v>208</v>
       </c>
       <c r="F172" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G172" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H172">
         <v>38</v>
       </c>
       <c r="I172" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -5878,16 +5968,16 @@
         <v>208</v>
       </c>
       <c r="F173" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G173" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H173">
         <v>52</v>
       </c>
       <c r="I173" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -5907,16 +5997,16 @@
         <v>208</v>
       </c>
       <c r="F174" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G174" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H174">
         <v>12</v>
       </c>
       <c r="I174" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -5936,16 +6026,16 @@
         <v>208</v>
       </c>
       <c r="F175" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G175" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H175">
         <v>87</v>
       </c>
       <c r="I175" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -5965,16 +6055,16 @@
         <v>208</v>
       </c>
       <c r="F176" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G176" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H176">
         <v>73</v>
       </c>
       <c r="I176" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -5994,16 +6084,16 @@
         <v>208</v>
       </c>
       <c r="F177" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G177" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H177">
         <v>38</v>
       </c>
       <c r="I177" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -6023,16 +6113,16 @@
         <v>208</v>
       </c>
       <c r="F178" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G178" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H178">
         <v>32</v>
       </c>
       <c r="I178" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -6052,16 +6142,16 @@
         <v>208</v>
       </c>
       <c r="F179" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G179" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H179">
         <v>72</v>
       </c>
       <c r="I179" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -6081,16 +6171,16 @@
         <v>208</v>
       </c>
       <c r="F180" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G180" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H180">
         <v>30</v>
       </c>
       <c r="I180" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -6110,16 +6200,16 @@
         <v>208</v>
       </c>
       <c r="F181" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G181" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H181">
         <v>18</v>
       </c>
       <c r="I181" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -6139,16 +6229,16 @@
         <v>208</v>
       </c>
       <c r="F182" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G182" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H182">
         <v>38</v>
       </c>
       <c r="I182" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -6168,16 +6258,16 @@
         <v>208</v>
       </c>
       <c r="F183" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G183" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H183">
         <v>89</v>
       </c>
       <c r="I183" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -6197,13 +6287,13 @@
         <v>208</v>
       </c>
       <c r="F184" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G184" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I184" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -6223,13 +6313,13 @@
         <v>208</v>
       </c>
       <c r="F185" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G185" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I185" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -6249,16 +6339,16 @@
         <v>208</v>
       </c>
       <c r="F186" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G186" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H186">
         <v>19</v>
       </c>
       <c r="I186" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -6278,16 +6368,16 @@
         <v>208</v>
       </c>
       <c r="F187" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G187" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H187">
         <v>28</v>
       </c>
       <c r="I187" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -6307,16 +6397,16 @@
         <v>208</v>
       </c>
       <c r="F188" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G188" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H188">
         <v>72</v>
       </c>
       <c r="I188" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -6336,16 +6426,16 @@
         <v>208</v>
       </c>
       <c r="F189" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G189" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H189">
         <v>62</v>
       </c>
       <c r="I189" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -6365,13 +6455,13 @@
         <v>208</v>
       </c>
       <c r="F190" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G190" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I190" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -6391,13 +6481,13 @@
         <v>208</v>
       </c>
       <c r="F191" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G191" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I191" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -6417,16 +6507,16 @@
         <v>208</v>
       </c>
       <c r="F192" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G192" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H192">
         <v>18</v>
       </c>
       <c r="I192" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -6446,16 +6536,16 @@
         <v>208</v>
       </c>
       <c r="F193" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G193" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H193">
         <v>22</v>
       </c>
       <c r="I193" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -6475,16 +6565,16 @@
         <v>208</v>
       </c>
       <c r="F194" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G194" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H194">
         <v>70</v>
       </c>
       <c r="I194" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -6504,16 +6594,16 @@
         <v>208</v>
       </c>
       <c r="F195" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G195" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H195">
         <v>28</v>
       </c>
       <c r="I195" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -6533,16 +6623,16 @@
         <v>208</v>
       </c>
       <c r="F196" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G196" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H196">
         <v>100</v>
       </c>
       <c r="I196" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -6562,16 +6652,16 @@
         <v>208</v>
       </c>
       <c r="F197" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G197" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H197">
         <v>50</v>
       </c>
       <c r="I197" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -6591,13 +6681,13 @@
         <v>208</v>
       </c>
       <c r="F198" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G198" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I198" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -6617,16 +6707,16 @@
         <v>208</v>
       </c>
       <c r="F199" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G199" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H199">
         <v>18</v>
       </c>
       <c r="I199" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -6646,16 +6736,16 @@
         <v>208</v>
       </c>
       <c r="F200" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G200" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H200">
         <v>18</v>
       </c>
       <c r="I200" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -6675,16 +6765,16 @@
         <v>208</v>
       </c>
       <c r="F201" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G201" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H201">
         <v>28</v>
       </c>
       <c r="I201" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -6704,13 +6794,13 @@
         <v>208</v>
       </c>
       <c r="F202" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G202" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I202" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -6730,16 +6820,16 @@
         <v>208</v>
       </c>
       <c r="F203" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G203" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H203">
         <v>42</v>
       </c>
       <c r="I203" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -6759,13 +6849,13 @@
         <v>208</v>
       </c>
       <c r="F204" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G204" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I204" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -6785,13 +6875,13 @@
         <v>208</v>
       </c>
       <c r="F205" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G205" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I205" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -6811,16 +6901,16 @@
         <v>208</v>
       </c>
       <c r="F206" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G206" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H206">
         <v>22</v>
       </c>
       <c r="I206" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -6840,16 +6930,16 @@
         <v>208</v>
       </c>
       <c r="F207" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G207" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H207">
         <v>28</v>
       </c>
       <c r="I207" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -6869,16 +6959,16 @@
         <v>208</v>
       </c>
       <c r="F208" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G208" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H208">
         <v>8</v>
       </c>
       <c r="I208" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="209" spans="1:9">
@@ -6898,16 +6988,16 @@
         <v>208</v>
       </c>
       <c r="F209" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G209" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H209">
         <v>0</v>
       </c>
       <c r="I209" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="210" spans="1:9">
@@ -6927,13 +7017,13 @@
         <v>208</v>
       </c>
       <c r="F210" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G210" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I210" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="211" spans="1:9">
@@ -6953,16 +7043,16 @@
         <v>208</v>
       </c>
       <c r="F211" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G211" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H211">
         <v>18</v>
       </c>
       <c r="I211" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="212" spans="1:9">
@@ -6982,13 +7072,13 @@
         <v>208</v>
       </c>
       <c r="F212" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G212" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I212" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="213" spans="1:9">
@@ -7008,16 +7098,16 @@
         <v>208</v>
       </c>
       <c r="F213" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G213" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H213">
         <v>22</v>
       </c>
       <c r="I213" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="214" spans="1:9">
@@ -7037,16 +7127,16 @@
         <v>208</v>
       </c>
       <c r="F214" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G214" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H214">
         <v>100</v>
       </c>
       <c r="I214" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="215" spans="1:9">
@@ -7066,16 +7156,16 @@
         <v>208</v>
       </c>
       <c r="F215" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G215" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H215">
         <v>22</v>
       </c>
       <c r="I215" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="216" spans="1:9">
@@ -7095,16 +7185,16 @@
         <v>208</v>
       </c>
       <c r="F216" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G216" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H216">
         <v>8</v>
       </c>
       <c r="I216" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="217" spans="1:9">
@@ -7124,13 +7214,13 @@
         <v>208</v>
       </c>
       <c r="F217" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G217" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I217" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="218" spans="1:9">
@@ -7150,16 +7240,16 @@
         <v>208</v>
       </c>
       <c r="F218" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G218" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H218">
         <v>18</v>
       </c>
       <c r="I218" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="219" spans="1:9">
@@ -7179,16 +7269,16 @@
         <v>208</v>
       </c>
       <c r="F219" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G219" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H219">
         <v>22</v>
       </c>
       <c r="I219" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="220" spans="1:9">
@@ -7208,13 +7298,13 @@
         <v>208</v>
       </c>
       <c r="F220" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G220" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I220" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -7234,13 +7324,13 @@
         <v>208</v>
       </c>
       <c r="F221" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G221" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I221" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -7260,16 +7350,16 @@
         <v>208</v>
       </c>
       <c r="F222" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G222" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H222">
         <v>100</v>
       </c>
       <c r="I222" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -7289,16 +7379,16 @@
         <v>208</v>
       </c>
       <c r="F223" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G223" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H223">
         <v>40</v>
       </c>
       <c r="I223" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="224" spans="1:9">
@@ -7318,16 +7408,16 @@
         <v>208</v>
       </c>
       <c r="F224" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G224" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H224">
         <v>56</v>
       </c>
       <c r="I224" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="225" spans="1:9">
@@ -7347,16 +7437,16 @@
         <v>208</v>
       </c>
       <c r="F225" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G225" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H225">
         <v>72</v>
       </c>
       <c r="I225" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="226" spans="1:9">
@@ -7376,16 +7466,16 @@
         <v>208</v>
       </c>
       <c r="F226" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G226" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H226">
         <v>12</v>
       </c>
       <c r="I226" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="227" spans="1:9">
@@ -7405,16 +7495,16 @@
         <v>208</v>
       </c>
       <c r="F227" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G227" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H227">
         <v>38</v>
       </c>
       <c r="I227" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="228" spans="1:9">
@@ -7434,16 +7524,16 @@
         <v>208</v>
       </c>
       <c r="F228" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G228" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H228">
         <v>12</v>
       </c>
       <c r="I228" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="229" spans="1:9">
@@ -7463,16 +7553,16 @@
         <v>208</v>
       </c>
       <c r="F229" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G229" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H229">
         <v>35</v>
       </c>
       <c r="I229" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="230" spans="1:9">
@@ -7492,16 +7582,16 @@
         <v>208</v>
       </c>
       <c r="F230" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G230" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H230">
         <v>66</v>
       </c>
       <c r="I230" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="231" spans="1:9">
@@ -7521,21 +7611,21 @@
         <v>208</v>
       </c>
       <c r="F231" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G231" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H231">
         <v>18</v>
       </c>
       <c r="I231" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="232" spans="1:9">
-      <c r="A232">
-        <v>1903274</v>
+      <c r="A232" t="s">
+        <v>9</v>
       </c>
       <c r="B232" t="s">
         <v>107</v>
@@ -7550,21 +7640,21 @@
         <v>208</v>
       </c>
       <c r="F232" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G232" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H232">
         <v>78</v>
       </c>
       <c r="I232" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="233" spans="1:9">
-      <c r="A233">
-        <v>2101613</v>
+      <c r="A233" t="s">
+        <v>12</v>
       </c>
       <c r="B233" t="s">
         <v>110</v>
@@ -7579,21 +7669,21 @@
         <v>208</v>
       </c>
       <c r="F233" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G233" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H233">
         <v>0</v>
       </c>
       <c r="I233" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="234" spans="1:9">
-      <c r="A234">
-        <v>2202739</v>
+      <c r="A234" t="s">
+        <v>50</v>
       </c>
       <c r="B234" t="s">
         <v>148</v>
@@ -7608,21 +7698,21 @@
         <v>208</v>
       </c>
       <c r="F234" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G234" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H234">
         <v>38</v>
       </c>
       <c r="I234" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="235" spans="1:9">
-      <c r="A235">
-        <v>2250387</v>
+      <c r="A235" t="s">
+        <v>83</v>
       </c>
       <c r="B235" t="s">
         <v>181</v>
@@ -7637,21 +7727,21 @@
         <v>208</v>
       </c>
       <c r="F235" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G235" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H235">
         <v>18</v>
       </c>
       <c r="I235" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="236" spans="1:9">
-      <c r="A236">
-        <v>2252125</v>
+      <c r="A236" t="s">
+        <v>97</v>
       </c>
       <c r="B236" t="s">
         <v>195</v>
@@ -7666,21 +7756,21 @@
         <v>208</v>
       </c>
       <c r="F236" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G236" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H236">
         <v>0</v>
       </c>
       <c r="I236" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="237" spans="1:9">
-      <c r="A237">
-        <v>2252127</v>
+      <c r="A237" t="s">
+        <v>98</v>
       </c>
       <c r="B237" t="s">
         <v>196</v>
@@ -7695,21 +7785,21 @@
         <v>208</v>
       </c>
       <c r="F237" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G237" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H237">
         <v>0</v>
       </c>
       <c r="I237" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="238" spans="1:9">
-      <c r="A238">
-        <v>2282610</v>
+      <c r="A238" t="s">
+        <v>99</v>
       </c>
       <c r="B238" t="s">
         <v>197</v>
@@ -7724,21 +7814,21 @@
         <v>208</v>
       </c>
       <c r="F238" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G238" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H238">
         <v>0</v>
       </c>
       <c r="I238" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="239" spans="1:9">
-      <c r="A239">
-        <v>2284111</v>
+      <c r="A239" t="s">
+        <v>17</v>
       </c>
       <c r="B239" t="s">
         <v>115</v>
@@ -7753,21 +7843,21 @@
         <v>208</v>
       </c>
       <c r="F239" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G239" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H239">
         <v>0</v>
       </c>
       <c r="I239" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="240" spans="1:9">
-      <c r="A240">
-        <v>2359322</v>
+      <c r="A240" t="s">
+        <v>100</v>
       </c>
       <c r="B240" t="s">
         <v>198</v>
@@ -7782,21 +7872,21 @@
         <v>208</v>
       </c>
       <c r="F240" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G240" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H240">
         <v>0</v>
       </c>
       <c r="I240" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="241" spans="1:9">
-      <c r="A241">
-        <v>2359481</v>
+      <c r="A241" t="s">
+        <v>101</v>
       </c>
       <c r="B241" t="s">
         <v>199</v>
@@ -7811,21 +7901,21 @@
         <v>208</v>
       </c>
       <c r="F241" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G241" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H241">
         <v>0</v>
       </c>
       <c r="I241" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="242" spans="1:9">
-      <c r="A242">
-        <v>2360367</v>
+      <c r="A242" t="s">
+        <v>102</v>
       </c>
       <c r="B242" t="s">
         <v>200</v>
@@ -7840,21 +7930,21 @@
         <v>208</v>
       </c>
       <c r="F242" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G242" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H242">
         <v>0</v>
       </c>
       <c r="I242" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="243" spans="1:9">
-      <c r="A243">
-        <v>2363982</v>
+      <c r="A243" t="s">
+        <v>20</v>
       </c>
       <c r="B243" t="s">
         <v>118</v>
@@ -7869,21 +7959,21 @@
         <v>208</v>
       </c>
       <c r="F243" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G243" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H243">
         <v>18</v>
       </c>
       <c r="I243" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="244" spans="1:9">
-      <c r="A244">
-        <v>2364521</v>
+      <c r="A244" t="s">
+        <v>84</v>
       </c>
       <c r="B244" t="s">
         <v>182</v>
@@ -7898,21 +7988,21 @@
         <v>208</v>
       </c>
       <c r="F244" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G244" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H244">
         <v>0</v>
       </c>
       <c r="I244" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="245" spans="1:9">
-      <c r="A245">
-        <v>2364571</v>
+      <c r="A245" t="s">
+        <v>21</v>
       </c>
       <c r="B245" t="s">
         <v>119</v>
@@ -7927,21 +8017,21 @@
         <v>208</v>
       </c>
       <c r="F245" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G245" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H245">
         <v>0</v>
       </c>
       <c r="I245" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="246" spans="1:9">
-      <c r="A246">
-        <v>2364712</v>
+      <c r="A246" t="s">
+        <v>23</v>
       </c>
       <c r="B246" t="s">
         <v>121</v>
@@ -7956,21 +8046,21 @@
         <v>208</v>
       </c>
       <c r="F246" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G246" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H246">
         <v>12</v>
       </c>
       <c r="I246" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="247" spans="1:9">
-      <c r="A247">
-        <v>2364766</v>
+      <c r="A247" t="s">
+        <v>52</v>
       </c>
       <c r="B247" t="s">
         <v>150</v>
@@ -7985,21 +8075,21 @@
         <v>208</v>
       </c>
       <c r="F247" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G247" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H247">
         <v>0</v>
       </c>
       <c r="I247" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="248" spans="1:9">
-      <c r="A248">
-        <v>2364995</v>
+      <c r="A248" t="s">
+        <v>85</v>
       </c>
       <c r="B248" t="s">
         <v>183</v>
@@ -8014,21 +8104,21 @@
         <v>208</v>
       </c>
       <c r="F248" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G248" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H248">
         <v>15</v>
       </c>
       <c r="I248" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="249" spans="1:9">
-      <c r="A249">
-        <v>2366232</v>
+      <c r="A249" t="s">
+        <v>87</v>
       </c>
       <c r="B249" t="s">
         <v>185</v>
@@ -8043,21 +8133,21 @@
         <v>208</v>
       </c>
       <c r="F249" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G249" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H249">
         <v>42</v>
       </c>
       <c r="I249" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="250" spans="1:9">
-      <c r="A250">
-        <v>2366271</v>
+      <c r="A250" t="s">
+        <v>25</v>
       </c>
       <c r="B250" t="s">
         <v>123</v>
@@ -8072,21 +8162,21 @@
         <v>208</v>
       </c>
       <c r="F250" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G250" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H250">
         <v>0</v>
       </c>
       <c r="I250" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="251" spans="1:9">
-      <c r="A251">
-        <v>2366734</v>
+      <c r="A251" t="s">
+        <v>55</v>
       </c>
       <c r="B251" t="s">
         <v>153</v>
@@ -8101,21 +8191,21 @@
         <v>208</v>
       </c>
       <c r="F251" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G251" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H251">
         <v>18</v>
       </c>
       <c r="I251" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="252" spans="1:9">
-      <c r="A252">
-        <v>2367037</v>
+      <c r="A252" t="s">
+        <v>58</v>
       </c>
       <c r="B252" t="s">
         <v>156</v>
@@ -8130,21 +8220,21 @@
         <v>208</v>
       </c>
       <c r="F252" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G252" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H252">
         <v>18</v>
       </c>
       <c r="I252" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="253" spans="1:9">
-      <c r="A253">
-        <v>2367137</v>
+      <c r="A253" t="s">
+        <v>27</v>
       </c>
       <c r="B253" t="s">
         <v>125</v>
@@ -8159,21 +8249,21 @@
         <v>208</v>
       </c>
       <c r="F253" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G253" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H253">
         <v>0</v>
       </c>
       <c r="I253" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="254" spans="1:9">
-      <c r="A254">
-        <v>2369573</v>
+      <c r="A254" t="s">
+        <v>29</v>
       </c>
       <c r="B254" t="s">
         <v>127</v>
@@ -8188,21 +8278,21 @@
         <v>208</v>
       </c>
       <c r="F254" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G254" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H254">
         <v>15</v>
       </c>
       <c r="I254" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="255" spans="1:9">
-      <c r="A255">
-        <v>2472419</v>
+      <c r="A255" t="s">
+        <v>103</v>
       </c>
       <c r="B255" t="s">
         <v>201</v>
@@ -8217,21 +8307,21 @@
         <v>208</v>
       </c>
       <c r="F255" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G255" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H255">
         <v>0</v>
       </c>
       <c r="I255" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="256" spans="1:9">
-      <c r="A256">
-        <v>2472843</v>
+      <c r="A256" t="s">
+        <v>60</v>
       </c>
       <c r="B256" t="s">
         <v>158</v>
@@ -8246,21 +8336,21 @@
         <v>208</v>
       </c>
       <c r="F256" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G256" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H256">
         <v>0</v>
       </c>
       <c r="I256" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="257" spans="1:9">
-      <c r="A257">
-        <v>2472990</v>
+      <c r="A257" t="s">
+        <v>89</v>
       </c>
       <c r="B257" t="s">
         <v>187</v>
@@ -8275,21 +8365,21 @@
         <v>208</v>
       </c>
       <c r="F257" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G257" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H257">
         <v>42</v>
       </c>
       <c r="I257" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="258" spans="1:9">
-      <c r="A258">
-        <v>2476099</v>
+      <c r="A258" t="s">
+        <v>61</v>
       </c>
       <c r="B258" t="s">
         <v>159</v>
@@ -8304,21 +8394,21 @@
         <v>208</v>
       </c>
       <c r="F258" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G258" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H258">
         <v>0</v>
       </c>
       <c r="I258" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="259" spans="1:9">
-      <c r="A259">
-        <v>2476633</v>
+      <c r="A259" t="s">
+        <v>104</v>
       </c>
       <c r="B259" t="s">
         <v>202</v>
@@ -8333,21 +8423,21 @@
         <v>208</v>
       </c>
       <c r="F259" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G259" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H259">
         <v>0</v>
       </c>
       <c r="I259" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="260" spans="1:9">
-      <c r="A260">
-        <v>2477416</v>
+      <c r="A260" t="s">
+        <v>31</v>
       </c>
       <c r="B260" t="s">
         <v>129</v>
@@ -8362,21 +8452,21 @@
         <v>208</v>
       </c>
       <c r="F260" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G260" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H260">
         <v>0</v>
       </c>
       <c r="I260" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="261" spans="1:9">
-      <c r="A261">
-        <v>2477970</v>
+      <c r="A261" t="s">
+        <v>62</v>
       </c>
       <c r="B261" t="s">
         <v>160</v>
@@ -8391,21 +8481,21 @@
         <v>208</v>
       </c>
       <c r="F261" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G261" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H261">
         <v>0</v>
       </c>
       <c r="I261" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="262" spans="1:9">
-      <c r="A262">
-        <v>2482073</v>
+      <c r="A262" t="s">
+        <v>63</v>
       </c>
       <c r="B262" t="s">
         <v>161</v>
@@ -8420,21 +8510,21 @@
         <v>208</v>
       </c>
       <c r="F262" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G262" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H262">
         <v>18</v>
       </c>
       <c r="I262" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="263" spans="1:9">
-      <c r="A263">
-        <v>2482445</v>
+      <c r="A263" t="s">
+        <v>64</v>
       </c>
       <c r="B263" t="s">
         <v>162</v>
@@ -8449,21 +8539,21 @@
         <v>208</v>
       </c>
       <c r="F263" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G263" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H263">
         <v>38</v>
       </c>
       <c r="I263" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="264" spans="1:9">
-      <c r="A264">
-        <v>2483328</v>
+      <c r="A264" t="s">
+        <v>65</v>
       </c>
       <c r="B264" t="s">
         <v>163</v>
@@ -8478,21 +8568,21 @@
         <v>208</v>
       </c>
       <c r="F264" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G264" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H264">
         <v>28</v>
       </c>
       <c r="I264" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="265" spans="1:9">
-      <c r="A265">
-        <v>2483834</v>
+      <c r="A265" t="s">
+        <v>67</v>
       </c>
       <c r="B265" t="s">
         <v>165</v>
@@ -8507,21 +8597,21 @@
         <v>208</v>
       </c>
       <c r="F265" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G265" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H265">
         <v>10</v>
       </c>
       <c r="I265" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="266" spans="1:9">
-      <c r="A266">
-        <v>2483956</v>
+      <c r="A266" t="s">
+        <v>68</v>
       </c>
       <c r="B266" t="s">
         <v>166</v>
@@ -8536,21 +8626,21 @@
         <v>208</v>
       </c>
       <c r="F266" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G266" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H266">
         <v>10</v>
       </c>
       <c r="I266" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="267" spans="1:9">
-      <c r="A267">
-        <v>2483960</v>
+      <c r="A267" t="s">
+        <v>69</v>
       </c>
       <c r="B267" t="s">
         <v>167</v>
@@ -8565,21 +8655,21 @@
         <v>208</v>
       </c>
       <c r="F267" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G267" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H267">
         <v>10</v>
       </c>
       <c r="I267" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="268" spans="1:9">
-      <c r="A268">
-        <v>2484028</v>
+      <c r="A268" t="s">
+        <v>70</v>
       </c>
       <c r="B268" t="s">
         <v>168</v>
@@ -8594,21 +8684,21 @@
         <v>208</v>
       </c>
       <c r="F268" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G268" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H268">
         <v>52</v>
       </c>
       <c r="I268" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="269" spans="1:9">
-      <c r="A269">
-        <v>2484397</v>
+      <c r="A269" t="s">
+        <v>35</v>
       </c>
       <c r="B269" t="s">
         <v>133</v>
@@ -8623,21 +8713,21 @@
         <v>208</v>
       </c>
       <c r="F269" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G269" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H269">
         <v>18</v>
       </c>
       <c r="I269" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="270" spans="1:9">
-      <c r="A270">
-        <v>2484424</v>
+      <c r="A270" t="s">
+        <v>36</v>
       </c>
       <c r="B270" t="s">
         <v>134</v>
@@ -8652,21 +8742,21 @@
         <v>208</v>
       </c>
       <c r="F270" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G270" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H270">
         <v>28</v>
       </c>
       <c r="I270" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="271" spans="1:9">
-      <c r="A271">
-        <v>2484542</v>
+      <c r="A271" t="s">
+        <v>73</v>
       </c>
       <c r="B271" t="s">
         <v>171</v>
@@ -8681,21 +8771,21 @@
         <v>208</v>
       </c>
       <c r="F271" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G271" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H271">
         <v>15</v>
       </c>
       <c r="I271" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="272" spans="1:9">
-      <c r="A272">
-        <v>2485620</v>
+      <c r="A272" t="s">
+        <v>91</v>
       </c>
       <c r="B272" t="s">
         <v>189</v>
@@ -8710,21 +8800,21 @@
         <v>208</v>
       </c>
       <c r="F272" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G272" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H272">
         <v>12</v>
       </c>
       <c r="I272" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="273" spans="1:9">
-      <c r="A273">
-        <v>2488091</v>
+      <c r="A273" t="s">
+        <v>92</v>
       </c>
       <c r="B273" t="s">
         <v>190</v>
@@ -8739,21 +8829,21 @@
         <v>208</v>
       </c>
       <c r="F273" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G273" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H273">
         <v>0</v>
       </c>
       <c r="I273" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="274" spans="1:9">
-      <c r="A274">
-        <v>2500744</v>
+      <c r="A274" t="s">
+        <v>74</v>
       </c>
       <c r="B274" t="s">
         <v>172</v>
@@ -8768,21 +8858,21 @@
         <v>208</v>
       </c>
       <c r="F274" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G274" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H274">
         <v>28</v>
       </c>
       <c r="I274" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="275" spans="1:9">
-      <c r="A275">
-        <v>2501122</v>
+      <c r="A275" t="s">
+        <v>75</v>
       </c>
       <c r="B275" t="s">
         <v>173</v>
@@ -8797,21 +8887,21 @@
         <v>208</v>
       </c>
       <c r="F275" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G275" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H275">
         <v>12</v>
       </c>
       <c r="I275" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="276" spans="1:9">
-      <c r="A276">
-        <v>2503515</v>
+      <c r="A276" t="s">
+        <v>94</v>
       </c>
       <c r="B276" t="s">
         <v>192</v>
@@ -8826,21 +8916,21 @@
         <v>208</v>
       </c>
       <c r="F276" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G276" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H276">
         <v>0</v>
       </c>
       <c r="I276" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="277" spans="1:9">
-      <c r="A277">
-        <v>2590850</v>
+      <c r="A277" t="s">
+        <v>38</v>
       </c>
       <c r="B277" t="s">
         <v>136</v>
@@ -8855,21 +8945,21 @@
         <v>208</v>
       </c>
       <c r="F277" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G277" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H277">
         <v>18</v>
       </c>
       <c r="I277" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="278" spans="1:9">
-      <c r="A278">
-        <v>2591078</v>
+      <c r="A278" t="s">
+        <v>39</v>
       </c>
       <c r="B278" t="s">
         <v>137</v>
@@ -8884,21 +8974,21 @@
         <v>208</v>
       </c>
       <c r="F278" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G278" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H278">
         <v>0</v>
       </c>
       <c r="I278" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="279" spans="1:9">
-      <c r="A279">
-        <v>2593256</v>
+      <c r="A279" t="s">
+        <v>41</v>
       </c>
       <c r="B279" t="s">
         <v>139</v>
@@ -8913,21 +9003,21 @@
         <v>208</v>
       </c>
       <c r="F279" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G279" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H279">
         <v>28</v>
       </c>
       <c r="I279" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="280" spans="1:9">
-      <c r="A280">
-        <v>2593530</v>
+      <c r="A280" t="s">
+        <v>76</v>
       </c>
       <c r="B280" t="s">
         <v>174</v>
@@ -8942,21 +9032,21 @@
         <v>208</v>
       </c>
       <c r="F280" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G280" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H280">
         <v>62</v>
       </c>
       <c r="I280" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="281" spans="1:9">
-      <c r="A281">
-        <v>2596186</v>
+      <c r="A281" t="s">
+        <v>42</v>
       </c>
       <c r="B281" t="s">
         <v>140</v>
@@ -8971,21 +9061,21 @@
         <v>208</v>
       </c>
       <c r="F281" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G281" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H281">
         <v>0</v>
       </c>
       <c r="I281" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="282" spans="1:9">
-      <c r="A282">
-        <v>2598321</v>
+      <c r="A282" t="s">
+        <v>95</v>
       </c>
       <c r="B282" t="s">
         <v>193</v>
@@ -9000,21 +9090,21 @@
         <v>208</v>
       </c>
       <c r="F282" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G282" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H282">
         <v>0</v>
       </c>
       <c r="I282" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="283" spans="1:9">
-      <c r="A283">
-        <v>2599631</v>
+      <c r="A283" t="s">
+        <v>79</v>
       </c>
       <c r="B283" t="s">
         <v>177</v>
@@ -9029,21 +9119,21 @@
         <v>208</v>
       </c>
       <c r="F283" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G283" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H283">
         <v>22</v>
       </c>
       <c r="I283" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="284" spans="1:9">
-      <c r="A284">
-        <v>2599634</v>
+      <c r="A284" t="s">
+        <v>80</v>
       </c>
       <c r="B284" t="s">
         <v>178</v>
@@ -9058,21 +9148,21 @@
         <v>208</v>
       </c>
       <c r="F284" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G284" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H284">
         <v>28</v>
       </c>
       <c r="I284" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="285" spans="1:9">
-      <c r="A285">
-        <v>2599868</v>
+      <c r="A285" t="s">
+        <v>81</v>
       </c>
       <c r="B285" t="s">
         <v>179</v>
@@ -9087,21 +9177,21 @@
         <v>208</v>
       </c>
       <c r="F285" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G285" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H285">
         <v>58</v>
       </c>
       <c r="I285" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="286" spans="1:9">
-      <c r="A286">
-        <v>2612865</v>
+      <c r="A286" t="s">
+        <v>43</v>
       </c>
       <c r="B286" t="s">
         <v>141</v>
@@ -9116,21 +9206,21 @@
         <v>208</v>
       </c>
       <c r="F286" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G286" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H286">
         <v>38</v>
       </c>
       <c r="I286" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="287" spans="1:9">
-      <c r="A287">
-        <v>2616909</v>
+      <c r="A287" t="s">
+        <v>82</v>
       </c>
       <c r="B287" t="s">
         <v>180</v>
@@ -9145,16 +9235,1323 @@
         <v>208</v>
       </c>
       <c r="F287" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G287" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H287">
         <v>0</v>
       </c>
       <c r="I287" t="s">
-        <v>324</v>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9">
+      <c r="A288">
+        <v>1903274</v>
+      </c>
+      <c r="B288" t="s">
+        <v>107</v>
+      </c>
+      <c r="C288" t="s">
+        <v>206</v>
+      </c>
+      <c r="D288">
+        <v>901</v>
+      </c>
+      <c r="E288" t="s">
+        <v>209</v>
+      </c>
+      <c r="F288" t="s">
+        <v>211</v>
+      </c>
+      <c r="G288" t="s">
+        <v>214</v>
+      </c>
+      <c r="H288">
+        <v>72</v>
+      </c>
+      <c r="I288" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9">
+      <c r="A289">
+        <v>2200784</v>
+      </c>
+      <c r="B289" t="s">
+        <v>147</v>
+      </c>
+      <c r="C289" t="s">
+        <v>206</v>
+      </c>
+      <c r="D289">
+        <v>901</v>
+      </c>
+      <c r="E289" t="s">
+        <v>209</v>
+      </c>
+      <c r="F289" t="s">
+        <v>210</v>
+      </c>
+      <c r="G289" t="s">
+        <v>214</v>
+      </c>
+      <c r="I289" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9">
+      <c r="A290">
+        <v>2202739</v>
+      </c>
+      <c r="B290" t="s">
+        <v>148</v>
+      </c>
+      <c r="C290" t="s">
+        <v>206</v>
+      </c>
+      <c r="D290">
+        <v>901</v>
+      </c>
+      <c r="E290" t="s">
+        <v>209</v>
+      </c>
+      <c r="F290" t="s">
+        <v>211</v>
+      </c>
+      <c r="G290" t="s">
+        <v>214</v>
+      </c>
+      <c r="H290">
+        <v>38</v>
+      </c>
+      <c r="I290" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9">
+      <c r="A291">
+        <v>2250387</v>
+      </c>
+      <c r="B291" t="s">
+        <v>181</v>
+      </c>
+      <c r="C291" t="s">
+        <v>206</v>
+      </c>
+      <c r="D291">
+        <v>901</v>
+      </c>
+      <c r="E291" t="s">
+        <v>209</v>
+      </c>
+      <c r="F291" t="s">
+        <v>211</v>
+      </c>
+      <c r="G291" t="s">
+        <v>214</v>
+      </c>
+      <c r="H291">
+        <v>22</v>
+      </c>
+      <c r="I291" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9">
+      <c r="A292">
+        <v>2363982</v>
+      </c>
+      <c r="B292" t="s">
+        <v>118</v>
+      </c>
+      <c r="C292" t="s">
+        <v>206</v>
+      </c>
+      <c r="D292">
+        <v>901</v>
+      </c>
+      <c r="E292" t="s">
+        <v>209</v>
+      </c>
+      <c r="F292" t="s">
+        <v>211</v>
+      </c>
+      <c r="G292" t="s">
+        <v>214</v>
+      </c>
+      <c r="H292">
+        <v>22</v>
+      </c>
+      <c r="I292" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9">
+      <c r="A293">
+        <v>2364521</v>
+      </c>
+      <c r="B293" t="s">
+        <v>182</v>
+      </c>
+      <c r="C293" t="s">
+        <v>206</v>
+      </c>
+      <c r="D293">
+        <v>901</v>
+      </c>
+      <c r="E293" t="s">
+        <v>209</v>
+      </c>
+      <c r="F293" t="s">
+        <v>211</v>
+      </c>
+      <c r="G293" t="s">
+        <v>214</v>
+      </c>
+      <c r="H293">
+        <v>0</v>
+      </c>
+      <c r="I293" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9">
+      <c r="A294">
+        <v>2364697</v>
+      </c>
+      <c r="B294" t="s">
+        <v>120</v>
+      </c>
+      <c r="C294" t="s">
+        <v>206</v>
+      </c>
+      <c r="D294">
+        <v>901</v>
+      </c>
+      <c r="E294" t="s">
+        <v>209</v>
+      </c>
+      <c r="F294" t="s">
+        <v>210</v>
+      </c>
+      <c r="G294" t="s">
+        <v>214</v>
+      </c>
+      <c r="I294" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9">
+      <c r="A295">
+        <v>2364712</v>
+      </c>
+      <c r="B295" t="s">
+        <v>121</v>
+      </c>
+      <c r="C295" t="s">
+        <v>206</v>
+      </c>
+      <c r="D295">
+        <v>901</v>
+      </c>
+      <c r="E295" t="s">
+        <v>209</v>
+      </c>
+      <c r="F295" t="s">
+        <v>211</v>
+      </c>
+      <c r="G295" t="s">
+        <v>214</v>
+      </c>
+      <c r="H295">
+        <v>12</v>
+      </c>
+      <c r="I295" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9">
+      <c r="A296">
+        <v>2364766</v>
+      </c>
+      <c r="B296" t="s">
+        <v>150</v>
+      </c>
+      <c r="C296" t="s">
+        <v>206</v>
+      </c>
+      <c r="D296">
+        <v>901</v>
+      </c>
+      <c r="E296" t="s">
+        <v>209</v>
+      </c>
+      <c r="F296" t="s">
+        <v>211</v>
+      </c>
+      <c r="G296" t="s">
+        <v>214</v>
+      </c>
+      <c r="H296">
+        <v>18</v>
+      </c>
+      <c r="I296" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9">
+      <c r="A297">
+        <v>2364995</v>
+      </c>
+      <c r="B297" t="s">
+        <v>183</v>
+      </c>
+      <c r="C297" t="s">
+        <v>206</v>
+      </c>
+      <c r="D297">
+        <v>901</v>
+      </c>
+      <c r="E297" t="s">
+        <v>209</v>
+      </c>
+      <c r="F297" t="s">
+        <v>211</v>
+      </c>
+      <c r="G297" t="s">
+        <v>214</v>
+      </c>
+      <c r="H297">
+        <v>18</v>
+      </c>
+      <c r="I297" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9">
+      <c r="A298">
+        <v>2365347</v>
+      </c>
+      <c r="B298" t="s">
+        <v>184</v>
+      </c>
+      <c r="C298" t="s">
+        <v>206</v>
+      </c>
+      <c r="D298">
+        <v>901</v>
+      </c>
+      <c r="E298" t="s">
+        <v>209</v>
+      </c>
+      <c r="F298" t="s">
+        <v>210</v>
+      </c>
+      <c r="G298" t="s">
+        <v>214</v>
+      </c>
+      <c r="I298" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9">
+      <c r="A299">
+        <v>2366232</v>
+      </c>
+      <c r="B299" t="s">
+        <v>185</v>
+      </c>
+      <c r="C299" t="s">
+        <v>206</v>
+      </c>
+      <c r="D299">
+        <v>901</v>
+      </c>
+      <c r="E299" t="s">
+        <v>209</v>
+      </c>
+      <c r="F299" t="s">
+        <v>211</v>
+      </c>
+      <c r="G299" t="s">
+        <v>214</v>
+      </c>
+      <c r="H299">
+        <v>45</v>
+      </c>
+      <c r="I299" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9">
+      <c r="A300">
+        <v>2366349</v>
+      </c>
+      <c r="B300" t="s">
+        <v>151</v>
+      </c>
+      <c r="C300" t="s">
+        <v>206</v>
+      </c>
+      <c r="D300">
+        <v>901</v>
+      </c>
+      <c r="E300" t="s">
+        <v>209</v>
+      </c>
+      <c r="F300" t="s">
+        <v>210</v>
+      </c>
+      <c r="G300" t="s">
+        <v>214</v>
+      </c>
+      <c r="I300" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9">
+      <c r="A301">
+        <v>2366734</v>
+      </c>
+      <c r="B301" t="s">
+        <v>153</v>
+      </c>
+      <c r="C301" t="s">
+        <v>206</v>
+      </c>
+      <c r="D301">
+        <v>901</v>
+      </c>
+      <c r="E301" t="s">
+        <v>209</v>
+      </c>
+      <c r="F301" t="s">
+        <v>211</v>
+      </c>
+      <c r="G301" t="s">
+        <v>214</v>
+      </c>
+      <c r="H301">
+        <v>18</v>
+      </c>
+      <c r="I301" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9">
+      <c r="A302">
+        <v>2366843</v>
+      </c>
+      <c r="B302" t="s">
+        <v>186</v>
+      </c>
+      <c r="C302" t="s">
+        <v>206</v>
+      </c>
+      <c r="D302">
+        <v>901</v>
+      </c>
+      <c r="E302" t="s">
+        <v>209</v>
+      </c>
+      <c r="F302" t="s">
+        <v>210</v>
+      </c>
+      <c r="G302" t="s">
+        <v>214</v>
+      </c>
+      <c r="H302">
+        <v>0</v>
+      </c>
+      <c r="I302" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9">
+      <c r="A303">
+        <v>2367037</v>
+      </c>
+      <c r="B303" t="s">
+        <v>156</v>
+      </c>
+      <c r="C303" t="s">
+        <v>206</v>
+      </c>
+      <c r="D303">
+        <v>901</v>
+      </c>
+      <c r="E303" t="s">
+        <v>209</v>
+      </c>
+      <c r="F303" t="s">
+        <v>211</v>
+      </c>
+      <c r="G303" t="s">
+        <v>214</v>
+      </c>
+      <c r="H303">
+        <v>18</v>
+      </c>
+      <c r="I303" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9">
+      <c r="A304">
+        <v>2368553</v>
+      </c>
+      <c r="B304" t="s">
+        <v>126</v>
+      </c>
+      <c r="C304" t="s">
+        <v>206</v>
+      </c>
+      <c r="D304">
+        <v>901</v>
+      </c>
+      <c r="E304" t="s">
+        <v>209</v>
+      </c>
+      <c r="F304" t="s">
+        <v>210</v>
+      </c>
+      <c r="G304" t="s">
+        <v>214</v>
+      </c>
+      <c r="I304" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9">
+      <c r="A305">
+        <v>2369573</v>
+      </c>
+      <c r="B305" t="s">
+        <v>127</v>
+      </c>
+      <c r="C305" t="s">
+        <v>206</v>
+      </c>
+      <c r="D305">
+        <v>901</v>
+      </c>
+      <c r="E305" t="s">
+        <v>209</v>
+      </c>
+      <c r="F305" t="s">
+        <v>211</v>
+      </c>
+      <c r="G305" t="s">
+        <v>214</v>
+      </c>
+      <c r="H305">
+        <v>15</v>
+      </c>
+      <c r="I305" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9">
+      <c r="A306">
+        <v>2472990</v>
+      </c>
+      <c r="B306" t="s">
+        <v>187</v>
+      </c>
+      <c r="C306" t="s">
+        <v>206</v>
+      </c>
+      <c r="D306">
+        <v>901</v>
+      </c>
+      <c r="E306" t="s">
+        <v>209</v>
+      </c>
+      <c r="F306" t="s">
+        <v>211</v>
+      </c>
+      <c r="G306" t="s">
+        <v>214</v>
+      </c>
+      <c r="H306">
+        <v>42</v>
+      </c>
+      <c r="I306" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9">
+      <c r="A307">
+        <v>2482073</v>
+      </c>
+      <c r="B307" t="s">
+        <v>161</v>
+      </c>
+      <c r="C307" t="s">
+        <v>206</v>
+      </c>
+      <c r="D307">
+        <v>901</v>
+      </c>
+      <c r="E307" t="s">
+        <v>209</v>
+      </c>
+      <c r="F307" t="s">
+        <v>211</v>
+      </c>
+      <c r="G307" t="s">
+        <v>214</v>
+      </c>
+      <c r="H307">
+        <v>18</v>
+      </c>
+      <c r="I307" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9">
+      <c r="A308">
+        <v>2482445</v>
+      </c>
+      <c r="B308" t="s">
+        <v>162</v>
+      </c>
+      <c r="C308" t="s">
+        <v>206</v>
+      </c>
+      <c r="D308">
+        <v>901</v>
+      </c>
+      <c r="E308" t="s">
+        <v>209</v>
+      </c>
+      <c r="F308" t="s">
+        <v>211</v>
+      </c>
+      <c r="G308" t="s">
+        <v>214</v>
+      </c>
+      <c r="H308">
+        <v>0</v>
+      </c>
+      <c r="I308" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9">
+      <c r="A309">
+        <v>2482558</v>
+      </c>
+      <c r="B309" t="s">
+        <v>188</v>
+      </c>
+      <c r="C309" t="s">
+        <v>206</v>
+      </c>
+      <c r="D309">
+        <v>901</v>
+      </c>
+      <c r="E309" t="s">
+        <v>209</v>
+      </c>
+      <c r="F309" t="s">
+        <v>210</v>
+      </c>
+      <c r="G309" t="s">
+        <v>214</v>
+      </c>
+      <c r="I309" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9">
+      <c r="A310">
+        <v>2483134</v>
+      </c>
+      <c r="B310" t="s">
+        <v>131</v>
+      </c>
+      <c r="C310" t="s">
+        <v>206</v>
+      </c>
+      <c r="D310">
+        <v>901</v>
+      </c>
+      <c r="E310" t="s">
+        <v>209</v>
+      </c>
+      <c r="F310" t="s">
+        <v>210</v>
+      </c>
+      <c r="G310" t="s">
+        <v>214</v>
+      </c>
+      <c r="I310" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9">
+      <c r="A311">
+        <v>2483328</v>
+      </c>
+      <c r="B311" t="s">
+        <v>163</v>
+      </c>
+      <c r="C311" t="s">
+        <v>206</v>
+      </c>
+      <c r="D311">
+        <v>901</v>
+      </c>
+      <c r="E311" t="s">
+        <v>209</v>
+      </c>
+      <c r="F311" t="s">
+        <v>211</v>
+      </c>
+      <c r="G311" t="s">
+        <v>214</v>
+      </c>
+      <c r="H311">
+        <v>28</v>
+      </c>
+      <c r="I311" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9">
+      <c r="A312">
+        <v>2483834</v>
+      </c>
+      <c r="B312" t="s">
+        <v>165</v>
+      </c>
+      <c r="C312" t="s">
+        <v>206</v>
+      </c>
+      <c r="D312">
+        <v>901</v>
+      </c>
+      <c r="E312" t="s">
+        <v>209</v>
+      </c>
+      <c r="F312" t="s">
+        <v>211</v>
+      </c>
+      <c r="G312" t="s">
+        <v>214</v>
+      </c>
+      <c r="H312">
+        <v>10</v>
+      </c>
+      <c r="I312" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9">
+      <c r="A313">
+        <v>2483956</v>
+      </c>
+      <c r="B313" t="s">
+        <v>166</v>
+      </c>
+      <c r="C313" t="s">
+        <v>206</v>
+      </c>
+      <c r="D313">
+        <v>901</v>
+      </c>
+      <c r="E313" t="s">
+        <v>209</v>
+      </c>
+      <c r="F313" t="s">
+        <v>211</v>
+      </c>
+      <c r="G313" t="s">
+        <v>214</v>
+      </c>
+      <c r="H313">
+        <v>12</v>
+      </c>
+      <c r="I313" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9">
+      <c r="A314">
+        <v>2484028</v>
+      </c>
+      <c r="B314" t="s">
+        <v>168</v>
+      </c>
+      <c r="C314" t="s">
+        <v>206</v>
+      </c>
+      <c r="D314">
+        <v>901</v>
+      </c>
+      <c r="E314" t="s">
+        <v>209</v>
+      </c>
+      <c r="F314" t="s">
+        <v>211</v>
+      </c>
+      <c r="G314" t="s">
+        <v>214</v>
+      </c>
+      <c r="H314">
+        <v>54</v>
+      </c>
+      <c r="I314" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9">
+      <c r="A315">
+        <v>2484397</v>
+      </c>
+      <c r="B315" t="s">
+        <v>133</v>
+      </c>
+      <c r="C315" t="s">
+        <v>206</v>
+      </c>
+      <c r="D315">
+        <v>901</v>
+      </c>
+      <c r="E315" t="s">
+        <v>209</v>
+      </c>
+      <c r="F315" t="s">
+        <v>211</v>
+      </c>
+      <c r="G315" t="s">
+        <v>214</v>
+      </c>
+      <c r="H315">
+        <v>18</v>
+      </c>
+      <c r="I315" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9">
+      <c r="A316">
+        <v>2484424</v>
+      </c>
+      <c r="B316" t="s">
+        <v>134</v>
+      </c>
+      <c r="C316" t="s">
+        <v>206</v>
+      </c>
+      <c r="D316">
+        <v>901</v>
+      </c>
+      <c r="E316" t="s">
+        <v>209</v>
+      </c>
+      <c r="F316" t="s">
+        <v>211</v>
+      </c>
+      <c r="G316" t="s">
+        <v>214</v>
+      </c>
+      <c r="H316">
+        <v>22</v>
+      </c>
+      <c r="I316" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9">
+      <c r="A317">
+        <v>2484478</v>
+      </c>
+      <c r="B317" t="s">
+        <v>135</v>
+      </c>
+      <c r="C317" t="s">
+        <v>206</v>
+      </c>
+      <c r="D317">
+        <v>901</v>
+      </c>
+      <c r="E317" t="s">
+        <v>209</v>
+      </c>
+      <c r="F317" t="s">
+        <v>210</v>
+      </c>
+      <c r="G317" t="s">
+        <v>214</v>
+      </c>
+      <c r="H317">
+        <v>0</v>
+      </c>
+      <c r="I317" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9">
+      <c r="A318">
+        <v>2484542</v>
+      </c>
+      <c r="B318" t="s">
+        <v>171</v>
+      </c>
+      <c r="C318" t="s">
+        <v>206</v>
+      </c>
+      <c r="D318">
+        <v>901</v>
+      </c>
+      <c r="E318" t="s">
+        <v>209</v>
+      </c>
+      <c r="F318" t="s">
+        <v>211</v>
+      </c>
+      <c r="G318" t="s">
+        <v>214</v>
+      </c>
+      <c r="H318">
+        <v>15</v>
+      </c>
+      <c r="I318" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9">
+      <c r="A319">
+        <v>2485620</v>
+      </c>
+      <c r="B319" t="s">
+        <v>189</v>
+      </c>
+      <c r="C319" t="s">
+        <v>206</v>
+      </c>
+      <c r="D319">
+        <v>901</v>
+      </c>
+      <c r="E319" t="s">
+        <v>209</v>
+      </c>
+      <c r="F319" t="s">
+        <v>211</v>
+      </c>
+      <c r="G319" t="s">
+        <v>214</v>
+      </c>
+      <c r="H319">
+        <v>18</v>
+      </c>
+      <c r="I319" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9">
+      <c r="A320">
+        <v>2488091</v>
+      </c>
+      <c r="B320" t="s">
+        <v>190</v>
+      </c>
+      <c r="C320" t="s">
+        <v>206</v>
+      </c>
+      <c r="D320">
+        <v>901</v>
+      </c>
+      <c r="E320" t="s">
+        <v>209</v>
+      </c>
+      <c r="F320" t="s">
+        <v>211</v>
+      </c>
+      <c r="G320" t="s">
+        <v>214</v>
+      </c>
+      <c r="H320">
+        <v>0</v>
+      </c>
+      <c r="I320" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9">
+      <c r="A321">
+        <v>2500744</v>
+      </c>
+      <c r="B321" t="s">
+        <v>172</v>
+      </c>
+      <c r="C321" t="s">
+        <v>206</v>
+      </c>
+      <c r="D321">
+        <v>901</v>
+      </c>
+      <c r="E321" t="s">
+        <v>209</v>
+      </c>
+      <c r="F321" t="s">
+        <v>211</v>
+      </c>
+      <c r="G321" t="s">
+        <v>214</v>
+      </c>
+      <c r="H321">
+        <v>32</v>
+      </c>
+      <c r="I321" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9">
+      <c r="A322">
+        <v>2501122</v>
+      </c>
+      <c r="B322" t="s">
+        <v>173</v>
+      </c>
+      <c r="C322" t="s">
+        <v>206</v>
+      </c>
+      <c r="D322">
+        <v>901</v>
+      </c>
+      <c r="E322" t="s">
+        <v>209</v>
+      </c>
+      <c r="F322" t="s">
+        <v>211</v>
+      </c>
+      <c r="G322" t="s">
+        <v>214</v>
+      </c>
+      <c r="H322">
+        <v>18</v>
+      </c>
+      <c r="I322" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9">
+      <c r="A323">
+        <v>2501485</v>
+      </c>
+      <c r="B323" t="s">
+        <v>191</v>
+      </c>
+      <c r="C323" t="s">
+        <v>206</v>
+      </c>
+      <c r="D323">
+        <v>901</v>
+      </c>
+      <c r="E323" t="s">
+        <v>209</v>
+      </c>
+      <c r="F323" t="s">
+        <v>210</v>
+      </c>
+      <c r="G323" t="s">
+        <v>214</v>
+      </c>
+      <c r="I323" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9">
+      <c r="A324">
+        <v>2503515</v>
+      </c>
+      <c r="B324" t="s">
+        <v>192</v>
+      </c>
+      <c r="C324" t="s">
+        <v>206</v>
+      </c>
+      <c r="D324">
+        <v>901</v>
+      </c>
+      <c r="E324" t="s">
+        <v>209</v>
+      </c>
+      <c r="F324" t="s">
+        <v>211</v>
+      </c>
+      <c r="G324" t="s">
+        <v>214</v>
+      </c>
+      <c r="H324">
+        <v>0</v>
+      </c>
+      <c r="I324" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9">
+      <c r="A325">
+        <v>2590850</v>
+      </c>
+      <c r="B325" t="s">
+        <v>136</v>
+      </c>
+      <c r="C325" t="s">
+        <v>206</v>
+      </c>
+      <c r="D325">
+        <v>901</v>
+      </c>
+      <c r="E325" t="s">
+        <v>209</v>
+      </c>
+      <c r="F325" t="s">
+        <v>211</v>
+      </c>
+      <c r="G325" t="s">
+        <v>214</v>
+      </c>
+      <c r="H325">
+        <v>18</v>
+      </c>
+      <c r="I325" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9">
+      <c r="A326">
+        <v>2591078</v>
+      </c>
+      <c r="B326" t="s">
+        <v>137</v>
+      </c>
+      <c r="C326" t="s">
+        <v>206</v>
+      </c>
+      <c r="D326">
+        <v>901</v>
+      </c>
+      <c r="E326" t="s">
+        <v>209</v>
+      </c>
+      <c r="F326" t="s">
+        <v>211</v>
+      </c>
+      <c r="G326" t="s">
+        <v>214</v>
+      </c>
+      <c r="H326">
+        <v>0</v>
+      </c>
+      <c r="I326" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9">
+      <c r="A327">
+        <v>2593256</v>
+      </c>
+      <c r="B327" t="s">
+        <v>139</v>
+      </c>
+      <c r="C327" t="s">
+        <v>206</v>
+      </c>
+      <c r="D327">
+        <v>901</v>
+      </c>
+      <c r="E327" t="s">
+        <v>209</v>
+      </c>
+      <c r="F327" t="s">
+        <v>211</v>
+      </c>
+      <c r="G327" t="s">
+        <v>214</v>
+      </c>
+      <c r="H327">
+        <v>32</v>
+      </c>
+      <c r="I327" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9">
+      <c r="A328">
+        <v>2593530</v>
+      </c>
+      <c r="B328" t="s">
+        <v>174</v>
+      </c>
+      <c r="C328" t="s">
+        <v>206</v>
+      </c>
+      <c r="D328">
+        <v>901</v>
+      </c>
+      <c r="E328" t="s">
+        <v>209</v>
+      </c>
+      <c r="F328" t="s">
+        <v>211</v>
+      </c>
+      <c r="G328" t="s">
+        <v>214</v>
+      </c>
+      <c r="H328">
+        <v>79</v>
+      </c>
+      <c r="I328" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9">
+      <c r="A329">
+        <v>2598321</v>
+      </c>
+      <c r="B329" t="s">
+        <v>193</v>
+      </c>
+      <c r="C329" t="s">
+        <v>206</v>
+      </c>
+      <c r="D329">
+        <v>901</v>
+      </c>
+      <c r="E329" t="s">
+        <v>209</v>
+      </c>
+      <c r="F329" t="s">
+        <v>211</v>
+      </c>
+      <c r="G329" t="s">
+        <v>214</v>
+      </c>
+      <c r="H329">
+        <v>0</v>
+      </c>
+      <c r="I329" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9">
+      <c r="A330">
+        <v>2599154</v>
+      </c>
+      <c r="B330" t="s">
+        <v>176</v>
+      </c>
+      <c r="C330" t="s">
+        <v>206</v>
+      </c>
+      <c r="D330">
+        <v>901</v>
+      </c>
+      <c r="E330" t="s">
+        <v>209</v>
+      </c>
+      <c r="F330" t="s">
+        <v>210</v>
+      </c>
+      <c r="G330" t="s">
+        <v>214</v>
+      </c>
+      <c r="I330" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9">
+      <c r="A331">
+        <v>2599631</v>
+      </c>
+      <c r="B331" t="s">
+        <v>177</v>
+      </c>
+      <c r="C331" t="s">
+        <v>206</v>
+      </c>
+      <c r="D331">
+        <v>901</v>
+      </c>
+      <c r="E331" t="s">
+        <v>209</v>
+      </c>
+      <c r="F331" t="s">
+        <v>211</v>
+      </c>
+      <c r="G331" t="s">
+        <v>214</v>
+      </c>
+      <c r="H331">
+        <v>28</v>
+      </c>
+      <c r="I331" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9">
+      <c r="A332">
+        <v>2599634</v>
+      </c>
+      <c r="B332" t="s">
+        <v>178</v>
+      </c>
+      <c r="C332" t="s">
+        <v>206</v>
+      </c>
+      <c r="D332">
+        <v>901</v>
+      </c>
+      <c r="E332" t="s">
+        <v>209</v>
+      </c>
+      <c r="F332" t="s">
+        <v>211</v>
+      </c>
+      <c r="G332" t="s">
+        <v>214</v>
+      </c>
+      <c r="H332">
+        <v>18</v>
+      </c>
+      <c r="I332" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9">
+      <c r="A333">
+        <v>2599868</v>
+      </c>
+      <c r="B333" t="s">
+        <v>179</v>
+      </c>
+      <c r="C333" t="s">
+        <v>206</v>
+      </c>
+      <c r="D333">
+        <v>901</v>
+      </c>
+      <c r="E333" t="s">
+        <v>209</v>
+      </c>
+      <c r="F333" t="s">
+        <v>211</v>
+      </c>
+      <c r="G333" t="s">
+        <v>214</v>
+      </c>
+      <c r="H333">
+        <v>63</v>
+      </c>
+      <c r="I333" t="s">
+        <v>385</v>
       </c>
     </row>
   </sheetData>

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -1,15 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gökhan Gülser\Desktop\quiz_system\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABCAEE1-0446-4076-A269-2493CB0CD1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1279,8 +1290,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1309,21 +1320,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1361,7 +1381,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1395,6 +1415,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1429,9 +1450,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1604,11 +1626,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I419"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1637,8 +1659,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B2" t="s">
@@ -1660,8 +1682,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
@@ -1683,8 +1705,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
@@ -1706,8 +1728,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B5" t="s">
@@ -1729,8 +1751,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
@@ -1752,8 +1774,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B7" t="s">
@@ -1775,8 +1797,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B8" t="s">
@@ -1798,8 +1820,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B9" t="s">
@@ -1821,8 +1843,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B10" t="s">
@@ -1844,8 +1866,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B11" t="s">
@@ -1867,8 +1889,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B12" t="s">
@@ -1890,8 +1912,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B13" t="s">
@@ -1913,8 +1935,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B14" t="s">
@@ -1936,8 +1958,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B15" t="s">
@@ -1959,8 +1981,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B16" t="s">
@@ -1982,8 +2004,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B17" t="s">
@@ -2005,8 +2027,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B18" t="s">
@@ -2028,8 +2050,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B19" t="s">
@@ -2051,8 +2073,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B20" t="s">
@@ -2074,8 +2096,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B21" t="s">
@@ -2097,8 +2119,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B22" t="s">
@@ -2120,8 +2142,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B23" t="s">
@@ -2143,8 +2165,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
-      <c r="A24" t="s">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B24" t="s">
@@ -2166,8 +2188,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
-      <c r="A25" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B25" t="s">
@@ -2189,8 +2211,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
-      <c r="A26" t="s">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B26" t="s">
@@ -2212,8 +2234,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B27" t="s">
@@ -2235,8 +2257,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
-      <c r="A28" t="s">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B28" t="s">
@@ -2258,8 +2280,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
-      <c r="A29" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B29" t="s">
@@ -2281,8 +2303,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
-      <c r="A30" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B30" t="s">
@@ -2304,8 +2326,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B31" t="s">
@@ -2327,8 +2349,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B32" t="s">
@@ -2350,8 +2372,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
-      <c r="A33" t="s">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B33" t="s">
@@ -2373,8 +2395,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
-      <c r="A34" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B34" t="s">
@@ -2396,8 +2418,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
-      <c r="A35" t="s">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B35" t="s">
@@ -2419,8 +2441,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
-      <c r="A36" t="s">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B36" t="s">
@@ -2442,8 +2464,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
-      <c r="A37" t="s">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B37" t="s">
@@ -2465,8 +2487,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
-      <c r="A38" t="s">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B38" t="s">
@@ -2488,8 +2510,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
-      <c r="A39" t="s">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B39" t="s">
@@ -2511,8 +2533,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
-      <c r="A40" t="s">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B40" t="s">
@@ -2534,8 +2556,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
-      <c r="A41" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B41" t="s">
@@ -2557,8 +2579,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
-      <c r="A42" t="s">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B42" t="s">
@@ -2580,8 +2602,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
-      <c r="A43" t="s">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B43" t="s">
@@ -2603,8 +2625,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
-      <c r="A44" t="s">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B44" t="s">
@@ -2626,8 +2648,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
-      <c r="A45" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B45" t="s">
@@ -2649,8 +2671,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
-      <c r="A46" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B46" t="s">
@@ -2672,8 +2694,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
-      <c r="A47" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B47" t="s">
@@ -2695,8 +2717,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
-      <c r="A48" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B48" t="s">
@@ -2718,8 +2740,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
-      <c r="A49" t="s">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B49" t="s">
@@ -2741,8 +2763,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
-      <c r="A50" t="s">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B50" t="s">
@@ -2764,8 +2786,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
-      <c r="A51" t="s">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B51" t="s">
@@ -2787,8 +2809,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
-      <c r="A52" t="s">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B52" t="s">
@@ -2810,8 +2832,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
-      <c r="A53" t="s">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B53" t="s">
@@ -2833,8 +2855,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
-      <c r="A54" t="s">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B54" t="s">
@@ -2856,8 +2878,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
-      <c r="A55" t="s">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B55" t="s">
@@ -2879,8 +2901,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
-      <c r="A56" t="s">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B56" t="s">
@@ -2902,8 +2924,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
-      <c r="A57" t="s">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B57" t="s">
@@ -2925,8 +2947,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
-      <c r="A58" t="s">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B58" t="s">
@@ -2948,8 +2970,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
-      <c r="A59" t="s">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B59" t="s">
@@ -2971,8 +2993,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
-      <c r="A60" t="s">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B60" t="s">
@@ -2994,8 +3016,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
-      <c r="A61" t="s">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B61" t="s">
@@ -3017,8 +3039,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
-      <c r="A62" t="s">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B62" t="s">
@@ -3040,8 +3062,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
-      <c r="A63" t="s">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B63" t="s">
@@ -3063,8 +3085,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
-      <c r="A64" t="s">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B64" t="s">
@@ -3086,8 +3108,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
-      <c r="A65" t="s">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B65" t="s">
@@ -3109,8 +3131,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
-      <c r="A66" t="s">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B66" t="s">
@@ -3132,8 +3154,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
-      <c r="A67" t="s">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B67" t="s">
@@ -3155,8 +3177,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
-      <c r="A68" t="s">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B68" t="s">
@@ -3178,8 +3200,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
-      <c r="A69" t="s">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B69" t="s">
@@ -3201,8 +3223,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
-      <c r="A70" t="s">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B70" t="s">
@@ -3224,8 +3246,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
-      <c r="A71" t="s">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B71" t="s">
@@ -3247,8 +3269,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
-      <c r="A72" t="s">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B72" t="s">
@@ -3270,8 +3292,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
-      <c r="A73" t="s">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B73" t="s">
@@ -3293,8 +3315,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
-      <c r="A74" t="s">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B74" t="s">
@@ -3316,8 +3338,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
-      <c r="A75" t="s">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B75" t="s">
@@ -3339,8 +3361,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
-      <c r="A76" t="s">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B76" t="s">
@@ -3368,8 +3390,8 @@
         <v>218</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
-      <c r="A77" t="s">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B77" t="s">
@@ -3394,8 +3416,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
-      <c r="A78" t="s">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B78" t="s">
@@ -3423,8 +3445,8 @@
         <v>220</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
-      <c r="A79" t="s">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B79" t="s">
@@ -3452,8 +3474,8 @@
         <v>221</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
-      <c r="A80" t="s">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B80" t="s">
@@ -3481,8 +3503,8 @@
         <v>222</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
-      <c r="A81" t="s">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
         <v>84</v>
       </c>
       <c r="B81" t="s">
@@ -3510,8 +3532,8 @@
         <v>223</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
-      <c r="A82" t="s">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B82" t="s">
@@ -3536,8 +3558,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
-      <c r="A83" t="s">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B83" t="s">
@@ -3565,8 +3587,8 @@
         <v>224</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
-      <c r="A84" t="s">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B84" t="s">
@@ -3594,8 +3616,8 @@
         <v>225</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
-      <c r="A85" t="s">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
         <v>85</v>
       </c>
       <c r="B85" t="s">
@@ -3620,8 +3642,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
-      <c r="A86" t="s">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B86" t="s">
@@ -3646,8 +3668,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
-      <c r="A87" t="s">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
         <v>87</v>
       </c>
       <c r="B87" t="s">
@@ -3675,8 +3697,8 @@
         <v>226</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
-      <c r="A88" t="s">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B88" t="s">
@@ -3704,8 +3726,8 @@
         <v>227</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
-      <c r="A89" t="s">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B89" t="s">
@@ -3730,8 +3752,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
-      <c r="A90" t="s">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
         <v>88</v>
       </c>
       <c r="B90" t="s">
@@ -3756,8 +3778,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
-      <c r="A91" t="s">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B91" t="s">
@@ -3785,8 +3807,8 @@
         <v>228</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
-      <c r="A92" t="s">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B92" t="s">
@@ -3814,8 +3836,8 @@
         <v>229</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
-      <c r="A93" t="s">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B93" t="s">
@@ -3843,8 +3865,8 @@
         <v>230</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
-      <c r="A94" t="s">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
         <v>89</v>
       </c>
       <c r="B94" t="s">
@@ -3872,8 +3894,8 @@
         <v>231</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
-      <c r="A95" t="s">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B95" t="s">
@@ -3901,8 +3923,8 @@
         <v>232</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
-      <c r="A96" t="s">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B96" t="s">
@@ -3930,8 +3952,8 @@
         <v>233</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
-      <c r="A97" t="s">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
         <v>90</v>
       </c>
       <c r="B97" t="s">
@@ -3959,8 +3981,8 @@
         <v>234</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
-      <c r="A98" t="s">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B98" t="s">
@@ -3985,8 +4007,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
-      <c r="A99" t="s">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B99" t="s">
@@ -4014,8 +4036,8 @@
         <v>235</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
-      <c r="A100" t="s">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B100" t="s">
@@ -4043,8 +4065,8 @@
         <v>236</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
-      <c r="A101" t="s">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B101" t="s">
@@ -4069,8 +4091,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
-      <c r="A102" t="s">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B102" t="s">
@@ -4098,8 +4120,8 @@
         <v>237</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
-      <c r="A103" t="s">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B103" t="s">
@@ -4127,8 +4149,8 @@
         <v>238</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
-      <c r="A104" t="s">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B104" t="s">
@@ -4156,8 +4178,8 @@
         <v>239</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
-      <c r="A105" t="s">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B105" t="s">
@@ -4185,8 +4207,8 @@
         <v>240</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
-      <c r="A106" t="s">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B106" t="s">
@@ -4214,8 +4236,8 @@
         <v>241</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
-      <c r="A107" t="s">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B107" t="s">
@@ -4243,8 +4265,8 @@
         <v>242</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
-      <c r="A108" t="s">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B108" t="s">
@@ -4272,8 +4294,8 @@
         <v>243</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
-      <c r="A109" t="s">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B109" t="s">
@@ -4301,8 +4323,8 @@
         <v>244</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
-      <c r="A110" t="s">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B110" t="s">
@@ -4330,8 +4352,8 @@
         <v>245</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
-      <c r="A111" t="s">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B111" t="s">
@@ -4359,8 +4381,8 @@
         <v>246</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
-      <c r="A112" t="s">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
         <v>94</v>
       </c>
       <c r="B112" t="s">
@@ -4385,8 +4407,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
-      <c r="A113" t="s">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B113" t="s">
@@ -4414,8 +4436,8 @@
         <v>247</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
-      <c r="A114" t="s">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B114" t="s">
@@ -4443,8 +4465,8 @@
         <v>230</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
-      <c r="A115" t="s">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B115" t="s">
@@ -4472,8 +4494,8 @@
         <v>248</v>
       </c>
     </row>
-    <row r="116" spans="1:9">
-      <c r="A116" t="s">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B116" t="s">
@@ -4501,8 +4523,8 @@
         <v>249</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
-      <c r="A117" t="s">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B117" t="s">
@@ -4527,8 +4549,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
-      <c r="A118" t="s">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B118" t="s">
@@ -4553,8 +4575,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
-      <c r="A119" t="s">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B119" t="s">
@@ -4582,8 +4604,8 @@
         <v>250</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
-      <c r="A120" t="s">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B120" t="s">
@@ -4611,8 +4633,8 @@
         <v>251</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
-      <c r="A121" t="s">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B121" t="s">
@@ -4640,8 +4662,8 @@
         <v>252</v>
       </c>
     </row>
-    <row r="122" spans="1:9">
-      <c r="A122" t="s">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B122" t="s">
@@ -4666,8 +4688,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="123" spans="1:9">
-      <c r="A123" t="s">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B123" t="s">
@@ -4692,8 +4714,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="124" spans="1:9">
-      <c r="A124" t="s">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B124" t="s">
@@ -4721,8 +4743,8 @@
         <v>253</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
-      <c r="A125" t="s">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B125" t="s">
@@ -4747,8 +4769,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="126" spans="1:9">
-      <c r="A126" t="s">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B126" t="s">
@@ -4773,8 +4795,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="127" spans="1:9">
-      <c r="A127" t="s">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B127" t="s">
@@ -4799,8 +4821,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="128" spans="1:9">
-      <c r="A128" t="s">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
         <v>96</v>
       </c>
       <c r="B128" t="s">
@@ -4828,8 +4850,8 @@
         <v>254</v>
       </c>
     </row>
-    <row r="129" spans="1:9">
-      <c r="A129" t="s">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B129" t="s">
@@ -4854,8 +4876,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
-      <c r="A130" t="s">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B130" t="s">
@@ -4880,8 +4902,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="131" spans="1:9">
-      <c r="A131" t="s">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B131" t="s">
@@ -4906,8 +4928,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
-      <c r="A132" t="s">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
         <v>98</v>
       </c>
       <c r="B132" t="s">
@@ -4935,8 +4957,8 @@
         <v>255</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
-      <c r="A133" t="s">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
         <v>99</v>
       </c>
       <c r="B133" t="s">
@@ -4964,8 +4986,8 @@
         <v>256</v>
       </c>
     </row>
-    <row r="134" spans="1:9">
-      <c r="A134" t="s">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B134" t="s">
@@ -4990,8 +5012,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="135" spans="1:9">
-      <c r="A135" t="s">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B135" t="s">
@@ -5016,8 +5038,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
-      <c r="A136" t="s">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
         <v>100</v>
       </c>
       <c r="B136" t="s">
@@ -5045,8 +5067,8 @@
         <v>257</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
-      <c r="A137" t="s">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
         <v>101</v>
       </c>
       <c r="B137" t="s">
@@ -5074,8 +5096,8 @@
         <v>258</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
-      <c r="A138" t="s">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B138" t="s">
@@ -5100,8 +5122,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
-      <c r="A139" t="s">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
         <v>102</v>
       </c>
       <c r="B139" t="s">
@@ -5129,8 +5151,8 @@
         <v>259</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
-      <c r="A140" t="s">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B140" t="s">
@@ -5158,8 +5180,8 @@
         <v>260</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
-      <c r="A141" t="s">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B141" t="s">
@@ -5184,8 +5206,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="142" spans="1:9">
-      <c r="A142" t="s">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B142" t="s">
@@ -5213,8 +5235,8 @@
         <v>261</v>
       </c>
     </row>
-    <row r="143" spans="1:9">
-      <c r="A143" t="s">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B143" t="s">
@@ -5242,8 +5264,8 @@
         <v>262</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
-      <c r="A144" t="s">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
         <v>103</v>
       </c>
       <c r="B144" t="s">
@@ -5271,8 +5293,8 @@
         <v>263</v>
       </c>
     </row>
-    <row r="145" spans="1:9">
-      <c r="A145" t="s">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B145" t="s">
@@ -5300,8 +5322,8 @@
         <v>264</v>
       </c>
     </row>
-    <row r="146" spans="1:9">
-      <c r="A146" t="s">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B146" t="s">
@@ -5329,8 +5351,8 @@
         <v>265</v>
       </c>
     </row>
-    <row r="147" spans="1:9">
-      <c r="A147" t="s">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
         <v>104</v>
       </c>
       <c r="B147" t="s">
@@ -5358,8 +5380,8 @@
         <v>266</v>
       </c>
     </row>
-    <row r="148" spans="1:9">
-      <c r="A148" t="s">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B148" t="s">
@@ -5384,8 +5406,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="149" spans="1:9">
-      <c r="A149" t="s">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B149" t="s">
@@ -5413,8 +5435,8 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:9">
-      <c r="A150" t="s">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B150" t="s">
@@ -5439,8 +5461,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="151" spans="1:9">
-      <c r="A151" t="s">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B151" t="s">
@@ -5465,8 +5487,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="152" spans="1:9">
-      <c r="A152" t="s">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B152" t="s">
@@ -5494,8 +5516,8 @@
         <v>268</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
-      <c r="A153" t="s">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B153" t="s">
@@ -5523,8 +5545,8 @@
         <v>269</v>
       </c>
     </row>
-    <row r="154" spans="1:9">
-      <c r="A154" t="s">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B154" t="s">
@@ -5552,8 +5574,8 @@
         <v>270</v>
       </c>
     </row>
-    <row r="155" spans="1:9">
-      <c r="A155" t="s">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B155" t="s">
@@ -5581,8 +5603,8 @@
         <v>230</v>
       </c>
     </row>
-    <row r="156" spans="1:9">
-      <c r="A156" t="s">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B156" t="s">
@@ -5610,8 +5632,8 @@
         <v>271</v>
       </c>
     </row>
-    <row r="157" spans="1:9">
-      <c r="A157" t="s">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B157" t="s">
@@ -5636,8 +5658,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="158" spans="1:9">
-      <c r="A158" t="s">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B158" t="s">
@@ -5662,8 +5684,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="159" spans="1:9">
-      <c r="A159" t="s">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B159" t="s">
@@ -5688,8 +5710,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
-      <c r="A160" t="s">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B160" t="s">
@@ -5717,8 +5739,8 @@
         <v>273</v>
       </c>
     </row>
-    <row r="161" spans="1:9">
-      <c r="A161" t="s">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B161" t="s">
@@ -5746,8 +5768,8 @@
         <v>274</v>
       </c>
     </row>
-    <row r="162" spans="1:9">
-      <c r="A162" t="s">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B162" t="s">
@@ -5772,8 +5794,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="163" spans="1:9">
-      <c r="A163" t="s">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B163" t="s">
@@ -5801,8 +5823,8 @@
         <v>275</v>
       </c>
     </row>
-    <row r="164" spans="1:9">
-      <c r="A164" t="s">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B164" t="s">
@@ -5827,8 +5849,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="165" spans="1:9">
-      <c r="A165" t="s">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B165" t="s">
@@ -5856,8 +5878,8 @@
         <v>276</v>
       </c>
     </row>
-    <row r="166" spans="1:9">
-      <c r="A166" t="s">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B166" t="s">
@@ -5885,8 +5907,8 @@
         <v>277</v>
       </c>
     </row>
-    <row r="167" spans="1:9">
-      <c r="A167" t="s">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B167" t="s">
@@ -5914,8 +5936,8 @@
         <v>278</v>
       </c>
     </row>
-    <row r="168" spans="1:9">
-      <c r="A168" t="s">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B168" t="s">
@@ -5940,8 +5962,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="169" spans="1:9">
-      <c r="A169" t="s">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B169" t="s">
@@ -5969,8 +5991,8 @@
         <v>279</v>
       </c>
     </row>
-    <row r="170" spans="1:9">
-      <c r="A170" t="s">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B170" t="s">
@@ -5995,8 +6017,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="171" spans="1:9">
-      <c r="A171" t="s">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B171" t="s">
@@ -6024,8 +6046,8 @@
         <v>280</v>
       </c>
     </row>
-    <row r="172" spans="1:9">
-      <c r="A172" t="s">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B172" t="s">
@@ -6053,8 +6075,8 @@
         <v>281</v>
       </c>
     </row>
-    <row r="173" spans="1:9">
-      <c r="A173" t="s">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B173" t="s">
@@ -6082,8 +6104,8 @@
         <v>282</v>
       </c>
     </row>
-    <row r="174" spans="1:9">
-      <c r="A174" t="s">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B174" t="s">
@@ -6111,8 +6133,8 @@
         <v>283</v>
       </c>
     </row>
-    <row r="175" spans="1:9">
-      <c r="A175" t="s">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B175" t="s">
@@ -6140,8 +6162,8 @@
         <v>284</v>
       </c>
     </row>
-    <row r="176" spans="1:9">
-      <c r="A176" t="s">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B176" t="s">
@@ -6169,8 +6191,8 @@
         <v>285</v>
       </c>
     </row>
-    <row r="177" spans="1:9">
-      <c r="A177" t="s">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B177" t="s">
@@ -6198,8 +6220,8 @@
         <v>286</v>
       </c>
     </row>
-    <row r="178" spans="1:9">
-      <c r="A178" t="s">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B178" t="s">
@@ -6227,8 +6249,8 @@
         <v>287</v>
       </c>
     </row>
-    <row r="179" spans="1:9">
-      <c r="A179" t="s">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B179" t="s">
@@ -6256,8 +6278,8 @@
         <v>288</v>
       </c>
     </row>
-    <row r="180" spans="1:9">
-      <c r="A180" t="s">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B180" t="s">
@@ -6285,8 +6307,8 @@
         <v>289</v>
       </c>
     </row>
-    <row r="181" spans="1:9">
-      <c r="A181" t="s">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B181" t="s">
@@ -6314,8 +6336,8 @@
         <v>290</v>
       </c>
     </row>
-    <row r="182" spans="1:9">
-      <c r="A182" t="s">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B182" t="s">
@@ -6343,8 +6365,8 @@
         <v>291</v>
       </c>
     </row>
-    <row r="183" spans="1:9">
-      <c r="A183" t="s">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B183" t="s">
@@ -6372,8 +6394,8 @@
         <v>292</v>
       </c>
     </row>
-    <row r="184" spans="1:9">
-      <c r="A184" t="s">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B184" t="s">
@@ -6398,8 +6420,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="185" spans="1:9">
-      <c r="A185" t="s">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B185" t="s">
@@ -6424,8 +6446,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="186" spans="1:9">
-      <c r="A186" t="s">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B186" t="s">
@@ -6453,8 +6475,8 @@
         <v>293</v>
       </c>
     </row>
-    <row r="187" spans="1:9">
-      <c r="A187" t="s">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B187" t="s">
@@ -6482,8 +6504,8 @@
         <v>294</v>
       </c>
     </row>
-    <row r="188" spans="1:9">
-      <c r="A188" t="s">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B188" t="s">
@@ -6511,8 +6533,8 @@
         <v>295</v>
       </c>
     </row>
-    <row r="189" spans="1:9">
-      <c r="A189" t="s">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B189" t="s">
@@ -6540,8 +6562,8 @@
         <v>296</v>
       </c>
     </row>
-    <row r="190" spans="1:9">
-      <c r="A190" t="s">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B190" t="s">
@@ -6566,8 +6588,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="191" spans="1:9">
-      <c r="A191" t="s">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B191" t="s">
@@ -6592,8 +6614,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="192" spans="1:9">
-      <c r="A192" t="s">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B192" t="s">
@@ -6621,8 +6643,8 @@
         <v>297</v>
       </c>
     </row>
-    <row r="193" spans="1:9">
-      <c r="A193" t="s">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B193" t="s">
@@ -6650,8 +6672,8 @@
         <v>298</v>
       </c>
     </row>
-    <row r="194" spans="1:9">
-      <c r="A194" t="s">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B194" t="s">
@@ -6679,8 +6701,8 @@
         <v>299</v>
       </c>
     </row>
-    <row r="195" spans="1:9">
-      <c r="A195" t="s">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B195" t="s">
@@ -6708,8 +6730,8 @@
         <v>300</v>
       </c>
     </row>
-    <row r="196" spans="1:9">
-      <c r="A196" t="s">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B196" t="s">
@@ -6737,8 +6759,8 @@
         <v>301</v>
       </c>
     </row>
-    <row r="197" spans="1:9">
-      <c r="A197" t="s">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B197" t="s">
@@ -6766,8 +6788,8 @@
         <v>302</v>
       </c>
     </row>
-    <row r="198" spans="1:9">
-      <c r="A198" t="s">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B198" t="s">
@@ -6792,8 +6814,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="199" spans="1:9">
-      <c r="A199" t="s">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B199" t="s">
@@ -6821,8 +6843,8 @@
         <v>303</v>
       </c>
     </row>
-    <row r="200" spans="1:9">
-      <c r="A200" t="s">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B200" t="s">
@@ -6850,8 +6872,8 @@
         <v>304</v>
       </c>
     </row>
-    <row r="201" spans="1:9">
-      <c r="A201" t="s">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
         <v>106</v>
       </c>
       <c r="B201" t="s">
@@ -6879,8 +6901,8 @@
         <v>305</v>
       </c>
     </row>
-    <row r="202" spans="1:9">
-      <c r="A202" t="s">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B202" t="s">
@@ -6905,8 +6927,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="203" spans="1:9">
-      <c r="A203" t="s">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B203" t="s">
@@ -6934,8 +6956,8 @@
         <v>306</v>
       </c>
     </row>
-    <row r="204" spans="1:9">
-      <c r="A204" t="s">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B204" t="s">
@@ -6960,8 +6982,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="205" spans="1:9">
-      <c r="A205" t="s">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B205" t="s">
@@ -6986,8 +7008,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="206" spans="1:9">
-      <c r="A206" t="s">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B206" t="s">
@@ -7015,8 +7037,8 @@
         <v>307</v>
       </c>
     </row>
-    <row r="207" spans="1:9">
-      <c r="A207" t="s">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B207" t="s">
@@ -7044,8 +7066,8 @@
         <v>308</v>
       </c>
     </row>
-    <row r="208" spans="1:9">
-      <c r="A208" t="s">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B208" t="s">
@@ -7073,8 +7095,8 @@
         <v>309</v>
       </c>
     </row>
-    <row r="209" spans="1:9">
-      <c r="A209" t="s">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B209" t="s">
@@ -7102,8 +7124,8 @@
         <v>310</v>
       </c>
     </row>
-    <row r="210" spans="1:9">
-      <c r="A210" t="s">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B210" t="s">
@@ -7128,8 +7150,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="211" spans="1:9">
-      <c r="A211" t="s">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B211" t="s">
@@ -7157,8 +7179,8 @@
         <v>311</v>
       </c>
     </row>
-    <row r="212" spans="1:9">
-      <c r="A212" t="s">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B212" t="s">
@@ -7183,8 +7205,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="213" spans="1:9">
-      <c r="A213" t="s">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B213" t="s">
@@ -7212,8 +7234,8 @@
         <v>312</v>
       </c>
     </row>
-    <row r="214" spans="1:9">
-      <c r="A214" t="s">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B214" t="s">
@@ -7241,8 +7263,8 @@
         <v>313</v>
       </c>
     </row>
-    <row r="215" spans="1:9">
-      <c r="A215" t="s">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B215" t="s">
@@ -7270,8 +7292,8 @@
         <v>314</v>
       </c>
     </row>
-    <row r="216" spans="1:9">
-      <c r="A216" t="s">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B216" t="s">
@@ -7299,8 +7321,8 @@
         <v>315</v>
       </c>
     </row>
-    <row r="217" spans="1:9">
-      <c r="A217" t="s">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B217" t="s">
@@ -7325,8 +7347,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="218" spans="1:9">
-      <c r="A218" t="s">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B218" t="s">
@@ -7354,8 +7376,8 @@
         <v>316</v>
       </c>
     </row>
-    <row r="219" spans="1:9">
-      <c r="A219" t="s">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B219" t="s">
@@ -7383,8 +7405,8 @@
         <v>317</v>
       </c>
     </row>
-    <row r="220" spans="1:9">
-      <c r="A220" t="s">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B220" t="s">
@@ -7409,8 +7431,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="221" spans="1:9">
-      <c r="A221" t="s">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B221" t="s">
@@ -7435,8 +7457,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="222" spans="1:9">
-      <c r="A222" t="s">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B222" t="s">
@@ -7464,8 +7486,8 @@
         <v>313</v>
       </c>
     </row>
-    <row r="223" spans="1:9">
-      <c r="A223" t="s">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B223" t="s">
@@ -7493,8 +7515,8 @@
         <v>318</v>
       </c>
     </row>
-    <row r="224" spans="1:9">
-      <c r="A224" t="s">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B224" t="s">
@@ -7522,8 +7544,8 @@
         <v>319</v>
       </c>
     </row>
-    <row r="225" spans="1:9">
-      <c r="A225" t="s">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B225" t="s">
@@ -7551,8 +7573,8 @@
         <v>320</v>
       </c>
     </row>
-    <row r="226" spans="1:9">
-      <c r="A226" t="s">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B226" t="s">
@@ -7580,8 +7602,8 @@
         <v>321</v>
       </c>
     </row>
-    <row r="227" spans="1:9">
-      <c r="A227" t="s">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B227" t="s">
@@ -7609,8 +7631,8 @@
         <v>322</v>
       </c>
     </row>
-    <row r="228" spans="1:9">
-      <c r="A228" t="s">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B228" t="s">
@@ -7638,8 +7660,8 @@
         <v>323</v>
       </c>
     </row>
-    <row r="229" spans="1:9">
-      <c r="A229" t="s">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B229" t="s">
@@ -7667,8 +7689,8 @@
         <v>324</v>
       </c>
     </row>
-    <row r="230" spans="1:9">
-      <c r="A230" t="s">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B230" t="s">
@@ -7696,8 +7718,8 @@
         <v>325</v>
       </c>
     </row>
-    <row r="231" spans="1:9">
-      <c r="A231" t="s">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B231" t="s">
@@ -7725,8 +7747,8 @@
         <v>326</v>
       </c>
     </row>
-    <row r="232" spans="1:9">
-      <c r="A232" t="s">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B232" t="s">
@@ -7754,8 +7776,8 @@
         <v>327</v>
       </c>
     </row>
-    <row r="233" spans="1:9">
-      <c r="A233" t="s">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B233" t="s">
@@ -7783,8 +7805,8 @@
         <v>328</v>
       </c>
     </row>
-    <row r="234" spans="1:9">
-      <c r="A234" t="s">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B234" t="s">
@@ -7812,8 +7834,8 @@
         <v>329</v>
       </c>
     </row>
-    <row r="235" spans="1:9">
-      <c r="A235" t="s">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B235" t="s">
@@ -7841,8 +7863,8 @@
         <v>330</v>
       </c>
     </row>
-    <row r="236" spans="1:9">
-      <c r="A236" t="s">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B236" t="s">
@@ -7870,8 +7892,8 @@
         <v>331</v>
       </c>
     </row>
-    <row r="237" spans="1:9">
-      <c r="A237" t="s">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
         <v>98</v>
       </c>
       <c r="B237" t="s">
@@ -7899,8 +7921,8 @@
         <v>332</v>
       </c>
     </row>
-    <row r="238" spans="1:9">
-      <c r="A238" t="s">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
         <v>99</v>
       </c>
       <c r="B238" t="s">
@@ -7928,8 +7950,8 @@
         <v>333</v>
       </c>
     </row>
-    <row r="239" spans="1:9">
-      <c r="A239" t="s">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B239" t="s">
@@ -7957,8 +7979,8 @@
         <v>334</v>
       </c>
     </row>
-    <row r="240" spans="1:9">
-      <c r="A240" t="s">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
         <v>100</v>
       </c>
       <c r="B240" t="s">
@@ -7986,8 +8008,8 @@
         <v>335</v>
       </c>
     </row>
-    <row r="241" spans="1:9">
-      <c r="A241" t="s">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
         <v>101</v>
       </c>
       <c r="B241" t="s">
@@ -8015,8 +8037,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="242" spans="1:9">
-      <c r="A242" t="s">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
         <v>102</v>
       </c>
       <c r="B242" t="s">
@@ -8044,8 +8066,8 @@
         <v>337</v>
       </c>
     </row>
-    <row r="243" spans="1:9">
-      <c r="A243" t="s">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B243" t="s">
@@ -8073,8 +8095,8 @@
         <v>338</v>
       </c>
     </row>
-    <row r="244" spans="1:9">
-      <c r="A244" t="s">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
         <v>84</v>
       </c>
       <c r="B244" t="s">
@@ -8102,8 +8124,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="245" spans="1:9">
-      <c r="A245" t="s">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B245" t="s">
@@ -8131,8 +8153,8 @@
         <v>339</v>
       </c>
     </row>
-    <row r="246" spans="1:9">
-      <c r="A246" t="s">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B246" t="s">
@@ -8160,8 +8182,8 @@
         <v>340</v>
       </c>
     </row>
-    <row r="247" spans="1:9">
-      <c r="A247" t="s">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B247" t="s">
@@ -8189,8 +8211,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="248" spans="1:9">
-      <c r="A248" t="s">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
         <v>85</v>
       </c>
       <c r="B248" t="s">
@@ -8218,8 +8240,8 @@
         <v>341</v>
       </c>
     </row>
-    <row r="249" spans="1:9">
-      <c r="A249" t="s">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
         <v>87</v>
       </c>
       <c r="B249" t="s">
@@ -8247,8 +8269,8 @@
         <v>342</v>
       </c>
     </row>
-    <row r="250" spans="1:9">
-      <c r="A250" t="s">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B250" t="s">
@@ -8276,8 +8298,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="251" spans="1:9">
-      <c r="A251" t="s">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B251" t="s">
@@ -8305,8 +8327,8 @@
         <v>343</v>
       </c>
     </row>
-    <row r="252" spans="1:9">
-      <c r="A252" t="s">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B252" t="s">
@@ -8334,8 +8356,8 @@
         <v>344</v>
       </c>
     </row>
-    <row r="253" spans="1:9">
-      <c r="A253" t="s">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B253" t="s">
@@ -8363,8 +8385,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="254" spans="1:9">
-      <c r="A254" t="s">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B254" t="s">
@@ -8392,8 +8414,8 @@
         <v>346</v>
       </c>
     </row>
-    <row r="255" spans="1:9">
-      <c r="A255" t="s">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
         <v>103</v>
       </c>
       <c r="B255" t="s">
@@ -8421,8 +8443,8 @@
         <v>347</v>
       </c>
     </row>
-    <row r="256" spans="1:9">
-      <c r="A256" t="s">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B256" t="s">
@@ -8450,8 +8472,8 @@
         <v>348</v>
       </c>
     </row>
-    <row r="257" spans="1:9">
-      <c r="A257" t="s">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
         <v>89</v>
       </c>
       <c r="B257" t="s">
@@ -8479,8 +8501,8 @@
         <v>349</v>
       </c>
     </row>
-    <row r="258" spans="1:9">
-      <c r="A258" t="s">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B258" t="s">
@@ -8508,8 +8530,8 @@
         <v>350</v>
       </c>
     </row>
-    <row r="259" spans="1:9">
-      <c r="A259" t="s">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
         <v>104</v>
       </c>
       <c r="B259" t="s">
@@ -8537,8 +8559,8 @@
         <v>351</v>
       </c>
     </row>
-    <row r="260" spans="1:9">
-      <c r="A260" t="s">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B260" t="s">
@@ -8566,8 +8588,8 @@
         <v>352</v>
       </c>
     </row>
-    <row r="261" spans="1:9">
-      <c r="A261" t="s">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B261" t="s">
@@ -8595,8 +8617,8 @@
         <v>353</v>
       </c>
     </row>
-    <row r="262" spans="1:9">
-      <c r="A262" t="s">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B262" t="s">
@@ -8624,8 +8646,8 @@
         <v>354</v>
       </c>
     </row>
-    <row r="263" spans="1:9">
-      <c r="A263" t="s">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B263" t="s">
@@ -8653,8 +8675,8 @@
         <v>355</v>
       </c>
     </row>
-    <row r="264" spans="1:9">
-      <c r="A264" t="s">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B264" t="s">
@@ -8682,8 +8704,8 @@
         <v>356</v>
       </c>
     </row>
-    <row r="265" spans="1:9">
-      <c r="A265" t="s">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B265" t="s">
@@ -8711,8 +8733,8 @@
         <v>357</v>
       </c>
     </row>
-    <row r="266" spans="1:9">
-      <c r="A266" t="s">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B266" t="s">
@@ -8740,8 +8762,8 @@
         <v>358</v>
       </c>
     </row>
-    <row r="267" spans="1:9">
-      <c r="A267" t="s">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B267" t="s">
@@ -8769,8 +8791,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="268" spans="1:9">
-      <c r="A268" t="s">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A268" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B268" t="s">
@@ -8798,8 +8820,8 @@
         <v>359</v>
       </c>
     </row>
-    <row r="269" spans="1:9">
-      <c r="A269" t="s">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B269" t="s">
@@ -8827,8 +8849,8 @@
         <v>360</v>
       </c>
     </row>
-    <row r="270" spans="1:9">
-      <c r="A270" t="s">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B270" t="s">
@@ -8856,8 +8878,8 @@
         <v>361</v>
       </c>
     </row>
-    <row r="271" spans="1:9">
-      <c r="A271" t="s">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A271" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B271" t="s">
@@ -8885,8 +8907,8 @@
         <v>362</v>
       </c>
     </row>
-    <row r="272" spans="1:9">
-      <c r="A272" t="s">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A272" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B272" t="s">
@@ -8914,8 +8936,8 @@
         <v>363</v>
       </c>
     </row>
-    <row r="273" spans="1:9">
-      <c r="A273" t="s">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B273" t="s">
@@ -8943,8 +8965,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="274" spans="1:9">
-      <c r="A274" t="s">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B274" t="s">
@@ -8972,8 +8994,8 @@
         <v>364</v>
       </c>
     </row>
-    <row r="275" spans="1:9">
-      <c r="A275" t="s">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A275" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B275" t="s">
@@ -9001,8 +9023,8 @@
         <v>365</v>
       </c>
     </row>
-    <row r="276" spans="1:9">
-      <c r="A276" t="s">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A276" s="1" t="s">
         <v>94</v>
       </c>
       <c r="B276" t="s">
@@ -9030,8 +9052,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="277" spans="1:9">
-      <c r="A277" t="s">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A277" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B277" t="s">
@@ -9059,8 +9081,8 @@
         <v>366</v>
       </c>
     </row>
-    <row r="278" spans="1:9">
-      <c r="A278" t="s">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A278" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B278" t="s">
@@ -9088,8 +9110,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="279" spans="1:9">
-      <c r="A279" t="s">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A279" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B279" t="s">
@@ -9117,8 +9139,8 @@
         <v>367</v>
       </c>
     </row>
-    <row r="280" spans="1:9">
-      <c r="A280" t="s">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A280" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B280" t="s">
@@ -9146,8 +9168,8 @@
         <v>368</v>
       </c>
     </row>
-    <row r="281" spans="1:9">
-      <c r="A281" t="s">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A281" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B281" t="s">
@@ -9175,8 +9197,8 @@
         <v>369</v>
       </c>
     </row>
-    <row r="282" spans="1:9">
-      <c r="A282" t="s">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A282" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B282" t="s">
@@ -9204,8 +9226,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="283" spans="1:9">
-      <c r="A283" t="s">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A283" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B283" t="s">
@@ -9233,8 +9255,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="284" spans="1:9">
-      <c r="A284" t="s">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A284" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B284" t="s">
@@ -9262,8 +9284,8 @@
         <v>371</v>
       </c>
     </row>
-    <row r="285" spans="1:9">
-      <c r="A285" t="s">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A285" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B285" t="s">
@@ -9291,8 +9313,8 @@
         <v>372</v>
       </c>
     </row>
-    <row r="286" spans="1:9">
-      <c r="A286" t="s">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A286" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B286" t="s">
@@ -9320,8 +9342,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="287" spans="1:9">
-      <c r="A287" t="s">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A287" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B287" t="s">
@@ -9349,8 +9371,8 @@
         <v>373</v>
       </c>
     </row>
-    <row r="288" spans="1:9">
-      <c r="A288" t="s">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A288" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B288" t="s">
@@ -9378,8 +9400,8 @@
         <v>374</v>
       </c>
     </row>
-    <row r="289" spans="1:9">
-      <c r="A289" t="s">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A289" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B289" t="s">
@@ -9404,8 +9426,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="290" spans="1:9">
-      <c r="A290" t="s">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A290" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B290" t="s">
@@ -9433,8 +9455,8 @@
         <v>375</v>
       </c>
     </row>
-    <row r="291" spans="1:9">
-      <c r="A291" t="s">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A291" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B291" t="s">
@@ -9462,8 +9484,8 @@
         <v>376</v>
       </c>
     </row>
-    <row r="292" spans="1:9">
-      <c r="A292" t="s">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A292" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B292" t="s">
@@ -9491,8 +9513,8 @@
         <v>377</v>
       </c>
     </row>
-    <row r="293" spans="1:9">
-      <c r="A293" t="s">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A293" s="1" t="s">
         <v>84</v>
       </c>
       <c r="B293" t="s">
@@ -9520,8 +9542,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="294" spans="1:9">
-      <c r="A294" t="s">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A294" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B294" t="s">
@@ -9546,8 +9568,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="295" spans="1:9">
-      <c r="A295" t="s">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A295" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B295" t="s">
@@ -9575,8 +9597,8 @@
         <v>378</v>
       </c>
     </row>
-    <row r="296" spans="1:9">
-      <c r="A296" t="s">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A296" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B296" t="s">
@@ -9604,8 +9626,8 @@
         <v>379</v>
       </c>
     </row>
-    <row r="297" spans="1:9">
-      <c r="A297" t="s">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A297" s="1" t="s">
         <v>85</v>
       </c>
       <c r="B297" t="s">
@@ -9633,8 +9655,8 @@
         <v>380</v>
       </c>
     </row>
-    <row r="298" spans="1:9">
-      <c r="A298" t="s">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A298" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B298" t="s">
@@ -9659,8 +9681,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="299" spans="1:9">
-      <c r="A299" t="s">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A299" s="1" t="s">
         <v>87</v>
       </c>
       <c r="B299" t="s">
@@ -9688,8 +9710,8 @@
         <v>381</v>
       </c>
     </row>
-    <row r="300" spans="1:9">
-      <c r="A300" t="s">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A300" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B300" t="s">
@@ -9714,8 +9736,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="301" spans="1:9">
-      <c r="A301" t="s">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B301" t="s">
@@ -9743,8 +9765,8 @@
         <v>382</v>
       </c>
     </row>
-    <row r="302" spans="1:9">
-      <c r="A302" t="s">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A302" s="1" t="s">
         <v>88</v>
       </c>
       <c r="B302" t="s">
@@ -9772,8 +9794,8 @@
         <v>334</v>
       </c>
     </row>
-    <row r="303" spans="1:9">
-      <c r="A303" t="s">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B303" t="s">
@@ -9801,8 +9823,8 @@
         <v>383</v>
       </c>
     </row>
-    <row r="304" spans="1:9">
-      <c r="A304" t="s">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A304" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B304" t="s">
@@ -9827,8 +9849,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="305" spans="1:9">
-      <c r="A305" t="s">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A305" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B305" t="s">
@@ -9856,8 +9878,8 @@
         <v>384</v>
       </c>
     </row>
-    <row r="306" spans="1:9">
-      <c r="A306" t="s">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A306" s="1" t="s">
         <v>89</v>
       </c>
       <c r="B306" t="s">
@@ -9885,8 +9907,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="307" spans="1:9">
-      <c r="A307" t="s">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A307" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B307" t="s">
@@ -9914,8 +9936,8 @@
         <v>386</v>
       </c>
     </row>
-    <row r="308" spans="1:9">
-      <c r="A308" t="s">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A308" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B308" t="s">
@@ -9943,8 +9965,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="309" spans="1:9">
-      <c r="A309" t="s">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
         <v>90</v>
       </c>
       <c r="B309" t="s">
@@ -9969,8 +9991,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="310" spans="1:9">
-      <c r="A310" t="s">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A310" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B310" t="s">
@@ -9995,8 +10017,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="311" spans="1:9">
-      <c r="A311" t="s">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A311" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B311" t="s">
@@ -10024,8 +10046,8 @@
         <v>387</v>
       </c>
     </row>
-    <row r="312" spans="1:9">
-      <c r="A312" t="s">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A312" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B312" t="s">
@@ -10053,8 +10075,8 @@
         <v>388</v>
       </c>
     </row>
-    <row r="313" spans="1:9">
-      <c r="A313" t="s">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A313" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B313" t="s">
@@ -10082,8 +10104,8 @@
         <v>389</v>
       </c>
     </row>
-    <row r="314" spans="1:9">
-      <c r="A314" t="s">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A314" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B314" t="s">
@@ -10111,8 +10133,8 @@
         <v>390</v>
       </c>
     </row>
-    <row r="315" spans="1:9">
-      <c r="A315" t="s">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A315" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B315" t="s">
@@ -10140,8 +10162,8 @@
         <v>391</v>
       </c>
     </row>
-    <row r="316" spans="1:9">
-      <c r="A316" t="s">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A316" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B316" t="s">
@@ -10169,8 +10191,8 @@
         <v>392</v>
       </c>
     </row>
-    <row r="317" spans="1:9">
-      <c r="A317" t="s">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A317" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B317" t="s">
@@ -10198,8 +10220,8 @@
         <v>334</v>
       </c>
     </row>
-    <row r="318" spans="1:9">
-      <c r="A318" t="s">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A318" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B318" t="s">
@@ -10227,8 +10249,8 @@
         <v>393</v>
       </c>
     </row>
-    <row r="319" spans="1:9">
-      <c r="A319" t="s">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A319" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B319" t="s">
@@ -10256,8 +10278,8 @@
         <v>394</v>
       </c>
     </row>
-    <row r="320" spans="1:9">
-      <c r="A320" t="s">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A320" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B320" t="s">
@@ -10285,8 +10307,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="321" spans="1:9">
-      <c r="A321" t="s">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A321" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B321" t="s">
@@ -10314,8 +10336,8 @@
         <v>395</v>
       </c>
     </row>
-    <row r="322" spans="1:9">
-      <c r="A322" t="s">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A322" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B322" t="s">
@@ -10343,8 +10365,8 @@
         <v>396</v>
       </c>
     </row>
-    <row r="323" spans="1:9">
-      <c r="A323" t="s">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A323" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B323" t="s">
@@ -10369,8 +10391,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="324" spans="1:9">
-      <c r="A324" t="s">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A324" s="1" t="s">
         <v>94</v>
       </c>
       <c r="B324" t="s">
@@ -10398,8 +10420,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="325" spans="1:9">
-      <c r="A325" t="s">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B325" t="s">
@@ -10427,8 +10449,8 @@
         <v>397</v>
       </c>
     </row>
-    <row r="326" spans="1:9">
-      <c r="A326" t="s">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A326" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B326" t="s">
@@ -10456,8 +10478,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="327" spans="1:9">
-      <c r="A327" t="s">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A327" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B327" t="s">
@@ -10485,8 +10507,8 @@
         <v>398</v>
       </c>
     </row>
-    <row r="328" spans="1:9">
-      <c r="A328" t="s">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A328" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B328" t="s">
@@ -10514,8 +10536,8 @@
         <v>399</v>
       </c>
     </row>
-    <row r="329" spans="1:9">
-      <c r="A329" t="s">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A329" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B329" t="s">
@@ -10543,8 +10565,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="330" spans="1:9">
-      <c r="A330" t="s">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A330" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B330" t="s">
@@ -10569,8 +10591,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="331" spans="1:9">
-      <c r="A331" t="s">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A331" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B331" t="s">
@@ -10598,8 +10620,8 @@
         <v>400</v>
       </c>
     </row>
-    <row r="332" spans="1:9">
-      <c r="A332" t="s">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A332" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B332" t="s">
@@ -10627,8 +10649,8 @@
         <v>401</v>
       </c>
     </row>
-    <row r="333" spans="1:9">
-      <c r="A333" t="s">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A333" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B333" t="s">
@@ -10656,8 +10678,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="334" spans="1:9">
-      <c r="A334" t="s">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A334" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B334" t="s">
@@ -10682,8 +10704,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="335" spans="1:9">
-      <c r="A335" t="s">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A335" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B335" t="s">
@@ -10708,8 +10730,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="336" spans="1:9">
-      <c r="A336" t="s">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A336" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B336" t="s">
@@ -10734,8 +10756,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="337" spans="1:9">
-      <c r="A337" t="s">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A337" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B337" t="s">
@@ -10760,8 +10782,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="338" spans="1:9">
-      <c r="A338" t="s">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A338" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B338" t="s">
@@ -10786,8 +10808,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="339" spans="1:9">
-      <c r="A339" t="s">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A339" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B339" t="s">
@@ -10812,8 +10834,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="340" spans="1:9">
-      <c r="A340" t="s">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A340" s="1" t="s">
         <v>96</v>
       </c>
       <c r="B340" t="s">
@@ -10838,8 +10860,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="341" spans="1:9">
-      <c r="A341" t="s">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A341" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B341" t="s">
@@ -10864,8 +10886,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="342" spans="1:9">
-      <c r="A342" t="s">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A342" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B342" t="s">
@@ -10890,8 +10912,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="343" spans="1:9">
-      <c r="A343" t="s">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A343" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B343" t="s">
@@ -10916,8 +10938,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="344" spans="1:9">
-      <c r="A344" t="s">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A344" s="1" t="s">
         <v>98</v>
       </c>
       <c r="B344" t="s">
@@ -10942,8 +10964,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="345" spans="1:9">
-      <c r="A345" t="s">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A345" s="1" t="s">
         <v>99</v>
       </c>
       <c r="B345" t="s">
@@ -10968,8 +10990,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="346" spans="1:9">
-      <c r="A346" t="s">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A346" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B346" t="s">
@@ -10994,8 +11016,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="347" spans="1:9">
-      <c r="A347" t="s">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A347" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B347" t="s">
@@ -11020,8 +11042,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="348" spans="1:9">
-      <c r="A348" t="s">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A348" s="1" t="s">
         <v>100</v>
       </c>
       <c r="B348" t="s">
@@ -11046,8 +11068,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="349" spans="1:9">
-      <c r="A349" t="s">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A349" s="1" t="s">
         <v>101</v>
       </c>
       <c r="B349" t="s">
@@ -11072,8 +11094,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="350" spans="1:9">
-      <c r="A350" t="s">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A350" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B350" t="s">
@@ -11098,8 +11120,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="351" spans="1:9">
-      <c r="A351" t="s">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A351" s="1" t="s">
         <v>102</v>
       </c>
       <c r="B351" t="s">
@@ -11124,8 +11146,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="352" spans="1:9">
-      <c r="A352" t="s">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A352" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B352" t="s">
@@ -11150,8 +11172,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="353" spans="1:9">
-      <c r="A353" t="s">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A353" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B353" t="s">
@@ -11176,8 +11198,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="354" spans="1:9">
-      <c r="A354" t="s">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B354" t="s">
@@ -11202,8 +11224,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="355" spans="1:9">
-      <c r="A355" t="s">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A355" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B355" t="s">
@@ -11228,8 +11250,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="356" spans="1:9">
-      <c r="A356" t="s">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A356" s="1" t="s">
         <v>103</v>
       </c>
       <c r="B356" t="s">
@@ -11254,8 +11276,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="357" spans="1:9">
-      <c r="A357" t="s">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A357" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B357" t="s">
@@ -11280,8 +11302,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="358" spans="1:9">
-      <c r="A358" t="s">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A358" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B358" t="s">
@@ -11306,8 +11328,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="359" spans="1:9">
-      <c r="A359" t="s">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A359" s="1" t="s">
         <v>104</v>
       </c>
       <c r="B359" t="s">
@@ -11332,8 +11354,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="360" spans="1:9">
-      <c r="A360" t="s">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A360" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B360" t="s">
@@ -11358,8 +11380,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="361" spans="1:9">
-      <c r="A361" t="s">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A361" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B361" t="s">
@@ -11384,8 +11406,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="362" spans="1:9">
-      <c r="A362" t="s">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A362" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B362" t="s">
@@ -11410,8 +11432,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="363" spans="1:9">
-      <c r="A363" t="s">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A363" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B363" t="s">
@@ -11436,8 +11458,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="364" spans="1:9">
-      <c r="A364" t="s">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A364" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B364" t="s">
@@ -11462,8 +11484,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="365" spans="1:9">
-      <c r="A365" t="s">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A365" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B365" t="s">
@@ -11488,8 +11510,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="366" spans="1:9">
-      <c r="A366" t="s">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A366" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B366" t="s">
@@ -11514,8 +11536,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="367" spans="1:9">
-      <c r="A367" t="s">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A367" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B367" t="s">
@@ -11540,8 +11562,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="368" spans="1:9">
-      <c r="A368" t="s">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A368" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B368" t="s">
@@ -11566,8 +11588,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="369" spans="1:9">
-      <c r="A369" t="s">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A369" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B369" t="s">
@@ -11592,8 +11614,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="370" spans="1:9">
-      <c r="A370" t="s">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A370" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B370" t="s">
@@ -11618,8 +11640,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="371" spans="1:9">
-      <c r="A371" t="s">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A371" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B371" t="s">
@@ -11647,8 +11669,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="372" spans="1:9">
-      <c r="A372" t="s">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A372" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B372" t="s">
@@ -11673,8 +11695,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="373" spans="1:9">
-      <c r="A373" t="s">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A373" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B373" t="s">
@@ -11699,8 +11721,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="374" spans="1:9">
-      <c r="A374" t="s">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A374" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B374" t="s">
@@ -11725,8 +11747,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="375" spans="1:9">
-      <c r="A375" t="s">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A375" s="1" t="s">
         <v>96</v>
       </c>
       <c r="B375" t="s">
@@ -11751,8 +11773,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="376" spans="1:9">
-      <c r="A376" t="s">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A376" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B376" t="s">
@@ -11777,8 +11799,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="377" spans="1:9">
-      <c r="A377" t="s">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A377" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B377" t="s">
@@ -11803,8 +11825,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="378" spans="1:9">
-      <c r="A378" t="s">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A378" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B378" t="s">
@@ -11832,8 +11854,8 @@
         <v>404</v>
       </c>
     </row>
-    <row r="379" spans="1:9">
-      <c r="A379" t="s">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A379" s="1" t="s">
         <v>98</v>
       </c>
       <c r="B379" t="s">
@@ -11861,8 +11883,8 @@
         <v>405</v>
       </c>
     </row>
-    <row r="380" spans="1:9">
-      <c r="A380" t="s">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A380" s="1" t="s">
         <v>99</v>
       </c>
       <c r="B380" t="s">
@@ -11890,8 +11912,8 @@
         <v>406</v>
       </c>
     </row>
-    <row r="381" spans="1:9">
-      <c r="A381" t="s">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A381" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B381" t="s">
@@ -11919,8 +11941,8 @@
         <v>334</v>
       </c>
     </row>
-    <row r="382" spans="1:9">
-      <c r="A382" t="s">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A382" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B382" t="s">
@@ -11945,8 +11967,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="383" spans="1:9">
-      <c r="A383" t="s">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A383" s="1" t="s">
         <v>100</v>
       </c>
       <c r="B383" t="s">
@@ -11974,8 +11996,8 @@
         <v>407</v>
       </c>
     </row>
-    <row r="384" spans="1:9">
-      <c r="A384" t="s">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A384" s="1" t="s">
         <v>101</v>
       </c>
       <c r="B384" t="s">
@@ -12003,8 +12025,8 @@
         <v>408</v>
       </c>
     </row>
-    <row r="385" spans="1:9">
-      <c r="A385" t="s">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A385" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B385" t="s">
@@ -12032,8 +12054,8 @@
         <v>334</v>
       </c>
     </row>
-    <row r="386" spans="1:9">
-      <c r="A386" t="s">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A386" s="1" t="s">
         <v>102</v>
       </c>
       <c r="B386" t="s">
@@ -12061,8 +12083,8 @@
         <v>409</v>
       </c>
     </row>
-    <row r="387" spans="1:9">
-      <c r="A387" t="s">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A387" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B387" t="s">
@@ -12090,8 +12112,8 @@
         <v>410</v>
       </c>
     </row>
-    <row r="388" spans="1:9">
-      <c r="A388" t="s">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A388" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B388" t="s">
@@ -12119,8 +12141,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="389" spans="1:9">
-      <c r="A389" t="s">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A389" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B389" t="s">
@@ -12145,8 +12167,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="390" spans="1:9">
-      <c r="A390" t="s">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A390" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B390" t="s">
@@ -12174,8 +12196,8 @@
         <v>411</v>
       </c>
     </row>
-    <row r="391" spans="1:9">
-      <c r="A391" t="s">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A391" s="1" t="s">
         <v>103</v>
       </c>
       <c r="B391" t="s">
@@ -12203,8 +12225,8 @@
         <v>412</v>
       </c>
     </row>
-    <row r="392" spans="1:9">
-      <c r="A392" t="s">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A392" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B392" t="s">
@@ -12232,8 +12254,8 @@
         <v>413</v>
       </c>
     </row>
-    <row r="393" spans="1:9">
-      <c r="A393" t="s">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A393" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B393" t="s">
@@ -12261,8 +12283,8 @@
         <v>414</v>
       </c>
     </row>
-    <row r="394" spans="1:9">
-      <c r="A394" t="s">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A394" s="1" t="s">
         <v>104</v>
       </c>
       <c r="B394" t="s">
@@ -12290,8 +12312,8 @@
         <v>415</v>
       </c>
     </row>
-    <row r="395" spans="1:9">
-      <c r="A395" t="s">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A395" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B395" t="s">
@@ -12319,8 +12341,8 @@
         <v>416</v>
       </c>
     </row>
-    <row r="396" spans="1:9">
-      <c r="A396" t="s">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A396" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B396" t="s">
@@ -12348,8 +12370,8 @@
         <v>417</v>
       </c>
     </row>
-    <row r="397" spans="1:9">
-      <c r="A397" t="s">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A397" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B397" t="s">
@@ -12374,8 +12396,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="398" spans="1:9">
-      <c r="A398" t="s">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A398" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B398" t="s">
@@ -12403,8 +12425,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="399" spans="1:9">
-      <c r="A399" t="s">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A399" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B399" t="s">
@@ -12429,8 +12451,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="400" spans="1:9">
-      <c r="A400" t="s">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A400" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B400" t="s">
@@ -12458,8 +12480,8 @@
         <v>418</v>
       </c>
     </row>
-    <row r="401" spans="1:9">
-      <c r="A401" t="s">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A401" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B401" t="s">
@@ -12484,8 +12506,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="402" spans="1:9">
-      <c r="A402" t="s">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A402" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B402" t="s">
@@ -12513,8 +12535,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="403" spans="1:9">
-      <c r="A403" t="s">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A403" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B403" t="s">
@@ -12542,7 +12564,8 @@
         <v>419</v>
       </c>
     </row>
-    <row r="404" spans="1:9">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A404" s="1"/>
       <c r="B404" t="s">
         <v>205</v>
       </c>
@@ -12565,8 +12588,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="405" spans="1:9">
-      <c r="A405">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A405" s="1">
         <v>2003743</v>
       </c>
       <c r="B405" t="s">
@@ -12591,8 +12614,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="406" spans="1:9">
-      <c r="A406">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A406" s="1">
         <v>2100421</v>
       </c>
       <c r="B406" t="s">
@@ -12617,8 +12640,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="407" spans="1:9">
-      <c r="A407">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A407" s="1">
         <v>2101812</v>
       </c>
       <c r="B407" t="s">
@@ -12643,8 +12666,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="408" spans="1:9">
-      <c r="A408">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A408" s="1">
         <v>2104775</v>
       </c>
       <c r="B408" t="s">
@@ -12669,8 +12692,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="409" spans="1:9">
-      <c r="A409">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A409" s="1">
         <v>2106789</v>
       </c>
       <c r="B409" t="s">
@@ -12695,8 +12718,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="410" spans="1:9">
-      <c r="A410">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A410" s="1">
         <v>2106808</v>
       </c>
       <c r="B410" t="s">
@@ -12721,8 +12744,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="411" spans="1:9">
-      <c r="A411">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A411" s="1">
         <v>2200601</v>
       </c>
       <c r="B411" t="s">
@@ -12747,8 +12770,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="412" spans="1:9">
-      <c r="A412">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A412" s="1">
         <v>2202877</v>
       </c>
       <c r="B412" t="s">
@@ -12773,8 +12796,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="413" spans="1:9">
-      <c r="A413">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A413" s="1">
         <v>2355702</v>
       </c>
       <c r="B413" t="s">
@@ -12799,8 +12822,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="414" spans="1:9">
-      <c r="A414">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A414" s="1">
         <v>2359764</v>
       </c>
       <c r="B414" t="s">
@@ -12828,8 +12851,8 @@
         <v>334</v>
       </c>
     </row>
-    <row r="415" spans="1:9">
-      <c r="A415">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A415" s="1">
         <v>2366906</v>
       </c>
       <c r="B415" t="s">
@@ -12854,8 +12877,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="416" spans="1:9">
-      <c r="A416">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A416" s="1">
         <v>2483434</v>
       </c>
       <c r="B416" t="s">
@@ -12880,8 +12903,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="417" spans="1:9">
-      <c r="A417">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A417" s="1">
         <v>2484262</v>
       </c>
       <c r="B417" t="s">
@@ -12906,8 +12929,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="418" spans="1:9">
-      <c r="A418">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A418" s="1">
         <v>2597847</v>
       </c>
       <c r="B418" t="s">
@@ -12932,7 +12955,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="419" spans="1:9">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>901</v>
       </c>

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3639" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3912" uniqueCount="482">
   <si>
     <t>student_id</t>
   </si>
@@ -1394,6 +1394,72 @@
   </si>
   <si>
     <t>You correctly set up the moment equation (400 = 0.066 × 6000 N) and found x = 0.066 m, which earns full credit for Part C. However, your resultant force was found incorrectly — you treated the problem as a force equilibrium (ΣFx = 0) rather than recognizing that the single resultant force equals the original 6 kN force in the +y direction, and you lost Part A, B, and D points for stating the resultant as -6j kN (in the wrong direction and component). The location x = 0.066 m is correct and well-demonstrated.</t>
+  </si>
+  <si>
+    <t>You correctly set up the ideal power formula and computed W_ideal = 784.8 kW, earning good credit for Parts A and B1. However, you applied the efficiency in the wrong direction for the turbine (multiplied instead of dividing for pump mode, and only computed the turbine output side without finding pump input power or the associated electricity cost), and you never calculated the annual dollar revenue or net annual revenue — losing most of Part B, Part C, and Part D points. To complete the problem, you needed to find pump electric input (784.8/0.75 = 1046 kW), compute annual costs and revenues in dollars using the given prices, and subtract to find net revenue (~$66,800/year.</t>
+  </si>
+  <si>
+    <t>You correctly identified the gh potential energy concept and applied the efficiency ratio and price difference in the right direction (subtracting cost from revenue), which shows good problem-solving structure. However, you used 7200 m³/h as your mass flow rate instead of converting to 2000 kg/s, which inflated all power values by a factor of 3.6, and you multiplied by efficiency for the pump instead of dividing, leading to further errors; additionally, 4380 hours per mode should be 3650 hours (10 h/day × 365 days). The correct net annual revenue is approximately $66,800/year.</t>
+  </si>
+  <si>
+    <t>You showed some correct ideas—recognizing that efficiency (0.75) matters and that the net revenue requires subtracting pumping cost from turbine revenue—but the fundamental approach of using volume (m³) rather than power (kW) based on m_dot × g × h led to incorrect results throughout. Your final answer of $10,220/year is far from the correct ~$66,800/year; to fix this, start by computing W_ideal = ρ × V̇ × g × h = 784.8 kW, then apply efficiency to get pump input and turbine output power before calculating energy costs.</t>
+  </si>
+  <si>
+    <t>You correctly found m_dot = 2000 kg/s, applied efficiencies in the right direction (divide for pump, multiply for turbine), and arrived at the correct net annual revenue of approximately $66,842 — excellent work overall. The ideal power computation line initially showed 392.4 kW (suggesting m = 1000 kg/s was used momentarily), but you correctly used 784.8 kW in subsequent steps, so only a minor partial deduction applies; additionally, the E_out × 0.12 line was difficult to read and lacked a clear intermediate result, costing a few presentation points. Keep showing your intermediate steps more clearly for full credit.</t>
+  </si>
+  <si>
+    <t>You correctly computed all key quantities: ṁ = 2000 kg/s, ideal power = 784.8 kW, pump input = 1046.4 kW, and turbine output = 588.6 kW, with efficiencies applied in the proper direction. Your final net annual revenue of $66,842 is essentially exact, and your solution is clearly organized with correct units throughout. Excellent work!</t>
+  </si>
+  <si>
+    <t>You correctly identified the formula ΔE = ṁgh and found ṁ = 2000 kg/s, which is great, but your arithmetic gives 740,000 W instead of the correct 784,800 W, and you did not apply the 75% efficiency (dividing by η for the pump, multiplying by η for the turbine). Additionally, you used the power value directly as an energy (kWh) without multiplying by the 10 hours of operation, which led to large errors in the cost and revenue calculations.</t>
+  </si>
+  <si>
+    <t>You correctly calculated the ideal power (0.78 MW) and applied the turbine efficiency properly to get 0.59 MW output, and your approach to computing daily revenues and costs was on the right track. However, you applied the pump efficiency in the wrong direction (you should divide by 0.75 for the pump, not multiply), and there is an arithmetic error in the daily net (760 - 295 = 465, not 413), costing you points in Parts A and D. Using 360 days is acceptable, but make sure to clearly state the final answer with units ($/year).</t>
+  </si>
+  <si>
+    <t>You correctly found the ideal power (784.8 kW) and applied the turbine efficiency properly to get 588.6 kW output, but for the pump mode you should divide the ideal power by efficiency (784.8/0.75 = 1046 kW input) rather than using the turbine output power as the pump cost basis, which cost you 6 points. Additionally, you used 12 hours instead of the given 10 hours per mode and did not convert your daily net revenue (~$494) to an annual figure (~$66,800/year), resulting in further deductions.</t>
+  </si>
+  <si>
+    <t>You correctly identified the ideal power (784,800 W) and mass flow rate (2000 kg/s), which is great work on the fundamentals. However, you used η = 70% instead of 75%, did not convert Watts to kilowatts before computing energy costs, did not apply the turbine efficiency to the output power, and used 0.5 instead of $0.12/kWh for the selling price — these errors compounded to give an incorrect final net revenue.</t>
+  </si>
+  <si>
+    <t>Excellent work! You correctly computed the ideal power (784.8 kW), pump input (1046.4 kW), turbine output (588.6 kW), and the net annual revenue of $66,838.8, which matches the reference solution almost exactly. A very minor point (3 pts) is deducted because the cost calculation shows 0.05 written as 0.05 but the intermediate value '523.2' is correct, suggesting a small transcription inconsistency — no further deductions apply.</t>
+  </si>
+  <si>
+    <t>You correctly computed the ideal power (784.8 kW), mass flow rate (2000 kg/s), turbine output (588.6 kW), and the annual revenue (~$257,800), showing strong understanding of the core concepts. However, for the pump mode you used the ideal power directly (784.8 kW) instead of dividing by the pump efficiency to get the required electrical input (~1046 kW), which caused the pump cost and final net revenue to be incorrect (-4 pts A3, -10 pts B2, -3 pts B3, -10 pts D1, -2 pts D2).</t>
+  </si>
+  <si>
+    <t>You correctly calculated the mass flow rate, ideal power (784.8 kW), and pump input power (1046.4 kW), and properly applied the efficiency by dividing for the pump mode — great work on Parts A and B. However, for the turbine mode you did not multiply the ideal power by the turbine efficiency to find the output power (~588.6 kW); instead you used the pump input power (1046.4 kW) directly multiplied by the electricity price, which led to an overstated turbine revenue and an incorrect net annual figure of $267,326 instead of ~$66,800. You lost 19 points in Parts C and D due to this efficiency error in the turbine calculation.</t>
+  </si>
+  <si>
+    <t>You correctly computed the ideal power (784.8 kW) and the pump input power (1046.4 kW), and your pumping cost calculation is perfect. However, for the turbine mode you forgot to apply the 75% efficiency to the output power — you should have used 784.8 × 0.75 = 588.6 kW for revenue calculations, not the ideal power directly, which caused your net annual revenue to be significantly overestimated (-18 pts in Parts C and D).</t>
+  </si>
+  <si>
+    <t>You correctly calculated the ideal power (784.8 kW) and the turbine output (588.6 kW), and your turbine revenue of ~$257,807 is spot on. However, for the pump mode you used the turbine output power (588.6 kW) instead of dividing the ideal power by efficiency to get the pump input (~1046 kW), which caused your pumping cost and net profit to be incorrect — the correct net revenue is approximately $66,800/year rather than $150,302.</t>
+  </si>
+  <si>
+    <t>You correctly found the mass flow rate, ideal power (~785 kW), and turbine output (~589 kW), and your turbine revenue calculation is spot-on. However, you did not apply the pump efficiency in the correct direction (you should divide by η_pump to get the larger electric input power of ~1046 kW), so your pump energy cost was underestimated, leading to an incorrect net profit of ~$150,387 instead of ~$66,800 — losing 6 pts on A3 and 10 pts on B2.</t>
+  </si>
+  <si>
+    <t>You correctly computed the mass flow rate (2000 kg/s), the ideal power (784.8 kW), and the turbine output (588.6 kW), earning strong marks in Parts A and C. However, for the pump mode you applied efficiency in the wrong direction (multiplying instead of dividing), giving a pumping cost of ~$107,420 instead of ~$191,000, which cost you points in Part B. Additionally, your final answer added the two costs together instead of subtracting the pumping cost from the turbine revenue, so the net annual revenue of ~$66,800 was not found, losing most of Part D.</t>
+  </si>
+  <si>
+    <t>You correctly identified that efficiency affects both the pumping cost and turbine revenue, and you attempted to find a net annual revenue — that shows good conceptual direction. However, your work is missing the fundamental physics setup (m_dot, g, h, ideal power calculation) and the intermediate power values, and your final net revenue of ~$191,625 is significantly off from the correct ~$66,800 because the efficiency was applied as a simple multiplier on prices rather than on the actual power flows. You lose most points in Parts A, B, C, and D for the missing derivations and incorrect methodology.</t>
+  </si>
+  <si>
+    <t>You correctly computed the mass flow rate, ideal power, and turbine output power, and properly calculated the net annual revenue. However, you applied the pump efficiency in the wrong direction — for the pump, you should divide the ideal power by 0.75 (not multiply), giving a pump input of ~1046 kW instead of ~784.8 kW, which cost you 6 points on A3; all subsequent steps were graded with full credit via error carried forward.</t>
+  </si>
+  <si>
+    <t>Excellent work — you correctly computed the ideal power (784.8 kW), pump input (1046.4 kW), turbine output (588.6 kW), and all annual cost/revenue figures with proper efficiency application. Your net annual revenue of $63,553.8/year is within the acceptable 5% tolerance of the reference answer (~$66,800), so no penalty is applied. A minor arithmetic slip in the daily cost ($532.2 instead of $523.2) caused a tiny deviation, but this falls within tolerance and costs only 3 points total.</t>
+  </si>
+  <si>
+    <t>You correctly computed the mass flow rate, ideal power (784 kW), and turbine output (588 kW), earning strong credit for Parts A and C. However, for the pump mode you applied efficiency in the wrong direction (multiplying by 0.75 instead of dividing), giving a pump input of 588 kW instead of 1046 kW, which costs you points in Part B; additionally, the annual cost calculation used the turbine output power for both modes rather than the correct higher pump input power, leading to an incorrect net revenue of ~$150,234 instead of ~$66,800, which reduces your Part D score.</t>
+  </si>
+  <si>
+    <t>You correctly identified the ideal power formula (ṁgh = 784.8 kW) and the general approach of subtracting pumping cost from turbine revenue, which earned substantial credit. However, you applied the pump efficiency in the wrong direction (multiplied by 0.75 instead of dividing, losing 6 pts for A3), and then applied efficiency a second time for the turbine instead of once (losing 6 pts in Part C), leading to a final net revenue of $5,110/year rather than the correct ~$66,800/year, costing 10 pts in Part D.</t>
+  </si>
+  <si>
+    <t>You correctly identified the mass flow rate (2000 kg/s) and applied the efficiencies in the correct direction (multiplying turbine output by η and dividing pump input by η), which shows good conceptual understanding. However, your unit conversion between power (kW) and energy (kWh) was inconsistent, and intermediate values for pump input power, turbine output power, annual cost, and annual revenue were not clearly shown, leading to a final net revenue (~$29,000) that is significantly off from the correct ~$66,800/year. Make sure to compute and clearly state each intermediate step separately.</t>
   </si>
 </sst>
 </file>
@@ -1725,7 +1791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I536"/>
+  <dimension ref="A1:I575"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -15104,8 +15170,8 @@
       </c>
     </row>
     <row r="498" spans="1:9">
-      <c r="A498">
-        <v>2003675</v>
+      <c r="A498" t="s">
+        <v>44</v>
       </c>
       <c r="B498" t="s">
         <v>182</v>
@@ -15130,8 +15196,8 @@
       </c>
     </row>
     <row r="499" spans="1:9">
-      <c r="A499">
-        <v>2003743</v>
+      <c r="A499" t="s">
+        <v>45</v>
       </c>
       <c r="B499" t="s">
         <v>183</v>
@@ -15156,8 +15222,8 @@
       </c>
     </row>
     <row r="500" spans="1:9">
-      <c r="A500">
-        <v>2101812</v>
+      <c r="A500" t="s">
+        <v>46</v>
       </c>
       <c r="B500" t="s">
         <v>184</v>
@@ -15182,8 +15248,8 @@
       </c>
     </row>
     <row r="501" spans="1:9">
-      <c r="A501">
-        <v>2102438</v>
+      <c r="A501" t="s">
+        <v>47</v>
       </c>
       <c r="B501" t="s">
         <v>185</v>
@@ -15208,8 +15274,8 @@
       </c>
     </row>
     <row r="502" spans="1:9">
-      <c r="A502">
-        <v>2104775</v>
+      <c r="A502" t="s">
+        <v>48</v>
       </c>
       <c r="B502" t="s">
         <v>186</v>
@@ -15234,8 +15300,8 @@
       </c>
     </row>
     <row r="503" spans="1:9">
-      <c r="A503">
-        <v>2200784</v>
+      <c r="A503" t="s">
+        <v>49</v>
       </c>
       <c r="B503" t="s">
         <v>187</v>
@@ -15260,8 +15326,8 @@
       </c>
     </row>
     <row r="504" spans="1:9">
-      <c r="A504">
-        <v>2202739</v>
+      <c r="A504" t="s">
+        <v>50</v>
       </c>
       <c r="B504" t="s">
         <v>188</v>
@@ -15286,8 +15352,8 @@
       </c>
     </row>
     <row r="505" spans="1:9">
-      <c r="A505">
-        <v>2202877</v>
+      <c r="A505" t="s">
+        <v>51</v>
       </c>
       <c r="B505" t="s">
         <v>189</v>
@@ -15312,8 +15378,8 @@
       </c>
     </row>
     <row r="506" spans="1:9">
-      <c r="A506">
-        <v>2364766</v>
+      <c r="A506" t="s">
+        <v>52</v>
       </c>
       <c r="B506" t="s">
         <v>190</v>
@@ -15338,8 +15404,8 @@
       </c>
     </row>
     <row r="507" spans="1:9">
-      <c r="A507">
-        <v>2366349</v>
+      <c r="A507" t="s">
+        <v>53</v>
       </c>
       <c r="B507" t="s">
         <v>191</v>
@@ -15364,8 +15430,8 @@
       </c>
     </row>
     <row r="508" spans="1:9">
-      <c r="A508">
-        <v>2366648</v>
+      <c r="A508" t="s">
+        <v>54</v>
       </c>
       <c r="B508" t="s">
         <v>192</v>
@@ -15390,8 +15456,8 @@
       </c>
     </row>
     <row r="509" spans="1:9">
-      <c r="A509">
-        <v>2366734</v>
+      <c r="A509" t="s">
+        <v>55</v>
       </c>
       <c r="B509" t="s">
         <v>193</v>
@@ -15416,8 +15482,8 @@
       </c>
     </row>
     <row r="510" spans="1:9">
-      <c r="A510">
-        <v>2366906</v>
+      <c r="A510" t="s">
+        <v>56</v>
       </c>
       <c r="B510" t="s">
         <v>194</v>
@@ -15442,8 +15508,8 @@
       </c>
     </row>
     <row r="511" spans="1:9">
-      <c r="A511">
-        <v>2366917</v>
+      <c r="A511" t="s">
+        <v>57</v>
       </c>
       <c r="B511" t="s">
         <v>195</v>
@@ -15468,8 +15534,8 @@
       </c>
     </row>
     <row r="512" spans="1:9">
-      <c r="A512">
-        <v>2367037</v>
+      <c r="A512" t="s">
+        <v>58</v>
       </c>
       <c r="B512" t="s">
         <v>196</v>
@@ -15494,8 +15560,8 @@
       </c>
     </row>
     <row r="513" spans="1:9">
-      <c r="A513">
-        <v>2368580</v>
+      <c r="A513" t="s">
+        <v>59</v>
       </c>
       <c r="B513" t="s">
         <v>197</v>
@@ -15520,8 +15586,8 @@
       </c>
     </row>
     <row r="514" spans="1:9">
-      <c r="A514">
-        <v>2472843</v>
+      <c r="A514" t="s">
+        <v>60</v>
       </c>
       <c r="B514" t="s">
         <v>198</v>
@@ -15546,8 +15612,8 @@
       </c>
     </row>
     <row r="515" spans="1:9">
-      <c r="A515">
-        <v>2476099</v>
+      <c r="A515" t="s">
+        <v>61</v>
       </c>
       <c r="B515" t="s">
         <v>199</v>
@@ -15572,8 +15638,8 @@
       </c>
     </row>
     <row r="516" spans="1:9">
-      <c r="A516">
-        <v>2477970</v>
+      <c r="A516" t="s">
+        <v>62</v>
       </c>
       <c r="B516" t="s">
         <v>200</v>
@@ -15598,8 +15664,8 @@
       </c>
     </row>
     <row r="517" spans="1:9">
-      <c r="A517">
-        <v>2482073</v>
+      <c r="A517" t="s">
+        <v>63</v>
       </c>
       <c r="B517" t="s">
         <v>201</v>
@@ -15624,8 +15690,8 @@
       </c>
     </row>
     <row r="518" spans="1:9">
-      <c r="A518">
-        <v>2482445</v>
+      <c r="A518" t="s">
+        <v>64</v>
       </c>
       <c r="B518" t="s">
         <v>202</v>
@@ -15650,8 +15716,8 @@
       </c>
     </row>
     <row r="519" spans="1:9">
-      <c r="A519">
-        <v>2483328</v>
+      <c r="A519" t="s">
+        <v>65</v>
       </c>
       <c r="B519" t="s">
         <v>203</v>
@@ -15676,8 +15742,8 @@
       </c>
     </row>
     <row r="520" spans="1:9">
-      <c r="A520">
-        <v>2483434</v>
+      <c r="A520" t="s">
+        <v>66</v>
       </c>
       <c r="B520" t="s">
         <v>204</v>
@@ -15702,8 +15768,8 @@
       </c>
     </row>
     <row r="521" spans="1:9">
-      <c r="A521">
-        <v>2483834</v>
+      <c r="A521" t="s">
+        <v>67</v>
       </c>
       <c r="B521" t="s">
         <v>205</v>
@@ -15728,8 +15794,8 @@
       </c>
     </row>
     <row r="522" spans="1:9">
-      <c r="A522">
-        <v>2483956</v>
+      <c r="A522" t="s">
+        <v>68</v>
       </c>
       <c r="B522" t="s">
         <v>206</v>
@@ -15754,8 +15820,8 @@
       </c>
     </row>
     <row r="523" spans="1:9">
-      <c r="A523">
-        <v>2483960</v>
+      <c r="A523" t="s">
+        <v>69</v>
       </c>
       <c r="B523" t="s">
         <v>207</v>
@@ -15780,8 +15846,8 @@
       </c>
     </row>
     <row r="524" spans="1:9">
-      <c r="A524">
-        <v>2484028</v>
+      <c r="A524" t="s">
+        <v>70</v>
       </c>
       <c r="B524" t="s">
         <v>208</v>
@@ -15806,8 +15872,8 @@
       </c>
     </row>
     <row r="525" spans="1:9">
-      <c r="A525">
-        <v>2484186</v>
+      <c r="A525" t="s">
+        <v>71</v>
       </c>
       <c r="B525" t="s">
         <v>209</v>
@@ -15832,8 +15898,8 @@
       </c>
     </row>
     <row r="526" spans="1:9">
-      <c r="A526">
-        <v>2484262</v>
+      <c r="A526" t="s">
+        <v>72</v>
       </c>
       <c r="B526" t="s">
         <v>210</v>
@@ -15858,8 +15924,8 @@
       </c>
     </row>
     <row r="527" spans="1:9">
-      <c r="A527">
-        <v>2484542</v>
+      <c r="A527" t="s">
+        <v>73</v>
       </c>
       <c r="B527" t="s">
         <v>211</v>
@@ -15884,8 +15950,8 @@
       </c>
     </row>
     <row r="528" spans="1:9">
-      <c r="A528">
-        <v>2500744</v>
+      <c r="A528" t="s">
+        <v>74</v>
       </c>
       <c r="B528" t="s">
         <v>212</v>
@@ -15910,8 +15976,8 @@
       </c>
     </row>
     <row r="529" spans="1:9">
-      <c r="A529">
-        <v>2501122</v>
+      <c r="A529" t="s">
+        <v>75</v>
       </c>
       <c r="B529" t="s">
         <v>213</v>
@@ -15936,8 +16002,8 @@
       </c>
     </row>
     <row r="530" spans="1:9">
-      <c r="A530">
-        <v>2593530</v>
+      <c r="A530" t="s">
+        <v>76</v>
       </c>
       <c r="B530" t="s">
         <v>214</v>
@@ -15962,8 +16028,8 @@
       </c>
     </row>
     <row r="531" spans="1:9">
-      <c r="A531">
-        <v>2596196</v>
+      <c r="A531" t="s">
+        <v>77</v>
       </c>
       <c r="B531" t="s">
         <v>215</v>
@@ -15988,8 +16054,8 @@
       </c>
     </row>
     <row r="532" spans="1:9">
-      <c r="A532">
-        <v>2599154</v>
+      <c r="A532" t="s">
+        <v>78</v>
       </c>
       <c r="B532" t="s">
         <v>216</v>
@@ -16014,8 +16080,8 @@
       </c>
     </row>
     <row r="533" spans="1:9">
-      <c r="A533">
-        <v>2599631</v>
+      <c r="A533" t="s">
+        <v>79</v>
       </c>
       <c r="B533" t="s">
         <v>217</v>
@@ -16040,8 +16106,8 @@
       </c>
     </row>
     <row r="534" spans="1:9">
-      <c r="A534">
-        <v>2599634</v>
+      <c r="A534" t="s">
+        <v>80</v>
       </c>
       <c r="B534" t="s">
         <v>218</v>
@@ -16066,8 +16132,8 @@
       </c>
     </row>
     <row r="535" spans="1:9">
-      <c r="A535">
-        <v>2599868</v>
+      <c r="A535" t="s">
+        <v>81</v>
       </c>
       <c r="B535" t="s">
         <v>219</v>
@@ -16092,8 +16158,8 @@
       </c>
     </row>
     <row r="536" spans="1:9">
-      <c r="A536">
-        <v>2616909</v>
+      <c r="A536" t="s">
+        <v>82</v>
       </c>
       <c r="B536" t="s">
         <v>220</v>
@@ -16115,6 +16181,1092 @@
       </c>
       <c r="I536" t="s">
         <v>312</v>
+      </c>
+    </row>
+    <row r="537" spans="1:9">
+      <c r="A537">
+        <v>2003675</v>
+      </c>
+      <c r="B537" t="s">
+        <v>182</v>
+      </c>
+      <c r="C537" t="s">
+        <v>246</v>
+      </c>
+      <c r="D537">
+        <v>902</v>
+      </c>
+      <c r="E537" t="s">
+        <v>251</v>
+      </c>
+      <c r="F537" t="s">
+        <v>252</v>
+      </c>
+      <c r="G537" t="s">
+        <v>256</v>
+      </c>
+      <c r="I537" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="538" spans="1:9">
+      <c r="A538">
+        <v>2003743</v>
+      </c>
+      <c r="B538" t="s">
+        <v>183</v>
+      </c>
+      <c r="C538" t="s">
+        <v>246</v>
+      </c>
+      <c r="D538">
+        <v>902</v>
+      </c>
+      <c r="E538" t="s">
+        <v>251</v>
+      </c>
+      <c r="F538" t="s">
+        <v>252</v>
+      </c>
+      <c r="G538" t="s">
+        <v>256</v>
+      </c>
+      <c r="I538" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="539" spans="1:9">
+      <c r="A539">
+        <v>2101812</v>
+      </c>
+      <c r="B539" t="s">
+        <v>184</v>
+      </c>
+      <c r="C539" t="s">
+        <v>246</v>
+      </c>
+      <c r="D539">
+        <v>902</v>
+      </c>
+      <c r="E539" t="s">
+        <v>251</v>
+      </c>
+      <c r="F539" t="s">
+        <v>252</v>
+      </c>
+      <c r="G539" t="s">
+        <v>256</v>
+      </c>
+      <c r="I539" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="540" spans="1:9">
+      <c r="A540">
+        <v>2102438</v>
+      </c>
+      <c r="B540" t="s">
+        <v>185</v>
+      </c>
+      <c r="C540" t="s">
+        <v>246</v>
+      </c>
+      <c r="D540">
+        <v>902</v>
+      </c>
+      <c r="E540" t="s">
+        <v>251</v>
+      </c>
+      <c r="F540" t="s">
+        <v>253</v>
+      </c>
+      <c r="G540" t="s">
+        <v>256</v>
+      </c>
+      <c r="H540">
+        <v>0</v>
+      </c>
+      <c r="I540" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="541" spans="1:9">
+      <c r="A541">
+        <v>2104775</v>
+      </c>
+      <c r="B541" t="s">
+        <v>186</v>
+      </c>
+      <c r="C541" t="s">
+        <v>246</v>
+      </c>
+      <c r="D541">
+        <v>902</v>
+      </c>
+      <c r="E541" t="s">
+        <v>251</v>
+      </c>
+      <c r="F541" t="s">
+        <v>253</v>
+      </c>
+      <c r="G541" t="s">
+        <v>256</v>
+      </c>
+      <c r="H541">
+        <v>32</v>
+      </c>
+      <c r="I541" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="542" spans="1:9">
+      <c r="A542">
+        <v>2200784</v>
+      </c>
+      <c r="B542" t="s">
+        <v>187</v>
+      </c>
+      <c r="C542" t="s">
+        <v>246</v>
+      </c>
+      <c r="D542">
+        <v>902</v>
+      </c>
+      <c r="E542" t="s">
+        <v>251</v>
+      </c>
+      <c r="F542" t="s">
+        <v>252</v>
+      </c>
+      <c r="G542" t="s">
+        <v>256</v>
+      </c>
+      <c r="I542" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="543" spans="1:9">
+      <c r="A543">
+        <v>2202739</v>
+      </c>
+      <c r="B543" t="s">
+        <v>188</v>
+      </c>
+      <c r="C543" t="s">
+        <v>246</v>
+      </c>
+      <c r="D543">
+        <v>902</v>
+      </c>
+      <c r="E543" t="s">
+        <v>251</v>
+      </c>
+      <c r="F543" t="s">
+        <v>253</v>
+      </c>
+      <c r="G543" t="s">
+        <v>256</v>
+      </c>
+      <c r="H543">
+        <v>47</v>
+      </c>
+      <c r="I543" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="544" spans="1:9">
+      <c r="A544">
+        <v>2202877</v>
+      </c>
+      <c r="B544" t="s">
+        <v>189</v>
+      </c>
+      <c r="C544" t="s">
+        <v>246</v>
+      </c>
+      <c r="D544">
+        <v>902</v>
+      </c>
+      <c r="E544" t="s">
+        <v>251</v>
+      </c>
+      <c r="F544" t="s">
+        <v>252</v>
+      </c>
+      <c r="G544" t="s">
+        <v>256</v>
+      </c>
+      <c r="I544" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="545" spans="1:9">
+      <c r="A545">
+        <v>2364766</v>
+      </c>
+      <c r="B545" t="s">
+        <v>190</v>
+      </c>
+      <c r="C545" t="s">
+        <v>246</v>
+      </c>
+      <c r="D545">
+        <v>902</v>
+      </c>
+      <c r="E545" t="s">
+        <v>251</v>
+      </c>
+      <c r="F545" t="s">
+        <v>253</v>
+      </c>
+      <c r="G545" t="s">
+        <v>256</v>
+      </c>
+      <c r="H545">
+        <v>18</v>
+      </c>
+      <c r="I545" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="546" spans="1:9">
+      <c r="A546">
+        <v>2366349</v>
+      </c>
+      <c r="B546" t="s">
+        <v>191</v>
+      </c>
+      <c r="C546" t="s">
+        <v>246</v>
+      </c>
+      <c r="D546">
+        <v>902</v>
+      </c>
+      <c r="E546" t="s">
+        <v>251</v>
+      </c>
+      <c r="F546" t="s">
+        <v>253</v>
+      </c>
+      <c r="G546" t="s">
+        <v>256</v>
+      </c>
+      <c r="H546">
+        <v>88</v>
+      </c>
+      <c r="I546" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="547" spans="1:9">
+      <c r="A547">
+        <v>2366648</v>
+      </c>
+      <c r="B547" t="s">
+        <v>192</v>
+      </c>
+      <c r="C547" t="s">
+        <v>246</v>
+      </c>
+      <c r="D547">
+        <v>902</v>
+      </c>
+      <c r="E547" t="s">
+        <v>251</v>
+      </c>
+      <c r="F547" t="s">
+        <v>253</v>
+      </c>
+      <c r="G547" t="s">
+        <v>256</v>
+      </c>
+      <c r="H547">
+        <v>100</v>
+      </c>
+      <c r="I547" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="548" spans="1:9">
+      <c r="A548">
+        <v>2366734</v>
+      </c>
+      <c r="B548" t="s">
+        <v>193</v>
+      </c>
+      <c r="C548" t="s">
+        <v>246</v>
+      </c>
+      <c r="D548">
+        <v>902</v>
+      </c>
+      <c r="E548" t="s">
+        <v>251</v>
+      </c>
+      <c r="F548" t="s">
+        <v>253</v>
+      </c>
+      <c r="G548" t="s">
+        <v>256</v>
+      </c>
+      <c r="H548">
+        <v>13</v>
+      </c>
+      <c r="I548" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="549" spans="1:9">
+      <c r="A549">
+        <v>2366906</v>
+      </c>
+      <c r="B549" t="s">
+        <v>194</v>
+      </c>
+      <c r="C549" t="s">
+        <v>246</v>
+      </c>
+      <c r="D549">
+        <v>902</v>
+      </c>
+      <c r="E549" t="s">
+        <v>251</v>
+      </c>
+      <c r="F549" t="s">
+        <v>252</v>
+      </c>
+      <c r="G549" t="s">
+        <v>256</v>
+      </c>
+      <c r="I549" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="550" spans="1:9">
+      <c r="A550">
+        <v>2366917</v>
+      </c>
+      <c r="B550" t="s">
+        <v>195</v>
+      </c>
+      <c r="C550" t="s">
+        <v>246</v>
+      </c>
+      <c r="D550">
+        <v>902</v>
+      </c>
+      <c r="E550" t="s">
+        <v>251</v>
+      </c>
+      <c r="F550" t="s">
+        <v>252</v>
+      </c>
+      <c r="G550" t="s">
+        <v>256</v>
+      </c>
+      <c r="I550" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="551" spans="1:9">
+      <c r="A551">
+        <v>2367037</v>
+      </c>
+      <c r="B551" t="s">
+        <v>196</v>
+      </c>
+      <c r="C551" t="s">
+        <v>246</v>
+      </c>
+      <c r="D551">
+        <v>902</v>
+      </c>
+      <c r="E551" t="s">
+        <v>251</v>
+      </c>
+      <c r="F551" t="s">
+        <v>253</v>
+      </c>
+      <c r="G551" t="s">
+        <v>256</v>
+      </c>
+      <c r="H551">
+        <v>79</v>
+      </c>
+      <c r="I551" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="552" spans="1:9">
+      <c r="A552">
+        <v>2368580</v>
+      </c>
+      <c r="B552" t="s">
+        <v>197</v>
+      </c>
+      <c r="C552" t="s">
+        <v>246</v>
+      </c>
+      <c r="D552">
+        <v>902</v>
+      </c>
+      <c r="E552" t="s">
+        <v>251</v>
+      </c>
+      <c r="F552" t="s">
+        <v>253</v>
+      </c>
+      <c r="G552" t="s">
+        <v>256</v>
+      </c>
+      <c r="H552">
+        <v>72</v>
+      </c>
+      <c r="I552" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="553" spans="1:9">
+      <c r="A553">
+        <v>2472843</v>
+      </c>
+      <c r="B553" t="s">
+        <v>198</v>
+      </c>
+      <c r="C553" t="s">
+        <v>246</v>
+      </c>
+      <c r="D553">
+        <v>902</v>
+      </c>
+      <c r="E553" t="s">
+        <v>251</v>
+      </c>
+      <c r="F553" t="s">
+        <v>253</v>
+      </c>
+      <c r="G553" t="s">
+        <v>256</v>
+      </c>
+      <c r="H553">
+        <v>32</v>
+      </c>
+      <c r="I553" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="554" spans="1:9">
+      <c r="A554">
+        <v>2476099</v>
+      </c>
+      <c r="B554" t="s">
+        <v>199</v>
+      </c>
+      <c r="C554" t="s">
+        <v>246</v>
+      </c>
+      <c r="D554">
+        <v>902</v>
+      </c>
+      <c r="E554" t="s">
+        <v>251</v>
+      </c>
+      <c r="F554" t="s">
+        <v>253</v>
+      </c>
+      <c r="G554" t="s">
+        <v>256</v>
+      </c>
+      <c r="H554">
+        <v>97</v>
+      </c>
+      <c r="I554" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="555" spans="1:9">
+      <c r="A555">
+        <v>2477970</v>
+      </c>
+      <c r="B555" t="s">
+        <v>200</v>
+      </c>
+      <c r="C555" t="s">
+        <v>246</v>
+      </c>
+      <c r="D555">
+        <v>902</v>
+      </c>
+      <c r="E555" t="s">
+        <v>251</v>
+      </c>
+      <c r="F555" t="s">
+        <v>252</v>
+      </c>
+      <c r="G555" t="s">
+        <v>256</v>
+      </c>
+      <c r="I555" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="556" spans="1:9">
+      <c r="A556">
+        <v>2482073</v>
+      </c>
+      <c r="B556" t="s">
+        <v>201</v>
+      </c>
+      <c r="C556" t="s">
+        <v>246</v>
+      </c>
+      <c r="D556">
+        <v>902</v>
+      </c>
+      <c r="E556" t="s">
+        <v>251</v>
+      </c>
+      <c r="F556" t="s">
+        <v>253</v>
+      </c>
+      <c r="G556" t="s">
+        <v>256</v>
+      </c>
+      <c r="H556">
+        <v>71</v>
+      </c>
+      <c r="I556" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="557" spans="1:9">
+      <c r="A557">
+        <v>2482445</v>
+      </c>
+      <c r="B557" t="s">
+        <v>202</v>
+      </c>
+      <c r="C557" t="s">
+        <v>246</v>
+      </c>
+      <c r="D557">
+        <v>902</v>
+      </c>
+      <c r="E557" t="s">
+        <v>251</v>
+      </c>
+      <c r="F557" t="s">
+        <v>253</v>
+      </c>
+      <c r="G557" t="s">
+        <v>256</v>
+      </c>
+      <c r="H557">
+        <v>64</v>
+      </c>
+      <c r="I557" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="558" spans="1:9">
+      <c r="A558">
+        <v>2483328</v>
+      </c>
+      <c r="B558" t="s">
+        <v>203</v>
+      </c>
+      <c r="C558" t="s">
+        <v>246</v>
+      </c>
+      <c r="D558">
+        <v>902</v>
+      </c>
+      <c r="E558" t="s">
+        <v>251</v>
+      </c>
+      <c r="F558" t="s">
+        <v>253</v>
+      </c>
+      <c r="G558" t="s">
+        <v>256</v>
+      </c>
+      <c r="H558">
+        <v>67</v>
+      </c>
+      <c r="I558" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="559" spans="1:9">
+      <c r="A559">
+        <v>2483434</v>
+      </c>
+      <c r="B559" t="s">
+        <v>204</v>
+      </c>
+      <c r="C559" t="s">
+        <v>246</v>
+      </c>
+      <c r="D559">
+        <v>902</v>
+      </c>
+      <c r="E559" t="s">
+        <v>251</v>
+      </c>
+      <c r="F559" t="s">
+        <v>252</v>
+      </c>
+      <c r="G559" t="s">
+        <v>256</v>
+      </c>
+      <c r="I559" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="560" spans="1:9">
+      <c r="A560">
+        <v>2483834</v>
+      </c>
+      <c r="B560" t="s">
+        <v>205</v>
+      </c>
+      <c r="C560" t="s">
+        <v>246</v>
+      </c>
+      <c r="D560">
+        <v>902</v>
+      </c>
+      <c r="E560" t="s">
+        <v>251</v>
+      </c>
+      <c r="F560" t="s">
+        <v>253</v>
+      </c>
+      <c r="G560" t="s">
+        <v>256</v>
+      </c>
+      <c r="H560">
+        <v>72</v>
+      </c>
+      <c r="I560" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="561" spans="1:9">
+      <c r="A561">
+        <v>2483956</v>
+      </c>
+      <c r="B561" t="s">
+        <v>206</v>
+      </c>
+      <c r="C561" t="s">
+        <v>246</v>
+      </c>
+      <c r="D561">
+        <v>902</v>
+      </c>
+      <c r="E561" t="s">
+        <v>251</v>
+      </c>
+      <c r="F561" t="s">
+        <v>252</v>
+      </c>
+      <c r="G561" t="s">
+        <v>256</v>
+      </c>
+      <c r="I561" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="562" spans="1:9">
+      <c r="A562">
+        <v>2483960</v>
+      </c>
+      <c r="B562" t="s">
+        <v>207</v>
+      </c>
+      <c r="C562" t="s">
+        <v>246</v>
+      </c>
+      <c r="D562">
+        <v>902</v>
+      </c>
+      <c r="E562" t="s">
+        <v>251</v>
+      </c>
+      <c r="F562" t="s">
+        <v>253</v>
+      </c>
+      <c r="G562" t="s">
+        <v>256</v>
+      </c>
+      <c r="H562">
+        <v>72</v>
+      </c>
+      <c r="I562" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="563" spans="1:9">
+      <c r="A563">
+        <v>2484028</v>
+      </c>
+      <c r="B563" t="s">
+        <v>208</v>
+      </c>
+      <c r="C563" t="s">
+        <v>246</v>
+      </c>
+      <c r="D563">
+        <v>902</v>
+      </c>
+      <c r="E563" t="s">
+        <v>251</v>
+      </c>
+      <c r="F563" t="s">
+        <v>253</v>
+      </c>
+      <c r="G563" t="s">
+        <v>256</v>
+      </c>
+      <c r="H563">
+        <v>52</v>
+      </c>
+      <c r="I563" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="564" spans="1:9">
+      <c r="A564">
+        <v>2484186</v>
+      </c>
+      <c r="B564" t="s">
+        <v>209</v>
+      </c>
+      <c r="C564" t="s">
+        <v>246</v>
+      </c>
+      <c r="D564">
+        <v>902</v>
+      </c>
+      <c r="E564" t="s">
+        <v>251</v>
+      </c>
+      <c r="F564" t="s">
+        <v>252</v>
+      </c>
+      <c r="G564" t="s">
+        <v>256</v>
+      </c>
+      <c r="I564" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="565" spans="1:9">
+      <c r="A565">
+        <v>2484262</v>
+      </c>
+      <c r="B565" t="s">
+        <v>210</v>
+      </c>
+      <c r="C565" t="s">
+        <v>246</v>
+      </c>
+      <c r="D565">
+        <v>902</v>
+      </c>
+      <c r="E565" t="s">
+        <v>251</v>
+      </c>
+      <c r="F565" t="s">
+        <v>252</v>
+      </c>
+      <c r="G565" t="s">
+        <v>256</v>
+      </c>
+      <c r="I565" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="566" spans="1:9">
+      <c r="A566">
+        <v>2484542</v>
+      </c>
+      <c r="B566" t="s">
+        <v>211</v>
+      </c>
+      <c r="C566" t="s">
+        <v>246</v>
+      </c>
+      <c r="D566">
+        <v>902</v>
+      </c>
+      <c r="E566" t="s">
+        <v>251</v>
+      </c>
+      <c r="F566" t="s">
+        <v>253</v>
+      </c>
+      <c r="G566" t="s">
+        <v>256</v>
+      </c>
+      <c r="H566">
+        <v>18</v>
+      </c>
+      <c r="I566" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="567" spans="1:9">
+      <c r="A567">
+        <v>2500744</v>
+      </c>
+      <c r="B567" t="s">
+        <v>212</v>
+      </c>
+      <c r="C567" t="s">
+        <v>246</v>
+      </c>
+      <c r="D567">
+        <v>902</v>
+      </c>
+      <c r="E567" t="s">
+        <v>251</v>
+      </c>
+      <c r="F567" t="s">
+        <v>252</v>
+      </c>
+      <c r="G567" t="s">
+        <v>256</v>
+      </c>
+      <c r="I567" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="568" spans="1:9">
+      <c r="A568">
+        <v>2501122</v>
+      </c>
+      <c r="B568" t="s">
+        <v>213</v>
+      </c>
+      <c r="C568" t="s">
+        <v>246</v>
+      </c>
+      <c r="D568">
+        <v>902</v>
+      </c>
+      <c r="E568" t="s">
+        <v>251</v>
+      </c>
+      <c r="F568" t="s">
+        <v>253</v>
+      </c>
+      <c r="G568" t="s">
+        <v>256</v>
+      </c>
+      <c r="H568">
+        <v>94</v>
+      </c>
+      <c r="I568" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="569" spans="1:9">
+      <c r="A569">
+        <v>2593530</v>
+      </c>
+      <c r="B569" t="s">
+        <v>214</v>
+      </c>
+      <c r="C569" t="s">
+        <v>246</v>
+      </c>
+      <c r="D569">
+        <v>902</v>
+      </c>
+      <c r="E569" t="s">
+        <v>251</v>
+      </c>
+      <c r="F569" t="s">
+        <v>253</v>
+      </c>
+      <c r="G569" t="s">
+        <v>256</v>
+      </c>
+      <c r="H569">
+        <v>97</v>
+      </c>
+      <c r="I569" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="570" spans="1:9">
+      <c r="A570">
+        <v>2596196</v>
+      </c>
+      <c r="B570" t="s">
+        <v>215</v>
+      </c>
+      <c r="C570" t="s">
+        <v>246</v>
+      </c>
+      <c r="D570">
+        <v>902</v>
+      </c>
+      <c r="E570" t="s">
+        <v>251</v>
+      </c>
+      <c r="F570" t="s">
+        <v>252</v>
+      </c>
+      <c r="G570" t="s">
+        <v>256</v>
+      </c>
+      <c r="I570" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="571" spans="1:9">
+      <c r="A571">
+        <v>2599154</v>
+      </c>
+      <c r="B571" t="s">
+        <v>216</v>
+      </c>
+      <c r="C571" t="s">
+        <v>246</v>
+      </c>
+      <c r="D571">
+        <v>902</v>
+      </c>
+      <c r="E571" t="s">
+        <v>251</v>
+      </c>
+      <c r="F571" t="s">
+        <v>252</v>
+      </c>
+      <c r="G571" t="s">
+        <v>256</v>
+      </c>
+      <c r="I571" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="572" spans="1:9">
+      <c r="A572">
+        <v>2599631</v>
+      </c>
+      <c r="B572" t="s">
+        <v>217</v>
+      </c>
+      <c r="C572" t="s">
+        <v>246</v>
+      </c>
+      <c r="D572">
+        <v>902</v>
+      </c>
+      <c r="E572" t="s">
+        <v>251</v>
+      </c>
+      <c r="F572" t="s">
+        <v>253</v>
+      </c>
+      <c r="G572" t="s">
+        <v>256</v>
+      </c>
+      <c r="H572">
+        <v>62</v>
+      </c>
+      <c r="I572" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="573" spans="1:9">
+      <c r="A573">
+        <v>2599634</v>
+      </c>
+      <c r="B573" t="s">
+        <v>218</v>
+      </c>
+      <c r="C573" t="s">
+        <v>246</v>
+      </c>
+      <c r="D573">
+        <v>902</v>
+      </c>
+      <c r="E573" t="s">
+        <v>251</v>
+      </c>
+      <c r="F573" t="s">
+        <v>253</v>
+      </c>
+      <c r="G573" t="s">
+        <v>256</v>
+      </c>
+      <c r="H573">
+        <v>62</v>
+      </c>
+      <c r="I573" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="574" spans="1:9">
+      <c r="A574">
+        <v>2599868</v>
+      </c>
+      <c r="B574" t="s">
+        <v>219</v>
+      </c>
+      <c r="C574" t="s">
+        <v>246</v>
+      </c>
+      <c r="D574">
+        <v>902</v>
+      </c>
+      <c r="E574" t="s">
+        <v>251</v>
+      </c>
+      <c r="F574" t="s">
+        <v>253</v>
+      </c>
+      <c r="G574" t="s">
+        <v>256</v>
+      </c>
+      <c r="H574">
+        <v>40</v>
+      </c>
+      <c r="I574" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="575" spans="1:9">
+      <c r="A575">
+        <v>2616909</v>
+      </c>
+      <c r="B575" t="s">
+        <v>220</v>
+      </c>
+      <c r="C575" t="s">
+        <v>246</v>
+      </c>
+      <c r="D575">
+        <v>902</v>
+      </c>
+      <c r="E575" t="s">
+        <v>251</v>
+      </c>
+      <c r="F575" t="s">
+        <v>252</v>
+      </c>
+      <c r="G575" t="s">
+        <v>256</v>
+      </c>
+      <c r="H575">
+        <v>0</v>
+      </c>
+      <c r="I575" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2107" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2119" uniqueCount="311">
   <si>
     <t>student_id</t>
   </si>
@@ -858,97 +858,100 @@
     <t>You correctly set up the geometry and position vectors, and your gear force resolution and M_x component are excellent. However, you subtracted the 200 N belt force instead of adding it (both belt forces act in the +x direction), which caused errors in R_x (-13 pts in Part B) and propagated into M_y and M_z (-20 pts in Part C), and the final answer lost 3 pts for the incorrect values. Keep up the solid method — fixing that sign error would have given you a much higher score!</t>
   </si>
   <si>
-    <t>You correctly set up the FBD, computed the beam weight and its location, resolved the 3 kN force into components, and found O_x = 1.5 kN and O_y = 6.1 kN — great work on Parts A and B. However, in the moment equation you applied the wrong sign to the 15 kN·m couple (it should be +15 CCW, not −15), which led to M_O = 37.55 kN·m instead of the correct 7.56 kN·m, costing you 25 points in Part C and the final answer points in Part D.</t>
-  </si>
-  <si>
-    <t>You correctly drew the FBD, computed the beam weight (4.905 kN), resolved the 3 kN force into components (1.5 kN and 2.60 kN), and found O_x = 1.5 kN — great work on those steps. However, your moment equation about O is missing key terms (the 1.4 kN force at A, the beam weight at midpoint 2.4 m, and the 15 kN·m couple is not treated correctly as a free moment), leading to an incorrect M_O = -11.16 kN·m instead of +7.56 kN·m, and O_y was not determined. You earn full credit for Part A and B1, but significant points are lost in B2, Part C, and Part D.</t>
-  </si>
-  <si>
-    <t>Excellent work! You correctly computed the beam weight, resolved the 3 kN force into components, applied all three equilibrium equations, and treated the 15 kN·m couple as a free moment with no moment arm. Your final answers — O_x = 1.50 kN, O_y = 6.103 kN, and M_O = 7.561 kN·m — are all within the acceptable tolerance of the reference solution.</t>
-  </si>
-  <si>
-    <t>You correctly identified the beam geometry, drew a reasonable FBD, and resolved the 3 kN force into components (2.5√3 and 2.5), which earns partial credit for Part A. However, you misinterpreted the 15 kN·m couple as a force (treating it as r·F = 15 kN and solving for F = 5 kN), then incorrectly used it as a moment by multiplying 5 × 3 = 15 kN·m with a moment arm — losing most of Parts B and C — and you did not solve for the fixed-support reactions O_x, O_y, and M_O, leaving Part D blank. The beam weight was also left in Newtons (5000 N) rather than converted to kN consistently, and the moment equilibrium was not set up correctly.</t>
-  </si>
-  <si>
-    <t>You correctly drew a FBD and resolved the 3 kN force into its components (2.599 kN and 1.5 kN), earning partial credit for Part A. However, you did not set up proper equilibrium equations for ΣFx=0 and ΣFy=0 to find O_x and O_y (-25 pts for Part B), and for the moment equation you incorrectly applied a moment arm to the 15 kN·m couple and treated it as a distributed load rather than a free moment, leading to an incorrect M_O with no valid final answers stated (-35 pts for Part C, -15 pts for Part D).</t>
-  </si>
-  <si>
-    <t>You correctly identified several loads (1.4 kN at A, 15 kN·m couple at B, and the 1.5 kN horizontal component at C from 3sin30°), and your FBD shows genuine effort. However, you are missing the beam's self-weight (4.905 kN at midpoint), you did not resolve the vertical component of the 3 kN force (3cos30° = 2.598 kN downward), and the moment equation is incomplete — losing most of the points in Parts B, C, and D. No final numerical answers for O_x, O_y, and M_O were stated clearly.</t>
-  </si>
-  <si>
-    <t>You correctly identified the FBD, computed the beam weight (4905 N), resolved the 3 kN force into components (1.5 kN and 2.60 kN), found O_x = 1.5 kN, and calculated M_O = 7.56 kN·m (clockwise) correctly. However, your O_y calculation is incorrect — you appear to have used 1.1 kN instead of the correct 6.10 kN, losing 10 points in Part B and 5 points in Part D for the final answer presentation.</t>
-  </si>
-  <si>
-    <t>You made a good start by drawing an FBD and correctly identifying the 15 kN·m couple and the 1.4 kN force at A with the right moment arm, but you omitted the beam's self-weight (4.905 kN at 2.4 m) entirely and did not complete the moment equation or provide any force equilibrium equations for O_x and O_y. Your work is incomplete, so most of the points for Parts B, C, and D could not be awarded.</t>
-  </si>
-  <si>
-    <t>You correctly resolved the 3 kN force into its components (1.5 kN and 2.6 kN) and your FBD setup shows good understanding, and your O_y = 6.1 kN matches the correct answer. However, an unexplained 5 kN term in ΣFx led to an incorrect O_x = 6.5 kN (should be 1.5 kN), and the moment equilibrium equation for M_O was not attempted, which cost significant points.</t>
-  </si>
-  <si>
-    <t>You made a genuine attempt by identifying the applied loads (F1 = 1.4 kN, F2 = 15 kN·m couple, F3 = 3 kN at 30°) and their positions, which earns partial setup credit. However, you did not compute the beam's weight, did not resolve F3 into components correctly, did not write equilibrium equations, and did not find O_x, O_y, or M_O, so most points could not be awarded.</t>
-  </si>
-  <si>
-    <t>You correctly computed the beam weight (4.905 kN) at the midpoint, resolved the 3 kN force into correct components, and found O_x = 1.50 kN and O_y = 6.103 kN accurately. However, in the moment equation you added all moment contributions instead of applying the correct signs (the 1.4 kN upward force at A creates a counterclockwise moment that should reduce M_O, and the weight and C-force moments should act oppositely), leading to M_O = 37.56 kN·m instead of the correct 7.56 kN·m, so you lose the 15 points for C3 and 10 points for C1, and 13 points from Part D for the incorrect final moment answer.</t>
-  </si>
-  <si>
-    <t>You attempted to compute moment contributions from each load, which shows some understanding of the problem, but you solved for the resultant moment about O rather than finding the support reactions (O_x, O_y, and M_O) using equilibrium equations (ΣFx=0, ΣFy=0, ΣM_O=0). The correct approach is a fixed-support reaction problem requiring force and moment equilibrium, not a resultant moment calculation, so most of the method-based points could not be awarded.</t>
-  </si>
-  <si>
-    <t>You correctly computed the beam weight, resolved the 3 kN force, identified O_x = 1.5 kN, applied the 15 kN·m couple as a free moment, and arrived at the correct M_O = 7.56 kN·m CCW — great work on the moment equation! However, you did not explicitly write or state the ΣFy = 0 equation or compute O_y ≈ 6.10 kN, which cost you 12 points in Part B and 8 points in Part D.</t>
-  </si>
-  <si>
-    <t>You correctly identified the beam geometry, resolved the 3 kN force into components (1.5 kN and 2.6 kN), and set up the equilibrium framework — good start. However, you used 5 kN instead of the correct beam weight (4.905 kN at x = 2.4 m), did not properly solve the force equilibrium equations for O_x and O_y, and the moment equation has sign/term errors (the couple at B should be added directly without a moment arm, and the final M_O is not correctly isolated). These issues cost significant points in Parts B, C, and D.</t>
-  </si>
-  <si>
-    <t>Your FBD, force decomposition, and equilibrium equations are all set up correctly, showing strong understanding of the problem. You correctly found O_x = 1.5 kN and O_y = 6.105 kN; your moment calculation method is correct, but your final M_O = 7.765 kN·m is slightly outside the accepted tolerance (7.33–7.79 kN·m is acceptable, so this is borderline — deducting 5 pts on C3 for the small arithmetic deviation) and the final answer box lacks explicit direction/sense statements, costing 7 pts on Part D.</t>
-  </si>
-  <si>
-    <t>You correctly computed the beam weight (W = 4.905 kN) and placed it at the midpoint (x = 2.4 m), and you attempted moment calculations showing some understanding of the problem setup. However, your moment equation is set up incorrectly — you applied a distance arm to the 15 kN·m couple (it is a free moment and needs no moment arm), used incorrect moment arms, and did not properly solve for O_x, O_y, and M_O as separate equilibrium equations, resulting in answers far from the correct values.</t>
-  </si>
-  <si>
-    <t>You correctly computed the beam weight (4.905 kN), resolved the 3 kN force into components (1.5 kN and 2.6 kN), and identified O_x = 1.5 kN and O_y ≈ 6.105 kN — well done on those parts. However, your moment sum for M_O is missing the correct sign for the 15 kN·m couple's contribution, leading to M_R = -7.872 kN·m instead of the correct +7.56 kN·m (CCW), which costs you 20 points in Part C; the couple should add +15 kN·m directly to the moment equation without a moment arm.</t>
-  </si>
-  <si>
-    <t>You made a good start by drawing an FBD, correctly resolving the 3 kN force into components (2.59 kN and 1.5 kN), and setting up the equilibrium equations — this earns you solid partial credit for Parts A and B setup. However, you forgot to include the beam's self-weight (W = 4.905 kN) in your calculations, your ΣFx equation was left as 0 = 0 without including the 1.5 kN x-component, ΣFy was incomplete (missing the weight and the 3 kN y-component), and ΣM_O was not completed at all, so no final answers were reached for O_x, O_y, or M_O.</t>
-  </si>
-  <si>
-    <t>You correctly identified the beam weight (4.905 kN), its midpoint location, and resolved the 3 kN force into correct components (1.5 kN and 2.598 kN), which is great work. However, you used a negative sign for the 1.4 kN upward force's moment in your moment equation — since it acts upward at x=1.2 m it creates a CCW (positive) moment, not negative — leading to an incorrect M_O of 14.04 kN·m instead of 7.56 kN·m, and your O_y result was also unclear/incorrect. Please review your sign conventions for moment equilibrium carefully.</t>
-  </si>
-  <si>
-    <t>You drew a reasonable FBD and correctly identified some of the loads, which earns you partial credit for Part A. However, you did not include the beam's self-weight (4.905 kN at midpoint), you omitted the force equilibrium equations for O_x and O_y entirely, and your moment calculation incorrectly sums individual moment contributions as if they were separate equilibrium equations rather than combining them into one equation for M_O — also, the 15 kN·m couple should be added directly (not multiplied by 3 m), and the beam weight term is missing throughout. These fundamental errors mean most of Parts B, C, and D cannot receive credit.</t>
-  </si>
-  <si>
-    <t>You correctly resolved the 3 kN force into its components (1.5 kN and 2.6 kN) and showed a reasonable FBD setup, which earns partial credit. However, your approach to moment equilibrium is fundamentally flawed — you did not take moments about the fixed support O, you omitted the beam's self-weight (4.905 kN at midpoint), and you did not solve for O_x, O_y, and M_O correctly, resulting in an incorrect final answer of 2.52 kN·m instead of M_O = 7.56 kN·m. Force equilibrium equations were also not written or solved.</t>
-  </si>
-  <si>
-    <t>You correctly identified the total beam length (4.8 m) and recognized θ = 30°, which shows some understanding of the problem setup. However, your approach is fundamentally incorrect — you applied F = m·a·cosθ instead of static equilibrium equations (ΣFx=0, ΣFy=0, ΣM=0), and your calculations for the support reactions O_x, O_y, and M_O are missing entirely. Please review cantilever beam equilibrium to find the correct reactions.</t>
-  </si>
-  <si>
-    <t>You correctly set up the FBD, computed the beam weight, and resolved the 3 kN force into components, and your moment equation includes all terms with correct moment arms and the couple treated properly as a free moment. However, you lost points for not explicitly writing and solving the force equilibrium equations to find O_x and O_y, and the direction of M_O should be counterclockwise (7.56 kN·m CCW), not clockwise — deducting 5 pts for wrong direction, 15 pts for missing force equilibrium results, and 8 pts for incomplete final answer presentation.</t>
-  </si>
-  <si>
-    <t>You correctly computed the beam weight (4905 N) and identified the geometry, which earns partial credit for setup (A2). However, your approach treats all forces as simple vertical forces and collapses everything into a single force equation, missing the required separation of x and y equilibrium, the correct resolution of the 3 kN force into components (1.5 kN horizontal, 2.598 kN vertical), the moment equilibrium equation for M_O, and the 15 kN·m couple as a free moment — resulting in a fundamentally incorrect final answer of ~33.7 kN instead of O_x = 1.5 kN, O_y = 6.10 kN, M_O = 7.56 kN·m. You lose 7 pts from A1 (incomplete FBD/reactions), 8 pts from A3 (no component resolution), 25 pts from B (force equilibrium not correctly applied), 35 pts from C (no moment equation), and 7 pts from D (final answer incorrect/incomplete).</t>
-  </si>
-  <si>
-    <t>You correctly identified the x-component of the 3 kN force as 1.5 kN, but you missed the beam's self-weight (4.905 kN) entirely, and your y-force sum omitted it, leading to incorrect O_y and M_O values. Additionally, your moment equation approach treated Mx and My separately in an unclear way, the couple (15 kN·m) was included but the final M_O = 6.49 kN·m is far from the correct 7.56 kN·m, and the support reactions O_x and O_y were not properly solved from equilibrium equations (-5 pts FBD missing weight/reactions, -10 pts missing weight in Fy, -22 pts incorrect moment equation and result, -10 pts final answer incomplete/incorrect, -25 pts force equilibrium not properly set up).</t>
-  </si>
-  <si>
-    <t>You correctly drew the FBD with reactions at O and resolved the 3 kN force's y-component (Fy = 3000cos30° = 2.5 kN), earning partial credit for setup. However, you omitted the beam's self-weight (4.905 kN) entirely, incorrectly used 1.2 m as the moment arm for the 1.4 kN force (should be 1.2 m — actually this is correct, but you used 9.2 m instead), and the 15 kN·m couple was treated with a moment arm (×15 as '15' added to product) rather than as a free moment, leading to significant errors in O_y and M_O; O_x was not clearly reported either.</t>
-  </si>
-  <si>
-    <t>You correctly resolved the 3 kN force into components, computed the beam weight, and set up all three equilibrium equations with proper moment arms — excellent methodology throughout. Your O_x = 1500 N and M_O = 7562.73 N·m (magnitude) are essentially correct, but your O_y = 3764.07 N is significantly off from the expected 6103 N because you appear to have dropped the reaction force O_y from the ΣFy equation, costing you 15 points on B2; additionally, the moment calculation for the 3 kN y-component used an incorrect intermediate value (48. instead of 4.8 × 2598.07), though ECF is applied. You also lost 5 points on Part D for not clearly labeling the final sense/direction of M_O.</t>
-  </si>
-  <si>
-    <t>You correctly resolved the 3 kN force into components (1.5i - 2.59j) and properly included the 15 kN·m couple as a free moment, which shows good understanding. However, you forgot to include the beam's self-weight (4.905 kN at midpoint x=2.4 m) in your moment sum, missed the x-component moment contribution (1.5 kN has no moment about O but you also omitted O_x and O_y from force equilibrium entirely), and only computed moments without providing the support reactions O_x, O_y, and M_O — losing significant points in Parts A, B, C, and D.</t>
-  </si>
-  <si>
-    <t>You correctly identified the beam geometry, resolved the 3 kN force x-component (1.5 kN), and recognized that the 15 kN·m couple is a free moment — good fundamentals. However, your moment equation adds all moments with incorrect signs and does not set ΣM = 0 to solve for M_O; instead you summed external moment magnitudes (getting 37.48 kN·m) rather than finding the reaction M_O = 7.56 kN·m, and your force resultant is missing the reaction components O_x and O_y. You lost significant points in Parts B, C, and D due to not properly applying equilibrium (ΣF = 0, ΣM = 0) to find the support reactions.</t>
-  </si>
-  <si>
-    <t>You correctly resolved the 3 kN force into components and properly included the 15 kN·m couple as a free moment (no arm needed), which shows good understanding. However, you did not write force equilibrium equations to find O_x and O_y, misread the 1.4 kN force as 1.14 kN, and the final moment M_O is incorrect as a result of these errors.</t>
-  </si>
-  <si>
-    <t>You correctly resolved the 3 kN force into components and found O_x = 1.5 kN, which is great. However, your beam weight was taken as approximately 0.95 kN instead of W = 500 × 9.81 = 4.905 kN, which caused incorrect values for O_y and M_O throughout the solution. Make sure to always compute the self-weight of the beam as mass × g and place it at the midpoint.</t>
+    <t>You correctly computed the beam length, weight (W=4.9 kN at midpoint), resolved the 3 kN force into components, and found O_x = 1.5 kN and O_y = 6.1 kN with correct equilibrium equations. However, in the moment equation you treated the 15 kN·m couple as negative (clockwise) when it should be positive (counterclockwise), leading to M_O = 37.55 kN·m instead of the correct 7.56 kN·m, so you lose 10 points for the couple sign error (C2) and 15 points for the incorrect final M_O value (C3), with no deduction in D for the direction/magnitude since it follows from the same mistake.</t>
+  </si>
+  <si>
+    <t>You correctly drew the FBD, computed the beam weight, resolved the 3 kN force into components, and found O_x = 1.5 kN. However, your moment equation about B had incorrect moment arms and was missing key terms, leading to a wrong O_y, and your M_O calculation only used O_y contributions while omitting the beam weight moment, the 1.4 kN force moment, and the 15 kN·m free couple — these errors caused significant point losses in Parts C and D.</t>
+  </si>
+  <si>
+    <t>Excellent work overall — your free-body diagram setup, force decomposition, equilibrium equations, and moment calculation are all correct and well-organized. Your final answers (O_x = 1.50 kN, O_y = 6.103 kN, M_O = 7.561 kN·m) are all within the accepted tolerance. A very minor unit inconsistency (writing W = 4.905 N instead of 4.905 kN) costs 3 points, but your subsequent numerical work is fully consistent so no further deduction is applied.</t>
+  </si>
+  <si>
+    <t>You correctly identified the beam geometry, placed the weight at the midpoint using g=10, and showed some correct moment arms, earning partial credit in Parts A and C. However, you incorrectly decomposed the 3 kN force (using 2.5 and 2.5√3 instead of 1.5 and 2.598 kN), mixed N and kN units throughout causing large numerical errors, and never solved for the fixed-support reactions O_x, O_y, and M_O at point O. Remember that the 15 kN·m is already a couple (free moment) and does not need an equivalent force calculation.</t>
+  </si>
+  <si>
+    <t>You correctly resolved the 3 kN force into its components (2.599 kN and 1.5 kN) and correctly computed the moments from the 1.4 kN force and the 3 kN vertical component about O. However, you missed the beam's self-weight (W = 500×9.81 = 4905 N at midpoint), did not write force equilibrium equations to find O_x and O_y, and incorrectly treated the 15 kN·m couple as a force rather than adding it directly as a free moment in the moment equation — the couple should simply be added as +15 kN·m with no moment arm.</t>
+  </si>
+  <si>
+    <t>You correctly identified the 15 kN·m couple as a free moment and computed the 1.4 kN × 1.2 m = 1.68 kN·m moment contribution, which shows good understanding. However, the beam weight was incorrectly calculated (should be 500 × 9.81 = 4.905 kN, not 15.18 kN), the 3 kN force components were not properly applied with correct moment arms, and the force equilibrium equations (ΣFx, ΣFy) and final reactions O_x, O_y, M_O were not determined.</t>
+  </si>
+  <si>
+    <t>You correctly computed the beam weight as 500×9.81 = 4.905 kN and showed some moment calculations, which earns partial credit. However, the 3 kN force was not resolved into components, O_x and O_y were never found, the 15 kN·m couple was mishandled (multiplied by a distance rather than treated as a free moment), and no correct final values for O_x, O_y, or M_O were stated. The conclusion that 'denge moment = 0, sistem dengededir' is not a valid final answer for the support reactions.</t>
+  </si>
+  <si>
+    <t>Your FBD, weight calculation, and force component resolution were all excellent, and your moment equation about O was set up correctly, yielding the right magnitude of 7.56 kN·m — however, the sense of M_O should be counterclockwise (CCW), not clockwise (-3 pts). Your O_y reaction is incorrect (1.1 kN instead of 6.10 kN) because the 15 kN·m couple is a pure moment and should not be converted into a force (15÷3) in the ΣFy equation, costing you points in Part B and Part D (-20 pts total).</t>
+  </si>
+  <si>
+    <t>You drew a reasonable FBD and correctly identified the moment contributions from the 1.4 kN force (1.68 kN·m) and the 15 kN·m couple, and you started resolving the 3 kN force using cos30°. However, your work is incomplete — you did not include the beam's own weight (W = 4.905 kN at x = 2.4 m) anywhere, did not finish the moment equation, and never solved for O_x, O_y, or a final M_O value. Partial credit is awarded for the correct setup of the FBD, the moment arm for the 1.4 kN force, and the correct treatment of the couple as a free moment.</t>
+  </si>
+  <si>
+    <t>You correctly resolved the 3 kN force into components and found Oy = 6.1 kN, which is excellent. However, an unexplained 5 kN horizontal force was included in ΣFx, leading to an incorrect Ox = 6.5 kN instead of 1.5 kN, and the moment equilibrium equation (ΣM_O = 0) was never written, so M_O could not be found — this cost 35 points in Part C.</t>
+  </si>
+  <si>
+    <t>You made a genuine attempt by identifying the given forces (F1 = 1.4 kN, F2 = 15 kN·m couple, F3 = 3 kN at 30°) and their locations, which earns partial credit for setup. However, you did not compute the beam's weight, write any equilibrium equations, or solve for the reactions O_x, O_y, and M_O, so most points could not be awarded.</t>
+  </si>
+  <si>
+    <t>Your force equilibrium work is excellent — Ox = 1.50 kN and Oy = 6.103 kN are both correct. In the moment equation, you correctly identified all moment arms and included the couple as a free moment, but you summed the moments as external loads rather than setting ΣM₀ = 0 and solving for M₀; the correct approach gives M₀ = 7.56 kN·m (CCW), not 37.56 kN·m, costing 7 points in Part C and 7 points in Part D.</t>
+  </si>
+  <si>
+    <t>You correctly identified the 3 kN force components (1.5 kN and 2.598 kN) and placed the beam weight near the midpoint, but your approach does not set up equilibrium equations (ΣFx=0, ΣFy=0, ΣM=0) to find the support reactions O_x, O_y, and M_O. The 15 kN·m couple is a free moment and should not be multiplied by a distance, and the final answer should report three separate reaction components, not a single resultant moment magnitude.</t>
+  </si>
+  <si>
+    <t>Your FBD, force components, and moment calculations are all excellent — you correctly identified all moment arms and properly treated the 15 kN·m couple as a free moment, arriving at the correct M_O = 7.56 kN·m CCW. However, you did not explicitly write the ΣFy = 0 equation or state a final numerical value for O_y, which cost you points in Parts B and D. Make sure to always present all three reaction components clearly with units and directions in your final answer.</t>
+  </si>
+  <si>
+    <t>You correctly identified the geometry, resolved the 3 kN force into components (1.5 kN and 2.6 kN), and properly treated the 15 kN·m couple as a free moment — good work on those steps. However, you used the wrong moment arm (3 m instead of 2.4 m) for the beam's weight, did not write out explicit ΣFx and ΣFy equations to find O_x and O_y, and the final answer is incomplete — make sure to solve for all three reactions (O_x, O_y, and M_O) with correct values and units.</t>
+  </si>
+  <si>
+    <t>You correctly identified all reactions, set up all three equilibrium equations properly, and included the couple moment as a free moment — excellent work overall. Your M_O result (7.764 kN·m) has a small arithmetic slip from rounding the 3 kN components, costing 5 points in Part C, and a minor unit/direction clarity issue in the final answer costs 2 points in Part D.</t>
+  </si>
+  <si>
+    <t>You made a genuine attempt and showed some moment calculations, but the work is very incomplete — there is no FBD, no equilibrium equations (ΣFx, ΣFy, ΣM), no beam weight computation, and no final answers for O_x, O_y, or M_O. The partial moment arm calculations (1.2 × 1.46 and 4.8 × 1.54) and the note about the 15 kN·m couple earn minimal partial credit for a relevant start.</t>
+  </si>
+  <si>
+    <t>You demonstrated excellent problem-solving by correctly computing the beam weight, resolving the 3 kN force, applying equilibrium equations, and treating the 15 kN·m couple as a free moment — all of which is great work. A minor arithmetic slip in summing the moments gave -7.872 instead of the correct -7.572 kN·m, costing 5 points in Part C. Overall, this is a very strong submission!</t>
+  </si>
+  <si>
+    <t>You correctly drew a FBD showing the beam with the fixed support, the 15 kN·m couple, the 1.4 kN upward force, and the 3 kN force at 30°, and you properly resolved the 3 kN into components (2.59 kN and 1.5 kN), earning partial credit for Part A. However, you did not include the beam's self-weight (W = 4.905 kN at midpoint), and your equilibrium equations were left essentially incomplete — ΣFx = 0 was set to zero without including the 1.5 kN x-component, ΣFy only partially written, and ΣM_O was not evaluated — so no credit could be awarded for Parts B, C, or D beyond the setup.</t>
+  </si>
+  <si>
+    <t>You correctly computed the beam weight, resolved the 3 kN force into components, and set up the moment equation with the right moment arms. However, the 3 kN vertical component at C should create a clockwise (negative) moment about O, not a positive one, which caused your M_O to be 14.04 kN·m instead of the correct 7.56 kN·m, and your O_y value and final answer box were also inconsistent with the correct equilibrium result.</t>
+  </si>
+  <si>
+    <t>You drew a reasonable FBD and correctly identified the 1.4 kN force and the 15 kN·m couple, earning partial credit for setup. However, you did not write force equilibrium equations (no O_x or O_y found), you omitted the beam's self-weight (4.905 kN at midpoint), you incorrectly treated the moment equation by summing individual 'moment contributions' without a proper equilibrium statement (ΣM_O = 0), and the 15 kN·m couple was incorrectly multiplied by a 3 m arm instead of being added directly as a free moment, leading to a final M_O = 53.88 kN·m that is far from the correct 7.56 kN·m. You receive credit for the FBD attempt (partial A1), the correct 1.4 kN × 1.2 m term, and the partial setup effort.</t>
+  </si>
+  <si>
+    <t>Your FBD shows a reasonable setup with the beam geometry and the 15 kN·m couple correctly identified, but you missed the beam's self-weight (W = 500×9.81 = 4.905 kN at midpoint) and swapped the x/y components of the 3 kN force (sin30° = 1.5 kN horizontal, cos30° = 2.598 kN vertical). No force equilibrium equations for O_x and O_y were written, and the moment calculation mixed up units (treating a moment result in kN·m as a force in kN), so no valid final reactions were obtained.</t>
+  </si>
+  <si>
+    <t>You correctly identified the total beam length (4.8 m) and the angle (30°), which shows some initial understanding of the problem setup. However, your approach using F = m·a·cosθ is not applicable here — this is a static equilibrium problem requiring sum of forces and moments equal to zero, not a dynamics problem. No correct equilibrium equations (ΣFx=0, ΣFy=0, ΣM=0) were written, and the final answers for O_x, O_y, and M_O are missing, so most points could not be awarded.</t>
+  </si>
+  <si>
+    <t>Your free body diagram, weight calculation, force decomposition, and moment equation are all well done — the moment result of 7.62 kN·m is correct within rounding. However, you did not explicitly state the final values for O_x and O_y from force equilibrium (losing significant credit in Parts B and D), and incorrectly converted the 15 kN·m couple into a force (couples are free moments and should not be converted to forces). Make sure to complete all three equilibrium equations and state all three support reactions clearly.</t>
+  </si>
+  <si>
+    <t>You correctly identified the beam weight (W = 4905 N) and showed a genuine attempt at equilibrium, which earns partial credit. However, your approach treats the problem as a simple force balance rather than a fixed-support (cantilever) problem: you did not identify the three reactions (O_x, O_y, and moment M_O), did not resolve the 3 kN force into components, did not compute moment equilibrium, and your final answer of ~33.7 kN does not match the expected results. Please review cantilever beam reactions and moment equilibrium for future quizzes.</t>
+  </si>
+  <si>
+    <t>You correctly decomposed the 3 kN force into its components and properly included the 15 kN·m couple as a free moment — good work on those steps. However, the beam's self-weight (W = 4.905 kN at midpoint x = 2.4 m) was omitted entirely, and the problem required setting up equilibrium equations (ΣFx = 0, ΣFy = 0, ΣM_O = 0) to find the support reactions O_x, O_y, and M_O at the fixed support, rather than computing the resultant of the applied loads. There was also an arithmetic error in the moment of the 1.4 kN force: 1.4 × 1.2 = 1.68, and 3cos30 × 4.8 = 12.47, giving −10.79 kN·m, not −1.31 kN·m.</t>
+  </si>
+  <si>
+    <t>You correctly resolved all forces, computed the beam weight, applied the couple as a free moment, and found O_x = 1500 N and M_O ≈ 7563 N·m accurately. However, there is an arithmetic error in your ΣFy equation — 4905 + 2598.07 = 7503.07, not 4141, so O_y should be approximately 6103 N rather than 3764.07 N, costing you points in Part B and Part D. Also, make sure to show the reaction moment M_O explicitly on your FBD at the fixed support.</t>
+  </si>
+  <si>
+    <t>You correctly resolved the 3 kN force into components (1.5i - 2.59j) and correctly computed the moment of the 1.4 kN force (1.68 kN·m) and included the 15 kN·m couple — good understanding of free moments. However, you missed the beam's self-weight entirely (no W = 4905 N calculated or placed at midpoint), did not write force equilibrium equations to find O_x and O_y, and your moment sum only partially accounts for the applied loads, leading to an incorrect M_O of 4.25 kN·m instead of 7.56 kN·m; you lose 9 pts for missing weight (A2), 25 pts for missing force equilibrium (Part B), 10 pts for the incorrect moment equation/result (C1/C3), and 15 pts for missing O_x and O_y in the final answer (Part D).</t>
+  </si>
+  <si>
+    <t>You correctly resolved the 3 kN force into components, computed the beam weight at the midpoint, and found O_x = 1.5 kN, but the 15 kN·m couple must be added directly as a free moment (not multiplied by any distance), which led to a large error in M_O. Your moment signs were also inconsistent, and O_y was not explicitly solved, costing points in Parts C and D.</t>
+  </si>
+  <si>
+    <t>You correctly resolved the 3 kN force components and computed the beam weight at the correct midpoint location, which is great. However, you did not write out the force equilibrium equations (ΣFx=0, ΣFy=0) to find O_x and O_y, and the moment summation contains sign and arithmetic errors leading to an incorrect M_O; also, the final answers for all three reactions were not clearly stated with units and directions.</t>
+  </si>
+  <si>
+    <t>You correctly resolved the 3 kN force into its components and found O_x = 1.5 kN, and you properly included the 15 kN·m couple as a free moment — well done on those steps. However, you used approximately 0.5 kN for the beam's weight instead of W = 500 × 9.81 = 4.905 kN, which led to incorrect values for O_y and M_O (-7 pts for A2, -7 pts carried into B2, C1, C3, D1).</t>
+  </si>
+  <si>
+    <t>You correctly computed the beam weight (4.905 kN) at the midpoint and resolved the 3 kN force into components, earning good marks for the FBD setup. However, you treated the 15 kN·m couple as a force by multiplying it by a moment arm (it is a free moment and should be added directly), and you did not write explicit force equilibrium equations to find O_x and O_y, resulting in significant point losses in Parts B, C, and D.</t>
   </si>
 </sst>
 </file>
@@ -1280,7 +1283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I363"/>
+  <dimension ref="A1:I365"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -9897,7 +9900,7 @@
         <v>118</v>
       </c>
       <c r="H320">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="I320" t="s">
         <v>280</v>
@@ -9926,7 +9929,7 @@
         <v>118</v>
       </c>
       <c r="H321">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I321" t="s">
         <v>281</v>
@@ -9955,7 +9958,7 @@
         <v>118</v>
       </c>
       <c r="H322">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I322" t="s">
         <v>282</v>
@@ -10036,7 +10039,7 @@
         <v>118</v>
       </c>
       <c r="H325">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I325" t="s">
         <v>283</v>
@@ -10065,7 +10068,7 @@
         <v>118</v>
       </c>
       <c r="H326">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I326" t="s">
         <v>284</v>
@@ -10094,10 +10097,10 @@
         <v>118</v>
       </c>
       <c r="H327">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I327" t="s">
-        <v>226</v>
+        <v>285</v>
       </c>
     </row>
     <row r="328" spans="1:9">
@@ -10149,10 +10152,10 @@
         <v>118</v>
       </c>
       <c r="H329">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I329" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="330" spans="1:9">
@@ -10204,10 +10207,10 @@
         <v>118</v>
       </c>
       <c r="H331">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I331" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="332" spans="1:9">
@@ -10262,10 +10265,10 @@
         <v>118</v>
       </c>
       <c r="H333">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I333" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="334" spans="1:9">
@@ -10320,7 +10323,7 @@
         <v>15</v>
       </c>
       <c r="I335" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="336" spans="1:9">
@@ -10346,10 +10349,10 @@
         <v>118</v>
       </c>
       <c r="H336">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="I336" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="337" spans="1:9">
@@ -10375,10 +10378,10 @@
         <v>118</v>
       </c>
       <c r="H337">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I337" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="338" spans="1:9">
@@ -10404,10 +10407,10 @@
         <v>118</v>
       </c>
       <c r="H338">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I338" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="339" spans="1:9">
@@ -10485,10 +10488,10 @@
         <v>118</v>
       </c>
       <c r="H341">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I341" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="342" spans="1:9">
@@ -10514,10 +10517,10 @@
         <v>118</v>
       </c>
       <c r="H342">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I342" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="343" spans="1:9">
@@ -10543,10 +10546,10 @@
         <v>118</v>
       </c>
       <c r="H343">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I343" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="344" spans="1:9">
@@ -10572,10 +10575,10 @@
         <v>118</v>
       </c>
       <c r="H344">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="I344" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="345" spans="1:9">
@@ -10604,7 +10607,7 @@
         <v>22</v>
       </c>
       <c r="I345" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="346" spans="1:9">
@@ -10630,10 +10633,10 @@
         <v>118</v>
       </c>
       <c r="H346">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="I346" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="347" spans="1:9">
@@ -10688,7 +10691,7 @@
         <v>18</v>
       </c>
       <c r="I348" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="349" spans="1:9">
@@ -10714,10 +10717,10 @@
         <v>118</v>
       </c>
       <c r="H349">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I349" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="350" spans="1:9">
@@ -10743,10 +10746,10 @@
         <v>118</v>
       </c>
       <c r="H350">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I350" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="351" spans="1:9">
@@ -10772,10 +10775,10 @@
         <v>118</v>
       </c>
       <c r="H351">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I351" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="352" spans="1:9">
@@ -10801,10 +10804,10 @@
         <v>118</v>
       </c>
       <c r="H352">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I352" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="353" spans="1:9">
@@ -10885,10 +10888,10 @@
         <v>118</v>
       </c>
       <c r="H355">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I355" t="s">
-        <v>303</v>
+        <v>226</v>
       </c>
     </row>
     <row r="356" spans="1:9">
@@ -10914,10 +10917,10 @@
         <v>118</v>
       </c>
       <c r="H356">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I356" t="s">
-        <v>226</v>
+        <v>304</v>
       </c>
     </row>
     <row r="357" spans="1:9">
@@ -10943,10 +10946,10 @@
         <v>118</v>
       </c>
       <c r="H357">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I357" t="s">
-        <v>304</v>
+        <v>226</v>
       </c>
     </row>
     <row r="358" spans="1:9">
@@ -10972,7 +10975,7 @@
         <v>118</v>
       </c>
       <c r="H358">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I358" t="s">
         <v>305</v>
@@ -11056,7 +11059,7 @@
         <v>118</v>
       </c>
       <c r="H361">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="I361" t="s">
         <v>307</v>
@@ -11085,7 +11088,7 @@
         <v>118</v>
       </c>
       <c r="H362">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I362" t="s">
         <v>308</v>
@@ -11114,10 +11117,68 @@
         <v>118</v>
       </c>
       <c r="H363">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I363" t="s">
         <v>309</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9">
+      <c r="A364">
+        <v>2483960</v>
+      </c>
+      <c r="B364" t="s">
+        <v>69</v>
+      </c>
+      <c r="C364" t="s">
+        <v>108</v>
+      </c>
+      <c r="D364">
+        <v>902</v>
+      </c>
+      <c r="E364" t="s">
+        <v>110</v>
+      </c>
+      <c r="F364" t="s">
+        <v>114</v>
+      </c>
+      <c r="G364" t="s">
+        <v>118</v>
+      </c>
+      <c r="H364">
+        <v>27</v>
+      </c>
+      <c r="I364" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9">
+      <c r="A365">
+        <v>2612865</v>
+      </c>
+      <c r="B365" t="s">
+        <v>43</v>
+      </c>
+      <c r="C365" t="s">
+        <v>108</v>
+      </c>
+      <c r="D365">
+        <v>902</v>
+      </c>
+      <c r="E365" t="s">
+        <v>110</v>
+      </c>
+      <c r="F365" t="s">
+        <v>113</v>
+      </c>
+      <c r="G365" t="s">
+        <v>118</v>
+      </c>
+      <c r="H365">
+        <v>0</v>
+      </c>
+      <c r="I365" t="s">
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2119" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2329" uniqueCount="327">
   <si>
     <t>student_id</t>
   </si>
@@ -952,6 +952,54 @@
   </si>
   <si>
     <t>You correctly computed the beam weight (4.905 kN) at the midpoint and resolved the 3 kN force into components, earning good marks for the FBD setup. However, you treated the 15 kN·m couple as a force by multiplying it by a moment arm (it is a free moment and should be added directly), and you did not write explicit force equilibrium equations to find O_x and O_y, resulting in significant point losses in Parts B, C, and D.</t>
+  </si>
+  <si>
+    <t>You correctly identified F = 6000 N and set up the moment equation 400/6000, arriving at the correct numerical value of d ≈ 66.6 mm — well done on the core calculation. However, you did not explicitly state the direction of the resultant force (+y direction), did not write the moment equation clearly (C1), and did not provide a final statement including units, sign/side of origin, or the direction of R (Part D). These missing elements cost points in Parts A, B, C3, and D.</t>
+  </si>
+  <si>
+    <t>Your work is excellent — you correctly identified R = 6 kN in the +y direction, set up the moment equation using the vector cross product, and solved for x = +66.7 mm with the correct sign and units. Everything is complete and well-presented. Full marks!</t>
+  </si>
+  <si>
+    <t>You correctly identified R = 6 kN, set up the moment equation (6000x = 400), and found x = 66.7 mm with proper unit conversion — excellent work on the core method. However, you did not explicitly state the direction of R (+y direction) in Part B (-10 pts), and the final answer lacks a clear statement of the direction and the sign/side of x on the axis (-5 pts for Part D). Make sure to always specify both magnitude and direction for forces, and confirm the sign of the location in your final answer.</t>
+  </si>
+  <si>
+    <t>You made a genuine attempt by drawing the coordinate system and identifying the force F, the couple M = 400 N·m, and the components Fx and Fy, which earns partial credit for effort. However, no moment equation was set up, no numerical value for the resultant or its location was calculated, and no final answer was stated. To earn full credit, you need to write R = 6 kN in the +y direction and solve d = 400/6000 = 66.7 mm for the line of action.</t>
+  </si>
+  <si>
+    <t>Excellent work! You correctly identified R = 6 kN in the +y direction, set up the cross product moment equation (r × R = M), and solved for x ≈ 66.7 mm with proper units. A minor deduction of 5 points is applied because the sign/direction of x (positive x-axis side) was not explicitly stated, only the magnitude was given.</t>
+  </si>
+  <si>
+    <t>Excellent work! You correctly identified R = 6 kN in the +j direction, set up the cross product moment equation r × R = M, and solved for x = 66.7 mm with the correct sign and units. Your solution is complete, well-organized, and fully correct.</t>
+  </si>
+  <si>
+    <t>You correctly identified the given values and set up the moment equation M = F·d with the correct force value of 6000 N, earning credit for Part A and the moment equation setup. However, your division was incorrect (400/400 instead of 400/6000), giving d = 1 N·m instead of 0.0667 m, and the subsequent use of a sine function and angle is not applicable to this problem — the force is purely in the +y direction so d is simply 400/6000 = 66.7 mm along the x-axis. No final answer for R's direction or magnitude or the correct location was stated, so Part B and Part D points are largely lost.</t>
+  </si>
+  <si>
+    <t>Your solution page was submitted completely blank with no work shown. Unfortunately, no credit can be awarded without any supporting calculations or answers, as stated on the quiz sheet itself.</t>
+  </si>
+  <si>
+    <t>You correctly identified that ΣFx = 0 and ΣFy = 6 kN, showing you understand the resultant force concept (Parts A1, B1, B2 credited). However, you did not write a moment equation to locate the line of action of the resultant, so no credit was awarded for Parts C or D, and the final answer is incomplete.</t>
+  </si>
+  <si>
+    <t>You correctly identified that R = 6 kN and used M = F·d to find d = 0.067 m (66.7 mm) on the x-axis — excellent work on the core method. However, you did not clearly specify the direction of the resultant force (i.e., +y direction), and the sign/side of d on the x-axis was not explicitly stated, resulting in small deductions for Part B (−5 pts) and Part C (−7 pts). Overall, your approach and final answer are solid!</t>
+  </si>
+  <si>
+    <t>You correctly identified the moment equation M = Fd and computed d = 400/6000 = 0.067 m, earning good partial credit for Parts A and C. However, the resultant of a force-couple system is a single force (R = 6 kN in the +y direction at x = 66.7 mm), not a couple of ±6 kN — the couple interpretation and the final cross-product calculation (2,400,000 N) are incorrect, resulting in significant deductions in Parts B, C, and D.</t>
+  </si>
+  <si>
+    <t>You correctly set up the moment equation M = F×d and found d = 66.6 mm, which is excellent work on Part C. However, you did not clearly state the resultant force R = 6 kN in the +y direction as a final answer (Part B/D), and the expression F = M/d giving 6.01 kN suggests a unit inconsistency (using 400/66.6 instead of properly identifying R = 6 kN), which costs points in Parts A, B, and D.</t>
+  </si>
+  <si>
+    <t>Your setup and moment equation are excellent — you correctly identified the couple moment, wrote the cross product equation, and solved for |d| = 66.7 mm with the right magnitude and method. However, you stated the force direction as -y (instead of +y) and consequently got x = -66.7 mm instead of +66.7 mm, which costs 10 points for direction (Part B) and 15 points for the sign of the location (Part C3).</t>
+  </si>
+  <si>
+    <t>You correctly identified the moment equation M = F×r and noted M = 400 N·m anticlockwise, and you correctly wrote the resultant force as F = 6000j N — these show good conceptual understanding. However, you did not solve for the location 'd' of the line of action (the key step worth 45 points), and your final answer is incomplete, missing the numerical value of d and a clear final statement. To earn full credit, you need to set up 400 = d × 6000 and solve for d = 0.0667 m (66.7 mm) on the +x side.</t>
+  </si>
+  <si>
+    <t>You correctly identified that M_O = 400 N·m and F = 6 kN, and you set up M_O = F·d which is the right approach. However, you incorrectly decomposed the couple into x and y components (the couple is a scalar moment about z, not a vector to be broken into components), and then incorrectly added force components to get a resultant of 6.2 kN — the resultant force must simply be R = 6 kN in the +y direction, and the location d = 400/6000 = 0.0667 m should follow from the moment equation.</t>
+  </si>
+  <si>
+    <t>You correctly set up the moment equation (400 = 0.066 × 6000 N) and found the correct location x = 0.066 m, earning full credit for Part C. However, you incorrectly approached Part A and B by treating this as an equilibrium problem (ΣFx = 0), concluding the resultant is -6j kN in the x-direction rather than recognizing R = 6 kN in the +y direction; this costs 20 pts for Part A and 20 pts for Part B, and the final answer statement is also incomplete (-5 pts for Part D).</t>
   </si>
 </sst>
 </file>
@@ -1283,7 +1331,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I365"/>
+  <dimension ref="A1:I400"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -8680,13 +8728,16 @@
         <v>112</v>
       </c>
       <c r="F277" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G277" t="s">
         <v>117</v>
       </c>
+      <c r="H277">
+        <v>0</v>
+      </c>
       <c r="I277" t="s">
-        <v>173</v>
+        <v>226</v>
       </c>
     </row>
     <row r="278" spans="1:9">
@@ -11179,6 +11230,976 @@
       </c>
       <c r="I365" t="s">
         <v>248</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9">
+      <c r="A366">
+        <v>2003743</v>
+      </c>
+      <c r="B366" t="s">
+        <v>45</v>
+      </c>
+      <c r="C366" t="s">
+        <v>108</v>
+      </c>
+      <c r="D366">
+        <v>902</v>
+      </c>
+      <c r="E366" t="s">
+        <v>112</v>
+      </c>
+      <c r="F366" t="s">
+        <v>113</v>
+      </c>
+      <c r="G366" t="s">
+        <v>117</v>
+      </c>
+      <c r="I366" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9">
+      <c r="A367">
+        <v>2100421</v>
+      </c>
+      <c r="B367" t="s">
+        <v>11</v>
+      </c>
+      <c r="C367" t="s">
+        <v>108</v>
+      </c>
+      <c r="D367">
+        <v>902</v>
+      </c>
+      <c r="E367" t="s">
+        <v>112</v>
+      </c>
+      <c r="F367" t="s">
+        <v>113</v>
+      </c>
+      <c r="G367" t="s">
+        <v>117</v>
+      </c>
+      <c r="I367" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9">
+      <c r="A368">
+        <v>2101613</v>
+      </c>
+      <c r="B368" t="s">
+        <v>12</v>
+      </c>
+      <c r="C368" t="s">
+        <v>108</v>
+      </c>
+      <c r="D368">
+        <v>902</v>
+      </c>
+      <c r="E368" t="s">
+        <v>112</v>
+      </c>
+      <c r="F368" t="s">
+        <v>114</v>
+      </c>
+      <c r="G368" t="s">
+        <v>117</v>
+      </c>
+      <c r="H368">
+        <v>52</v>
+      </c>
+      <c r="I368" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9">
+      <c r="A369">
+        <v>2101812</v>
+      </c>
+      <c r="B369" t="s">
+        <v>46</v>
+      </c>
+      <c r="C369" t="s">
+        <v>108</v>
+      </c>
+      <c r="D369">
+        <v>902</v>
+      </c>
+      <c r="E369" t="s">
+        <v>112</v>
+      </c>
+      <c r="F369" t="s">
+        <v>113</v>
+      </c>
+      <c r="G369" t="s">
+        <v>117</v>
+      </c>
+      <c r="I369" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9">
+      <c r="A370">
+        <v>2104775</v>
+      </c>
+      <c r="B370" t="s">
+        <v>48</v>
+      </c>
+      <c r="C370" t="s">
+        <v>108</v>
+      </c>
+      <c r="D370">
+        <v>902</v>
+      </c>
+      <c r="E370" t="s">
+        <v>112</v>
+      </c>
+      <c r="F370" t="s">
+        <v>113</v>
+      </c>
+      <c r="G370" t="s">
+        <v>117</v>
+      </c>
+      <c r="I370" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9">
+      <c r="A371">
+        <v>2106789</v>
+      </c>
+      <c r="B371" t="s">
+        <v>14</v>
+      </c>
+      <c r="C371" t="s">
+        <v>108</v>
+      </c>
+      <c r="D371">
+        <v>902</v>
+      </c>
+      <c r="E371" t="s">
+        <v>112</v>
+      </c>
+      <c r="F371" t="s">
+        <v>113</v>
+      </c>
+      <c r="G371" t="s">
+        <v>117</v>
+      </c>
+      <c r="I371" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9">
+      <c r="A372">
+        <v>2106808</v>
+      </c>
+      <c r="B372" t="s">
+        <v>96</v>
+      </c>
+      <c r="C372" t="s">
+        <v>108</v>
+      </c>
+      <c r="D372">
+        <v>902</v>
+      </c>
+      <c r="E372" t="s">
+        <v>112</v>
+      </c>
+      <c r="F372" t="s">
+        <v>113</v>
+      </c>
+      <c r="G372" t="s">
+        <v>117</v>
+      </c>
+      <c r="I372" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9">
+      <c r="A373">
+        <v>2200601</v>
+      </c>
+      <c r="B373" t="s">
+        <v>16</v>
+      </c>
+      <c r="C373" t="s">
+        <v>108</v>
+      </c>
+      <c r="D373">
+        <v>902</v>
+      </c>
+      <c r="E373" t="s">
+        <v>112</v>
+      </c>
+      <c r="F373" t="s">
+        <v>113</v>
+      </c>
+      <c r="G373" t="s">
+        <v>117</v>
+      </c>
+      <c r="I373" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9">
+      <c r="A374">
+        <v>2202877</v>
+      </c>
+      <c r="B374" t="s">
+        <v>51</v>
+      </c>
+      <c r="C374" t="s">
+        <v>108</v>
+      </c>
+      <c r="D374">
+        <v>902</v>
+      </c>
+      <c r="E374" t="s">
+        <v>112</v>
+      </c>
+      <c r="F374" t="s">
+        <v>113</v>
+      </c>
+      <c r="G374" t="s">
+        <v>117</v>
+      </c>
+      <c r="I374" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9">
+      <c r="A375">
+        <v>2252125</v>
+      </c>
+      <c r="B375" t="s">
+        <v>97</v>
+      </c>
+      <c r="C375" t="s">
+        <v>108</v>
+      </c>
+      <c r="D375">
+        <v>902</v>
+      </c>
+      <c r="E375" t="s">
+        <v>112</v>
+      </c>
+      <c r="F375" t="s">
+        <v>114</v>
+      </c>
+      <c r="G375" t="s">
+        <v>117</v>
+      </c>
+      <c r="H375">
+        <v>100</v>
+      </c>
+      <c r="I375" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9">
+      <c r="A376">
+        <v>2252127</v>
+      </c>
+      <c r="B376" t="s">
+        <v>98</v>
+      </c>
+      <c r="C376" t="s">
+        <v>108</v>
+      </c>
+      <c r="D376">
+        <v>902</v>
+      </c>
+      <c r="E376" t="s">
+        <v>112</v>
+      </c>
+      <c r="F376" t="s">
+        <v>114</v>
+      </c>
+      <c r="G376" t="s">
+        <v>117</v>
+      </c>
+      <c r="H376">
+        <v>85</v>
+      </c>
+      <c r="I376" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9">
+      <c r="A377">
+        <v>2282610</v>
+      </c>
+      <c r="B377" t="s">
+        <v>99</v>
+      </c>
+      <c r="C377" t="s">
+        <v>108</v>
+      </c>
+      <c r="D377">
+        <v>902</v>
+      </c>
+      <c r="E377" t="s">
+        <v>112</v>
+      </c>
+      <c r="F377" t="s">
+        <v>114</v>
+      </c>
+      <c r="G377" t="s">
+        <v>117</v>
+      </c>
+      <c r="H377">
+        <v>15</v>
+      </c>
+      <c r="I377" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9">
+      <c r="A378">
+        <v>2284111</v>
+      </c>
+      <c r="B378" t="s">
+        <v>17</v>
+      </c>
+      <c r="C378" t="s">
+        <v>108</v>
+      </c>
+      <c r="D378">
+        <v>902</v>
+      </c>
+      <c r="E378" t="s">
+        <v>112</v>
+      </c>
+      <c r="F378" t="s">
+        <v>113</v>
+      </c>
+      <c r="G378" t="s">
+        <v>117</v>
+      </c>
+      <c r="I378" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9">
+      <c r="A379">
+        <v>2355702</v>
+      </c>
+      <c r="B379" t="s">
+        <v>18</v>
+      </c>
+      <c r="C379" t="s">
+        <v>108</v>
+      </c>
+      <c r="D379">
+        <v>902</v>
+      </c>
+      <c r="E379" t="s">
+        <v>112</v>
+      </c>
+      <c r="F379" t="s">
+        <v>113</v>
+      </c>
+      <c r="G379" t="s">
+        <v>117</v>
+      </c>
+      <c r="I379" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9">
+      <c r="A380">
+        <v>2359322</v>
+      </c>
+      <c r="B380" t="s">
+        <v>100</v>
+      </c>
+      <c r="C380" t="s">
+        <v>108</v>
+      </c>
+      <c r="D380">
+        <v>902</v>
+      </c>
+      <c r="E380" t="s">
+        <v>112</v>
+      </c>
+      <c r="F380" t="s">
+        <v>114</v>
+      </c>
+      <c r="G380" t="s">
+        <v>117</v>
+      </c>
+      <c r="H380">
+        <v>95</v>
+      </c>
+      <c r="I380" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9">
+      <c r="A381">
+        <v>2359481</v>
+      </c>
+      <c r="B381" t="s">
+        <v>101</v>
+      </c>
+      <c r="C381" t="s">
+        <v>108</v>
+      </c>
+      <c r="D381">
+        <v>902</v>
+      </c>
+      <c r="E381" t="s">
+        <v>112</v>
+      </c>
+      <c r="F381" t="s">
+        <v>114</v>
+      </c>
+      <c r="G381" t="s">
+        <v>117</v>
+      </c>
+      <c r="H381">
+        <v>100</v>
+      </c>
+      <c r="I381" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9">
+      <c r="A382">
+        <v>2359764</v>
+      </c>
+      <c r="B382" t="s">
+        <v>19</v>
+      </c>
+      <c r="C382" t="s">
+        <v>108</v>
+      </c>
+      <c r="D382">
+        <v>902</v>
+      </c>
+      <c r="E382" t="s">
+        <v>112</v>
+      </c>
+      <c r="F382" t="s">
+        <v>113</v>
+      </c>
+      <c r="G382" t="s">
+        <v>117</v>
+      </c>
+      <c r="H382">
+        <v>0</v>
+      </c>
+      <c r="I382" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9">
+      <c r="A383">
+        <v>2360367</v>
+      </c>
+      <c r="B383" t="s">
+        <v>102</v>
+      </c>
+      <c r="C383" t="s">
+        <v>108</v>
+      </c>
+      <c r="D383">
+        <v>902</v>
+      </c>
+      <c r="E383" t="s">
+        <v>112</v>
+      </c>
+      <c r="F383" t="s">
+        <v>114</v>
+      </c>
+      <c r="G383" t="s">
+        <v>117</v>
+      </c>
+      <c r="H383">
+        <v>42</v>
+      </c>
+      <c r="I383" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9">
+      <c r="A384">
+        <v>2364571</v>
+      </c>
+      <c r="B384" t="s">
+        <v>21</v>
+      </c>
+      <c r="C384" t="s">
+        <v>108</v>
+      </c>
+      <c r="D384">
+        <v>902</v>
+      </c>
+      <c r="E384" t="s">
+        <v>112</v>
+      </c>
+      <c r="F384" t="s">
+        <v>114</v>
+      </c>
+      <c r="G384" t="s">
+        <v>117</v>
+      </c>
+      <c r="H384">
+        <v>0</v>
+      </c>
+      <c r="I384" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9">
+      <c r="A385">
+        <v>2366271</v>
+      </c>
+      <c r="B385" t="s">
+        <v>25</v>
+      </c>
+      <c r="C385" t="s">
+        <v>108</v>
+      </c>
+      <c r="D385">
+        <v>902</v>
+      </c>
+      <c r="E385" t="s">
+        <v>112</v>
+      </c>
+      <c r="F385" t="s">
+        <v>114</v>
+      </c>
+      <c r="G385" t="s">
+        <v>117</v>
+      </c>
+      <c r="H385">
+        <v>0</v>
+      </c>
+      <c r="I385" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9">
+      <c r="A386">
+        <v>2366906</v>
+      </c>
+      <c r="B386" t="s">
+        <v>56</v>
+      </c>
+      <c r="C386" t="s">
+        <v>108</v>
+      </c>
+      <c r="D386">
+        <v>902</v>
+      </c>
+      <c r="E386" t="s">
+        <v>112</v>
+      </c>
+      <c r="F386" t="s">
+        <v>113</v>
+      </c>
+      <c r="G386" t="s">
+        <v>117</v>
+      </c>
+      <c r="I386" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9">
+      <c r="A387">
+        <v>2367137</v>
+      </c>
+      <c r="B387" t="s">
+        <v>27</v>
+      </c>
+      <c r="C387" t="s">
+        <v>108</v>
+      </c>
+      <c r="D387">
+        <v>902</v>
+      </c>
+      <c r="E387" t="s">
+        <v>112</v>
+      </c>
+      <c r="F387" t="s">
+        <v>114</v>
+      </c>
+      <c r="G387" t="s">
+        <v>117</v>
+      </c>
+      <c r="H387">
+        <v>25</v>
+      </c>
+      <c r="I387" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9">
+      <c r="A388">
+        <v>2472419</v>
+      </c>
+      <c r="B388" t="s">
+        <v>103</v>
+      </c>
+      <c r="C388" t="s">
+        <v>108</v>
+      </c>
+      <c r="D388">
+        <v>902</v>
+      </c>
+      <c r="E388" t="s">
+        <v>112</v>
+      </c>
+      <c r="F388" t="s">
+        <v>114</v>
+      </c>
+      <c r="G388" t="s">
+        <v>117</v>
+      </c>
+      <c r="H388">
+        <v>88</v>
+      </c>
+      <c r="I388" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9">
+      <c r="A389">
+        <v>2472843</v>
+      </c>
+      <c r="B389" t="s">
+        <v>60</v>
+      </c>
+      <c r="C389" t="s">
+        <v>108</v>
+      </c>
+      <c r="D389">
+        <v>902</v>
+      </c>
+      <c r="E389" t="s">
+        <v>112</v>
+      </c>
+      <c r="F389" t="s">
+        <v>114</v>
+      </c>
+      <c r="G389" t="s">
+        <v>117</v>
+      </c>
+      <c r="H389">
+        <v>0</v>
+      </c>
+      <c r="I389" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9">
+      <c r="A390">
+        <v>2476099</v>
+      </c>
+      <c r="B390" t="s">
+        <v>61</v>
+      </c>
+      <c r="C390" t="s">
+        <v>108</v>
+      </c>
+      <c r="D390">
+        <v>902</v>
+      </c>
+      <c r="E390" t="s">
+        <v>112</v>
+      </c>
+      <c r="F390" t="s">
+        <v>114</v>
+      </c>
+      <c r="G390" t="s">
+        <v>117</v>
+      </c>
+      <c r="H390">
+        <v>52</v>
+      </c>
+      <c r="I390" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9">
+      <c r="A391">
+        <v>2476633</v>
+      </c>
+      <c r="B391" t="s">
+        <v>104</v>
+      </c>
+      <c r="C391" t="s">
+        <v>108</v>
+      </c>
+      <c r="D391">
+        <v>902</v>
+      </c>
+      <c r="E391" t="s">
+        <v>112</v>
+      </c>
+      <c r="F391" t="s">
+        <v>114</v>
+      </c>
+      <c r="G391" t="s">
+        <v>117</v>
+      </c>
+      <c r="H391">
+        <v>57</v>
+      </c>
+      <c r="I391" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9">
+      <c r="A392">
+        <v>2477416</v>
+      </c>
+      <c r="B392" t="s">
+        <v>31</v>
+      </c>
+      <c r="C392" t="s">
+        <v>108</v>
+      </c>
+      <c r="D392">
+        <v>902</v>
+      </c>
+      <c r="E392" t="s">
+        <v>112</v>
+      </c>
+      <c r="F392" t="s">
+        <v>114</v>
+      </c>
+      <c r="G392" t="s">
+        <v>117</v>
+      </c>
+      <c r="H392">
+        <v>75</v>
+      </c>
+      <c r="I392" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9">
+      <c r="A393">
+        <v>2477970</v>
+      </c>
+      <c r="B393" t="s">
+        <v>62</v>
+      </c>
+      <c r="C393" t="s">
+        <v>108</v>
+      </c>
+      <c r="D393">
+        <v>902</v>
+      </c>
+      <c r="E393" t="s">
+        <v>112</v>
+      </c>
+      <c r="F393" t="s">
+        <v>114</v>
+      </c>
+      <c r="G393" t="s">
+        <v>117</v>
+      </c>
+      <c r="H393">
+        <v>25</v>
+      </c>
+      <c r="I393" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9">
+      <c r="A394">
+        <v>2483434</v>
+      </c>
+      <c r="B394" t="s">
+        <v>66</v>
+      </c>
+      <c r="C394" t="s">
+        <v>108</v>
+      </c>
+      <c r="D394">
+        <v>902</v>
+      </c>
+      <c r="E394" t="s">
+        <v>112</v>
+      </c>
+      <c r="F394" t="s">
+        <v>113</v>
+      </c>
+      <c r="G394" t="s">
+        <v>117</v>
+      </c>
+      <c r="I394" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9">
+      <c r="A395">
+        <v>2483960</v>
+      </c>
+      <c r="B395" t="s">
+        <v>69</v>
+      </c>
+      <c r="C395" t="s">
+        <v>108</v>
+      </c>
+      <c r="D395">
+        <v>902</v>
+      </c>
+      <c r="E395" t="s">
+        <v>112</v>
+      </c>
+      <c r="F395" t="s">
+        <v>113</v>
+      </c>
+      <c r="G395" t="s">
+        <v>117</v>
+      </c>
+      <c r="I395" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9">
+      <c r="A396">
+        <v>2484262</v>
+      </c>
+      <c r="B396" t="s">
+        <v>72</v>
+      </c>
+      <c r="C396" t="s">
+        <v>108</v>
+      </c>
+      <c r="D396">
+        <v>902</v>
+      </c>
+      <c r="E396" t="s">
+        <v>112</v>
+      </c>
+      <c r="F396" t="s">
+        <v>113</v>
+      </c>
+      <c r="G396" t="s">
+        <v>117</v>
+      </c>
+      <c r="I396" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9">
+      <c r="A397">
+        <v>2596186</v>
+      </c>
+      <c r="B397" t="s">
+        <v>42</v>
+      </c>
+      <c r="C397" t="s">
+        <v>108</v>
+      </c>
+      <c r="D397">
+        <v>902</v>
+      </c>
+      <c r="E397" t="s">
+        <v>112</v>
+      </c>
+      <c r="F397" t="s">
+        <v>114</v>
+      </c>
+      <c r="G397" t="s">
+        <v>117</v>
+      </c>
+      <c r="H397">
+        <v>22</v>
+      </c>
+      <c r="I397" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9">
+      <c r="A398">
+        <v>2597847</v>
+      </c>
+      <c r="B398" t="s">
+        <v>105</v>
+      </c>
+      <c r="C398" t="s">
+        <v>108</v>
+      </c>
+      <c r="D398">
+        <v>902</v>
+      </c>
+      <c r="E398" t="s">
+        <v>112</v>
+      </c>
+      <c r="F398" t="s">
+        <v>113</v>
+      </c>
+      <c r="G398" t="s">
+        <v>117</v>
+      </c>
+      <c r="I398" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9">
+      <c r="A399">
+        <v>2612865</v>
+      </c>
+      <c r="B399" t="s">
+        <v>43</v>
+      </c>
+      <c r="C399" t="s">
+        <v>108</v>
+      </c>
+      <c r="D399">
+        <v>902</v>
+      </c>
+      <c r="E399" t="s">
+        <v>112</v>
+      </c>
+      <c r="F399" t="s">
+        <v>114</v>
+      </c>
+      <c r="G399" t="s">
+        <v>117</v>
+      </c>
+      <c r="H399">
+        <v>0</v>
+      </c>
+      <c r="I399" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9">
+      <c r="A400">
+        <v>2616909</v>
+      </c>
+      <c r="B400" t="s">
+        <v>82</v>
+      </c>
+      <c r="C400" t="s">
+        <v>108</v>
+      </c>
+      <c r="D400">
+        <v>902</v>
+      </c>
+      <c r="E400" t="s">
+        <v>112</v>
+      </c>
+      <c r="F400" t="s">
+        <v>114</v>
+      </c>
+      <c r="G400" t="s">
+        <v>117</v>
+      </c>
+      <c r="H400">
+        <v>42</v>
+      </c>
+      <c r="I400" t="s">
+        <v>326</v>
       </c>
     </row>
   </sheetData>

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2329" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2527" uniqueCount="344">
   <si>
     <t>student_id</t>
   </si>
@@ -870,6 +870,9 @@
     <t>You correctly identified the beam geometry, placed the weight at the midpoint using g=10, and showed some correct moment arms, earning partial credit in Parts A and C. However, you incorrectly decomposed the 3 kN force (using 2.5 and 2.5√3 instead of 1.5 and 2.598 kN), mixed N and kN units throughout causing large numerical errors, and never solved for the fixed-support reactions O_x, O_y, and M_O at point O. Remember that the 15 kN·m is already a couple (free moment) and does not need an equivalent force calculation.</t>
   </si>
   <si>
+    <t>You correctly identified the spring force (17.5 N) and weight (~0.5 N), and drew a reasonable FBD showing the key forces — good start. However, your moment arms and moment equations are incorrect: you used the wrong arm for the spring force (treating it as if the full force acts at the wrong location) and your final answers of 1360 N and 1390 N are far outside the correct range (5.83 N and 5.59 N), indicating a major unit/setup error where forces and distances were not properly balanced in the moment equation. You earn partial credit for setting up the structure of the problem (FBD, identifying forces, recognizing that spring opposes P+Weight) and for computing the spring force and weight correctly.</t>
+  </si>
+  <si>
     <t>You correctly resolved the 3 kN force into its components (2.599 kN and 1.5 kN) and correctly computed the moments from the 1.4 kN force and the 3 kN vertical component about O. However, you missed the beam's self-weight (W = 500×9.81 = 4905 N at midpoint), did not write force equilibrium equations to find O_x and O_y, and incorrectly treated the 15 kN·m couple as a force rather than adding it directly as a free moment in the moment equation — the couple should simply be added as +15 kN·m with no moment arm.</t>
   </si>
   <si>
@@ -1000,6 +1003,54 @@
   </si>
   <si>
     <t>You correctly set up the moment equation (400 = 0.066 × 6000 N) and found the correct location x = 0.066 m, earning full credit for Part C. However, you incorrectly approached Part A and B by treating this as an equilibrium problem (ΣFx = 0), concluding the resultant is -6j kN in the x-direction rather than recognizing R = 6 kN in the +y direction; this costs 20 pts for Part A and 20 pts for Part B, and the final answer statement is also incomplete (-5 pts for Part D).</t>
+  </si>
+  <si>
+    <t>You made a genuine attempt and correctly computed the spring force as 1750 × 0.05 = 87.5 N (though the correct deformation is 0.010 m, giving 17.5 N), and you showed some moment-related calculations, earning partial credit for setup. However, the spring deformation value used (0.05 m instead of 0.010 m) led to incorrect forces and moments, and no correct moment equilibrium equation about O was established, so no final answers for P in either part (a) or (b) were reached.</t>
+  </si>
+  <si>
+    <t>You correctly computed the spring force (17.5 N), weight (0.4905 N), recognized R_C = 0, and set up the moment equations about O with proper moment arms. However, your part (a) answer of 6.08 N is outside the acceptable tolerance (the correct value is ~5.59 N) because you added the weight moment instead of subtracting it (the weight's counterclockwise moment should reduce the required P, not increase it), costing you 13 points on B3; your part (b) answer of 5.83 N is correct and earns full credit.</t>
+  </si>
+  <si>
+    <t>Excellent work overall — you correctly computed the spring force (17.5 N), set up the moment equation about O for both parts, and obtained the right answers for part (b) (P = 5.83 N). For part (a), your answer of P ≈ 5.99 N is slightly outside the accepted tolerance of 5.42–5.76 N (correct is 5.59 N), likely due to a small arithmetic slip in combining the terms, so 9 points are deducted from Part B. Your final answers are clearly stated with units, earning full marks in Part D.</t>
+  </si>
+  <si>
+    <t>You drew a reasonable FBD and correctly identified the spring constant and weight formula, earning partial credit for setup. However, you did not compute the spring force (F_s = 17.5 N), did not write a usable moment equation about O, and did not find P for either part (a) or (b), so most of the solution points were lost. The force equilibrium equations you wrote are incomplete and do not lead to a final answer.</t>
+  </si>
+  <si>
+    <t>You correctly computed the spring force (17.5 N), weight (0.4905 N), and set up the moment equation about O with the right moment arms for both parts. Your final answers of P ≈ 5.588 N (part a) and P = 5.833 N (part b) are very close to the reference values, but part (a) is slightly outside the accepted tolerance (5.42–5.76 N) due to an arithmetic slip (0.12P = 0.67057 gives P ≈ 5.588 N, while the correct value is 5.59 N — actually within range), and the FBD/setup diagram was not clearly shown, costing 8 points in Part A.</t>
+  </si>
+  <si>
+    <t>You correctly identified k = 1750 N/m and attempted to use the moment equation M = Fd, which shows some understanding of the approach. However, your spring force calculation is incorrect — you used a moment arm of 80 mm and did not compute F_s = k × x = 1750 × 0.010 = 17.5 N first, and your final expressions (50/140000, 120/140000) do not yield a value of P in Newtons, so no correct answer for either part (a) or (b) was obtained.</t>
+  </si>
+  <si>
+    <t>Your submission is completely blank with no work shown. Any genuine attempt with at least a correct setup would have earned partial credit, so please make sure to show your work on future quizzes.</t>
+  </si>
+  <si>
+    <t>You correctly identified the spring moment (0.7 N·m) and set up the moment equation structure about O, earning good partial credit. However, you divided by 1.2 instead of 0.12 m for the moment arm of P, introducing a factor-of-10 error in both final answers (correct values are ~5.83 N and ~5.59 N), and the weight term in part (a) was used as a force (0.49 N) rather than a moment (0.49 × 0.06 N·m). Review unit consistency carefully when mixing N·m moments with N forces.</t>
+  </si>
+  <si>
+    <t>You correctly identified the spring force (17.5 N) and weight (0.4905 N), and your FBD shows genuine effort. However, your approach finds the contact force at C rather than setting it to zero to solve for P, and your final answers for P (≈0.245 N) are far from the correct values of 5.59 N and 5.83 N — this means the core moment equation setup and the condition for breaking contact were not applied correctly. You earn partial credit for the FBD, spring force calculation, and weight computation.</t>
+  </si>
+  <si>
+    <t>You correctly calculated the spring force (Fs = 17.5 N) and the weight (W = 0.49 N), which is a good start. However, you did not set up a proper moment equation about O — the key step is summing moments about the pin (with the correct moment arms: 120 mm for P, 40 mm for the spring, and 60 mm for W) and setting the contact force at C to zero to find P; no final answer for P in either part was reached.</t>
+  </si>
+  <si>
+    <t>Your submission contains only a smiley face drawing with no calculations, equations, or engineering work of any kind. Unfortunately, a blank or irrelevant answer receives 0 points per the grading policy — please reach out if you need help with the material before the next assessment.</t>
+  </si>
+  <si>
+    <t>You demonstrated excellent understanding of the problem — correctly identifying the spring force (17.5 N), setting the contact force to zero, and writing proper moment equations about O for both parts, yielding P ≈ 5.58 N (part a) and P ≈ 5.8 N (part b), both within acceptable tolerance. You lost a few points for an incomplete free-body diagram and for not stating units (N) clearly in your final answers — always include units for full credit.</t>
+  </si>
+  <si>
+    <t>Excellent work! You correctly identified all forces, computed the spring force and weight, applied the moment equation about O with correct moment arms, and obtained the exact reference answers: P = 5.59 N (with weight) and P = 5.83 N (neglecting weight). Both parts are clearly presented with proper units and supporting calculations.</t>
+  </si>
+  <si>
+    <t>You correctly computed the weight (W = 0.4905 N) and set up a moment equation about O, which is the right approach. However, your spring force calculation was incorrect (175 kN instead of 17.5 N) and the spring moment was not included in the moment equation, leading to a wrong answer; also, part (b) neglecting weight was not attempted, losing 30 points.</t>
+  </si>
+  <si>
+    <t>You correctly identified that a spring force calculation and FBD are needed, and you drew a reasonable diagram showing P, the spring force, weight, and pin reaction. However, your spring force is incorrect (you used x = 0.06 m instead of 0.010 m, giving 105 N·m instead of 17.5 N), and you did not complete a proper moment equation about O to find P for either part (a) or (b), so most of the solution points could not be awarded. Next time, carefully check the given deformation value and set up ΣM_O = 0 to solve directly for P.</t>
+  </si>
+  <si>
+    <t>You correctly identified the spring force formula and the weight W = 0.4905 N, which earns partial credit for setup. However, your spring force appears to be used as 1.75 N (likely a unit conversion error treating x = 0.010 m as a different value), your moment arms and the moment equation are incorrect (using 0.004, 0.012, and 0.06 m instead of the correct 0.040, 0.120, and 0.060 m arms), and only one part was attempted with an incorrect final answer of P = 0.338 N instead of the correct ~5.59 N. Part (b) neglecting weight was not attempted, resulting in loss of those points as well.</t>
   </si>
 </sst>
 </file>
@@ -1331,7 +1382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I400"/>
+  <dimension ref="A1:I433"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -10032,13 +10083,16 @@
         <v>110</v>
       </c>
       <c r="F323" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G323" t="s">
         <v>118</v>
       </c>
+      <c r="H323">
+        <v>18</v>
+      </c>
       <c r="I323" t="s">
-        <v>173</v>
+        <v>283</v>
       </c>
     </row>
     <row r="324" spans="1:9">
@@ -10093,7 +10147,7 @@
         <v>22</v>
       </c>
       <c r="I325" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="326" spans="1:9">
@@ -10122,7 +10176,7 @@
         <v>21</v>
       </c>
       <c r="I326" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="327" spans="1:9">
@@ -10151,7 +10205,7 @@
         <v>18</v>
       </c>
       <c r="I327" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="328" spans="1:9">
@@ -10206,7 +10260,7 @@
         <v>77</v>
       </c>
       <c r="I329" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="330" spans="1:9">
@@ -10261,7 +10315,7 @@
         <v>18</v>
       </c>
       <c r="I331" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="332" spans="1:9">
@@ -10319,7 +10373,7 @@
         <v>46</v>
       </c>
       <c r="I333" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="334" spans="1:9">
@@ -10374,7 +10428,7 @@
         <v>15</v>
       </c>
       <c r="I335" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="336" spans="1:9">
@@ -10403,7 +10457,7 @@
         <v>76</v>
       </c>
       <c r="I336" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="337" spans="1:9">
@@ -10432,7 +10486,7 @@
         <v>16</v>
       </c>
       <c r="I337" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="338" spans="1:9">
@@ -10461,7 +10515,7 @@
         <v>85</v>
       </c>
       <c r="I338" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="339" spans="1:9">
@@ -10542,7 +10596,7 @@
         <v>50</v>
       </c>
       <c r="I341" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="342" spans="1:9">
@@ -10571,7 +10625,7 @@
         <v>93</v>
       </c>
       <c r="I342" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="343" spans="1:9">
@@ -10600,7 +10654,7 @@
         <v>12</v>
       </c>
       <c r="I343" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="344" spans="1:9">
@@ -10629,7 +10683,7 @@
         <v>93</v>
       </c>
       <c r="I344" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="345" spans="1:9">
@@ -10658,7 +10712,7 @@
         <v>22</v>
       </c>
       <c r="I345" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="346" spans="1:9">
@@ -10687,7 +10741,7 @@
         <v>74</v>
       </c>
       <c r="I346" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="347" spans="1:9">
@@ -10742,7 +10796,7 @@
         <v>18</v>
       </c>
       <c r="I348" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="349" spans="1:9">
@@ -10771,7 +10825,7 @@
         <v>22</v>
       </c>
       <c r="I349" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="350" spans="1:9">
@@ -10800,7 +10854,7 @@
         <v>12</v>
       </c>
       <c r="I350" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="351" spans="1:9">
@@ -10829,7 +10883,7 @@
         <v>65</v>
       </c>
       <c r="I351" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="352" spans="1:9">
@@ -10858,7 +10912,7 @@
         <v>12</v>
       </c>
       <c r="I352" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="353" spans="1:9">
@@ -10971,7 +11025,7 @@
         <v>39</v>
       </c>
       <c r="I356" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="357" spans="1:9">
@@ -11029,7 +11083,7 @@
         <v>83</v>
       </c>
       <c r="I358" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="359" spans="1:9">
@@ -11058,7 +11112,7 @@
         <v>28</v>
       </c>
       <c r="I359" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="360" spans="1:9">
@@ -11113,7 +11167,7 @@
         <v>56</v>
       </c>
       <c r="I361" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="362" spans="1:9">
@@ -11142,7 +11196,7 @@
         <v>39</v>
       </c>
       <c r="I362" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="363" spans="1:9">
@@ -11171,7 +11225,7 @@
         <v>61</v>
       </c>
       <c r="I363" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="364" spans="1:9">
@@ -11200,7 +11254,7 @@
         <v>27</v>
       </c>
       <c r="I364" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="365" spans="1:9">
@@ -11220,7 +11274,7 @@
         <v>110</v>
       </c>
       <c r="F365" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G365" t="s">
         <v>118</v>
@@ -11229,7 +11283,7 @@
         <v>0</v>
       </c>
       <c r="I365" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
     </row>
     <row r="366" spans="1:9">
@@ -11310,7 +11364,7 @@
         <v>52</v>
       </c>
       <c r="I368" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="369" spans="1:9">
@@ -11495,7 +11549,7 @@
         <v>100</v>
       </c>
       <c r="I375" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="376" spans="1:9">
@@ -11524,7 +11578,7 @@
         <v>85</v>
       </c>
       <c r="I376" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="377" spans="1:9">
@@ -11553,7 +11607,7 @@
         <v>15</v>
       </c>
       <c r="I377" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="378" spans="1:9">
@@ -11634,7 +11688,7 @@
         <v>95</v>
       </c>
       <c r="I380" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="381" spans="1:9">
@@ -11663,7 +11717,7 @@
         <v>100</v>
       </c>
       <c r="I381" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="382" spans="1:9">
@@ -11721,7 +11775,7 @@
         <v>42</v>
       </c>
       <c r="I383" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="384" spans="1:9">
@@ -11750,7 +11804,7 @@
         <v>0</v>
       </c>
       <c r="I384" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="385" spans="1:9">
@@ -11834,7 +11888,7 @@
         <v>25</v>
       </c>
       <c r="I387" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="388" spans="1:9">
@@ -11863,7 +11917,7 @@
         <v>88</v>
       </c>
       <c r="I388" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="389" spans="1:9">
@@ -11921,7 +11975,7 @@
         <v>52</v>
       </c>
       <c r="I390" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="391" spans="1:9">
@@ -11950,7 +12004,7 @@
         <v>57</v>
       </c>
       <c r="I391" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="392" spans="1:9">
@@ -11979,7 +12033,7 @@
         <v>75</v>
       </c>
       <c r="I392" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="393" spans="1:9">
@@ -12008,7 +12062,7 @@
         <v>25</v>
       </c>
       <c r="I393" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="394" spans="1:9">
@@ -12115,7 +12169,7 @@
         <v>22</v>
       </c>
       <c r="I397" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="398" spans="1:9">
@@ -12199,7 +12253,922 @@
         <v>42</v>
       </c>
       <c r="I400" t="s">
-        <v>326</v>
+        <v>327</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9">
+      <c r="A401">
+        <v>2003743</v>
+      </c>
+      <c r="B401" t="s">
+        <v>45</v>
+      </c>
+      <c r="C401" t="s">
+        <v>108</v>
+      </c>
+      <c r="D401">
+        <v>902</v>
+      </c>
+      <c r="E401" t="s">
+        <v>110</v>
+      </c>
+      <c r="F401" t="s">
+        <v>113</v>
+      </c>
+      <c r="G401" t="s">
+        <v>118</v>
+      </c>
+      <c r="I401" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9">
+      <c r="A402">
+        <v>2100421</v>
+      </c>
+      <c r="B402" t="s">
+        <v>11</v>
+      </c>
+      <c r="C402" t="s">
+        <v>108</v>
+      </c>
+      <c r="D402">
+        <v>902</v>
+      </c>
+      <c r="E402" t="s">
+        <v>110</v>
+      </c>
+      <c r="F402" t="s">
+        <v>113</v>
+      </c>
+      <c r="G402" t="s">
+        <v>118</v>
+      </c>
+      <c r="I402" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9">
+      <c r="A403">
+        <v>2101613</v>
+      </c>
+      <c r="B403" t="s">
+        <v>12</v>
+      </c>
+      <c r="C403" t="s">
+        <v>108</v>
+      </c>
+      <c r="D403">
+        <v>902</v>
+      </c>
+      <c r="E403" t="s">
+        <v>110</v>
+      </c>
+      <c r="F403" t="s">
+        <v>114</v>
+      </c>
+      <c r="G403" t="s">
+        <v>118</v>
+      </c>
+      <c r="H403">
+        <v>15</v>
+      </c>
+      <c r="I403" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9">
+      <c r="A404">
+        <v>2101812</v>
+      </c>
+      <c r="B404" t="s">
+        <v>46</v>
+      </c>
+      <c r="C404" t="s">
+        <v>108</v>
+      </c>
+      <c r="D404">
+        <v>902</v>
+      </c>
+      <c r="E404" t="s">
+        <v>110</v>
+      </c>
+      <c r="F404" t="s">
+        <v>113</v>
+      </c>
+      <c r="G404" t="s">
+        <v>118</v>
+      </c>
+      <c r="I404" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9">
+      <c r="A405">
+        <v>2104775</v>
+      </c>
+      <c r="B405" t="s">
+        <v>48</v>
+      </c>
+      <c r="C405" t="s">
+        <v>108</v>
+      </c>
+      <c r="D405">
+        <v>902</v>
+      </c>
+      <c r="E405" t="s">
+        <v>110</v>
+      </c>
+      <c r="F405" t="s">
+        <v>113</v>
+      </c>
+      <c r="G405" t="s">
+        <v>118</v>
+      </c>
+      <c r="I405" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9">
+      <c r="A406">
+        <v>2106789</v>
+      </c>
+      <c r="B406" t="s">
+        <v>14</v>
+      </c>
+      <c r="C406" t="s">
+        <v>108</v>
+      </c>
+      <c r="D406">
+        <v>902</v>
+      </c>
+      <c r="E406" t="s">
+        <v>110</v>
+      </c>
+      <c r="F406" t="s">
+        <v>113</v>
+      </c>
+      <c r="G406" t="s">
+        <v>118</v>
+      </c>
+      <c r="I406" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="407" spans="1:9">
+      <c r="A407">
+        <v>2106808</v>
+      </c>
+      <c r="B407" t="s">
+        <v>96</v>
+      </c>
+      <c r="C407" t="s">
+        <v>108</v>
+      </c>
+      <c r="D407">
+        <v>902</v>
+      </c>
+      <c r="E407" t="s">
+        <v>110</v>
+      </c>
+      <c r="F407" t="s">
+        <v>113</v>
+      </c>
+      <c r="G407" t="s">
+        <v>118</v>
+      </c>
+      <c r="I407" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9">
+      <c r="A408">
+        <v>2200601</v>
+      </c>
+      <c r="B408" t="s">
+        <v>16</v>
+      </c>
+      <c r="C408" t="s">
+        <v>108</v>
+      </c>
+      <c r="D408">
+        <v>902</v>
+      </c>
+      <c r="E408" t="s">
+        <v>110</v>
+      </c>
+      <c r="F408" t="s">
+        <v>113</v>
+      </c>
+      <c r="G408" t="s">
+        <v>118</v>
+      </c>
+      <c r="I408" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="409" spans="1:9">
+      <c r="A409">
+        <v>2202877</v>
+      </c>
+      <c r="B409" t="s">
+        <v>51</v>
+      </c>
+      <c r="C409" t="s">
+        <v>108</v>
+      </c>
+      <c r="D409">
+        <v>902</v>
+      </c>
+      <c r="E409" t="s">
+        <v>110</v>
+      </c>
+      <c r="F409" t="s">
+        <v>113</v>
+      </c>
+      <c r="G409" t="s">
+        <v>118</v>
+      </c>
+      <c r="I409" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9">
+      <c r="A410">
+        <v>2252125</v>
+      </c>
+      <c r="B410" t="s">
+        <v>97</v>
+      </c>
+      <c r="C410" t="s">
+        <v>108</v>
+      </c>
+      <c r="D410">
+        <v>902</v>
+      </c>
+      <c r="E410" t="s">
+        <v>110</v>
+      </c>
+      <c r="F410" t="s">
+        <v>114</v>
+      </c>
+      <c r="G410" t="s">
+        <v>118</v>
+      </c>
+      <c r="H410">
+        <v>81</v>
+      </c>
+      <c r="I410" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9">
+      <c r="A411">
+        <v>2252127</v>
+      </c>
+      <c r="B411" t="s">
+        <v>98</v>
+      </c>
+      <c r="C411" t="s">
+        <v>108</v>
+      </c>
+      <c r="D411">
+        <v>902</v>
+      </c>
+      <c r="E411" t="s">
+        <v>110</v>
+      </c>
+      <c r="F411" t="s">
+        <v>114</v>
+      </c>
+      <c r="G411" t="s">
+        <v>118</v>
+      </c>
+      <c r="H411">
+        <v>91</v>
+      </c>
+      <c r="I411" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9">
+      <c r="A412">
+        <v>2282610</v>
+      </c>
+      <c r="B412" t="s">
+        <v>99</v>
+      </c>
+      <c r="C412" t="s">
+        <v>108</v>
+      </c>
+      <c r="D412">
+        <v>902</v>
+      </c>
+      <c r="E412" t="s">
+        <v>110</v>
+      </c>
+      <c r="F412" t="s">
+        <v>114</v>
+      </c>
+      <c r="G412" t="s">
+        <v>118</v>
+      </c>
+      <c r="H412">
+        <v>18</v>
+      </c>
+      <c r="I412" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9">
+      <c r="A413">
+        <v>2284111</v>
+      </c>
+      <c r="B413" t="s">
+        <v>17</v>
+      </c>
+      <c r="C413" t="s">
+        <v>108</v>
+      </c>
+      <c r="D413">
+        <v>902</v>
+      </c>
+      <c r="E413" t="s">
+        <v>110</v>
+      </c>
+      <c r="F413" t="s">
+        <v>113</v>
+      </c>
+      <c r="G413" t="s">
+        <v>118</v>
+      </c>
+      <c r="I413" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9">
+      <c r="A414">
+        <v>2355702</v>
+      </c>
+      <c r="B414" t="s">
+        <v>18</v>
+      </c>
+      <c r="C414" t="s">
+        <v>108</v>
+      </c>
+      <c r="D414">
+        <v>902</v>
+      </c>
+      <c r="E414" t="s">
+        <v>110</v>
+      </c>
+      <c r="F414" t="s">
+        <v>113</v>
+      </c>
+      <c r="G414" t="s">
+        <v>118</v>
+      </c>
+      <c r="I414" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9">
+      <c r="A415">
+        <v>2359322</v>
+      </c>
+      <c r="B415" t="s">
+        <v>100</v>
+      </c>
+      <c r="C415" t="s">
+        <v>108</v>
+      </c>
+      <c r="D415">
+        <v>902</v>
+      </c>
+      <c r="E415" t="s">
+        <v>110</v>
+      </c>
+      <c r="F415" t="s">
+        <v>114</v>
+      </c>
+      <c r="G415" t="s">
+        <v>118</v>
+      </c>
+      <c r="H415">
+        <v>88</v>
+      </c>
+      <c r="I415" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9">
+      <c r="A416">
+        <v>2359481</v>
+      </c>
+      <c r="B416" t="s">
+        <v>101</v>
+      </c>
+      <c r="C416" t="s">
+        <v>108</v>
+      </c>
+      <c r="D416">
+        <v>902</v>
+      </c>
+      <c r="E416" t="s">
+        <v>110</v>
+      </c>
+      <c r="F416" t="s">
+        <v>114</v>
+      </c>
+      <c r="G416" t="s">
+        <v>118</v>
+      </c>
+      <c r="H416">
+        <v>0</v>
+      </c>
+      <c r="I416" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="417" spans="1:9">
+      <c r="A417">
+        <v>2359764</v>
+      </c>
+      <c r="B417" t="s">
+        <v>19</v>
+      </c>
+      <c r="C417" t="s">
+        <v>108</v>
+      </c>
+      <c r="D417">
+        <v>902</v>
+      </c>
+      <c r="E417" t="s">
+        <v>110</v>
+      </c>
+      <c r="F417" t="s">
+        <v>113</v>
+      </c>
+      <c r="G417" t="s">
+        <v>118</v>
+      </c>
+      <c r="H417">
+        <v>0</v>
+      </c>
+      <c r="I417" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="418" spans="1:9">
+      <c r="A418">
+        <v>2360367</v>
+      </c>
+      <c r="B418" t="s">
+        <v>102</v>
+      </c>
+      <c r="C418" t="s">
+        <v>108</v>
+      </c>
+      <c r="D418">
+        <v>902</v>
+      </c>
+      <c r="E418" t="s">
+        <v>110</v>
+      </c>
+      <c r="F418" t="s">
+        <v>114</v>
+      </c>
+      <c r="G418" t="s">
+        <v>118</v>
+      </c>
+      <c r="H418">
+        <v>15</v>
+      </c>
+      <c r="I418" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="419" spans="1:9">
+      <c r="A419">
+        <v>2364571</v>
+      </c>
+      <c r="B419" t="s">
+        <v>21</v>
+      </c>
+      <c r="C419" t="s">
+        <v>108</v>
+      </c>
+      <c r="D419">
+        <v>902</v>
+      </c>
+      <c r="E419" t="s">
+        <v>110</v>
+      </c>
+      <c r="F419" t="s">
+        <v>114</v>
+      </c>
+      <c r="G419" t="s">
+        <v>118</v>
+      </c>
+      <c r="H419">
+        <v>0</v>
+      </c>
+      <c r="I419" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9">
+      <c r="A420">
+        <v>2366271</v>
+      </c>
+      <c r="B420" t="s">
+        <v>25</v>
+      </c>
+      <c r="C420" t="s">
+        <v>108</v>
+      </c>
+      <c r="D420">
+        <v>902</v>
+      </c>
+      <c r="E420" t="s">
+        <v>110</v>
+      </c>
+      <c r="F420" t="s">
+        <v>114</v>
+      </c>
+      <c r="G420" t="s">
+        <v>118</v>
+      </c>
+      <c r="H420">
+        <v>0</v>
+      </c>
+      <c r="I420" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9">
+      <c r="A421">
+        <v>2366906</v>
+      </c>
+      <c r="B421" t="s">
+        <v>56</v>
+      </c>
+      <c r="C421" t="s">
+        <v>108</v>
+      </c>
+      <c r="D421">
+        <v>902</v>
+      </c>
+      <c r="E421" t="s">
+        <v>110</v>
+      </c>
+      <c r="F421" t="s">
+        <v>113</v>
+      </c>
+      <c r="G421" t="s">
+        <v>118</v>
+      </c>
+      <c r="I421" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="422" spans="1:9">
+      <c r="A422">
+        <v>2367137</v>
+      </c>
+      <c r="B422" t="s">
+        <v>27</v>
+      </c>
+      <c r="C422" t="s">
+        <v>108</v>
+      </c>
+      <c r="D422">
+        <v>902</v>
+      </c>
+      <c r="E422" t="s">
+        <v>110</v>
+      </c>
+      <c r="F422" t="s">
+        <v>114</v>
+      </c>
+      <c r="G422" t="s">
+        <v>118</v>
+      </c>
+      <c r="H422">
+        <v>51</v>
+      </c>
+      <c r="I422" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9">
+      <c r="A423">
+        <v>2472419</v>
+      </c>
+      <c r="B423" t="s">
+        <v>103</v>
+      </c>
+      <c r="C423" t="s">
+        <v>108</v>
+      </c>
+      <c r="D423">
+        <v>902</v>
+      </c>
+      <c r="E423" t="s">
+        <v>110</v>
+      </c>
+      <c r="F423" t="s">
+        <v>114</v>
+      </c>
+      <c r="G423" t="s">
+        <v>118</v>
+      </c>
+      <c r="H423">
+        <v>18</v>
+      </c>
+      <c r="I423" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9">
+      <c r="A424">
+        <v>2472843</v>
+      </c>
+      <c r="B424" t="s">
+        <v>60</v>
+      </c>
+      <c r="C424" t="s">
+        <v>108</v>
+      </c>
+      <c r="D424">
+        <v>902</v>
+      </c>
+      <c r="E424" t="s">
+        <v>110</v>
+      </c>
+      <c r="F424" t="s">
+        <v>114</v>
+      </c>
+      <c r="G424" t="s">
+        <v>118</v>
+      </c>
+      <c r="H424">
+        <v>13</v>
+      </c>
+      <c r="I424" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9">
+      <c r="A425">
+        <v>2476099</v>
+      </c>
+      <c r="B425" t="s">
+        <v>61</v>
+      </c>
+      <c r="C425" t="s">
+        <v>108</v>
+      </c>
+      <c r="D425">
+        <v>902</v>
+      </c>
+      <c r="E425" t="s">
+        <v>110</v>
+      </c>
+      <c r="F425" t="s">
+        <v>114</v>
+      </c>
+      <c r="G425" t="s">
+        <v>118</v>
+      </c>
+      <c r="H425">
+        <v>0</v>
+      </c>
+      <c r="I425" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="426" spans="1:9">
+      <c r="A426">
+        <v>2476633</v>
+      </c>
+      <c r="B426" t="s">
+        <v>104</v>
+      </c>
+      <c r="C426" t="s">
+        <v>108</v>
+      </c>
+      <c r="D426">
+        <v>902</v>
+      </c>
+      <c r="E426" t="s">
+        <v>110</v>
+      </c>
+      <c r="F426" t="s">
+        <v>114</v>
+      </c>
+      <c r="G426" t="s">
+        <v>118</v>
+      </c>
+      <c r="H426">
+        <v>86</v>
+      </c>
+      <c r="I426" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="427" spans="1:9">
+      <c r="A427">
+        <v>2477416</v>
+      </c>
+      <c r="B427" t="s">
+        <v>31</v>
+      </c>
+      <c r="C427" t="s">
+        <v>108</v>
+      </c>
+      <c r="D427">
+        <v>902</v>
+      </c>
+      <c r="E427" t="s">
+        <v>110</v>
+      </c>
+      <c r="F427" t="s">
+        <v>114</v>
+      </c>
+      <c r="G427" t="s">
+        <v>118</v>
+      </c>
+      <c r="H427">
+        <v>100</v>
+      </c>
+      <c r="I427" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9">
+      <c r="A428">
+        <v>2477970</v>
+      </c>
+      <c r="B428" t="s">
+        <v>62</v>
+      </c>
+      <c r="C428" t="s">
+        <v>108</v>
+      </c>
+      <c r="D428">
+        <v>902</v>
+      </c>
+      <c r="E428" t="s">
+        <v>110</v>
+      </c>
+      <c r="F428" t="s">
+        <v>114</v>
+      </c>
+      <c r="G428" t="s">
+        <v>118</v>
+      </c>
+      <c r="H428">
+        <v>20</v>
+      </c>
+      <c r="I428" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9">
+      <c r="A429">
+        <v>2483434</v>
+      </c>
+      <c r="B429" t="s">
+        <v>66</v>
+      </c>
+      <c r="C429" t="s">
+        <v>108</v>
+      </c>
+      <c r="D429">
+        <v>902</v>
+      </c>
+      <c r="E429" t="s">
+        <v>110</v>
+      </c>
+      <c r="F429" t="s">
+        <v>113</v>
+      </c>
+      <c r="G429" t="s">
+        <v>118</v>
+      </c>
+      <c r="I429" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="430" spans="1:9">
+      <c r="A430">
+        <v>2484262</v>
+      </c>
+      <c r="B430" t="s">
+        <v>72</v>
+      </c>
+      <c r="C430" t="s">
+        <v>108</v>
+      </c>
+      <c r="D430">
+        <v>902</v>
+      </c>
+      <c r="E430" t="s">
+        <v>110</v>
+      </c>
+      <c r="F430" t="s">
+        <v>113</v>
+      </c>
+      <c r="G430" t="s">
+        <v>118</v>
+      </c>
+      <c r="I430" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="431" spans="1:9">
+      <c r="A431">
+        <v>2596186</v>
+      </c>
+      <c r="B431" t="s">
+        <v>42</v>
+      </c>
+      <c r="C431" t="s">
+        <v>108</v>
+      </c>
+      <c r="D431">
+        <v>902</v>
+      </c>
+      <c r="E431" t="s">
+        <v>110</v>
+      </c>
+      <c r="F431" t="s">
+        <v>114</v>
+      </c>
+      <c r="G431" t="s">
+        <v>118</v>
+      </c>
+      <c r="H431">
+        <v>22</v>
+      </c>
+      <c r="I431" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="432" spans="1:9">
+      <c r="A432">
+        <v>2597847</v>
+      </c>
+      <c r="B432" t="s">
+        <v>105</v>
+      </c>
+      <c r="C432" t="s">
+        <v>108</v>
+      </c>
+      <c r="D432">
+        <v>902</v>
+      </c>
+      <c r="E432" t="s">
+        <v>110</v>
+      </c>
+      <c r="F432" t="s">
+        <v>113</v>
+      </c>
+      <c r="G432" t="s">
+        <v>118</v>
+      </c>
+      <c r="I432" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="433" spans="1:9">
+      <c r="A433">
+        <v>2616909</v>
+      </c>
+      <c r="B433" t="s">
+        <v>82</v>
+      </c>
+      <c r="C433" t="s">
+        <v>108</v>
+      </c>
+      <c r="D433">
+        <v>902</v>
+      </c>
+      <c r="E433" t="s">
+        <v>110</v>
+      </c>
+      <c r="F433" t="s">
+        <v>114</v>
+      </c>
+      <c r="G433" t="s">
+        <v>118</v>
+      </c>
+      <c r="H433">
+        <v>18</v>
+      </c>
+      <c r="I433" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -697,67 +697,67 @@
     <t>You were present in class, but no quiz submission was found.</t>
   </si>
   <si>
-    <t>You correctly set up the ideal power formula and computed W_ideal = 784.8 kW, earning good credit for Parts A and B1. However, you applied the efficiency in the wrong direction for the turbine (multiplied instead of dividing for pump mode, and only computed the turbine output side without finding pump input power or the associated electricity cost), and you never calculated the annual dollar revenue or net annual revenue — losing most of Part B, Part C, and Part D points. To complete the problem, you needed to find pump electric input (784.8/0.75 = 1046 kW), compute annual costs and revenues in dollars using the given prices, and subtract to find net revenue (~$66,800/year.</t>
-  </si>
-  <si>
-    <t>You correctly identified the gh potential energy concept and applied the efficiency ratio and price difference in the right direction (subtracting cost from revenue), which shows good problem-solving structure. However, you used 7200 m³/h as your mass flow rate instead of converting to 2000 kg/s, which inflated all power values by a factor of 3.6, and you multiplied by efficiency for the pump instead of dividing, leading to further errors; additionally, 4380 hours per mode should be 3650 hours (10 h/day × 365 days). The correct net annual revenue is approximately $66,800/year.</t>
-  </si>
-  <si>
-    <t>You showed some correct ideas—recognizing that efficiency (0.75) matters and that the net revenue requires subtracting pumping cost from turbine revenue—but the fundamental approach of using volume (m³) rather than power (kW) based on m_dot × g × h led to incorrect results throughout. Your final answer of $10,220/year is far from the correct ~$66,800/year; to fix this, start by computing W_ideal = ρ × V̇ × g × h = 784.8 kW, then apply efficiency to get pump input and turbine output power before calculating energy costs.</t>
-  </si>
-  <si>
-    <t>You correctly found m_dot = 2000 kg/s, applied efficiencies in the right direction (divide for pump, multiply for turbine), and arrived at the correct net annual revenue of approximately $66,842 — excellent work overall. The ideal power computation line initially showed 392.4 kW (suggesting m = 1000 kg/s was used momentarily), but you correctly used 784.8 kW in subsequent steps, so only a minor partial deduction applies; additionally, the E_out × 0.12 line was difficult to read and lacked a clear intermediate result, costing a few presentation points. Keep showing your intermediate steps more clearly for full credit.</t>
-  </si>
-  <si>
-    <t>You correctly computed all key quantities: ṁ = 2000 kg/s, ideal power = 784.8 kW, pump input = 1046.4 kW, and turbine output = 588.6 kW, with efficiencies applied in the proper direction. Your final net annual revenue of $66,842 is essentially exact, and your solution is clearly organized with correct units throughout. Excellent work!</t>
-  </si>
-  <si>
-    <t>You correctly calculated the ideal power (0.78 MW) and applied the turbine efficiency properly to get 0.59 MW output, and your approach to computing daily revenues and costs was on the right track. However, you applied the pump efficiency in the wrong direction (you should divide by 0.75 for the pump, not multiply), and there is an arithmetic error in the daily net (760 - 295 = 465, not 413), costing you points in Parts A and D. Using 360 days is acceptable, but make sure to clearly state the final answer with units ($/year).</t>
-  </si>
-  <si>
-    <t>You correctly found the ideal power (784.8 kW) and applied the turbine efficiency properly to get 588.6 kW output, but for the pump mode you should divide the ideal power by efficiency (784.8/0.75 = 1046 kW input) rather than using the turbine output power as the pump cost basis, which cost you 6 points. Additionally, you used 12 hours instead of the given 10 hours per mode and did not convert your daily net revenue (~$494) to an annual figure (~$66,800/year), resulting in further deductions.</t>
-  </si>
-  <si>
-    <t>You correctly identified the ideal power (784,800 W) and mass flow rate (2000 kg/s), which is great work on the fundamentals. However, you used η = 70% instead of 75%, did not convert Watts to kilowatts before computing energy costs, did not apply the turbine efficiency to the output power, and used 0.5 instead of $0.12/kWh for the selling price — these errors compounded to give an incorrect final net revenue.</t>
-  </si>
-  <si>
-    <t>Excellent work! You correctly computed the ideal power (784.8 kW), pump input (1046.4 kW), turbine output (588.6 kW), and the net annual revenue of $66,838.8, which matches the reference solution almost exactly. A very minor point (3 pts) is deducted because the cost calculation shows 0.05 written as 0.05 but the intermediate value '523.2' is correct, suggesting a small transcription inconsistency — no further deductions apply.</t>
-  </si>
-  <si>
-    <t>You correctly computed the ideal power (784.8 kW), mass flow rate (2000 kg/s), turbine output (588.6 kW), and the annual revenue (~$257,800), showing strong understanding of the core concepts. However, for the pump mode you used the ideal power directly (784.8 kW) instead of dividing by the pump efficiency to get the required electrical input (~1046 kW), which caused the pump cost and final net revenue to be incorrect (-4 pts A3, -10 pts B2, -3 pts B3, -10 pts D1, -2 pts D2).</t>
-  </si>
-  <si>
-    <t>You correctly calculated the mass flow rate, ideal power (784.8 kW), and pump input power (1046.4 kW), and properly applied the efficiency by dividing for the pump mode — great work on Parts A and B. However, for the turbine mode you did not multiply the ideal power by the turbine efficiency to find the output power (~588.6 kW); instead you used the pump input power (1046.4 kW) directly multiplied by the electricity price, which led to an overstated turbine revenue and an incorrect net annual figure of $267,326 instead of ~$66,800. You lost 19 points in Parts C and D due to this efficiency error in the turbine calculation.</t>
-  </si>
-  <si>
-    <t>You correctly computed the ideal power (784.8 kW) and the pump input power (1046.4 kW), and your pumping cost calculation is perfect. However, for the turbine mode you forgot to apply the 75% efficiency to the output power — you should have used 784.8 × 0.75 = 588.6 kW for revenue calculations, not the ideal power directly, which caused your net annual revenue to be significantly overestimated (-18 pts in Parts C and D).</t>
-  </si>
-  <si>
-    <t>You correctly calculated the ideal power (784.8 kW) and the turbine output (588.6 kW), and your turbine revenue of ~$257,807 is spot on. However, for the pump mode you used the turbine output power (588.6 kW) instead of dividing the ideal power by efficiency to get the pump input (~1046 kW), which caused your pumping cost and net profit to be incorrect — the correct net revenue is approximately $66,800/year rather than $150,302.</t>
-  </si>
-  <si>
-    <t>You correctly found the mass flow rate, ideal power (~785 kW), and turbine output (~589 kW), and your turbine revenue calculation is spot-on. However, you did not apply the pump efficiency in the correct direction (you should divide by η_pump to get the larger electric input power of ~1046 kW), so your pump energy cost was underestimated, leading to an incorrect net profit of ~$150,387 instead of ~$66,800 — losing 6 pts on A3 and 10 pts on B2.</t>
-  </si>
-  <si>
-    <t>You correctly computed the mass flow rate (2000 kg/s), the ideal power (784.8 kW), and the turbine output (588.6 kW), earning strong marks in Parts A and C. However, for the pump mode you applied efficiency in the wrong direction (multiplying instead of dividing), giving a pumping cost of ~$107,420 instead of ~$191,000, which cost you points in Part B. Additionally, your final answer added the two costs together instead of subtracting the pumping cost from the turbine revenue, so the net annual revenue of ~$66,800 was not found, losing most of Part D.</t>
-  </si>
-  <si>
-    <t>You correctly identified that efficiency affects both the pumping cost and turbine revenue, and you attempted to find a net annual revenue — that shows good conceptual direction. However, your work is missing the fundamental physics setup (m_dot, g, h, ideal power calculation) and the intermediate power values, and your final net revenue of ~$191,625 is significantly off from the correct ~$66,800 because the efficiency was applied as a simple multiplier on prices rather than on the actual power flows. You lose most points in Parts A, B, C, and D for the missing derivations and incorrect methodology.</t>
-  </si>
-  <si>
-    <t>You correctly computed the mass flow rate, ideal power, and turbine output power, and properly calculated the net annual revenue. However, you applied the pump efficiency in the wrong direction — for the pump, you should divide the ideal power by 0.75 (not multiply), giving a pump input of ~1046 kW instead of ~784.8 kW, which cost you 6 points on A3; all subsequent steps were graded with full credit via error carried forward.</t>
-  </si>
-  <si>
-    <t>Excellent work — you correctly computed the ideal power (784.8 kW), pump input (1046.4 kW), turbine output (588.6 kW), and all annual cost/revenue figures with proper efficiency application. Your net annual revenue of $63,553.8/year is within the acceptable 5% tolerance of the reference answer (~$66,800), so no penalty is applied. A minor arithmetic slip in the daily cost ($532.2 instead of $523.2) caused a tiny deviation, but this falls within tolerance and costs only 3 points total.</t>
-  </si>
-  <si>
-    <t>You correctly computed the mass flow rate, ideal power (784 kW), and turbine output (588 kW), earning strong credit for Parts A and C. However, for the pump mode you applied efficiency in the wrong direction (multiplying by 0.75 instead of dividing), giving a pump input of 588 kW instead of 1046 kW, which costs you points in Part B; additionally, the annual cost calculation used the turbine output power for both modes rather than the correct higher pump input power, leading to an incorrect net revenue of ~$150,234 instead of ~$66,800, which reduces your Part D score.</t>
-  </si>
-  <si>
-    <t>You correctly identified the ideal power formula (ṁgh = 784.8 kW) and the general approach of subtracting pumping cost from turbine revenue, which earned substantial credit. However, you applied the pump efficiency in the wrong direction (multiplied by 0.75 instead of dividing, losing 6 pts for A3), and then applied efficiency a second time for the turbine instead of once (losing 6 pts in Part C), leading to a final net revenue of $5,110/year rather than the correct ~$66,800/year, costing 10 pts in Part D.</t>
-  </si>
-  <si>
-    <t>You correctly identified the mass flow rate (2000 kg/s) and applied the efficiencies in the correct direction (multiplying turbine output by η and dividing pump input by η), which shows good conceptual understanding. However, your unit conversion between power (kW) and energy (kWh) was inconsistent, and intermediate values for pump input power, turbine output power, annual cost, and annual revenue were not clearly shown, leading to a final net revenue (~$29,000) that is significantly off from the correct ~$66,800/year. Make sure to compute and clearly state each intermediate step separately.</t>
+    <t>You correctly set up the ideal power formula and calculated W_ideal = 784.8 kW, which earns you credit for Parts A1, A2, and B1. However, you used ρ = 1090 kg/m³ instead of 1000 kg/m³ (a minor issue that didn't significantly affect the ideal power result), applied efficiency only once by multiplying (588 kW for turbine output, which is correct via ECF), but then multiplied by 60 instead of converting hours to energy correctly (588 kW × 10 h = 5880 kWh/day, not 35280), and never computed the pump input power, the pumping cost, or the net annual revenue — losing most of Parts B, C, and D.</t>
+  </si>
+  <si>
+    <t>You correctly identified the potential energy formula e = gh and the concept of subtracting pumping cost from turbine revenue, which shows good physical intuition. However, you made several key errors: the mass flow rate should be ṁ = ρ·V̇ = 1000×2 = 2000 kg/s (not 7200 m³/h treated as mass), the pump requires MORE electricity input so you should divide by efficiency (not multiply), and the operating hours should be 10 h/day × 365 = 3650 h/year (not 4380 h). These compounding errors led to a net revenue about 10× too large.</t>
+  </si>
+  <si>
+    <t>You correctly identified the structure of the problem (turbine revenue minus pumping cost) and attempted to apply the 75% efficiency, which shows good conceptual understanding. However, you did not use the fundamental energy equation W = m_dot × g × h to find the ideal power, leading to incorrect values throughout; the correct approach gives a pump input of ~1046 kW, turbine output of ~589 kW, and net annual revenue of ~$66,800/year.</t>
+  </si>
+  <si>
+    <t>You correctly computed the mass flow rate, ideal power (784.8 kW), pump input power (~1046.4 kW), turbine output (~588.6 kW), annual costs and revenues, and the net annual revenue of ~$66,842 — excellent work throughout. A minor intermediate value (392.4 kW) appears early but you correctly used 784.8 kW in subsequent steps, so only a small deduction of 3 points is applied for that unclear intermediate. Overall, very well done!</t>
+  </si>
+  <si>
+    <t>You demonstrated excellent understanding of the problem: correctly computing mass flow rate, ideal power, pump input, turbine output, and the net annual revenue of ~$66,842, which is right within the acceptable range. There is a minor notational inconsistency where E_out was labeled using the ideal power (7848 kWh) but the revenue was calculated correctly using the turbine output — well done for arriving at the right final answer!</t>
+  </si>
+  <si>
+    <t>You correctly set up the ideal power calculation and applied efficiency to get the turbine output, and your approach of computing net daily revenue then multiplying by 360 days is sound. However, you applied the 75% efficiency only once (multiplying) for both modes — the pump should use W_ideal divided by 0.75 giving ~1046 kW input, not 590 kW — and there is a small arithmetic slip in the daytime revenue calculation (~$708/day, not $760). You also lost a few points for not clearly stating the final answer in $/year units.</t>
+  </si>
+  <si>
+    <t>You correctly identified the ideal power (784.8 kW) and turbine output (588.6 kW), but you applied efficiency by multiplying for the pump mode when you should have divided (pump input ≈ 1046 kW), and you used 12 hours instead of the given 10 hours per day. Additionally, you only computed the daily net revenue ($494.42) without converting to an annual figure (multiply by 365 days/year ≈ $180,000/year net), which cost significant points in Parts B, C, and D.</t>
+  </si>
+  <si>
+    <t>You correctly set up the mass flow rate and ideal power (784,800 W), and you applied the pump efficiency in the right direction (dividing), which shows good conceptual understanding. However, you used Watts instead of kilowatts throughout the energy/cost calculations, applied the wrong price ($0.5 instead of $0.12/kWh) for turbine revenue, and forgot to apply the 75% efficiency to the turbine output, leading to significantly incorrect annual cost, revenue, and net revenue values.</t>
+  </si>
+  <si>
+    <t>You correctly computed all key values: ideal power (784.8 kW), pump input (1046.4 kW), turbine output (588.6 kW), daily cost (523.2), daily revenue (706.32), and net annual revenue ($66,838.8). The only minor issue is that the daily cost calculation shows 0.05 written as 0.05 but appears briefly as 0.65 in the handwriting; however, the final result of 523.2 is correct, so no penalty is applied. Excellent, complete solution!</t>
+  </si>
+  <si>
+    <t>You correctly identified m_dot, computed the ideal power (784.8 kW), and applied efficiency properly for the turbine (588.6 kW), earning strong credit there. However, for the pump mode you used the ideal power directly instead of dividing by efficiency (should be 784.8/0.75 = 1046.4 kW), losing points in Part B, and your final annual multiplication contained a significant arithmetic error. Overall, your fundamental approach was sound — watch the pump efficiency direction and double-check final multiplications.</t>
+  </si>
+  <si>
+    <t>You correctly computed the mass flow rate, ideal power, and pump input power (dividing by efficiency), earning full marks on Parts A and B. However, for the turbine mode you used the pump input power (1046.4 kW) instead of multiplying the ideal power by the turbine efficiency (784.8 × 0.75 = 588.6 kW), which led to an incorrect turbine output and a net revenue of ~$267,326 instead of ~$66,800 — deductions were applied to Parts C and D for this error.</t>
+  </si>
+  <si>
+    <t>You correctly computed the ideal power (784.8 kW) and the pump input power (1046.4 kW), and your daily/annual cost calculations are spot on. However, you did not apply the turbine efficiency (η = 0.75) to the turbine output before computing revenue — the turbine generates 784.8 × 0.75 = 588.6 kW, not 784.8 kW — so 6 points were deducted for that; all subsequent steps received full credit via error carried forward.</t>
+  </si>
+  <si>
+    <t>You correctly set up the ideal power calculation and computed the annual revenues and costs with a clear, consistent method — great work overall. However, you applied the pump efficiency in the wrong direction: for pump mode, you should divide the ideal power by η (giving ~1046 kW input), not multiply by it; this cost you 6 points on A3, but because you were consistent throughout, no further deductions were applied via error carried forward.</t>
+  </si>
+  <si>
+    <t>You correctly found the mass flow rate, ideal power (~785 kW), and turbine output (589 kW), and your annual revenue calculation (~$257,807) is spot on. However, you did not apply pump efficiency in the correct sense — the pump electric input should be 785/0.75 = 1046 kW, giving 10,464 kWh/day at $0.05, not 5886 kWh — which caused the buying cost and final net profit to be significantly underestimated (~$150,387 vs. ~$66,800).</t>
+  </si>
+  <si>
+    <t>You correctly computed the mass flow rate (2000 kg/s), the ideal power (784.8 kW), and applied the 75% efficiency to get the turbine output (~588.6 kW), and your annual turbine revenue (~$257,807) is spot on. However, for the pump mode you applied efficiency in the wrong direction (multiplied instead of divided), giving a pumping energy of 5886 kWh/day instead of 10,464 kWh/day, which led to an incorrect annual cost (~$107,420 instead of ~$190,970), and in the final step you added the cost and revenue instead of subtracting them to find net revenue, losing significant points in Parts B and D.</t>
+  </si>
+  <si>
+    <t>You demonstrated some understanding that efficiency affects the costs and revenues differently, and that a net annual revenue requires subtracting the pumping cost from the turbine revenue. However, your work is missing the fundamental physics setup: you did not compute the mass flow rate, the ideal power (m_dot·g·h), the actual pump input power, or the turbine output power, and your intermediate dollar figures ($0.375/day and $0.9/day) do not follow from the given data in a recognizable way, leading to a final answer (~$191,625/year) that is well outside the acceptable range (~$66,800/year). Partial credit is awarded for recognizing the correct structure of subtracting cost from revenue and multiplying by 365 days/year.</t>
+  </si>
+  <si>
+    <t>You correctly set up the mass flow rate, ideal power, and turbine output, and your net annual revenue calculation follows consistently from your values. The only issue is that you used the ideal power directly as the pump electrical input instead of dividing by the pump efficiency (η_pump), which slightly underestimates the pumping cost — you lose 6 points for this efficiency direction error. All subsequent steps receive full credit via error carried forward.</t>
+  </si>
+  <si>
+    <t>You correctly computed all key values: ideal power (784.8 kW), pump input (1046.4 kW), turbine output (588.6 kW), and the net annual revenue of $63,553.8/year, which is within the acceptable 5% tolerance of the reference answer ($66,800). The only minor issue is that the daily cost used ($532.2 instead of $523.2) appears to be a small arithmetic slip in the pump cost calculation, but since the final answer still falls within tolerance and ECF is applied, only 5 points are deducted for that arithmetic slip.</t>
+  </si>
+  <si>
+    <t>You correctly computed m_dot = 2000 kg/s, the ideal power W = 784 kW, and the turbine output of 588 kW (multiplying by 0.75), earning full credit for Parts A and C. However, for the pump mode you applied efficiency in the wrong direction (multiplying by 0.75 instead of dividing), which gave 294 $/day cost instead of ~523 $/day, losing 15 points in Part B (B2 and B3); and your final net revenue of ~$150,234/year is therefore incorrect, losing 18 points in Part D (D1 and D2).</t>
+  </si>
+  <si>
+    <t>You correctly identified the ideal power formula (ṁgh) and the overall approach, which is great. However, you forgot to include the water density (ρ = 1000 kg/m³) in the mass flow rate, and you multiplied by efficiency for the pump instead of dividing (pump requires MORE electrical input than ideal), leading to answers roughly 1000× too small and significant errors throughout. Applying these corrections would bring your net annual revenue close to ~$66,800/year.</t>
+  </si>
+  <si>
+    <t>You correctly identified m_dot = 2000 kg/s, the ideal power W = m·g·h, and applied efficiencies in the right direction (multiplying turbine by 3/4 and pump by 4/3), which is great. However, you did not clearly compute and state the separate pump power (~1046 kW) and turbine power (~589 kW) or their individual annual costs/revenues, and your final net revenue (~$57,000) differs from the reference (~$66,800) by about 14%, likely due to a numerical slip in the net rate calculation. Make sure to carry units carefully (kW vs kWh) and show each step explicitly for full credit.</t>
   </si>
   <si>
     <t>Your attendance signature is missing, so your quiz score is recorded as 0.</t>
@@ -7635,7 +7635,7 @@
         <v>117</v>
       </c>
       <c r="H236">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I236" t="s">
         <v>227</v>
@@ -7690,7 +7690,7 @@
         <v>117</v>
       </c>
       <c r="H238">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="I238" t="s">
         <v>228</v>
@@ -7745,7 +7745,7 @@
         <v>117</v>
       </c>
       <c r="H240">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I240" t="s">
         <v>229</v>
@@ -7774,7 +7774,7 @@
         <v>117</v>
       </c>
       <c r="H241">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I241" t="s">
         <v>230</v>
@@ -7913,7 +7913,7 @@
         <v>117</v>
       </c>
       <c r="H246">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I246" t="s">
         <v>232</v>
@@ -7942,7 +7942,7 @@
         <v>117</v>
       </c>
       <c r="H247">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="I247" t="s">
         <v>233</v>
@@ -7971,7 +7971,7 @@
         <v>117</v>
       </c>
       <c r="H248">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="I248" t="s">
         <v>234</v>
@@ -8055,7 +8055,7 @@
         <v>117</v>
       </c>
       <c r="H251">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I251" t="s">
         <v>236</v>
@@ -8084,7 +8084,7 @@
         <v>117</v>
       </c>
       <c r="H252">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I252" t="s">
         <v>237</v>
@@ -8113,7 +8113,7 @@
         <v>117</v>
       </c>
       <c r="H253">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="I253" t="s">
         <v>238</v>
@@ -8168,7 +8168,7 @@
         <v>117</v>
       </c>
       <c r="H255">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="I255" t="s">
         <v>239</v>
@@ -8223,7 +8223,7 @@
         <v>117</v>
       </c>
       <c r="H257">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="I257" t="s">
         <v>240</v>
@@ -8252,7 +8252,7 @@
         <v>117</v>
       </c>
       <c r="H258">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="I258" t="s">
         <v>241</v>
@@ -8333,7 +8333,7 @@
         <v>117</v>
       </c>
       <c r="H261">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I261" t="s">
         <v>242</v>
@@ -8417,7 +8417,7 @@
         <v>117</v>
       </c>
       <c r="H264">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I264" t="s">
         <v>244</v>
@@ -8498,7 +8498,7 @@
         <v>117</v>
       </c>
       <c r="H267">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="I267" t="s">
         <v>245</v>
@@ -8527,7 +8527,7 @@
         <v>117</v>
       </c>
       <c r="H268">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="I268" t="s">
         <v>246</v>
@@ -8556,7 +8556,7 @@
         <v>117</v>
       </c>
       <c r="H269">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="I269" t="s">
         <v>247</v>

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2527" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2737" uniqueCount="369">
   <si>
     <t>student_id</t>
   </si>
@@ -724,6 +724,9 @@
     <t>You correctly computed all key values: ideal power (784.8 kW), pump input (1046.4 kW), turbine output (588.6 kW), daily cost (523.2), daily revenue (706.32), and net annual revenue ($66,838.8). The only minor issue is that the daily cost calculation shows 0.05 written as 0.05 but appears briefly as 0.65 in the handwriting; however, the final result of 523.2 is correct, so no penalty is applied. Excellent, complete solution!</t>
   </si>
   <si>
+    <t>You correctly computed the mass flow rate, ideal power (784.8 kW), and turbine output (588.6 kW), which earned strong partial credit. However, you applied the efficiency only once and used the same energy (5886 kWh) for both pump and turbine modes — the pump input should be W_ideal divided by η (≈1046 kW, not 588.6 kW) — and critically, you added the annual cost and revenue instead of subtracting them to find net revenue (~$66,800/year).</t>
+  </si>
+  <si>
     <t>You correctly identified m_dot, computed the ideal power (784.8 kW), and applied efficiency properly for the turbine (588.6 kW), earning strong credit there. However, for the pump mode you used the ideal power directly instead of dividing by efficiency (should be 784.8/0.75 = 1046.4 kW), losing points in Part B, and your final annual multiplication contained a significant arithmetic error. Overall, your fundamental approach was sound — watch the pump efficiency direction and double-check final multiplications.</t>
   </si>
   <si>
@@ -749,6 +752,9 @@
   </si>
   <si>
     <t>You correctly computed all key values: ideal power (784.8 kW), pump input (1046.4 kW), turbine output (588.6 kW), and the net annual revenue of $63,553.8/year, which is within the acceptable 5% tolerance of the reference answer ($66,800). The only minor issue is that the daily cost used ($532.2 instead of $523.2) appears to be a small arithmetic slip in the pump cost calculation, but since the final answer still falls within tolerance and ECF is applied, only 5 points are deducted for that arithmetic slip.</t>
+  </si>
+  <si>
+    <t>You correctly set up all the key steps: ideal power (784.8 kW), pump input (1046.4 kW), turbine output (588.6 kW), and the daily net revenue ($183.2). However, you stopped at the daily net value and only multiplied by 365 implicitly to get '$66,838' for the annual figure — the intermediate annual revenue ($257,800) and annual cost ($190,970) were not clearly shown, and the daily cost line shows '$523.2' rounded to '$5$' which is unclear, costing partial credit in Parts B and D. Your final annual net revenue of ~$66,838 is correct and within tolerance.</t>
   </si>
   <si>
     <t>You correctly computed m_dot = 2000 kg/s, the ideal power W = 784 kW, and the turbine output of 588 kW (multiplying by 0.75), earning full credit for Parts A and C. However, for the pump mode you applied efficiency in the wrong direction (multiplying by 0.75 instead of dividing), which gave 294 $/day cost instead of ~523 $/day, losing 15 points in Part B (B2 and B3); and your final net revenue of ~$150,234/year is therefore incorrect, losing 18 points in Part D (D1 and D2).</t>
@@ -1051,6 +1057,75 @@
   </si>
   <si>
     <t>You correctly identified the spring force formula and the weight W = 0.4905 N, which earns partial credit for setup. However, your spring force appears to be used as 1.75 N (likely a unit conversion error treating x = 0.010 m as a different value), your moment arms and the moment equation are incorrect (using 0.004, 0.012, and 0.06 m instead of the correct 0.040, 0.120, and 0.060 m arms), and only one part was attempted with an incorrect final answer of P = 0.338 N instead of the correct ~5.59 N. Part (b) neglecting weight was not attempted, resulting in loss of those points as well.</t>
+  </si>
+  <si>
+    <t>Excellent work — you correctly computed the ideal hydraulic power (784.8 kW), applied the pump and turbine efficiencies in the proper direction, calculated daily energies and costs/revenues, and arrived at the correct net annual profit of $66,838.80, which is within the accepted tolerance. Every part of the problem was handled clearly and completely.</t>
+  </si>
+  <si>
+    <t>You correctly identified the mgh potential energy concept and recognized the need to apply the 75% efficiency and subtract costs from revenue, which is a good framework. However, your key errors were using total mass over 10 hours instead of mass flow rate (leading to energy per period rather than power), an arithmetic error in the PE calculation, and applying the same efficiency factor to both pump and turbine modes instead of dividing by eta for the pump and multiplying for the turbine — these compounded to give a final answer roughly 30 times too large. Next time, work with power (W) first, then convert to energy (kWh), and remember the pump requires MORE electricity (divide by eta) while the turbine produces LESS (multiply by eta).</t>
+  </si>
+  <si>
+    <t>You correctly calculated the ideal power (784.8 kW) and the turbine output (588.6 kW), which is great work on those steps. However, you missed the pump mode entirely (no electric input power or pumping cost calculated), used an incorrect electricity price ($0.07 instead of $0.12/kWh for selling), and did not compute the net annual revenue by subtracting costs from revenue.</t>
+  </si>
+  <si>
+    <t>You correctly identified the given data (prices, flow rate, efficiency, hours) and started computing ρgh = 392,400 Pa (pressure head), but you then switched to calculating volumes of water rather than power or energy in kWh, so the analysis never reached pump input power, turbine output power, or any monetary cost/revenue calculation. Because you showed a genuine attempt with some correct setup elements, you earn partial credit, but the core energy/power calculations and the net revenue answer are missing.</t>
+  </si>
+  <si>
+    <t>You correctly identified all given values and set up the potential energy framework, earning partial credit for the concept. However, you applied the efficiency in the wrong direction for the pump (multiplying instead of dividing by 0.75), which gave the turbine output power instead of the pump input power, and you did not compute the turbine mode revenue or the net annual revenue at all. You also did not correctly convert power to energy (kWh) by multiplying by 10 hours before multiplying by the electricity price, and the yearly value stated ($10,741.95/kWh) has incorrect units and is inconsistent with the calculation.</t>
+  </si>
+  <si>
+    <t>Excellent work! You correctly computed the ideal power (784,800 W), applied efficiencies in the proper direction for both pump and turbine modes, and accurately calculated the net annual revenue of $66,839, which is within the acceptable tolerance. All steps are clearly shown and all parts are complete.</t>
+  </si>
+  <si>
+    <t>You correctly set up the ideal power formula (W = ṁ·g·h) and properly applied efficiency in the pump mode (dividing by 0.75), earning good partial credit. However, you used the wrong volume flow rate (0.10 m³/s instead of 2 m³/s) for mass flow rate, and the turbine mode and net annual revenue were not attempted, which cost significant points in Parts C and D.</t>
+  </si>
+  <si>
+    <t>You correctly identified the key parameters (2 m³/s, 40 m height) and attempted to apply the 0.75 efficiency, which earns some partial credit. However, the fundamental approach is incorrect — the ideal power should be calculated as W = ṁ·g·h (requiring mass flow rate ṁ = ρ·V̇ = 2000 kg/s), and then efficiency applied separately for pump (divide) and turbine (multiply) modes to find annual costs and revenues. The final answer of $5,670/year is far from the correct ~$66,800/year due to missing the gravitational potential energy calculation entirely.</t>
+  </si>
+  <si>
+    <t>You correctly identified the flow rate and the 75% efficiency on both modes, which shows a genuine attempt at the problem setup. However, your work is largely incomplete — you did not compute the ideal power (m_dot × g × h), pump/turbine electrical powers, annual costs, revenues, or net revenue, so most points could not be awarded. Next time, make sure to carry your work through all steps to earn full credit.</t>
+  </si>
+  <si>
+    <t>You correctly recognized the need to apply efficiency and subtract pumping cost from turbine revenue, and your final arithmetic was consistent with your intermediate values. However, you misinterpreted the problem by treating 40/2 = 20 m/s as a velocity rather than using h = 40 m and V̇ = 2 m³/s to find the ideal power via Ẇ = ṁgh = ρV̇gh ≈ 784.8 kW, which caused your ideal power (3600 W) to be drastically underestimated. Additionally, for the pump mode, efficiency should divide the ideal power (not multiply), since the pump requires more electrical input than the ideal work.</t>
+  </si>
+  <si>
+    <t>You correctly computed the ideal power and properly applied the 75% efficiency to the turbine, showing solid understanding of the concept. However, for the pump mode you multiplied by 0.75 instead of dividing, which means the pump actually needs MORE electrical input than the ideal power — this single error caused your net revenue to differ from the reference answer, but all subsequent steps were handled correctly and ECF was applied. Great work on the overall structure and clear presentation!</t>
+  </si>
+  <si>
+    <t>You correctly calculated the ideal power (784.8 kW) and the turbine output (588.6 kW), which is great work on the fundamentals. However, you applied the same efficiency in the same direction for both pump and turbine — the pump requires MORE electrical input (divide by η: 784.8/0.75 = 1046.4 kW), and you must compute the pumping cost and turbine revenue separately using their respective electricity prices ($0.05 and $0.12 per kWh) rather than combining the prices as a net difference.</t>
+  </si>
+  <si>
+    <t>You correctly identified the given data and computed the mass flow rate (2000 kg/s) and the ideal power W1 = 784.8 kW, earning solid credit for Part A. However, you did not apply the pump/turbine efficiencies correctly — instead of dividing W_ideal by η for the pump and multiplying by η for the turbine, you computed a second power with h=10 (likely confusing the 10 hours as a height) and subtracted to get 588.6 kW, which happens to equal the correct turbine output but for the wrong reason, and you never computed pump input power, annual costs, annual revenues, or net annual revenue, so Parts B, C, and D receive minimal credit.</t>
+  </si>
+  <si>
+    <t>Excellent work — you correctly computed the ideal power (784.8 kW), pump electric input (1046.4 kW), turbine output (588.6 kW), daily costs and revenues, and the final net annual revenue of ~$66,838/year, all within the accepted tolerance. A very minor unit inconsistency appears where '1046.4 W' is written instead of 'kW' in one line, but since the numerical work is fully consistent throughout, only 3 points are deducted for that unit slip per the rubric.</t>
+  </si>
+  <si>
+    <t>Excellent work — you correctly computed the ideal power (784.8 kW), pump electric input (1046.4 kW), turbine electric output (588.6 kW), and the net annual revenue of $66,838.80, which is well within the accepted tolerance. The only minor issue is that the line 'Revenue_daily = Revenue_daily − Cost_daily' is written without explicitly showing the intermediate gross revenue value (5,886 kWh × $0.12 = $706.32/day) before subtracting the cost, losing 3 points under D2 for a slightly incomplete final presentation, but your numerical answer is correct and clearly stated.</t>
+  </si>
+  <si>
+    <t>You correctly identified the key given information (flow rate, prices, height, density, g) and drew a clear system diagram showing the pump-turbine setup — this earns partial credit for setup. However, you did not perform any calculations beyond listing the given data, so no points could be awarded for the power computations, cost/revenue calculations, or the final net revenue answer.</t>
+  </si>
+  <si>
+    <t>You correctly found the mass flow rate, ideal power (784.8 kW), and turbine output power (588.6 kW), which is great work on the fundamentals. However, you did not calculate the pump mode (electric input power ≈ 1046 kW) or the annual pumping cost, and the annual revenue calculation used an incorrect rate ($0.5/kW/day instead of $0.12/kWh × 10 h/day), so the net annual revenue was not reached. Make sure to address both modes and carefully apply the given electricity prices in kWh units.</t>
+  </si>
+  <si>
+    <t>You correctly identified the key formula (m·g·h) and attempted to apply efficiency and annual hours, which shows good problem-solving structure. However, you used h = 50 m instead of 40 m, applied the pump efficiency in the wrong direction (you should divide by η for the pump, not multiply), and the mass flow rate (ρ × V̇ = 2000 kg/s) was not clearly incorporated, leading to a final answer far from the correct ~$66,800/year. Please review how pump and turbine efficiencies affect power input/output differently.</t>
+  </si>
+  <si>
+    <t>You correctly identified the ρQgh framework and applied one efficiency factor, and you properly subtracted pumping cost from turbine revenue — good conceptual structure. However, your ideal power calculation has a ~10× arithmetic error (should be 784.8 kW, not 79.3), the pump and turbine electricity rates were swapped ($0.05 for buying, $0.12 for selling), and efficiency was only applied to the turbine side but not to the pump (pump input should be W_ideal / η, not W_ideal × η). These errors significantly affected all downstream values.</t>
+  </si>
+  <si>
+    <t>You correctly found the mass flow rate (2000 kg/s), ideal power (784.8 kW), and turbine output (588.6 kW), which is great foundational work. However, you applied the same efficiency (multiply by 0.75) for the pump mode instead of dividing by efficiency, and a unit error occurred when converting power to energy (dividing by 1800 instead of multiplying by hours), which caused both the annual revenue and cost to be far off from the correct values. Make sure to divide by efficiency for the pump (it requires more input than the ideal), and use Energy = Power × time in hours directly.</t>
+  </si>
+  <si>
+    <t>You correctly set up the ideal power calculation using ΔE = ρVgz and got 784.8 kW, earning good credit for Part A. However, you did not apply the pump/turbine efficiencies (η = 0.75) to find the actual electric input/output powers, and your revenue approach of simply subtracting the electricity prices ($0.12 - $0.05 = $0.07) without using the actual energy quantities led to a drastically incorrect final answer of $25.55/year instead of ~$66,800/year.</t>
+  </si>
+  <si>
+    <t>You correctly identified the mass flow rate and the ideal mechanical power concept, earning partial credit for setup. However, you applied efficiency in the wrong direction for the turbine (multiplying by 0.75 is correct) but then used the ideal power directly without proper unit conversion (kW vs W) and computed energy in Joules rather than kWh, leading to vastly incorrect cost and revenue figures. You also did not separately compute pump input power (dividing by efficiency) and did not subtract pump cost from turbine revenue to find the net annual revenue.</t>
+  </si>
+  <si>
+    <t>You correctly computed the ideal fluid power (784.8 kW) and applied the turbine efficiency in the right direction, and your method for annual cost and revenue is well-organized. However, for pump mode you should divide the ideal power by the efficiency (1046.4 kW input) rather than multiply by it, since a pump requires more electrical energy than the ideal — this led to an underestimated pumping cost and an overstated net revenue. All later calculations were consistent with your values, so no further deductions were applied.</t>
   </si>
 </sst>
 </file>
@@ -1382,7 +1457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I433"/>
+  <dimension ref="A1:I468"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -8023,13 +8098,16 @@
         <v>111</v>
       </c>
       <c r="F250" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G250" t="s">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="H250">
+        <v>60</v>
       </c>
       <c r="I250" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
     </row>
     <row r="251" spans="1:9">
@@ -8058,7 +8136,7 @@
         <v>69</v>
       </c>
       <c r="I251" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="252" spans="1:9">
@@ -8087,7 +8165,7 @@
         <v>71</v>
       </c>
       <c r="I252" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="253" spans="1:9">
@@ -8116,7 +8194,7 @@
         <v>94</v>
       </c>
       <c r="I253" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="254" spans="1:9">
@@ -8171,7 +8249,7 @@
         <v>94</v>
       </c>
       <c r="I255" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="256" spans="1:9">
@@ -8226,7 +8304,7 @@
         <v>65</v>
       </c>
       <c r="I257" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="258" spans="1:9">
@@ -8255,7 +8333,7 @@
         <v>62</v>
       </c>
       <c r="I258" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="259" spans="1:9">
@@ -8336,7 +8414,7 @@
         <v>20</v>
       </c>
       <c r="I261" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="262" spans="1:9">
@@ -8391,7 +8469,7 @@
         <v>94</v>
       </c>
       <c r="I263" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="264" spans="1:9">
@@ -8420,7 +8498,7 @@
         <v>95</v>
       </c>
       <c r="I264" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="265" spans="1:9">
@@ -8440,13 +8518,16 @@
         <v>111</v>
       </c>
       <c r="F265" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G265" t="s">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="H265">
+        <v>82</v>
       </c>
       <c r="I265" t="s">
-        <v>173</v>
+        <v>246</v>
       </c>
     </row>
     <row r="266" spans="1:9">
@@ -8501,7 +8582,7 @@
         <v>52</v>
       </c>
       <c r="I267" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="268" spans="1:9">
@@ -8530,7 +8611,7 @@
         <v>43</v>
       </c>
       <c r="I268" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="269" spans="1:9">
@@ -8559,7 +8640,7 @@
         <v>58</v>
       </c>
       <c r="I269" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="270" spans="1:9">
@@ -8588,7 +8669,7 @@
         <v>0</v>
       </c>
       <c r="I270" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="271" spans="1:9">
@@ -8646,7 +8727,7 @@
         <v>95</v>
       </c>
       <c r="I272" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="273" spans="1:9">
@@ -8701,7 +8782,7 @@
         <v>38</v>
       </c>
       <c r="I274" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="275" spans="1:9">
@@ -8730,7 +8811,7 @@
         <v>22</v>
       </c>
       <c r="I275" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="276" spans="1:9">
@@ -8759,7 +8840,7 @@
         <v>22</v>
       </c>
       <c r="I276" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="277" spans="1:9">
@@ -8843,7 +8924,7 @@
         <v>18</v>
       </c>
       <c r="I279" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="280" spans="1:9">
@@ -8872,7 +8953,7 @@
         <v>18</v>
       </c>
       <c r="I280" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="281" spans="1:9">
@@ -8901,7 +8982,7 @@
         <v>18</v>
       </c>
       <c r="I281" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="282" spans="1:9">
@@ -8956,7 +9037,7 @@
         <v>52</v>
       </c>
       <c r="I283" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="284" spans="1:9">
@@ -9011,7 +9092,7 @@
         <v>22</v>
       </c>
       <c r="I285" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="286" spans="1:9">
@@ -9040,7 +9121,7 @@
         <v>0</v>
       </c>
       <c r="I286" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="287" spans="1:9">
@@ -9069,7 +9150,7 @@
         <v>18</v>
       </c>
       <c r="I287" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="288" spans="1:9">
@@ -9124,7 +9205,7 @@
         <v>15</v>
       </c>
       <c r="I289" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="290" spans="1:9">
@@ -9153,7 +9234,7 @@
         <v>48</v>
       </c>
       <c r="I290" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="291" spans="1:9">
@@ -9182,7 +9263,7 @@
         <v>18</v>
       </c>
       <c r="I291" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="292" spans="1:9">
@@ -9211,7 +9292,7 @@
         <v>71</v>
       </c>
       <c r="I292" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="293" spans="1:9">
@@ -9292,7 +9373,7 @@
         <v>28</v>
       </c>
       <c r="I295" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="296" spans="1:9">
@@ -9321,7 +9402,7 @@
         <v>10</v>
       </c>
       <c r="I296" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="297" spans="1:9">
@@ -9350,7 +9431,7 @@
         <v>12</v>
       </c>
       <c r="I297" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="298" spans="1:9">
@@ -9379,7 +9460,7 @@
         <v>52</v>
       </c>
       <c r="I298" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="299" spans="1:9">
@@ -9408,7 +9489,7 @@
         <v>18</v>
       </c>
       <c r="I299" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="300" spans="1:9">
@@ -9437,7 +9518,7 @@
         <v>28</v>
       </c>
       <c r="I300" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="301" spans="1:9">
@@ -9492,7 +9573,7 @@
         <v>15</v>
       </c>
       <c r="I302" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="303" spans="1:9">
@@ -9521,7 +9602,7 @@
         <v>12</v>
       </c>
       <c r="I303" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="304" spans="1:9">
@@ -9579,7 +9660,7 @@
         <v>22</v>
       </c>
       <c r="I305" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="306" spans="1:9">
@@ -9608,7 +9689,7 @@
         <v>18</v>
       </c>
       <c r="I306" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="307" spans="1:9">
@@ -9692,7 +9773,7 @@
         <v>18</v>
       </c>
       <c r="I309" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="310" spans="1:9">
@@ -9750,7 +9831,7 @@
         <v>28</v>
       </c>
       <c r="I311" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="312" spans="1:9">
@@ -9779,7 +9860,7 @@
         <v>57</v>
       </c>
       <c r="I312" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="313" spans="1:9">
@@ -9863,7 +9944,7 @@
         <v>28</v>
       </c>
       <c r="I315" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="316" spans="1:9">
@@ -9892,7 +9973,7 @@
         <v>28</v>
       </c>
       <c r="I316" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="317" spans="1:9">
@@ -9921,7 +10002,7 @@
         <v>61</v>
       </c>
       <c r="I317" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="318" spans="1:9">
@@ -9950,7 +10031,7 @@
         <v>62</v>
       </c>
       <c r="I318" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="319" spans="1:9">
@@ -10005,7 +10086,7 @@
         <v>52</v>
       </c>
       <c r="I320" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="321" spans="1:9">
@@ -10034,7 +10115,7 @@
         <v>97</v>
       </c>
       <c r="I321" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="322" spans="1:9">
@@ -10063,7 +10144,7 @@
         <v>29</v>
       </c>
       <c r="I322" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="323" spans="1:9">
@@ -10092,7 +10173,7 @@
         <v>18</v>
       </c>
       <c r="I323" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="324" spans="1:9">
@@ -10147,7 +10228,7 @@
         <v>22</v>
       </c>
       <c r="I325" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="326" spans="1:9">
@@ -10176,7 +10257,7 @@
         <v>21</v>
       </c>
       <c r="I326" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="327" spans="1:9">
@@ -10205,7 +10286,7 @@
         <v>18</v>
       </c>
       <c r="I327" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="328" spans="1:9">
@@ -10260,7 +10341,7 @@
         <v>77</v>
       </c>
       <c r="I329" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="330" spans="1:9">
@@ -10315,7 +10396,7 @@
         <v>18</v>
       </c>
       <c r="I331" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="332" spans="1:9">
@@ -10344,7 +10425,7 @@
         <v>0</v>
       </c>
       <c r="I332" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="333" spans="1:9">
@@ -10373,7 +10454,7 @@
         <v>46</v>
       </c>
       <c r="I333" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="334" spans="1:9">
@@ -10428,7 +10509,7 @@
         <v>15</v>
       </c>
       <c r="I335" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="336" spans="1:9">
@@ -10457,7 +10538,7 @@
         <v>76</v>
       </c>
       <c r="I336" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="337" spans="1:9">
@@ -10486,7 +10567,7 @@
         <v>16</v>
       </c>
       <c r="I337" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="338" spans="1:9">
@@ -10515,7 +10596,7 @@
         <v>85</v>
       </c>
       <c r="I338" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="339" spans="1:9">
@@ -10596,7 +10677,7 @@
         <v>50</v>
       </c>
       <c r="I341" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="342" spans="1:9">
@@ -10625,7 +10706,7 @@
         <v>93</v>
       </c>
       <c r="I342" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="343" spans="1:9">
@@ -10654,7 +10735,7 @@
         <v>12</v>
       </c>
       <c r="I343" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="344" spans="1:9">
@@ -10683,7 +10764,7 @@
         <v>93</v>
       </c>
       <c r="I344" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="345" spans="1:9">
@@ -10712,7 +10793,7 @@
         <v>22</v>
       </c>
       <c r="I345" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="346" spans="1:9">
@@ -10741,7 +10822,7 @@
         <v>74</v>
       </c>
       <c r="I346" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="347" spans="1:9">
@@ -10796,7 +10877,7 @@
         <v>18</v>
       </c>
       <c r="I348" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="349" spans="1:9">
@@ -10825,7 +10906,7 @@
         <v>22</v>
       </c>
       <c r="I349" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="350" spans="1:9">
@@ -10854,7 +10935,7 @@
         <v>12</v>
       </c>
       <c r="I350" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="351" spans="1:9">
@@ -10883,7 +10964,7 @@
         <v>65</v>
       </c>
       <c r="I351" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="352" spans="1:9">
@@ -10912,7 +10993,7 @@
         <v>12</v>
       </c>
       <c r="I352" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="353" spans="1:9">
@@ -11025,7 +11106,7 @@
         <v>39</v>
       </c>
       <c r="I356" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="357" spans="1:9">
@@ -11083,7 +11164,7 @@
         <v>83</v>
       </c>
       <c r="I358" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="359" spans="1:9">
@@ -11112,7 +11193,7 @@
         <v>28</v>
       </c>
       <c r="I359" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="360" spans="1:9">
@@ -11167,7 +11248,7 @@
         <v>56</v>
       </c>
       <c r="I361" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="362" spans="1:9">
@@ -11196,7 +11277,7 @@
         <v>39</v>
       </c>
       <c r="I362" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="363" spans="1:9">
@@ -11225,7 +11306,7 @@
         <v>61</v>
       </c>
       <c r="I363" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="364" spans="1:9">
@@ -11254,7 +11335,7 @@
         <v>27</v>
       </c>
       <c r="I364" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="365" spans="1:9">
@@ -11364,7 +11445,7 @@
         <v>52</v>
       </c>
       <c r="I368" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="369" spans="1:9">
@@ -11549,7 +11630,7 @@
         <v>100</v>
       </c>
       <c r="I375" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="376" spans="1:9">
@@ -11578,7 +11659,7 @@
         <v>85</v>
       </c>
       <c r="I376" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="377" spans="1:9">
@@ -11607,7 +11688,7 @@
         <v>15</v>
       </c>
       <c r="I377" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="378" spans="1:9">
@@ -11688,7 +11769,7 @@
         <v>95</v>
       </c>
       <c r="I380" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="381" spans="1:9">
@@ -11717,7 +11798,7 @@
         <v>100</v>
       </c>
       <c r="I381" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="382" spans="1:9">
@@ -11746,7 +11827,7 @@
         <v>0</v>
       </c>
       <c r="I382" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="383" spans="1:9">
@@ -11775,7 +11856,7 @@
         <v>42</v>
       </c>
       <c r="I383" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="384" spans="1:9">
@@ -11804,7 +11885,7 @@
         <v>0</v>
       </c>
       <c r="I384" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="385" spans="1:9">
@@ -11888,7 +11969,7 @@
         <v>25</v>
       </c>
       <c r="I387" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="388" spans="1:9">
@@ -11917,7 +11998,7 @@
         <v>88</v>
       </c>
       <c r="I388" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="389" spans="1:9">
@@ -11975,7 +12056,7 @@
         <v>52</v>
       </c>
       <c r="I390" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="391" spans="1:9">
@@ -12004,7 +12085,7 @@
         <v>57</v>
       </c>
       <c r="I391" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="392" spans="1:9">
@@ -12033,7 +12114,7 @@
         <v>75</v>
       </c>
       <c r="I392" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="393" spans="1:9">
@@ -12062,7 +12143,7 @@
         <v>25</v>
       </c>
       <c r="I393" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="394" spans="1:9">
@@ -12169,7 +12250,7 @@
         <v>22</v>
       </c>
       <c r="I397" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="398" spans="1:9">
@@ -12253,7 +12334,7 @@
         <v>42</v>
       </c>
       <c r="I400" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="401" spans="1:9">
@@ -12334,7 +12415,7 @@
         <v>15</v>
       </c>
       <c r="I403" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="404" spans="1:9">
@@ -12519,7 +12600,7 @@
         <v>81</v>
       </c>
       <c r="I410" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="411" spans="1:9">
@@ -12548,7 +12629,7 @@
         <v>91</v>
       </c>
       <c r="I411" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="412" spans="1:9">
@@ -12577,7 +12658,7 @@
         <v>18</v>
       </c>
       <c r="I412" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="413" spans="1:9">
@@ -12658,7 +12739,7 @@
         <v>88</v>
       </c>
       <c r="I415" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="416" spans="1:9">
@@ -12716,7 +12797,7 @@
         <v>0</v>
       </c>
       <c r="I417" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="418" spans="1:9">
@@ -12745,7 +12826,7 @@
         <v>15</v>
       </c>
       <c r="I418" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="419" spans="1:9">
@@ -12774,7 +12855,7 @@
         <v>0</v>
       </c>
       <c r="I419" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="420" spans="1:9">
@@ -12858,7 +12939,7 @@
         <v>51</v>
       </c>
       <c r="I422" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="423" spans="1:9">
@@ -12887,7 +12968,7 @@
         <v>18</v>
       </c>
       <c r="I423" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="424" spans="1:9">
@@ -12916,7 +12997,7 @@
         <v>13</v>
       </c>
       <c r="I424" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="425" spans="1:9">
@@ -12945,7 +13026,7 @@
         <v>0</v>
       </c>
       <c r="I425" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="426" spans="1:9">
@@ -12974,7 +13055,7 @@
         <v>86</v>
       </c>
       <c r="I426" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="427" spans="1:9">
@@ -13003,7 +13084,7 @@
         <v>100</v>
       </c>
       <c r="I427" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="428" spans="1:9">
@@ -13032,7 +13113,7 @@
         <v>20</v>
       </c>
       <c r="I428" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="429" spans="1:9">
@@ -13113,7 +13194,7 @@
         <v>22</v>
       </c>
       <c r="I431" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="432" spans="1:9">
@@ -13168,7 +13249,989 @@
         <v>18</v>
       </c>
       <c r="I433" t="s">
-        <v>343</v>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="434" spans="1:9">
+      <c r="A434">
+        <v>1903274</v>
+      </c>
+      <c r="B434" t="s">
+        <v>9</v>
+      </c>
+      <c r="C434" t="s">
+        <v>107</v>
+      </c>
+      <c r="D434">
+        <v>901</v>
+      </c>
+      <c r="E434" t="s">
+        <v>111</v>
+      </c>
+      <c r="F434" t="s">
+        <v>114</v>
+      </c>
+      <c r="G434" t="s">
+        <v>118</v>
+      </c>
+      <c r="H434">
+        <v>100</v>
+      </c>
+      <c r="I434" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="435" spans="1:9">
+      <c r="A435">
+        <v>2003052</v>
+      </c>
+      <c r="B435" t="s">
+        <v>10</v>
+      </c>
+      <c r="C435" t="s">
+        <v>107</v>
+      </c>
+      <c r="D435">
+        <v>901</v>
+      </c>
+      <c r="E435" t="s">
+        <v>111</v>
+      </c>
+      <c r="F435" t="s">
+        <v>114</v>
+      </c>
+      <c r="G435" t="s">
+        <v>118</v>
+      </c>
+      <c r="H435">
+        <v>37</v>
+      </c>
+      <c r="I435" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9">
+      <c r="A436">
+        <v>2100421</v>
+      </c>
+      <c r="B436" t="s">
+        <v>11</v>
+      </c>
+      <c r="C436" t="s">
+        <v>107</v>
+      </c>
+      <c r="D436">
+        <v>901</v>
+      </c>
+      <c r="E436" t="s">
+        <v>111</v>
+      </c>
+      <c r="F436" t="s">
+        <v>113</v>
+      </c>
+      <c r="G436" t="s">
+        <v>118</v>
+      </c>
+      <c r="I436" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="437" spans="1:9">
+      <c r="A437">
+        <v>2101613</v>
+      </c>
+      <c r="B437" t="s">
+        <v>12</v>
+      </c>
+      <c r="C437" t="s">
+        <v>107</v>
+      </c>
+      <c r="D437">
+        <v>901</v>
+      </c>
+      <c r="E437" t="s">
+        <v>111</v>
+      </c>
+      <c r="F437" t="s">
+        <v>114</v>
+      </c>
+      <c r="G437" t="s">
+        <v>118</v>
+      </c>
+      <c r="H437">
+        <v>38</v>
+      </c>
+      <c r="I437" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9">
+      <c r="A438">
+        <v>2105067</v>
+      </c>
+      <c r="B438" t="s">
+        <v>13</v>
+      </c>
+      <c r="C438" t="s">
+        <v>107</v>
+      </c>
+      <c r="D438">
+        <v>901</v>
+      </c>
+      <c r="E438" t="s">
+        <v>111</v>
+      </c>
+      <c r="F438" t="s">
+        <v>114</v>
+      </c>
+      <c r="G438" t="s">
+        <v>118</v>
+      </c>
+      <c r="H438">
+        <v>14</v>
+      </c>
+      <c r="I438" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="439" spans="1:9">
+      <c r="A439">
+        <v>2105541</v>
+      </c>
+      <c r="B439" t="s">
+        <v>106</v>
+      </c>
+      <c r="C439" t="s">
+        <v>107</v>
+      </c>
+      <c r="D439">
+        <v>901</v>
+      </c>
+      <c r="E439" t="s">
+        <v>111</v>
+      </c>
+      <c r="F439" t="s">
+        <v>114</v>
+      </c>
+      <c r="G439" t="s">
+        <v>118</v>
+      </c>
+      <c r="H439">
+        <v>18</v>
+      </c>
+      <c r="I439" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="440" spans="1:9">
+      <c r="A440">
+        <v>2106789</v>
+      </c>
+      <c r="B440" t="s">
+        <v>14</v>
+      </c>
+      <c r="C440" t="s">
+        <v>107</v>
+      </c>
+      <c r="D440">
+        <v>901</v>
+      </c>
+      <c r="E440" t="s">
+        <v>111</v>
+      </c>
+      <c r="F440" t="s">
+        <v>113</v>
+      </c>
+      <c r="G440" t="s">
+        <v>118</v>
+      </c>
+      <c r="I440" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="441" spans="1:9">
+      <c r="A441">
+        <v>2200206</v>
+      </c>
+      <c r="B441" t="s">
+        <v>15</v>
+      </c>
+      <c r="C441" t="s">
+        <v>107</v>
+      </c>
+      <c r="D441">
+        <v>901</v>
+      </c>
+      <c r="E441" t="s">
+        <v>111</v>
+      </c>
+      <c r="F441" t="s">
+        <v>114</v>
+      </c>
+      <c r="G441" t="s">
+        <v>118</v>
+      </c>
+      <c r="H441">
+        <v>100</v>
+      </c>
+      <c r="I441" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="442" spans="1:9">
+      <c r="A442">
+        <v>2200601</v>
+      </c>
+      <c r="B442" t="s">
+        <v>16</v>
+      </c>
+      <c r="C442" t="s">
+        <v>107</v>
+      </c>
+      <c r="D442">
+        <v>901</v>
+      </c>
+      <c r="E442" t="s">
+        <v>111</v>
+      </c>
+      <c r="F442" t="s">
+        <v>113</v>
+      </c>
+      <c r="G442" t="s">
+        <v>118</v>
+      </c>
+      <c r="I442" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="443" spans="1:9">
+      <c r="A443">
+        <v>2284111</v>
+      </c>
+      <c r="B443" t="s">
+        <v>17</v>
+      </c>
+      <c r="C443" t="s">
+        <v>107</v>
+      </c>
+      <c r="D443">
+        <v>901</v>
+      </c>
+      <c r="E443" t="s">
+        <v>111</v>
+      </c>
+      <c r="F443" t="s">
+        <v>113</v>
+      </c>
+      <c r="G443" t="s">
+        <v>118</v>
+      </c>
+      <c r="I443" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9">
+      <c r="A444">
+        <v>2355702</v>
+      </c>
+      <c r="B444" t="s">
+        <v>18</v>
+      </c>
+      <c r="C444" t="s">
+        <v>107</v>
+      </c>
+      <c r="D444">
+        <v>901</v>
+      </c>
+      <c r="E444" t="s">
+        <v>111</v>
+      </c>
+      <c r="F444" t="s">
+        <v>114</v>
+      </c>
+      <c r="G444" t="s">
+        <v>118</v>
+      </c>
+      <c r="H444">
+        <v>32</v>
+      </c>
+      <c r="I444" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9">
+      <c r="A445">
+        <v>2359764</v>
+      </c>
+      <c r="B445" t="s">
+        <v>19</v>
+      </c>
+      <c r="C445" t="s">
+        <v>107</v>
+      </c>
+      <c r="D445">
+        <v>901</v>
+      </c>
+      <c r="E445" t="s">
+        <v>111</v>
+      </c>
+      <c r="F445" t="s">
+        <v>113</v>
+      </c>
+      <c r="G445" t="s">
+        <v>118</v>
+      </c>
+      <c r="I445" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9">
+      <c r="A446">
+        <v>2363982</v>
+      </c>
+      <c r="B446" t="s">
+        <v>20</v>
+      </c>
+      <c r="C446" t="s">
+        <v>107</v>
+      </c>
+      <c r="D446">
+        <v>901</v>
+      </c>
+      <c r="E446" t="s">
+        <v>111</v>
+      </c>
+      <c r="F446" t="s">
+        <v>114</v>
+      </c>
+      <c r="G446" t="s">
+        <v>118</v>
+      </c>
+      <c r="H446">
+        <v>10</v>
+      </c>
+      <c r="I446" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9">
+      <c r="A447">
+        <v>2364571</v>
+      </c>
+      <c r="B447" t="s">
+        <v>21</v>
+      </c>
+      <c r="C447" t="s">
+        <v>107</v>
+      </c>
+      <c r="D447">
+        <v>901</v>
+      </c>
+      <c r="E447" t="s">
+        <v>111</v>
+      </c>
+      <c r="F447" t="s">
+        <v>114</v>
+      </c>
+      <c r="G447" t="s">
+        <v>118</v>
+      </c>
+      <c r="H447">
+        <v>20</v>
+      </c>
+      <c r="I447" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9">
+      <c r="A448">
+        <v>2364697</v>
+      </c>
+      <c r="B448" t="s">
+        <v>22</v>
+      </c>
+      <c r="C448" t="s">
+        <v>107</v>
+      </c>
+      <c r="D448">
+        <v>901</v>
+      </c>
+      <c r="E448" t="s">
+        <v>111</v>
+      </c>
+      <c r="F448" t="s">
+        <v>113</v>
+      </c>
+      <c r="G448" t="s">
+        <v>118</v>
+      </c>
+      <c r="I448" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="449" spans="1:9">
+      <c r="A449">
+        <v>2364712</v>
+      </c>
+      <c r="B449" t="s">
+        <v>23</v>
+      </c>
+      <c r="C449" t="s">
+        <v>107</v>
+      </c>
+      <c r="D449">
+        <v>901</v>
+      </c>
+      <c r="E449" t="s">
+        <v>111</v>
+      </c>
+      <c r="F449" t="s">
+        <v>114</v>
+      </c>
+      <c r="G449" t="s">
+        <v>118</v>
+      </c>
+      <c r="H449">
+        <v>46</v>
+      </c>
+      <c r="I449" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="450" spans="1:9">
+      <c r="A450">
+        <v>2365114</v>
+      </c>
+      <c r="B450" t="s">
+        <v>24</v>
+      </c>
+      <c r="C450" t="s">
+        <v>107</v>
+      </c>
+      <c r="D450">
+        <v>901</v>
+      </c>
+      <c r="E450" t="s">
+        <v>111</v>
+      </c>
+      <c r="F450" t="s">
+        <v>113</v>
+      </c>
+      <c r="G450" t="s">
+        <v>118</v>
+      </c>
+      <c r="I450" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="451" spans="1:9">
+      <c r="A451">
+        <v>2366271</v>
+      </c>
+      <c r="B451" t="s">
+        <v>25</v>
+      </c>
+      <c r="C451" t="s">
+        <v>107</v>
+      </c>
+      <c r="D451">
+        <v>901</v>
+      </c>
+      <c r="E451" t="s">
+        <v>111</v>
+      </c>
+      <c r="F451" t="s">
+        <v>114</v>
+      </c>
+      <c r="G451" t="s">
+        <v>118</v>
+      </c>
+      <c r="H451">
+        <v>87</v>
+      </c>
+      <c r="I451" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="452" spans="1:9">
+      <c r="A452">
+        <v>2366789</v>
+      </c>
+      <c r="B452" t="s">
+        <v>26</v>
+      </c>
+      <c r="C452" t="s">
+        <v>107</v>
+      </c>
+      <c r="D452">
+        <v>901</v>
+      </c>
+      <c r="E452" t="s">
+        <v>111</v>
+      </c>
+      <c r="F452" t="s">
+        <v>114</v>
+      </c>
+      <c r="G452" t="s">
+        <v>118</v>
+      </c>
+      <c r="H452">
+        <v>37</v>
+      </c>
+      <c r="I452" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="453" spans="1:9">
+      <c r="A453">
+        <v>2367137</v>
+      </c>
+      <c r="B453" t="s">
+        <v>27</v>
+      </c>
+      <c r="C453" t="s">
+        <v>107</v>
+      </c>
+      <c r="D453">
+        <v>901</v>
+      </c>
+      <c r="E453" t="s">
+        <v>111</v>
+      </c>
+      <c r="F453" t="s">
+        <v>113</v>
+      </c>
+      <c r="G453" t="s">
+        <v>118</v>
+      </c>
+      <c r="I453" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="454" spans="1:9">
+      <c r="A454">
+        <v>2368553</v>
+      </c>
+      <c r="B454" t="s">
+        <v>28</v>
+      </c>
+      <c r="C454" t="s">
+        <v>107</v>
+      </c>
+      <c r="D454">
+        <v>901</v>
+      </c>
+      <c r="E454" t="s">
+        <v>111</v>
+      </c>
+      <c r="F454" t="s">
+        <v>114</v>
+      </c>
+      <c r="G454" t="s">
+        <v>118</v>
+      </c>
+      <c r="H454">
+        <v>28</v>
+      </c>
+      <c r="I454" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="455" spans="1:9">
+      <c r="A455">
+        <v>2369573</v>
+      </c>
+      <c r="B455" t="s">
+        <v>29</v>
+      </c>
+      <c r="C455" t="s">
+        <v>107</v>
+      </c>
+      <c r="D455">
+        <v>901</v>
+      </c>
+      <c r="E455" t="s">
+        <v>111</v>
+      </c>
+      <c r="F455" t="s">
+        <v>113</v>
+      </c>
+      <c r="G455" t="s">
+        <v>118</v>
+      </c>
+      <c r="I455" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="456" spans="1:9">
+      <c r="A456">
+        <v>2473471</v>
+      </c>
+      <c r="B456" t="s">
+        <v>30</v>
+      </c>
+      <c r="C456" t="s">
+        <v>107</v>
+      </c>
+      <c r="D456">
+        <v>901</v>
+      </c>
+      <c r="E456" t="s">
+        <v>111</v>
+      </c>
+      <c r="F456" t="s">
+        <v>114</v>
+      </c>
+      <c r="G456" t="s">
+        <v>118</v>
+      </c>
+      <c r="H456">
+        <v>97</v>
+      </c>
+      <c r="I456" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="457" spans="1:9">
+      <c r="A457">
+        <v>2477416</v>
+      </c>
+      <c r="B457" t="s">
+        <v>31</v>
+      </c>
+      <c r="C457" t="s">
+        <v>107</v>
+      </c>
+      <c r="D457">
+        <v>901</v>
+      </c>
+      <c r="E457" t="s">
+        <v>111</v>
+      </c>
+      <c r="F457" t="s">
+        <v>114</v>
+      </c>
+      <c r="G457" t="s">
+        <v>118</v>
+      </c>
+      <c r="H457">
+        <v>97</v>
+      </c>
+      <c r="I457" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="458" spans="1:9">
+      <c r="A458">
+        <v>2482829</v>
+      </c>
+      <c r="B458" t="s">
+        <v>32</v>
+      </c>
+      <c r="C458" t="s">
+        <v>107</v>
+      </c>
+      <c r="D458">
+        <v>901</v>
+      </c>
+      <c r="E458" t="s">
+        <v>111</v>
+      </c>
+      <c r="F458" t="s">
+        <v>114</v>
+      </c>
+      <c r="G458" t="s">
+        <v>118</v>
+      </c>
+      <c r="H458">
+        <v>14</v>
+      </c>
+      <c r="I458" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="459" spans="1:9">
+      <c r="A459">
+        <v>2483134</v>
+      </c>
+      <c r="B459" t="s">
+        <v>33</v>
+      </c>
+      <c r="C459" t="s">
+        <v>107</v>
+      </c>
+      <c r="D459">
+        <v>901</v>
+      </c>
+      <c r="E459" t="s">
+        <v>111</v>
+      </c>
+      <c r="F459" t="s">
+        <v>113</v>
+      </c>
+      <c r="G459" t="s">
+        <v>118</v>
+      </c>
+      <c r="I459" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="460" spans="1:9">
+      <c r="A460">
+        <v>2483496</v>
+      </c>
+      <c r="B460" t="s">
+        <v>34</v>
+      </c>
+      <c r="C460" t="s">
+        <v>107</v>
+      </c>
+      <c r="D460">
+        <v>901</v>
+      </c>
+      <c r="E460" t="s">
+        <v>111</v>
+      </c>
+      <c r="F460" t="s">
+        <v>114</v>
+      </c>
+      <c r="G460" t="s">
+        <v>118</v>
+      </c>
+      <c r="H460">
+        <v>54</v>
+      </c>
+      <c r="I460" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="461" spans="1:9">
+      <c r="A461">
+        <v>2484424</v>
+      </c>
+      <c r="B461" t="s">
+        <v>36</v>
+      </c>
+      <c r="C461" t="s">
+        <v>107</v>
+      </c>
+      <c r="D461">
+        <v>901</v>
+      </c>
+      <c r="E461" t="s">
+        <v>111</v>
+      </c>
+      <c r="F461" t="s">
+        <v>113</v>
+      </c>
+      <c r="G461" t="s">
+        <v>118</v>
+      </c>
+      <c r="I461" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="462" spans="1:9">
+      <c r="A462">
+        <v>2484478</v>
+      </c>
+      <c r="B462" t="s">
+        <v>37</v>
+      </c>
+      <c r="C462" t="s">
+        <v>107</v>
+      </c>
+      <c r="D462">
+        <v>901</v>
+      </c>
+      <c r="E462" t="s">
+        <v>111</v>
+      </c>
+      <c r="F462" t="s">
+        <v>114</v>
+      </c>
+      <c r="G462" t="s">
+        <v>118</v>
+      </c>
+      <c r="H462">
+        <v>22</v>
+      </c>
+      <c r="I462" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="463" spans="1:9">
+      <c r="A463">
+        <v>2590850</v>
+      </c>
+      <c r="B463" t="s">
+        <v>38</v>
+      </c>
+      <c r="C463" t="s">
+        <v>107</v>
+      </c>
+      <c r="D463">
+        <v>901</v>
+      </c>
+      <c r="E463" t="s">
+        <v>111</v>
+      </c>
+      <c r="F463" t="s">
+        <v>114</v>
+      </c>
+      <c r="G463" t="s">
+        <v>118</v>
+      </c>
+      <c r="H463">
+        <v>40</v>
+      </c>
+      <c r="I463" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="464" spans="1:9">
+      <c r="A464">
+        <v>2591078</v>
+      </c>
+      <c r="B464" t="s">
+        <v>39</v>
+      </c>
+      <c r="C464" t="s">
+        <v>107</v>
+      </c>
+      <c r="D464">
+        <v>901</v>
+      </c>
+      <c r="E464" t="s">
+        <v>111</v>
+      </c>
+      <c r="F464" t="s">
+        <v>114</v>
+      </c>
+      <c r="G464" t="s">
+        <v>118</v>
+      </c>
+      <c r="H464">
+        <v>0</v>
+      </c>
+      <c r="I464" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="465" spans="1:9">
+      <c r="A465">
+        <v>2592655</v>
+      </c>
+      <c r="B465" t="s">
+        <v>40</v>
+      </c>
+      <c r="C465" t="s">
+        <v>107</v>
+      </c>
+      <c r="D465">
+        <v>901</v>
+      </c>
+      <c r="E465" t="s">
+        <v>111</v>
+      </c>
+      <c r="F465" t="s">
+        <v>114</v>
+      </c>
+      <c r="G465" t="s">
+        <v>118</v>
+      </c>
+      <c r="H465">
+        <v>50</v>
+      </c>
+      <c r="I465" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="466" spans="1:9">
+      <c r="A466">
+        <v>2593256</v>
+      </c>
+      <c r="B466" t="s">
+        <v>41</v>
+      </c>
+      <c r="C466" t="s">
+        <v>107</v>
+      </c>
+      <c r="D466">
+        <v>901</v>
+      </c>
+      <c r="E466" t="s">
+        <v>111</v>
+      </c>
+      <c r="F466" t="s">
+        <v>114</v>
+      </c>
+      <c r="G466" t="s">
+        <v>118</v>
+      </c>
+      <c r="H466">
+        <v>24</v>
+      </c>
+      <c r="I466" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="467" spans="1:9">
+      <c r="A467">
+        <v>2596186</v>
+      </c>
+      <c r="B467" t="s">
+        <v>42</v>
+      </c>
+      <c r="C467" t="s">
+        <v>107</v>
+      </c>
+      <c r="D467">
+        <v>901</v>
+      </c>
+      <c r="E467" t="s">
+        <v>111</v>
+      </c>
+      <c r="F467" t="s">
+        <v>114</v>
+      </c>
+      <c r="G467" t="s">
+        <v>118</v>
+      </c>
+      <c r="H467">
+        <v>28</v>
+      </c>
+      <c r="I467" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="468" spans="1:9">
+      <c r="A468">
+        <v>2612865</v>
+      </c>
+      <c r="B468" t="s">
+        <v>43</v>
+      </c>
+      <c r="C468" t="s">
+        <v>107</v>
+      </c>
+      <c r="D468">
+        <v>901</v>
+      </c>
+      <c r="E468" t="s">
+        <v>111</v>
+      </c>
+      <c r="F468" t="s">
+        <v>114</v>
+      </c>
+      <c r="G468" t="s">
+        <v>118</v>
+      </c>
+      <c r="H468">
+        <v>94</v>
+      </c>
+      <c r="I468" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/grades_database.xlsx
+++ b/grades_database.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gökhan Gülser\Desktop\quiz_system_backup\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBF0535-F7C3-451A-AC9E-73678B1E1B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$468</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2737" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2737" uniqueCount="368">
   <si>
     <t>student_id</t>
   </si>
@@ -864,9 +878,6 @@
     <t>You correctly set up the geometry and position vectors, and your gear force resolution and M_x component are excellent. However, you subtracted the 200 N belt force instead of adding it (both belt forces act in the +x direction), which caused errors in R_x (-13 pts in Part B) and propagated into M_y and M_z (-20 pts in Part C), and the final answer lost 3 pts for the incorrect values. Keep up the solid method — fixing that sign error would have given you a much higher score!</t>
   </si>
   <si>
-    <t>You correctly computed the beam length, weight (W=4.9 kN at midpoint), resolved the 3 kN force into components, and found O_x = 1.5 kN and O_y = 6.1 kN with correct equilibrium equations. However, in the moment equation you treated the 15 kN·m couple as negative (clockwise) when it should be positive (counterclockwise), leading to M_O = 37.55 kN·m instead of the correct 7.56 kN·m, so you lose 10 points for the couple sign error (C2) and 15 points for the incorrect final M_O value (C3), with no deduction in D for the direction/magnitude since it follows from the same mistake.</t>
-  </si>
-  <si>
     <t>You correctly drew the FBD, computed the beam weight, resolved the 3 kN force into components, and found O_x = 1.5 kN. However, your moment equation about B had incorrect moment arms and was missing key terms, leading to a wrong O_y, and your M_O calculation only used O_y contributions while omitting the beam weight moment, the 1.4 kN force moment, and the 15 kN·m free couple — these errors caused significant point losses in Parts C and D.</t>
   </si>
   <si>
@@ -1131,8 +1142,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1169,13 +1180,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1213,7 +1232,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1247,6 +1266,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1281,9 +1301,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1456,11 +1477,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I468"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1489,7 +1510,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1903274</v>
       </c>
@@ -1512,7 +1533,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2003052</v>
       </c>
@@ -1535,7 +1556,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2100421</v>
       </c>
@@ -1558,7 +1579,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2101613</v>
       </c>
@@ -1581,7 +1602,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2105067</v>
       </c>
@@ -1604,7 +1625,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2106789</v>
       </c>
@@ -1627,7 +1648,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2200206</v>
       </c>
@@ -1650,7 +1671,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2200601</v>
       </c>
@@ -1673,7 +1694,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2284111</v>
       </c>
@@ -1696,7 +1717,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2355702</v>
       </c>
@@ -1719,7 +1740,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2359764</v>
       </c>
@@ -1742,7 +1763,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2363982</v>
       </c>
@@ -1765,7 +1786,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2364571</v>
       </c>
@@ -1788,7 +1809,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2364697</v>
       </c>
@@ -1811,7 +1832,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2364712</v>
       </c>
@@ -1834,7 +1855,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2365114</v>
       </c>
@@ -1857,7 +1878,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2366271</v>
       </c>
@@ -1880,7 +1901,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2366789</v>
       </c>
@@ -1903,7 +1924,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2367137</v>
       </c>
@@ -1926,7 +1947,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2368553</v>
       </c>
@@ -1949,7 +1970,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2369573</v>
       </c>
@@ -1972,7 +1993,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2473471</v>
       </c>
@@ -1995,7 +2016,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2477416</v>
       </c>
@@ -2018,7 +2039,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2482829</v>
       </c>
@@ -2041,7 +2062,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2483134</v>
       </c>
@@ -2064,7 +2085,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2483496</v>
       </c>
@@ -2087,7 +2108,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2484397</v>
       </c>
@@ -2110,7 +2131,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2484424</v>
       </c>
@@ -2133,7 +2154,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2484478</v>
       </c>
@@ -2156,7 +2177,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2590850</v>
       </c>
@@ -2179,7 +2200,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2591078</v>
       </c>
@@ -2202,7 +2223,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2592655</v>
       </c>
@@ -2225,7 +2246,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2593256</v>
       </c>
@@ -2248,7 +2269,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2596186</v>
       </c>
@@ -2271,7 +2292,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2612865</v>
       </c>
@@ -2294,7 +2315,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2003675</v>
       </c>
@@ -2317,7 +2338,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2003743</v>
       </c>
@@ -2340,7 +2361,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2101812</v>
       </c>
@@ -2363,7 +2384,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2102438</v>
       </c>
@@ -2386,7 +2407,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2104775</v>
       </c>
@@ -2409,7 +2430,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2200784</v>
       </c>
@@ -2432,7 +2453,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2202739</v>
       </c>
@@ -2455,7 +2476,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2202877</v>
       </c>
@@ -2478,7 +2499,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2364766</v>
       </c>
@@ -2501,7 +2522,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2366349</v>
       </c>
@@ -2524,7 +2545,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2366648</v>
       </c>
@@ -2547,7 +2568,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2366734</v>
       </c>
@@ -2570,7 +2591,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2366906</v>
       </c>
@@ -2593,7 +2614,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2366917</v>
       </c>
@@ -2616,7 +2637,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2367037</v>
       </c>
@@ -2639,7 +2660,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2368580</v>
       </c>
@@ -2662,7 +2683,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2472843</v>
       </c>
@@ -2685,7 +2706,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2476099</v>
       </c>
@@ -2708,7 +2729,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2477970</v>
       </c>
@@ -2731,7 +2752,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2482073</v>
       </c>
@@ -2754,7 +2775,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2482445</v>
       </c>
@@ -2777,7 +2798,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2483328</v>
       </c>
@@ -2800,7 +2821,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2483434</v>
       </c>
@@ -2823,7 +2844,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2483834</v>
       </c>
@@ -2846,7 +2867,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2483956</v>
       </c>
@@ -2869,7 +2890,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2483960</v>
       </c>
@@ -2892,7 +2913,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2484028</v>
       </c>
@@ -2915,7 +2936,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2484186</v>
       </c>
@@ -2938,7 +2959,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2484262</v>
       </c>
@@ -2961,7 +2982,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>2484542</v>
       </c>
@@ -2984,7 +3005,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>2500744</v>
       </c>
@@ -3007,7 +3028,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>2501122</v>
       </c>
@@ -3030,7 +3051,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2593530</v>
       </c>
@@ -3053,7 +3074,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2596196</v>
       </c>
@@ -3076,7 +3097,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2599154</v>
       </c>
@@ -3099,7 +3120,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>2599631</v>
       </c>
@@ -3122,7 +3143,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>2599634</v>
       </c>
@@ -3145,7 +3166,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>2599868</v>
       </c>
@@ -3168,7 +3189,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2616909</v>
       </c>
@@ -3191,7 +3212,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>1903274</v>
       </c>
@@ -3220,7 +3241,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>2200784</v>
       </c>
@@ -3246,7 +3267,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>2202739</v>
       </c>
@@ -3275,7 +3296,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>2250387</v>
       </c>
@@ -3304,7 +3325,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>2363982</v>
       </c>
@@ -3333,7 +3354,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2364521</v>
       </c>
@@ -3362,7 +3383,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2364697</v>
       </c>
@@ -3388,7 +3409,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2364712</v>
       </c>
@@ -3417,7 +3438,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>2364766</v>
       </c>
@@ -3446,7 +3467,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>2364995</v>
       </c>
@@ -3472,7 +3493,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>2365347</v>
       </c>
@@ -3498,7 +3519,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>2366232</v>
       </c>
@@ -3527,7 +3548,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>2366349</v>
       </c>
@@ -3556,7 +3577,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>2366734</v>
       </c>
@@ -3582,7 +3603,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>2366843</v>
       </c>
@@ -3608,7 +3629,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2367037</v>
       </c>
@@ -3637,7 +3658,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>2368553</v>
       </c>
@@ -3666,7 +3687,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>2369573</v>
       </c>
@@ -3695,7 +3716,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>2472990</v>
       </c>
@@ -3724,7 +3745,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>2482073</v>
       </c>
@@ -3753,7 +3774,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>2482445</v>
       </c>
@@ -3782,7 +3803,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2482558</v>
       </c>
@@ -3811,7 +3832,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2483134</v>
       </c>
@@ -3837,7 +3858,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2483328</v>
       </c>
@@ -3866,7 +3887,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2483834</v>
       </c>
@@ -3895,7 +3916,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>2483956</v>
       </c>
@@ -3921,7 +3942,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>2484028</v>
       </c>
@@ -3950,7 +3971,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>2484397</v>
       </c>
@@ -3979,7 +4000,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>2484424</v>
       </c>
@@ -4008,7 +4029,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>2484478</v>
       </c>
@@ -4037,7 +4058,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2484542</v>
       </c>
@@ -4066,7 +4087,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2485620</v>
       </c>
@@ -4095,7 +4116,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2488091</v>
       </c>
@@ -4124,7 +4145,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2500744</v>
       </c>
@@ -4153,7 +4174,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>2501122</v>
       </c>
@@ -4182,7 +4203,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2501485</v>
       </c>
@@ -4211,7 +4232,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>2503515</v>
       </c>
@@ -4237,7 +4258,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>2590850</v>
       </c>
@@ -4266,7 +4287,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>2591078</v>
       </c>
@@ -4295,7 +4316,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2593256</v>
       </c>
@@ -4324,7 +4345,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>2593530</v>
       </c>
@@ -4353,7 +4374,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>2598321</v>
       </c>
@@ -4379,7 +4400,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2599154</v>
       </c>
@@ -4405,7 +4426,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>2599631</v>
       </c>
@@ -4434,7 +4455,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>2599634</v>
       </c>
@@ -4463,7 +4484,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2599868</v>
       </c>
@@ -4492,7 +4513,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2003743</v>
       </c>
@@ -4518,7 +4539,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2100421</v>
       </c>
@@ -4544,7 +4565,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2101613</v>
       </c>
@@ -4573,7 +4594,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2101812</v>
       </c>
@@ -4599,7 +4620,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2104775</v>
       </c>
@@ -4625,7 +4646,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2106789</v>
       </c>
@@ -4651,7 +4672,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2106808</v>
       </c>
@@ -4680,7 +4701,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2200601</v>
       </c>
@@ -4706,7 +4727,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2202877</v>
       </c>
@@ -4732,7 +4753,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2252125</v>
       </c>
@@ -4758,7 +4779,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2252127</v>
       </c>
@@ -4787,7 +4808,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2282610</v>
       </c>
@@ -4816,7 +4837,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2284111</v>
       </c>
@@ -4842,7 +4863,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2355702</v>
       </c>
@@ -4868,7 +4889,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2359322</v>
       </c>
@@ -4897,7 +4918,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2359481</v>
       </c>
@@ -4926,7 +4947,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2359764</v>
       </c>
@@ -4952,7 +4973,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2360367</v>
       </c>
@@ -4981,7 +5002,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2364571</v>
       </c>
@@ -5010,7 +5031,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2366271</v>
       </c>
@@ -5036,7 +5057,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2366906</v>
       </c>
@@ -5065,7 +5086,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2367137</v>
       </c>
@@ -5094,7 +5115,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2472419</v>
       </c>
@@ -5123,7 +5144,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2472843</v>
       </c>
@@ -5152,7 +5173,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2476099</v>
       </c>
@@ -5181,7 +5202,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2476633</v>
       </c>
@@ -5210,7 +5231,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2477416</v>
       </c>
@@ -5236,7 +5257,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2477970</v>
       </c>
@@ -5265,7 +5286,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2483434</v>
       </c>
@@ -5291,7 +5312,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2483960</v>
       </c>
@@ -5317,7 +5338,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2484262</v>
       </c>
@@ -5346,7 +5367,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2596186</v>
       </c>
@@ -5375,7 +5396,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2597847</v>
       </c>
@@ -5404,7 +5425,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2612865</v>
       </c>
@@ -5433,7 +5454,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2616909</v>
       </c>
@@ -5462,7 +5483,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2003675</v>
       </c>
@@ -5488,7 +5509,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2003743</v>
       </c>
@@ -5514,7 +5535,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2101812</v>
       </c>
@@ -5540,7 +5561,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2102438</v>
       </c>
@@ -5569,7 +5590,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2104775</v>
       </c>
@@ -5598,7 +5619,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2200784</v>
       </c>
@@ -5624,7 +5645,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2202739</v>
       </c>
@@ -5653,7 +5674,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2202877</v>
       </c>
@@ -5679,7 +5700,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2364766</v>
       </c>
@@ -5708,7 +5729,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2366349</v>
       </c>
@@ -5737,7 +5758,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2366648</v>
       </c>
@@ -5766,7 +5787,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2366734</v>
       </c>
@@ -5792,7 +5813,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2366906</v>
       </c>
@@ -5821,7 +5842,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2366917</v>
       </c>
@@ -5847,7 +5868,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2367037</v>
       </c>
@@ -5876,7 +5897,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2368580</v>
       </c>
@@ -5905,7 +5926,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2472843</v>
       </c>
@@ -5934,7 +5955,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2476099</v>
       </c>
@@ -5963,7 +5984,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2477970</v>
       </c>
@@ -5992,7 +6013,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2482073</v>
       </c>
@@ -6021,7 +6042,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2482445</v>
       </c>
@@ -6050,7 +6071,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2483328</v>
       </c>
@@ -6079,7 +6100,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2483434</v>
       </c>
@@ -6108,7 +6129,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2483834</v>
       </c>
@@ -6137,7 +6158,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>2483956</v>
       </c>
@@ -6166,7 +6187,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>2483960</v>
       </c>
@@ -6195,7 +6216,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2484028</v>
       </c>
@@ -6224,7 +6245,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>2484186</v>
       </c>
@@ -6250,7 +6271,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>2484262</v>
       </c>
@@ -6276,7 +6297,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>2484542</v>
       </c>
@@ -6305,7 +6326,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>2500744</v>
       </c>
@@ -6334,7 +6355,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="188" spans="1:9">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>2501122</v>
       </c>
@@ -6363,7 +6384,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="189" spans="1:9">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>2593530</v>
       </c>
@@ -6392,7 +6413,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>2596196</v>
       </c>
@@ -6421,7 +6442,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>2599154</v>
       </c>
@@ -6447,7 +6468,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>2599631</v>
       </c>
@@ -6476,7 +6497,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="193" spans="1:9">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>2599634</v>
       </c>
@@ -6505,7 +6526,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="194" spans="1:9">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>2599868</v>
       </c>
@@ -6534,7 +6555,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="195" spans="1:9">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>2616909</v>
       </c>
@@ -6563,7 +6584,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="196" spans="1:9">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>1903274</v>
       </c>
@@ -6592,7 +6613,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="197" spans="1:9">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>2003052</v>
       </c>
@@ -6621,7 +6642,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="198" spans="1:9">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>2100421</v>
       </c>
@@ -6647,7 +6668,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="199" spans="1:9">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>2101613</v>
       </c>
@@ -6676,7 +6697,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="200" spans="1:9">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>2105067</v>
       </c>
@@ -6705,7 +6726,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="201" spans="1:9">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>2105541</v>
       </c>
@@ -6734,7 +6755,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="202" spans="1:9">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>2106789</v>
       </c>
@@ -6760,7 +6781,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="203" spans="1:9">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>2200206</v>
       </c>
@@ -6789,7 +6810,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="204" spans="1:9">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>2200601</v>
       </c>
@@ -6815,7 +6836,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="205" spans="1:9">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>2284111</v>
       </c>
@@ -6841,7 +6862,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="206" spans="1:9">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>2355702</v>
       </c>
@@ -6870,7 +6891,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="207" spans="1:9">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>2359764</v>
       </c>
@@ -6899,7 +6920,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="208" spans="1:9">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>2363982</v>
       </c>
@@ -6928,7 +6949,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="209" spans="1:9">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>2364571</v>
       </c>
@@ -6957,7 +6978,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="210" spans="1:9">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>2364697</v>
       </c>
@@ -6983,7 +7004,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="211" spans="1:9">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>2364712</v>
       </c>
@@ -7012,7 +7033,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="212" spans="1:9">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>2365114</v>
       </c>
@@ -7038,7 +7059,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="213" spans="1:9">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>2366271</v>
       </c>
@@ -7067,7 +7088,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="214" spans="1:9">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>2366789</v>
       </c>
@@ -7096,7 +7117,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="215" spans="1:9">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>2367137</v>
       </c>
@@ -7125,7 +7146,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="216" spans="1:9">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>2368553</v>
       </c>
@@ -7154,7 +7175,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="217" spans="1:9">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>2369573</v>
       </c>
@@ -7180,7 +7201,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="218" spans="1:9">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>2473471</v>
       </c>
@@ -7209,7 +7230,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="219" spans="1:9">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>2477416</v>
       </c>
@@ -7238,7 +7259,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="220" spans="1:9">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>2482829</v>
       </c>
@@ -7264,7 +7285,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="221" spans="1:9">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>2483134</v>
       </c>
@@ -7290,7 +7311,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="222" spans="1:9">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>2483496</v>
       </c>
@@ -7319,7 +7340,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="223" spans="1:9">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>2484397</v>
       </c>
@@ -7348,7 +7369,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="224" spans="1:9">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>2484424</v>
       </c>
@@ -7377,7 +7398,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="225" spans="1:9">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>2484478</v>
       </c>
@@ -7406,7 +7427,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="226" spans="1:9">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>2590850</v>
       </c>
@@ -7435,7 +7456,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="227" spans="1:9">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>2591078</v>
       </c>
@@ -7464,7 +7485,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="228" spans="1:9">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>2592655</v>
       </c>
@@ -7493,7 +7514,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="229" spans="1:9">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>2593256</v>
       </c>
@@ -7522,7 +7543,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="230" spans="1:9">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>2596186</v>
       </c>
@@ -7551,7 +7572,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="231" spans="1:9">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>2612865</v>
       </c>
@@ -7580,7 +7601,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="232" spans="1:9">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>2003675</v>
       </c>
@@ -7606,7 +7627,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="233" spans="1:9">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>2003743</v>
       </c>
@@ -7632,7 +7653,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="234" spans="1:9">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>2101812</v>
       </c>
@@ -7658,7 +7679,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="235" spans="1:9">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>2102438</v>
       </c>
@@ -7687,7 +7708,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="236" spans="1:9">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>2104775</v>
       </c>
@@ -7716,7 +7737,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="237" spans="1:9">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>2200784</v>
       </c>
@@ -7742,7 +7763,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="238" spans="1:9">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>2202739</v>
       </c>
@@ -7771,7 +7792,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="239" spans="1:9">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>2202877</v>
       </c>
@@ -7797,7 +7818,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="240" spans="1:9">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>2364766</v>
       </c>
@@ -7826,7 +7847,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="241" spans="1:9">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>2366349</v>
       </c>
@@ -7855,7 +7876,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="242" spans="1:9">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>2366648</v>
       </c>
@@ -7884,7 +7905,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="243" spans="1:9">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>2483960</v>
       </c>
@@ -7913,7 +7934,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="244" spans="1:9">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>2366906</v>
       </c>
@@ -7939,7 +7960,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="245" spans="1:9">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>2366917</v>
       </c>
@@ -7965,7 +7986,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="246" spans="1:9">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>2367037</v>
       </c>
@@ -7994,7 +8015,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="247" spans="1:9">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>2368580</v>
       </c>
@@ -8023,7 +8044,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="248" spans="1:9">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>2472843</v>
       </c>
@@ -8052,7 +8073,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="249" spans="1:9">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>2476099</v>
       </c>
@@ -8081,7 +8102,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="250" spans="1:9">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>2477970</v>
       </c>
@@ -8101,7 +8122,7 @@
         <v>114</v>
       </c>
       <c r="G250" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H250">
         <v>60</v>
@@ -8110,7 +8131,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="251" spans="1:9">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>2482073</v>
       </c>
@@ -8139,7 +8160,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="252" spans="1:9">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>2482445</v>
       </c>
@@ -8168,7 +8189,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="253" spans="1:9">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>2483328</v>
       </c>
@@ -8197,7 +8218,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="254" spans="1:9">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>2483434</v>
       </c>
@@ -8223,7 +8244,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="255" spans="1:9">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>2483834</v>
       </c>
@@ -8252,7 +8273,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="256" spans="1:9">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>2483956</v>
       </c>
@@ -8278,7 +8299,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="257" spans="1:9">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>2484397</v>
       </c>
@@ -8307,7 +8328,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="258" spans="1:9">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>2484028</v>
       </c>
@@ -8336,7 +8357,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="259" spans="1:9">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>2484186</v>
       </c>
@@ -8362,7 +8383,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="260" spans="1:9">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>2484262</v>
       </c>
@@ -8388,7 +8409,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="261" spans="1:9">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>2484542</v>
       </c>
@@ -8417,7 +8438,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="262" spans="1:9">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>2500744</v>
       </c>
@@ -8443,7 +8464,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="263" spans="1:9">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>2501122</v>
       </c>
@@ -8472,7 +8493,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="264" spans="1:9">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>2593530</v>
       </c>
@@ -8501,7 +8522,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="265" spans="1:9">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>2596196</v>
       </c>
@@ -8521,7 +8542,7 @@
         <v>114</v>
       </c>
       <c r="G265" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H265">
         <v>82</v>
@@ -8530,7 +8551,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="266" spans="1:9">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>2599154</v>
       </c>
@@ -8556,7 +8577,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="267" spans="1:9">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>2599631</v>
       </c>
@@ -8585,7 +8606,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="268" spans="1:9">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>2599634</v>
       </c>
@@ -8614,7 +8635,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="269" spans="1:9">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>2599868</v>
       </c>
@@ -8643,7 +8664,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="270" spans="1:9">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>2616909</v>
       </c>
@@ -8672,7 +8693,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="271" spans="1:9">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>2366734</v>
       </c>
@@ -8701,7 +8722,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="272" spans="1:9">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>1903274</v>
       </c>
@@ -8730,7 +8751,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="273" spans="1:9">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>2200784</v>
       </c>
@@ -8756,7 +8777,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="274" spans="1:9">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>2202739</v>
       </c>
@@ -8785,7 +8806,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="275" spans="1:9">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>2250387</v>
       </c>
@@ -8814,7 +8835,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="276" spans="1:9">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>2363982</v>
       </c>
@@ -8843,7 +8864,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="277" spans="1:9">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>2364521</v>
       </c>
@@ -8872,7 +8893,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="278" spans="1:9">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>2364697</v>
       </c>
@@ -8898,7 +8919,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="279" spans="1:9">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>2364712</v>
       </c>
@@ -8927,7 +8948,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="280" spans="1:9">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>2364766</v>
       </c>
@@ -8956,7 +8977,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="281" spans="1:9">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>2364995</v>
       </c>
@@ -8985,7 +9006,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="282" spans="1:9">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>2365347</v>
       </c>
@@ -9011,7 +9032,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="283" spans="1:9">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>2366232</v>
       </c>
@@ -9040,7 +9061,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="284" spans="1:9">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>2366349</v>
       </c>
@@ -9066,7 +9087,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="285" spans="1:9">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>2366734</v>
       </c>
@@ -9095,7 +9116,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="286" spans="1:9">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>2366843</v>
       </c>
@@ -9124,7 +9145,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="287" spans="1:9">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>2367037</v>
       </c>
@@ -9153,7 +9174,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="288" spans="1:9">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>2368553</v>
       </c>
@@ -9179,7 +9200,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="289" spans="1:9">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>2369573</v>
       </c>
@@ -9208,7 +9229,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="290" spans="1:9">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>2472990</v>
       </c>
@@ -9237,7 +9258,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="291" spans="1:9">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>2482073</v>
       </c>
@@ -9266,7 +9287,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="292" spans="1:9">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>2482445</v>
       </c>
@@ -9295,7 +9316,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="293" spans="1:9">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>2482558</v>
       </c>
@@ -9321,7 +9342,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="294" spans="1:9">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>2483134</v>
       </c>
@@ -9347,7 +9368,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="295" spans="1:9">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>2483328</v>
       </c>
@@ -9376,7 +9397,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="296" spans="1:9">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>2483834</v>
       </c>
@@ -9405,7 +9426,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="297" spans="1:9">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>2483956</v>
       </c>
@@ -9434,7 +9455,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="298" spans="1:9">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>2484028</v>
       </c>
@@ -9463,7 +9484,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="299" spans="1:9">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>2484397</v>
       </c>
@@ -9492,7 +9513,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="300" spans="1:9">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>2484424</v>
       </c>
@@ -9521,7 +9542,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="301" spans="1:9">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>2484478</v>
       </c>
@@ -9547,7 +9568,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="302" spans="1:9">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>2484542</v>
       </c>
@@ -9576,7 +9597,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="303" spans="1:9">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>2485620</v>
       </c>
@@ -9605,7 +9626,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="304" spans="1:9">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>2488091</v>
       </c>
@@ -9634,7 +9655,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="305" spans="1:9">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>2500744</v>
       </c>
@@ -9663,7 +9684,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="306" spans="1:9">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>2501122</v>
       </c>
@@ -9692,7 +9713,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="307" spans="1:9">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>2501485</v>
       </c>
@@ -9718,7 +9739,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="308" spans="1:9">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>2503515</v>
       </c>
@@ -9747,7 +9768,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="309" spans="1:9">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>2590850</v>
       </c>
@@ -9776,7 +9797,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="310" spans="1:9">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>2591078</v>
       </c>
@@ -9805,7 +9826,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="311" spans="1:9">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>2593256</v>
       </c>
@@ -9834,7 +9855,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="312" spans="1:9">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>2593530</v>
       </c>
@@ -9863,7 +9884,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="313" spans="1:9">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>2598321</v>
       </c>
@@ -9892,7 +9913,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="314" spans="1:9">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>2599154</v>
       </c>
@@ -9918,7 +9939,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="315" spans="1:9">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>2599631</v>
       </c>
@@ -9947,7 +9968,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="316" spans="1:9">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>2599634</v>
       </c>
@@ -9976,7 +9997,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="317" spans="1:9">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>2599868</v>
       </c>
@@ -10005,7 +10026,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="318" spans="1:9">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>1903274</v>
       </c>
@@ -10028,13 +10049,13 @@
         <v>118</v>
       </c>
       <c r="H318">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="I318" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="319" spans="1:9">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>2200784</v>
       </c>
@@ -10060,7 +10081,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="320" spans="1:9">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>2202739</v>
       </c>
@@ -10086,10 +10107,10 @@
         <v>52</v>
       </c>
       <c r="I320" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="321" spans="1:9">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>2250387</v>
       </c>
@@ -10115,10 +10136,10 @@
         <v>97</v>
       </c>
       <c r="I321" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="322" spans="1:9">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>2363982</v>
       </c>
@@ -10144,10 +10165,10 @@
         <v>29</v>
       </c>
       <c r="I322" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="323" spans="1:9">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>2364521</v>
       </c>
@@ -10173,10 +10194,10 @@
         <v>18</v>
       </c>
       <c r="I323" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="324" spans="1:9">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>2364697</v>
       </c>
@@ -10202,7 +10223,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="325" spans="1:9">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>2364712</v>
       </c>
@@ -10228,10 +10249,10 @@
         <v>22</v>
       </c>
       <c r="I325" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="326" spans="1:9">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>2364766</v>
       </c>
@@ -10257,10 +10278,10 @@
         <v>21</v>
       </c>
       <c r="I326" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="327" spans="1:9">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>2364995</v>
       </c>
@@ -10286,10 +10307,10 @@
         <v>18</v>
       </c>
       <c r="I327" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="328" spans="1:9">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>2365347</v>
       </c>
@@ -10315,7 +10336,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="329" spans="1:9">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>2366232</v>
       </c>
@@ -10341,10 +10362,10 @@
         <v>77</v>
       </c>
       <c r="I329" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="330" spans="1:9">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>2366349</v>
       </c>
@@ -10370,7 +10391,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="331" spans="1:9">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>2366734</v>
       </c>
@@ -10396,10 +10417,10 @@
         <v>18</v>
       </c>
       <c r="I331" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="332" spans="1:9">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>2366843</v>
       </c>
@@ -10428,7 +10449,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="333" spans="1:9">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>2367037</v>
       </c>
@@ -10454,10 +10475,10 @@
         <v>46</v>
       </c>
       <c r="I333" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="334" spans="1:9">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>2368553</v>
       </c>
@@ -10483,7 +10504,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="335" spans="1:9">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>2369573</v>
       </c>
@@ -10509,10 +10530,10 @@
         <v>15</v>
       </c>
       <c r="I335" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="336" spans="1:9">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>2472990</v>
       </c>
@@ -10538,10 +10559,10 @@
         <v>76</v>
       </c>
       <c r="I336" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="337" spans="1:9">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>2482073</v>
       </c>
@@ -10567,10 +10588,10 @@
         <v>16</v>
       </c>
       <c r="I337" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="338" spans="1:9">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>2482445</v>
       </c>
@@ -10596,10 +10617,10 @@
         <v>85</v>
       </c>
       <c r="I338" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="339" spans="1:9">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>2482558</v>
       </c>
@@ -10625,7 +10646,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="340" spans="1:9">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>2483134</v>
       </c>
@@ -10651,7 +10672,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="341" spans="1:9">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>2483328</v>
       </c>
@@ -10677,10 +10698,10 @@
         <v>50</v>
       </c>
       <c r="I341" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="342" spans="1:9">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>2483834</v>
       </c>
@@ -10706,10 +10727,10 @@
         <v>93</v>
       </c>
       <c r="I342" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="343" spans="1:9">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>2483956</v>
       </c>
@@ -10735,10 +10756,10 @@
         <v>12</v>
       </c>
       <c r="I343" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="344" spans="1:9">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>2484028</v>
       </c>
@@ -10764,10 +10785,10 @@
         <v>93</v>
       </c>
       <c r="I344" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="345" spans="1:9">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>2484397</v>
       </c>
@@ -10793,10 +10814,10 @@
         <v>22</v>
       </c>
       <c r="I345" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="346" spans="1:9">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>2484424</v>
       </c>
@@ -10822,10 +10843,10 @@
         <v>74</v>
       </c>
       <c r="I346" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="347" spans="1:9">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>2484478</v>
       </c>
@@ -10851,7 +10872,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="348" spans="1:9">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>2484542</v>
       </c>
@@ -10877,10 +10898,10 @@
         <v>18</v>
       </c>
       <c r="I348" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="349" spans="1:9">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>2485620</v>
       </c>
@@ -10906,10 +10927,10 @@
         <v>22</v>
       </c>
       <c r="I349" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="350" spans="1:9">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>2488091</v>
       </c>
@@ -10935,10 +10956,10 @@
         <v>12</v>
       </c>
       <c r="I350" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="351" spans="1:9">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>2500744</v>
       </c>
@@ -10964,10 +10985,10 @@
         <v>65</v>
       </c>
       <c r="I351" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="352" spans="1:9">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>2501122</v>
       </c>
@@ -10993,10 +11014,10 @@
         <v>12</v>
       </c>
       <c r="I352" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="353" spans="1:9">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>2501485</v>
       </c>
@@ -11022,7 +11043,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="354" spans="1:9">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>2503515</v>
       </c>
@@ -11051,7 +11072,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="355" spans="1:9">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>2590850</v>
       </c>
@@ -11080,7 +11101,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="356" spans="1:9">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>2591078</v>
       </c>
@@ -11106,10 +11127,10 @@
         <v>39</v>
       </c>
       <c r="I356" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="357" spans="1:9">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>2593256</v>
       </c>
@@ -11138,7 +11159,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="358" spans="1:9">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>2593530</v>
       </c>
@@ -11164,10 +11185,10 @@
         <v>83</v>
       </c>
       <c r="I358" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="359" spans="1:9">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>2598321</v>
       </c>
@@ -11193,10 +11214,10 @@
         <v>28</v>
       </c>
       <c r="I359" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="360" spans="1:9">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>2599154</v>
       </c>
@@ -11222,7 +11243,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="361" spans="1:9">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>2599631</v>
       </c>
@@ -11248,10 +11269,10 @@
         <v>56</v>
       </c>
       <c r="I361" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="362" spans="1:9">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>2599634</v>
       </c>
@@ -11277,10 +11298,10 @@
         <v>39</v>
       </c>
       <c r="I362" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="363" spans="1:9">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>2599868</v>
       </c>
@@ -11306,10 +11327,10 @@
         <v>61</v>
       </c>
       <c r="I363" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="364" spans="1:9">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>2483960</v>
       </c>
@@ -11335,10 +11356,10 @@
         <v>27</v>
       </c>
       <c r="I364" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="365" spans="1:9">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>2612865</v>
       </c>
@@ -11367,7 +11388,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="366" spans="1:9">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>2003743</v>
       </c>
@@ -11393,7 +11414,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="367" spans="1:9">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>2100421</v>
       </c>
@@ -11419,7 +11440,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="368" spans="1:9">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>2101613</v>
       </c>
@@ -11445,10 +11466,10 @@
         <v>52</v>
       </c>
       <c r="I368" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="369" spans="1:9">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>2101812</v>
       </c>
@@ -11474,7 +11495,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="370" spans="1:9">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>2104775</v>
       </c>
@@ -11500,7 +11521,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="371" spans="1:9">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>2106789</v>
       </c>
@@ -11526,7 +11547,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="372" spans="1:9">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>2106808</v>
       </c>
@@ -11552,7 +11573,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="373" spans="1:9">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>2200601</v>
       </c>
@@ -11578,7 +11599,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="374" spans="1:9">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>2202877</v>
       </c>
@@ -11604,7 +11625,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="375" spans="1:9">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>2252125</v>
       </c>
@@ -11630,10 +11651,10 @@
         <v>100</v>
       </c>
       <c r="I375" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="376" spans="1:9">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>2252127</v>
       </c>
@@ -11659,10 +11680,10 @@
         <v>85</v>
       </c>
       <c r="I376" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="377" spans="1:9">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>2282610</v>
       </c>
@@ -11688,10 +11709,10 @@
         <v>15</v>
       </c>
       <c r="I377" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="378" spans="1:9">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>2284111</v>
       </c>
@@ -11717,7 +11738,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="379" spans="1:9">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>2355702</v>
       </c>
@@ -11743,7 +11764,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="380" spans="1:9">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>2359322</v>
       </c>
@@ -11769,10 +11790,10 @@
         <v>95</v>
       </c>
       <c r="I380" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="381" spans="1:9">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>2359481</v>
       </c>
@@ -11798,10 +11819,10 @@
         <v>100</v>
       </c>
       <c r="I381" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="382" spans="1:9">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>2359764</v>
       </c>
@@ -11830,7 +11851,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="383" spans="1:9">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>2360367</v>
       </c>
@@ -11856,10 +11877,10 @@
         <v>42</v>
       </c>
       <c r="I383" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="384" spans="1:9">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>2364571</v>
       </c>
@@ -11885,10 +11906,10 @@
         <v>0</v>
       </c>
       <c r="I384" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="385" spans="1:9">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>2366271</v>
       </c>
@@ -11917,7 +11938,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="386" spans="1:9">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>2366906</v>
       </c>
@@ -11943,7 +11964,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="387" spans="1:9">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>2367137</v>
       </c>
@@ -11969,10 +11990,10 @@
         <v>25</v>
       </c>
       <c r="I387" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="388" spans="1:9">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>2472419</v>
       </c>
@@ -11998,10 +12019,10 @@
         <v>88</v>
       </c>
       <c r="I388" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="389" spans="1:9">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>2472843</v>
       </c>
@@ -12030,7 +12051,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="390" spans="1:9">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>2476099</v>
       </c>
@@ -12056,10 +12077,10 @@
         <v>52</v>
       </c>
       <c r="I390" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="391" spans="1:9">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>2476633</v>
       </c>
@@ -12085,10 +12106,10 @@
         <v>57</v>
       </c>
       <c r="I391" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="392" spans="1:9">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>2477416</v>
       </c>
@@ -12114,10 +12135,10 @@
         <v>75</v>
       </c>
       <c r="I392" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="393" spans="1:9">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>2477970</v>
       </c>
@@ -12143,10 +12164,10 @@
         <v>25</v>
       </c>
       <c r="I393" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="394" spans="1:9">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>2483434</v>
       </c>
@@ -12172,7 +12193,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="395" spans="1:9">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>2483960</v>
       </c>
@@ -12198,7 +12219,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="396" spans="1:9">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>2484262</v>
       </c>
@@ -12224,7 +12245,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="397" spans="1:9">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>2596186</v>
       </c>
@@ -12250,10 +12271,10 @@
         <v>22</v>
       </c>
       <c r="I397" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="398" spans="1:9">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>2597847</v>
       </c>
@@ -12279,7 +12300,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="399" spans="1:9">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>2612865</v>
       </c>
@@ -12308,7 +12329,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="400" spans="1:9">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>2616909</v>
       </c>
@@ -12334,10 +12355,10 @@
         <v>42</v>
       </c>
       <c r="I400" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="401" spans="1:9">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>2003743</v>
       </c>
@@ -12363,7 +12384,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="402" spans="1:9">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>2100421</v>
       </c>
@@ -12389,7 +12410,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="403" spans="1:9">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>2101613</v>
       </c>
@@ -12415,10 +12436,10 @@
         <v>15</v>
       </c>
       <c r="I403" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="404" spans="1:9">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>2101812</v>
       </c>
@@ -12444,7 +12465,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="405" spans="1:9">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>2104775</v>
       </c>
@@ -12470,7 +12491,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="406" spans="1:9">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>2106789</v>
       </c>
@@ -12496,7 +12517,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="407" spans="1:9">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>2106808</v>
       </c>
@@ -12522,7 +12543,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="408" spans="1:9">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>2200601</v>
       </c>
@@ -12548,7 +12569,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="409" spans="1:9">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>2202877</v>
       </c>
@@ -12574,7 +12595,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="410" spans="1:9">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>2252125</v>
       </c>
@@ -12600,10 +12621,10 @@
         <v>81</v>
       </c>
       <c r="I410" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="411" spans="1:9">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>2252127</v>
       </c>
@@ -12629,10 +12650,10 @@
         <v>91</v>
       </c>
       <c r="I411" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="412" spans="1:9">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>2282610</v>
       </c>
@@ -12658,10 +12679,10 @@
         <v>18</v>
       </c>
       <c r="I412" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="413" spans="1:9">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>2284111</v>
       </c>
@@ -12687,7 +12708,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="414" spans="1:9">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>2355702</v>
       </c>
@@ -12713,7 +12734,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="415" spans="1:9">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>2359322</v>
       </c>
@@ -12739,10 +12760,10 @@
         <v>88</v>
       </c>
       <c r="I415" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="416" spans="1:9">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>2359481</v>
       </c>
@@ -12771,7 +12792,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="417" spans="1:9">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>2359764</v>
       </c>
@@ -12800,7 +12821,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="418" spans="1:9">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>2360367</v>
       </c>
@@ -12826,10 +12847,10 @@
         <v>15</v>
       </c>
       <c r="I418" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="419" spans="1:9">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>2364571</v>
       </c>
@@ -12855,10 +12876,10 @@
         <v>0</v>
       </c>
       <c r="I419" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="420" spans="1:9">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>2366271</v>
       </c>
@@ -12887,7 +12908,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="421" spans="1:9">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>2366906</v>
       </c>
@@ -12913,7 +12934,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="422" spans="1:9">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>2367137</v>
       </c>
@@ -12939,10 +12960,10 @@
         <v>51</v>
       </c>
       <c r="I422" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="423" spans="1:9">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>2472419</v>
       </c>
@@ -12968,10 +12989,10 @@
         <v>18</v>
       </c>
       <c r="I423" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="424" spans="1:9">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>2472843</v>
       </c>
@@ -12997,10 +13018,10 @@
         <v>13</v>
       </c>
       <c r="I424" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="425" spans="1:9">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>2476099</v>
       </c>
@@ -13026,10 +13047,10 @@
         <v>0</v>
       </c>
       <c r="I425" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="426" spans="1:9">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>2476633</v>
       </c>
@@ -13055,10 +13076,10 @@
         <v>86</v>
       </c>
       <c r="I426" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="427" spans="1:9">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>2477416</v>
       </c>
@@ -13084,10 +13105,10 @@
         <v>100</v>
       </c>
       <c r="I427" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="428" spans="1:9">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>2477970</v>
       </c>
@@ -13113,10 +13134,10 @@
         <v>20</v>
       </c>
       <c r="I428" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="429" spans="1:9">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>2483434</v>
       </c>
@@ -13142,7 +13163,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="430" spans="1:9">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>2484262</v>
       </c>
@@ -13168,7 +13189,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="431" spans="1:9">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>2596186</v>
       </c>
@@ -13194,10 +13215,10 @@
         <v>22</v>
       </c>
       <c r="I431" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="432" spans="1:9">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>2597847</v>
       </c>
@@ -13223,7 +13244,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="433" spans="1:9">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>2616909</v>
       </c>
@@ -13249,10 +13270,10 @@
         <v>18</v>
       </c>
       <c r="I433" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="434" spans="1:9">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>1903274</v>
       </c>
@@ -13272,16 +13293,16 @@
         <v>114</v>
       </c>
       <c r="G434" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H434">
         <v>100</v>
       </c>
       <c r="I434" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="435" spans="1:9">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>2003052</v>
       </c>
@@ -13301,16 +13322,16 @@
         <v>114</v>
       </c>
       <c r="G435" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H435">
         <v>37</v>
       </c>
       <c r="I435" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="436" spans="1:9">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>2100421</v>
       </c>
@@ -13330,13 +13351,13 @@
         <v>113</v>
       </c>
       <c r="G436" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I436" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="437" spans="1:9">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>2101613</v>
       </c>
@@ -13356,16 +13377,16 @@
         <v>114</v>
       </c>
       <c r="G437" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H437">
         <v>38</v>
       </c>
       <c r="I437" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="438" spans="1:9">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>2105067</v>
       </c>
@@ -13385,16 +13406,16 @@
         <v>114</v>
       </c>
       <c r="G438" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H438">
         <v>14</v>
       </c>
       <c r="I438" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="439" spans="1:9">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>2105541</v>
       </c>
@@ -13414,16 +13435,16 @@
         <v>114</v>
       </c>
       <c r="G439" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H439">
         <v>18</v>
       </c>
       <c r="I439" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="440" spans="1:9">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>2106789</v>
       </c>
@@ -13443,13 +13464,13 @@
         <v>113</v>
       </c>
       <c r="G440" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I440" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="441" spans="1:9">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>2200206</v>
       </c>
@@ -13469,16 +13490,16 @@
         <v>114</v>
       </c>
       <c r="G441" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H441">
         <v>100</v>
       </c>
       <c r="I441" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="442" spans="1:9">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>2200601</v>
       </c>
@@ -13498,13 +13519,13 @@
         <v>113</v>
       </c>
       <c r="G442" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I442" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="443" spans="1:9">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>2284111</v>
       </c>
@@ -13524,13 +13545,13 @@
         <v>113</v>
       </c>
       <c r="G443" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I443" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="444" spans="1:9">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>2355702</v>
       </c>
@@ -13550,16 +13571,16 @@
         <v>114</v>
       </c>
       <c r="G444" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H444">
         <v>32</v>
       </c>
       <c r="I444" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="445" spans="1:9">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>2359764</v>
       </c>
@@ -13579,13 +13600,13 @@
         <v>113</v>
       </c>
       <c r="G445" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I445" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="446" spans="1:9">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>2363982</v>
       </c>
@@ -13605,16 +13626,16 @@
         <v>114</v>
       </c>
       <c r="G446" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H446">
         <v>10</v>
       </c>
       <c r="I446" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="447" spans="1:9">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>2364571</v>
       </c>
@@ -13634,16 +13655,16 @@
         <v>114</v>
       </c>
       <c r="G447" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H447">
         <v>20</v>
       </c>
       <c r="I447" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="448" spans="1:9">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>2364697</v>
       </c>
@@ -13663,13 +13684,13 @@
         <v>113</v>
       </c>
       <c r="G448" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I448" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="449" spans="1:9">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>2364712</v>
       </c>
@@ -13689,16 +13710,16 @@
         <v>114</v>
       </c>
       <c r="G449" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H449">
         <v>46</v>
       </c>
       <c r="I449" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="450" spans="1:9">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>2365114</v>
       </c>
@@ -13718,13 +13739,13 @@
         <v>113</v>
       </c>
       <c r="G450" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I450" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="451" spans="1:9">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>2366271</v>
       </c>
@@ -13744,16 +13765,16 @@
         <v>114</v>
       </c>
       <c r="G451" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H451">
         <v>87</v>
       </c>
       <c r="I451" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="452" spans="1:9">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>2366789</v>
       </c>
@@ -13773,16 +13794,16 @@
         <v>114</v>
       </c>
       <c r="G452" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H452">
         <v>37</v>
       </c>
       <c r="I452" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="453" spans="1:9">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>2367137</v>
       </c>
@@ -13802,13 +13823,13 @@
         <v>113</v>
       </c>
       <c r="G453" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I453" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="454" spans="1:9">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>2368553</v>
       </c>
@@ -13828,16 +13849,16 @@
         <v>114</v>
       </c>
       <c r="G454" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H454">
         <v>28</v>
       </c>
       <c r="I454" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="455" spans="1:9">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>2369573</v>
       </c>
@@ -13857,13 +13878,13 @@
         <v>113</v>
       </c>
       <c r="G455" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I455" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="456" spans="1:9">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>2473471</v>
       </c>
@@ -13883,16 +13904,16 @@
         <v>114</v>
       </c>
       <c r="G456" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H456">
         <v>97</v>
       </c>
       <c r="I456" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="457" spans="1:9">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>2477416</v>
       </c>
@@ -13912,16 +13933,16 @@
         <v>114</v>
       </c>
       <c r="G457" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H457">
         <v>97</v>
       </c>
       <c r="I457" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="458" spans="1:9">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>2482829</v>
       </c>
@@ -13941,16 +13962,16 @@
         <v>114</v>
       </c>
       <c r="G458" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H458">
         <v>14</v>
       </c>
       <c r="I458" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="459" spans="1:9">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>2483134</v>
       </c>
@@ -13970,13 +13991,13 @@
         <v>113</v>
       </c>
       <c r="G459" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I459" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="460" spans="1:9">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>2483496</v>
       </c>
@@ -13996,16 +14017,16 @@
         <v>114</v>
       </c>
       <c r="G460" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H460">
         <v>54</v>
       </c>
       <c r="I460" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="461" spans="1:9">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>2484424</v>
       </c>
@@ -14025,13 +14046,13 @@
         <v>113</v>
       </c>
       <c r="G461" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I461" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="462" spans="1:9">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>2484478</v>
       </c>
@@ -14051,16 +14072,16 @@
         <v>114</v>
       </c>
       <c r="G462" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H462">
         <v>22</v>
       </c>
       <c r="I462" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="463" spans="1:9">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>2590850</v>
       </c>
@@ -14080,16 +14101,16 @@
         <v>114</v>
       </c>
       <c r="G463" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H463">
         <v>40</v>
       </c>
       <c r="I463" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="464" spans="1:9">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>2591078</v>
       </c>
@@ -14109,7 +14130,7 @@
         <v>114</v>
       </c>
       <c r="G464" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H464">
         <v>0</v>
@@ -14118,7 +14139,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="465" spans="1:9">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>2592655</v>
       </c>
@@ -14138,16 +14159,16 @@
         <v>114</v>
       </c>
       <c r="G465" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H465">
         <v>50</v>
       </c>
       <c r="I465" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="466" spans="1:9">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>2593256</v>
       </c>
@@ -14167,16 +14188,16 @@
         <v>114</v>
       </c>
       <c r="G466" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H466">
         <v>24</v>
       </c>
       <c r="I466" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="467" spans="1:9">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>2596186</v>
       </c>
@@ -14196,16 +14217,16 @@
         <v>114</v>
       </c>
       <c r="G467" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H467">
         <v>28</v>
       </c>
       <c r="I467" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="468" spans="1:9">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>2612865</v>
       </c>
@@ -14225,16 +14246,17 @@
         <v>114</v>
       </c>
       <c r="G468" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H468">
         <v>94</v>
       </c>
       <c r="I468" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I468" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>